--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="S73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="S92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="S93" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="S94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="S95" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="S98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="S102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="S103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="S106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="S110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="S111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="S114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="S117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="S118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="S120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="S121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="S122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="S123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="S126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="S127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="S128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="S130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="S131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="S132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="S133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="S134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="S135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="S137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="S138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="S139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="S140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="S141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="S142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="S143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="S144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="S145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="S146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="S147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="S148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="S149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="S150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="S151" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S152" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="S153" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="S154" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="S155" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="S156" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="S157" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="S158" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="S159" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="S160" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="S161" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="S162" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="S163" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="S164" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="S165" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="S166" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="S167" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="S168" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="S169" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="S170" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="S171" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="S172" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="S173" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="S174" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="S175" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="S176" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="S177" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="S178" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
       </c>
       <c r="S179" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="S180" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="S181" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="S182" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="S183" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="S184" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="S185" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="S186" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="S187" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="S188" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19073,7 +19073,7 @@
       </c>
       <c r="S189" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="S190" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="S191" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="S192" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="S193" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="S194" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="S195" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="S196" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="S197" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="S198" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="S199" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="S200" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="S201" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="S202" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S203" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="S204" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="S205" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="S206" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S207" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S208" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="S209" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="S210" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="S211" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="S212" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="S213" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21498,7 @@
       </c>
       <c r="S214" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="S215" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="S216" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="S217" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="S218" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="S219" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="S220" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="S221" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="S222" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="S223" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="S224" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22565,7 +22565,7 @@
       </c>
       <c r="S225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22662,7 +22662,7 @@
       </c>
       <c r="S226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="S227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="S228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -22953,7 +22953,7 @@
       </c>
       <c r="S229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="S230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="S231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="S232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="S233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23438,7 +23438,7 @@
       </c>
       <c r="S234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="S235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="S236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="S237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="S238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
       </c>
       <c r="S239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="S241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="S242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="S244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="S245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
       </c>
       <c r="S246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24699,7 +24699,7 @@
       </c>
       <c r="S247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24796,7 @@
       </c>
       <c r="S248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24893,7 +24893,7 @@
       </c>
       <c r="S249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="S250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="S251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25184,7 +25184,7 @@
       </c>
       <c r="S252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="S253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="S254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25475,7 @@
       </c>
       <c r="S255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="S256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="S257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="S258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="S259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="S260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="S261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="S262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="S263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="S264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="S265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
       </c>
       <c r="S266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="S267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
       </c>
       <c r="S268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26833,7 +26833,7 @@
       </c>
       <c r="S269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -26930,7 +26930,7 @@
       </c>
       <c r="S270" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27027,7 @@
       </c>
       <c r="S271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="S272" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="S273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27318,7 +27318,7 @@
       </c>
       <c r="S274" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="S275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27512,7 @@
       </c>
       <c r="S276" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="S277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="S278" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="S279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27900,7 @@
       </c>
       <c r="S280" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="S281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="S282" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28191,7 +28191,7 @@
       </c>
       <c r="S283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="S284" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="S285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="S286" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28579,7 +28579,7 @@
       </c>
       <c r="S287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="S288" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,7 @@
       </c>
       <c r="S289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S290" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="S291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="S292" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29161,7 @@
       </c>
       <c r="S293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="S294" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
       </c>
       <c r="S295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29452,7 +29452,7 @@
       </c>
       <c r="S296" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="S297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="S298" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29743,7 +29743,7 @@
       </c>
       <c r="S299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="S300" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="S301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30034,7 @@
       </c>
       <c r="S302" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="S303" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30228,7 +30228,7 @@
       </c>
       <c r="S304" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30325,7 @@
       </c>
       <c r="S305" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="S306" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S307" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="S308" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="S309" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="S310" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -30907,7 +30907,7 @@
       </c>
       <c r="S311" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31004,7 +31004,7 @@
       </c>
       <c r="S312" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31101,7 +31101,7 @@
       </c>
       <c r="S313" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31198,7 +31198,7 @@
       </c>
       <c r="S314" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31295,7 @@
       </c>
       <c r="S315" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="S316" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="S317" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31586,7 @@
       </c>
       <c r="S318" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="S319" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="S320" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="S321" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -31974,7 +31974,7 @@
       </c>
       <c r="S322" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="S323" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32168,7 +32168,7 @@
       </c>
       <c r="S324" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32265,7 +32265,7 @@
       </c>
       <c r="S325" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="S326" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32459,7 @@
       </c>
       <c r="S327" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="S328" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="S329" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
       </c>
       <c r="S330" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32847,7 +32847,7 @@
       </c>
       <c r="S331" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="S332" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="S333" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S334" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="S335" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="S336" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
       </c>
       <c r="S337" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="S338" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33623,7 +33623,7 @@
       </c>
       <c r="S339" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="S340" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33817,7 @@
       </c>
       <c r="S341" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="S342" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
       </c>
       <c r="S343" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34108,7 @@
       </c>
       <c r="S344" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="S345" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="S346" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34399,7 +34399,7 @@
       </c>
       <c r="S347" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="S348" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34593,7 +34593,7 @@
       </c>
       <c r="S349" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34690,7 +34690,7 @@
       </c>
       <c r="S350" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="S351" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="S352" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -34981,7 +34981,7 @@
       </c>
       <c r="S353" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="S354" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="S355" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35272,7 +35272,7 @@
       </c>
       <c r="S356" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="S357" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35466,7 +35466,7 @@
       </c>
       <c r="S358" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35563,7 +35563,7 @@
       </c>
       <c r="S359" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35660,7 @@
       </c>
       <c r="S360" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35757,7 +35757,7 @@
       </c>
       <c r="S361" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35854,7 +35854,7 @@
       </c>
       <c r="S362" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="S363" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36048,7 +36048,7 @@
       </c>
       <c r="S364" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36145,7 +36145,7 @@
       </c>
       <c r="S365" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="S366" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36339,7 +36339,7 @@
       </c>
       <c r="S367" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="S368" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="S369" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36630,7 +36630,7 @@
       </c>
       <c r="S370" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36727,7 +36727,7 @@
       </c>
       <c r="S371" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36824,7 +36824,7 @@
       </c>
       <c r="S372" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="S373" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37018,7 +37018,7 @@
       </c>
       <c r="S374" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="S375" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="S376" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37309,7 @@
       </c>
       <c r="S377" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S378" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="S379" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="S380" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="S381" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37794,7 +37794,7 @@
       </c>
       <c r="S382" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37891,7 +37891,7 @@
       </c>
       <c r="S383" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -37988,7 +37988,7 @@
       </c>
       <c r="S384" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38085,7 +38085,7 @@
       </c>
       <c r="S385" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38182,7 +38182,7 @@
       </c>
       <c r="S386" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="S387" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38376,7 +38376,7 @@
       </c>
       <c r="S388" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38473,7 +38473,7 @@
       </c>
       <c r="S389" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38570,7 +38570,7 @@
       </c>
       <c r="S390" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38667,7 +38667,7 @@
       </c>
       <c r="S391" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38764,7 +38764,7 @@
       </c>
       <c r="S392" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="S393" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -38958,7 +38958,7 @@
       </c>
       <c r="S394" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39055,7 +39055,7 @@
       </c>
       <c r="S395" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39152,7 +39152,7 @@
       </c>
       <c r="S396" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39249,7 @@
       </c>
       <c r="S397" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39346,7 +39346,7 @@
       </c>
       <c r="S398" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39443,7 +39443,7 @@
       </c>
       <c r="S399" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="S400" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39637,7 +39637,7 @@
       </c>
       <c r="S401" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39734,7 +39734,7 @@
       </c>
       <c r="S402" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39831,7 +39831,7 @@
       </c>
       <c r="S403" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -39928,7 +39928,7 @@
       </c>
       <c r="S404" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40025,7 +40025,7 @@
       </c>
       <c r="S405" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="S406" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40219,7 +40219,7 @@
       </c>
       <c r="S407" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40316,7 +40316,7 @@
       </c>
       <c r="S408" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40413,7 +40413,7 @@
       </c>
       <c r="S409" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40510,7 +40510,7 @@
       </c>
       <c r="S410" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40607,7 +40607,7 @@
       </c>
       <c r="S411" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40704,7 +40704,7 @@
       </c>
       <c r="S412" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S413" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="S414" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -40995,7 +40995,7 @@
       </c>
       <c r="S415" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41092,7 +41092,7 @@
       </c>
       <c r="S416" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="S417" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41286,7 +41286,7 @@
       </c>
       <c r="S418" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41383,7 +41383,7 @@
       </c>
       <c r="S419" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41480,7 +41480,7 @@
       </c>
       <c r="S420" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41577,7 +41577,7 @@
       </c>
       <c r="S421" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41674,7 +41674,7 @@
       </c>
       <c r="S422" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41771,7 +41771,7 @@
       </c>
       <c r="S423" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41868,7 +41868,7 @@
       </c>
       <c r="S424" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S425" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="S426" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="S427" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="S428" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42353,7 +42353,7 @@
       </c>
       <c r="S429" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42450,7 +42450,7 @@
       </c>
       <c r="S430" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42547,7 +42547,7 @@
       </c>
       <c r="S431" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42644,7 +42644,7 @@
       </c>
       <c r="S432" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42741,7 +42741,7 @@
       </c>
       <c r="S433" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42838,7 +42838,7 @@
       </c>
       <c r="S434" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -42935,7 +42935,7 @@
       </c>
       <c r="S435" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43032,7 +43032,7 @@
       </c>
       <c r="S436" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="S437" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="S438" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="S439" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43420,7 +43420,7 @@
       </c>
       <c r="S440" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43517,7 +43517,7 @@
       </c>
       <c r="S441" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="S442" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43711,7 @@
       </c>
       <c r="S443" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43808,7 +43808,7 @@
       </c>
       <c r="S444" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -43905,7 +43905,7 @@
       </c>
       <c r="S445" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44002,7 +44002,7 @@
       </c>
       <c r="S446" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44099,7 +44099,7 @@
       </c>
       <c r="S447" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44196,7 +44196,7 @@
       </c>
       <c r="S448" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44293,7 +44293,7 @@
       </c>
       <c r="S449" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44390,7 +44390,7 @@
       </c>
       <c r="S450" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="S451" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="S452" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44681,7 +44681,7 @@
       </c>
       <c r="S453" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44778,7 +44778,7 @@
       </c>
       <c r="S454" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44875,7 +44875,7 @@
       </c>
       <c r="S455" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -44972,7 +44972,7 @@
       </c>
       <c r="S456" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
       </c>
       <c r="S457" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45166,7 +45166,7 @@
       </c>
       <c r="S458" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45263,7 +45263,7 @@
       </c>
       <c r="S459" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45360,7 +45360,7 @@
       </c>
       <c r="S460" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45457,7 +45457,7 @@
       </c>
       <c r="S461" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45554,7 +45554,7 @@
       </c>
       <c r="S462" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="S463" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="S464" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45845,7 +45845,7 @@
       </c>
       <c r="S465" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -45942,7 +45942,7 @@
       </c>
       <c r="S466" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46039,7 +46039,7 @@
       </c>
       <c r="S467" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46136,7 +46136,7 @@
       </c>
       <c r="S468" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="S469" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46330,7 +46330,7 @@
       </c>
       <c r="S470" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="S471" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46524,7 +46524,7 @@
       </c>
       <c r="S472" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46621,7 +46621,7 @@
       </c>
       <c r="S473" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46718,7 +46718,7 @@
       </c>
       <c r="S474" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46815,7 +46815,7 @@
       </c>
       <c r="S475" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -46912,7 +46912,7 @@
       </c>
       <c r="S476" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47009,7 +47009,7 @@
       </c>
       <c r="S477" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47106,7 +47106,7 @@
       </c>
       <c r="S478" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47203,7 +47203,7 @@
       </c>
       <c r="S479" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S480" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="S481" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47494,7 +47494,7 @@
       </c>
       <c r="S482" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47591,7 +47591,7 @@
       </c>
       <c r="S483" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47688,7 +47688,7 @@
       </c>
       <c r="S484" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47785,7 +47785,7 @@
       </c>
       <c r="S485" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47882,7 +47882,7 @@
       </c>
       <c r="S486" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -47979,7 +47979,7 @@
       </c>
       <c r="S487" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48076,7 +48076,7 @@
       </c>
       <c r="S488" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48173,7 +48173,7 @@
       </c>
       <c r="S489" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48270,7 +48270,7 @@
       </c>
       <c r="S490" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48367,7 +48367,7 @@
       </c>
       <c r="S491" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48464,7 +48464,7 @@
       </c>
       <c r="S492" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="S493" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48658,7 +48658,7 @@
       </c>
       <c r="S494" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="S495" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48852,7 +48852,7 @@
       </c>
       <c r="S496" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -48949,7 +48949,7 @@
       </c>
       <c r="S497" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49046,7 +49046,7 @@
       </c>
       <c r="S498" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49143,7 +49143,7 @@
       </c>
       <c r="S499" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49240,7 +49240,7 @@
       </c>
       <c r="S500" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49337,7 +49337,7 @@
       </c>
       <c r="S501" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49434,7 +49434,7 @@
       </c>
       <c r="S502" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49531,7 +49531,7 @@
       </c>
       <c r="S503" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49628,7 +49628,7 @@
       </c>
       <c r="S504" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49725,7 +49725,7 @@
       </c>
       <c r="S505" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49822,7 +49822,7 @@
       </c>
       <c r="S506" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -49919,7 +49919,7 @@
       </c>
       <c r="S507" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50016,7 +50016,7 @@
       </c>
       <c r="S508" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50113,7 +50113,7 @@
       </c>
       <c r="S509" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50210,7 +50210,7 @@
       </c>
       <c r="S510" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50307,7 +50307,7 @@
       </c>
       <c r="S511" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50404,7 +50404,7 @@
       </c>
       <c r="S512" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50501,7 +50501,7 @@
       </c>
       <c r="S513" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50598,7 +50598,7 @@
       </c>
       <c r="S514" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50695,7 +50695,7 @@
       </c>
       <c r="S515" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S516" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50889,7 +50889,7 @@
       </c>
       <c r="S517" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -50986,7 +50986,7 @@
       </c>
       <c r="S518" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51083,7 +51083,7 @@
       </c>
       <c r="S519" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51180,7 +51180,7 @@
       </c>
       <c r="S520" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51277,7 +51277,7 @@
       </c>
       <c r="S521" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="S522" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="S523" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51568,7 +51568,7 @@
       </c>
       <c r="S524" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51665,7 +51665,7 @@
       </c>
       <c r="S525" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51762,7 +51762,7 @@
       </c>
       <c r="S526" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51859,7 +51859,7 @@
       </c>
       <c r="S527" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -51956,7 +51956,7 @@
       </c>
       <c r="S528" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="S529" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52150,7 +52150,7 @@
       </c>
       <c r="S530" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="S531" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52344,7 +52344,7 @@
       </c>
       <c r="S532" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52441,7 +52441,7 @@
       </c>
       <c r="S533" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52538,7 +52538,7 @@
       </c>
       <c r="S534" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="S535" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52732,7 +52732,7 @@
       </c>
       <c r="S536" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52829,7 +52829,7 @@
       </c>
       <c r="S537" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -52926,7 +52926,7 @@
       </c>
       <c r="S538" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53023,7 +53023,7 @@
       </c>
       <c r="S539" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53120,7 +53120,7 @@
       </c>
       <c r="S540" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53217,7 +53217,7 @@
       </c>
       <c r="S541" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53314,7 +53314,7 @@
       </c>
       <c r="S542" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53411,7 +53411,7 @@
       </c>
       <c r="S543" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53508,7 +53508,7 @@
       </c>
       <c r="S544" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53605,7 +53605,7 @@
       </c>
       <c r="S545" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53702,7 +53702,7 @@
       </c>
       <c r="S546" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53799,7 +53799,7 @@
       </c>
       <c r="S547" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53896,7 +53896,7 @@
       </c>
       <c r="S548" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -53993,7 +53993,7 @@
       </c>
       <c r="S549" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54090,7 +54090,7 @@
       </c>
       <c r="S550" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54187,7 +54187,7 @@
       </c>
       <c r="S551" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54284,7 +54284,7 @@
       </c>
       <c r="S552" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54381,7 +54381,7 @@
       </c>
       <c r="S553" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54478,7 +54478,7 @@
       </c>
       <c r="S554" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54575,7 +54575,7 @@
       </c>
       <c r="S555" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54672,7 +54672,7 @@
       </c>
       <c r="S556" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54769,7 +54769,7 @@
       </c>
       <c r="S557" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54866,7 +54866,7 @@
       </c>
       <c r="S558" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -54963,7 +54963,7 @@
       </c>
       <c r="S559" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55060,7 +55060,7 @@
       </c>
       <c r="S560" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55157,7 +55157,7 @@
       </c>
       <c r="S561" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55254,7 +55254,7 @@
       </c>
       <c r="S562" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55351,7 +55351,7 @@
       </c>
       <c r="S563" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55448,7 +55448,7 @@
       </c>
       <c r="S564" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55545,7 +55545,7 @@
       </c>
       <c r="S565" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55642,7 +55642,7 @@
       </c>
       <c r="S566" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55739,7 +55739,7 @@
       </c>
       <c r="S567" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55836,7 +55836,7 @@
       </c>
       <c r="S568" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -55933,7 +55933,7 @@
       </c>
       <c r="S569" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56030,7 +56030,7 @@
       </c>
       <c r="S570" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56127,7 +56127,7 @@
       </c>
       <c r="S571" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56224,7 +56224,7 @@
       </c>
       <c r="S572" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56321,7 +56321,7 @@
       </c>
       <c r="S573" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56418,7 +56418,7 @@
       </c>
       <c r="S574" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56515,7 +56515,7 @@
       </c>
       <c r="S575" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56612,7 +56612,7 @@
       </c>
       <c r="S576" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56709,7 +56709,7 @@
       </c>
       <c r="S577" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S578" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -56903,7 +56903,7 @@
       </c>
       <c r="S579" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57000,7 +57000,7 @@
       </c>
       <c r="S580" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="S581" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57194,7 +57194,7 @@
       </c>
       <c r="S582" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57291,7 +57291,7 @@
       </c>
       <c r="S583" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="S584" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57485,7 +57485,7 @@
       </c>
       <c r="S585" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57582,7 +57582,7 @@
       </c>
       <c r="S586" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57679,7 +57679,7 @@
       </c>
       <c r="S587" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57776,7 +57776,7 @@
       </c>
       <c r="S588" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57873,7 +57873,7 @@
       </c>
       <c r="S589" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -57970,7 +57970,7 @@
       </c>
       <c r="S590" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58067,7 +58067,7 @@
       </c>
       <c r="S591" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58164,7 +58164,7 @@
       </c>
       <c r="S592" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58261,7 +58261,7 @@
       </c>
       <c r="S593" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58358,7 +58358,7 @@
       </c>
       <c r="S594" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58455,7 +58455,7 @@
       </c>
       <c r="S595" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58552,7 +58552,7 @@
       </c>
       <c r="S596" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58649,7 +58649,7 @@
       </c>
       <c r="S597" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58746,7 +58746,7 @@
       </c>
       <c r="S598" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58843,7 +58843,7 @@
       </c>
       <c r="S599" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -58940,7 +58940,7 @@
       </c>
       <c r="S600" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59037,7 +59037,7 @@
       </c>
       <c r="S601" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59134,7 +59134,7 @@
       </c>
       <c r="S602" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59231,7 +59231,7 @@
       </c>
       <c r="S603" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59328,7 +59328,7 @@
       </c>
       <c r="S604" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59425,7 +59425,7 @@
       </c>
       <c r="S605" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="S606" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S607" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59716,7 +59716,7 @@
       </c>
       <c r="S608" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59813,7 +59813,7 @@
       </c>
       <c r="S609" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -59910,7 +59910,7 @@
       </c>
       <c r="S610" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60007,7 +60007,7 @@
       </c>
       <c r="S611" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60104,7 +60104,7 @@
       </c>
       <c r="S612" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60201,7 +60201,7 @@
       </c>
       <c r="S613" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S614" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60395,7 +60395,7 @@
       </c>
       <c r="S615" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60492,7 +60492,7 @@
       </c>
       <c r="S616" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60589,7 +60589,7 @@
       </c>
       <c r="S617" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60686,7 +60686,7 @@
       </c>
       <c r="S618" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60783,7 +60783,7 @@
       </c>
       <c r="S619" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60880,7 +60880,7 @@
       </c>
       <c r="S620" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -60977,7 +60977,7 @@
       </c>
       <c r="S621" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61074,7 +61074,7 @@
       </c>
       <c r="S622" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61171,7 +61171,7 @@
       </c>
       <c r="S623" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61268,7 +61268,7 @@
       </c>
       <c r="S624" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61365,7 +61365,7 @@
       </c>
       <c r="S625" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61462,7 +61462,7 @@
       </c>
       <c r="S626" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61559,7 +61559,7 @@
       </c>
       <c r="S627" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61656,7 +61656,7 @@
       </c>
       <c r="S628" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61753,7 +61753,7 @@
       </c>
       <c r="S629" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61850,7 +61850,7 @@
       </c>
       <c r="S630" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -61947,7 +61947,7 @@
       </c>
       <c r="S631" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62044,7 +62044,7 @@
       </c>
       <c r="S632" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62141,7 +62141,7 @@
       </c>
       <c r="S633" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62238,7 +62238,7 @@
       </c>
       <c r="S634" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62335,7 +62335,7 @@
       </c>
       <c r="S635" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62432,7 +62432,7 @@
       </c>
       <c r="S636" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62529,7 +62529,7 @@
       </c>
       <c r="S637" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62626,7 +62626,7 @@
       </c>
       <c r="S638" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62723,7 +62723,7 @@
       </c>
       <c r="S639" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62820,7 +62820,7 @@
       </c>
       <c r="S640" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -62917,7 +62917,7 @@
       </c>
       <c r="S641" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63014,7 +63014,7 @@
       </c>
       <c r="S642" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63111,7 +63111,7 @@
       </c>
       <c r="S643" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63208,7 +63208,7 @@
       </c>
       <c r="S644" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63305,7 +63305,7 @@
       </c>
       <c r="S645" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63402,7 +63402,7 @@
       </c>
       <c r="S646" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63499,7 +63499,7 @@
       </c>
       <c r="S647" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="S648" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63693,7 +63693,7 @@
       </c>
       <c r="S649" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63790,7 +63790,7 @@
       </c>
       <c r="S650" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63887,7 +63887,7 @@
       </c>
       <c r="S651" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -63984,7 +63984,7 @@
       </c>
       <c r="S652" s="15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$656</definedName>
@@ -934,7 +934,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="S73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="S92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="S93" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="S94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="S95" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="S98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="S102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="S103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="S106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="S110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="S111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="S114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="S117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="S118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="S120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="S121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="S122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="S123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="S126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="S127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="S128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="S130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="S131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="S132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="S133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="S134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="S135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="S137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="S138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="S139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="S140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="S141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="S142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="S143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="S144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="S145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="S146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="S147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="S148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="S149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="S150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15347,32 +15347,32 @@
       </c>
       <c r="K151" s="10" t="inlineStr">
         <is>
-          <t>BTS에서 제 최애는 정국이에요.</t>
+          <t>우리 그룹에서 제 최애는 막내예요.</t>
         </is>
       </c>
       <c r="L151" s="10" t="inlineStr">
         <is>
-          <t>My ultimate bias in BTS is Jungkook.</t>
+          <t>My ultimate bias in the group is the maknae.</t>
         </is>
       </c>
       <c r="M151" s="10" t="inlineStr">
         <is>
-          <t>Mi bias favorito en BTS es Jungkook.</t>
+          <t>Mi bias favorito del grupo es el maknae.</t>
         </is>
       </c>
       <c r="N151" s="10" t="inlineStr">
         <is>
-          <t>在BTS裡我的本命是Jungkook。</t>
+          <t>在這個團裡，我的本命是忙內。</t>
         </is>
       </c>
       <c r="O151" s="10" t="inlineStr">
         <is>
-          <t>在BTS里我的本命是Jungkook。</t>
+          <t>在这个团里，我的本命是忙内。</t>
         </is>
       </c>
       <c r="P151" s="10" t="inlineStr">
         <is>
-          <t>BTSで私の推しはジョングクです。</t>
+          <t>グループの中で私の推しはマンネです。</t>
         </is>
       </c>
       <c r="Q151" s="10" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="S151" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S152" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="S153" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="S154" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="S155" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="S156" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="S157" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="S158" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="S159" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="S160" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="S161" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="S162" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="S163" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="S164" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="S165" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="S166" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="S167" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="S168" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="S169" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="S170" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="S171" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="S172" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="S173" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="S174" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="S175" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="S176" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="S177" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="S178" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
       </c>
       <c r="S179" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="S180" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="S181" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="S182" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="S183" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="S184" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="S185" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="S186" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="S187" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="S188" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19073,7 +19073,7 @@
       </c>
       <c r="S189" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="S190" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="S191" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="S192" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="S193" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="S194" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="S195" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="S196" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="S197" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="S198" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="S199" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="S200" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="S201" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="S202" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S203" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="S204" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="S205" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="S206" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S207" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S208" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="S209" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="S210" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="S211" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="S212" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="S213" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21498,7 @@
       </c>
       <c r="S214" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="S215" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="S216" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="S217" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="S218" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="S219" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="S220" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="S221" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="S222" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="S223" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="S224" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22565,7 +22565,7 @@
       </c>
       <c r="S225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22662,7 +22662,7 @@
       </c>
       <c r="S226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="S227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="S228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -22953,7 +22953,7 @@
       </c>
       <c r="S229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="S230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="S231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="S232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="S233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23438,7 +23438,7 @@
       </c>
       <c r="S234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="S235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="S236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="S237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="S238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
       </c>
       <c r="S239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="S241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="S242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="S244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="S245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
       </c>
       <c r="S246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24699,7 +24699,7 @@
       </c>
       <c r="S247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24796,7 @@
       </c>
       <c r="S248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24893,7 +24893,7 @@
       </c>
       <c r="S249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="S250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="S251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25184,7 +25184,7 @@
       </c>
       <c r="S252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="S253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="S254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25475,7 @@
       </c>
       <c r="S255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="S256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="S257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="S258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="S259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="S260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="S261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="S262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="S263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="S264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="S265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
       </c>
       <c r="S266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="S267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
       </c>
       <c r="S268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26833,7 +26833,7 @@
       </c>
       <c r="S269" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -26930,7 +26930,7 @@
       </c>
       <c r="S270" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27027,7 @@
       </c>
       <c r="S271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="S272" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="S273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27318,7 +27318,7 @@
       </c>
       <c r="S274" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="S275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27512,7 @@
       </c>
       <c r="S276" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="S277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="S278" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="S279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27900,7 @@
       </c>
       <c r="S280" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="S281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="S282" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28191,7 +28191,7 @@
       </c>
       <c r="S283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="S284" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="S285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="S286" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28579,7 +28579,7 @@
       </c>
       <c r="S287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="S288" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,7 @@
       </c>
       <c r="S289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S290" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="S291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="S292" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29161,7 @@
       </c>
       <c r="S293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="S294" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
       </c>
       <c r="S295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29452,7 +29452,7 @@
       </c>
       <c r="S296" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="S297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="S298" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29743,7 +29743,7 @@
       </c>
       <c r="S299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="S300" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="S301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30034,7 @@
       </c>
       <c r="S302" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="S303" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30228,7 +30228,7 @@
       </c>
       <c r="S304" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30325,7 @@
       </c>
       <c r="S305" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="S306" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S307" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="S308" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="S309" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="S310" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -30907,7 +30907,7 @@
       </c>
       <c r="S311" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31004,7 +31004,7 @@
       </c>
       <c r="S312" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31101,7 +31101,7 @@
       </c>
       <c r="S313" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31198,7 +31198,7 @@
       </c>
       <c r="S314" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31295,7 @@
       </c>
       <c r="S315" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="S316" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="S317" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31586,7 @@
       </c>
       <c r="S318" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="S319" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="S320" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="S321" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31974,7 +31974,7 @@
       </c>
       <c r="S322" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="S323" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32168,7 +32168,7 @@
       </c>
       <c r="S324" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32265,7 +32265,7 @@
       </c>
       <c r="S325" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="S326" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32459,7 @@
       </c>
       <c r="S327" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="S328" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="S329" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
       </c>
       <c r="S330" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32847,7 +32847,7 @@
       </c>
       <c r="S331" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="S332" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="S333" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S334" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="S335" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="S336" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
       </c>
       <c r="S337" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="S338" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33623,7 +33623,7 @@
       </c>
       <c r="S339" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="S340" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33817,7 @@
       </c>
       <c r="S341" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="S342" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
       </c>
       <c r="S343" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34108,7 @@
       </c>
       <c r="S344" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="S345" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="S346" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34399,7 +34399,7 @@
       </c>
       <c r="S347" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="S348" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34593,7 +34593,7 @@
       </c>
       <c r="S349" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34690,7 +34690,7 @@
       </c>
       <c r="S350" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="S351" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="S352" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -34981,7 +34981,7 @@
       </c>
       <c r="S353" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="S354" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="S355" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35272,7 +35272,7 @@
       </c>
       <c r="S356" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="S357" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35466,7 +35466,7 @@
       </c>
       <c r="S358" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35563,7 +35563,7 @@
       </c>
       <c r="S359" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35660,7 @@
       </c>
       <c r="S360" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35757,7 +35757,7 @@
       </c>
       <c r="S361" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35854,7 +35854,7 @@
       </c>
       <c r="S362" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="S363" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36048,7 +36048,7 @@
       </c>
       <c r="S364" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36145,7 +36145,7 @@
       </c>
       <c r="S365" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="S366" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36339,7 +36339,7 @@
       </c>
       <c r="S367" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="S368" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="S369" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36630,7 +36630,7 @@
       </c>
       <c r="S370" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36727,7 +36727,7 @@
       </c>
       <c r="S371" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36824,7 +36824,7 @@
       </c>
       <c r="S372" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="S373" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37018,7 +37018,7 @@
       </c>
       <c r="S374" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="S375" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="S376" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37309,7 @@
       </c>
       <c r="S377" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S378" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="S379" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="S380" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="S381" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37794,7 +37794,7 @@
       </c>
       <c r="S382" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37891,7 +37891,7 @@
       </c>
       <c r="S383" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -37988,7 +37988,7 @@
       </c>
       <c r="S384" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38085,7 +38085,7 @@
       </c>
       <c r="S385" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38182,7 +38182,7 @@
       </c>
       <c r="S386" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="S387" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38376,7 +38376,7 @@
       </c>
       <c r="S388" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38473,7 +38473,7 @@
       </c>
       <c r="S389" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38570,7 +38570,7 @@
       </c>
       <c r="S390" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38667,7 +38667,7 @@
       </c>
       <c r="S391" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38764,7 +38764,7 @@
       </c>
       <c r="S392" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="S393" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -38958,7 +38958,7 @@
       </c>
       <c r="S394" s="11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39055,7 +39055,7 @@
       </c>
       <c r="S395" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39152,7 +39152,7 @@
       </c>
       <c r="S396" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39249,7 @@
       </c>
       <c r="S397" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39346,7 +39346,7 @@
       </c>
       <c r="S398" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39443,7 +39443,7 @@
       </c>
       <c r="S399" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="S400" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39637,7 +39637,7 @@
       </c>
       <c r="S401" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39734,7 +39734,7 @@
       </c>
       <c r="S402" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39831,7 +39831,7 @@
       </c>
       <c r="S403" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -39928,7 +39928,7 @@
       </c>
       <c r="S404" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40025,7 +40025,7 @@
       </c>
       <c r="S405" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="S406" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40219,7 +40219,7 @@
       </c>
       <c r="S407" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40316,7 +40316,7 @@
       </c>
       <c r="S408" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40413,7 +40413,7 @@
       </c>
       <c r="S409" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40510,7 +40510,7 @@
       </c>
       <c r="S410" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40607,7 +40607,7 @@
       </c>
       <c r="S411" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40704,7 +40704,7 @@
       </c>
       <c r="S412" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S413" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="S414" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -40995,7 +40995,7 @@
       </c>
       <c r="S415" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41092,7 +41092,7 @@
       </c>
       <c r="S416" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="S417" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41286,7 +41286,7 @@
       </c>
       <c r="S418" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41383,7 +41383,7 @@
       </c>
       <c r="S419" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41480,7 +41480,7 @@
       </c>
       <c r="S420" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41577,7 +41577,7 @@
       </c>
       <c r="S421" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41674,7 +41674,7 @@
       </c>
       <c r="S422" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41771,7 +41771,7 @@
       </c>
       <c r="S423" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41868,7 +41868,7 @@
       </c>
       <c r="S424" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S425" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="S426" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="S427" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="S428" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42353,7 +42353,7 @@
       </c>
       <c r="S429" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42450,7 +42450,7 @@
       </c>
       <c r="S430" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42547,7 +42547,7 @@
       </c>
       <c r="S431" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42644,7 +42644,7 @@
       </c>
       <c r="S432" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42741,7 +42741,7 @@
       </c>
       <c r="S433" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42838,7 +42838,7 @@
       </c>
       <c r="S434" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -42935,7 +42935,7 @@
       </c>
       <c r="S435" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43032,7 +43032,7 @@
       </c>
       <c r="S436" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="S437" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="S438" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="S439" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43420,7 +43420,7 @@
       </c>
       <c r="S440" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43517,7 +43517,7 @@
       </c>
       <c r="S441" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="S442" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43711,7 @@
       </c>
       <c r="S443" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43808,7 +43808,7 @@
       </c>
       <c r="S444" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -43905,7 +43905,7 @@
       </c>
       <c r="S445" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44002,7 +44002,7 @@
       </c>
       <c r="S446" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44099,7 +44099,7 @@
       </c>
       <c r="S447" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44196,7 +44196,7 @@
       </c>
       <c r="S448" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44293,7 +44293,7 @@
       </c>
       <c r="S449" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44390,7 +44390,7 @@
       </c>
       <c r="S450" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="S451" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="S452" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44681,7 +44681,7 @@
       </c>
       <c r="S453" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44778,7 +44778,7 @@
       </c>
       <c r="S454" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44875,7 +44875,7 @@
       </c>
       <c r="S455" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -44972,7 +44972,7 @@
       </c>
       <c r="S456" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
       </c>
       <c r="S457" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45166,7 +45166,7 @@
       </c>
       <c r="S458" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45263,7 +45263,7 @@
       </c>
       <c r="S459" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45360,7 +45360,7 @@
       </c>
       <c r="S460" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45457,7 +45457,7 @@
       </c>
       <c r="S461" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45554,7 +45554,7 @@
       </c>
       <c r="S462" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="S463" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="S464" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45845,7 +45845,7 @@
       </c>
       <c r="S465" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -45942,7 +45942,7 @@
       </c>
       <c r="S466" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46039,7 +46039,7 @@
       </c>
       <c r="S467" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46136,7 +46136,7 @@
       </c>
       <c r="S468" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="S469" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46330,7 +46330,7 @@
       </c>
       <c r="S470" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="S471" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46524,7 +46524,7 @@
       </c>
       <c r="S472" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46621,7 +46621,7 @@
       </c>
       <c r="S473" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46718,7 +46718,7 @@
       </c>
       <c r="S474" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46815,7 +46815,7 @@
       </c>
       <c r="S475" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -46912,7 +46912,7 @@
       </c>
       <c r="S476" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47009,7 +47009,7 @@
       </c>
       <c r="S477" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47106,7 +47106,7 @@
       </c>
       <c r="S478" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47203,7 +47203,7 @@
       </c>
       <c r="S479" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S480" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="S481" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47494,7 +47494,7 @@
       </c>
       <c r="S482" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47591,7 +47591,7 @@
       </c>
       <c r="S483" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47688,7 +47688,7 @@
       </c>
       <c r="S484" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47785,7 +47785,7 @@
       </c>
       <c r="S485" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47882,7 +47882,7 @@
       </c>
       <c r="S486" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -47979,7 +47979,7 @@
       </c>
       <c r="S487" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48076,7 +48076,7 @@
       </c>
       <c r="S488" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48173,7 +48173,7 @@
       </c>
       <c r="S489" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48270,7 +48270,7 @@
       </c>
       <c r="S490" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48367,7 +48367,7 @@
       </c>
       <c r="S491" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48464,7 +48464,7 @@
       </c>
       <c r="S492" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="S493" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48658,7 +48658,7 @@
       </c>
       <c r="S494" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="S495" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48852,7 +48852,7 @@
       </c>
       <c r="S496" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -48949,7 +48949,7 @@
       </c>
       <c r="S497" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49046,7 +49046,7 @@
       </c>
       <c r="S498" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49143,7 +49143,7 @@
       </c>
       <c r="S499" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49240,7 +49240,7 @@
       </c>
       <c r="S500" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49337,7 +49337,7 @@
       </c>
       <c r="S501" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49434,7 +49434,7 @@
       </c>
       <c r="S502" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49531,7 +49531,7 @@
       </c>
       <c r="S503" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49628,7 +49628,7 @@
       </c>
       <c r="S504" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49725,7 +49725,7 @@
       </c>
       <c r="S505" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49822,7 +49822,7 @@
       </c>
       <c r="S506" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -49919,7 +49919,7 @@
       </c>
       <c r="S507" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50016,7 +50016,7 @@
       </c>
       <c r="S508" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50113,7 +50113,7 @@
       </c>
       <c r="S509" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50210,7 +50210,7 @@
       </c>
       <c r="S510" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50307,7 +50307,7 @@
       </c>
       <c r="S511" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50404,7 +50404,7 @@
       </c>
       <c r="S512" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50501,7 +50501,7 @@
       </c>
       <c r="S513" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50598,7 +50598,7 @@
       </c>
       <c r="S514" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50695,7 +50695,7 @@
       </c>
       <c r="S515" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S516" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50889,7 +50889,7 @@
       </c>
       <c r="S517" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -50986,7 +50986,7 @@
       </c>
       <c r="S518" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51083,7 +51083,7 @@
       </c>
       <c r="S519" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51180,7 +51180,7 @@
       </c>
       <c r="S520" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51277,7 +51277,7 @@
       </c>
       <c r="S521" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="S522" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="S523" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51568,7 +51568,7 @@
       </c>
       <c r="S524" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51665,7 +51665,7 @@
       </c>
       <c r="S525" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51762,7 +51762,7 @@
       </c>
       <c r="S526" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51859,7 +51859,7 @@
       </c>
       <c r="S527" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -51956,7 +51956,7 @@
       </c>
       <c r="S528" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="S529" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52150,7 +52150,7 @@
       </c>
       <c r="S530" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="S531" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52344,7 +52344,7 @@
       </c>
       <c r="S532" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52441,7 +52441,7 @@
       </c>
       <c r="S533" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52538,7 +52538,7 @@
       </c>
       <c r="S534" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="S535" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52732,7 +52732,7 @@
       </c>
       <c r="S536" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52829,7 +52829,7 @@
       </c>
       <c r="S537" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -52926,7 +52926,7 @@
       </c>
       <c r="S538" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53023,7 +53023,7 @@
       </c>
       <c r="S539" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53120,7 +53120,7 @@
       </c>
       <c r="S540" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53217,7 +53217,7 @@
       </c>
       <c r="S541" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53314,7 +53314,7 @@
       </c>
       <c r="S542" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53411,7 +53411,7 @@
       </c>
       <c r="S543" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53508,7 +53508,7 @@
       </c>
       <c r="S544" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53605,7 +53605,7 @@
       </c>
       <c r="S545" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53702,7 +53702,7 @@
       </c>
       <c r="S546" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53799,7 +53799,7 @@
       </c>
       <c r="S547" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53896,7 +53896,7 @@
       </c>
       <c r="S548" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -53993,7 +53993,7 @@
       </c>
       <c r="S549" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54090,7 +54090,7 @@
       </c>
       <c r="S550" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54187,7 +54187,7 @@
       </c>
       <c r="S551" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54284,7 +54284,7 @@
       </c>
       <c r="S552" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54381,7 +54381,7 @@
       </c>
       <c r="S553" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54478,7 +54478,7 @@
       </c>
       <c r="S554" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54575,7 +54575,7 @@
       </c>
       <c r="S555" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54672,7 +54672,7 @@
       </c>
       <c r="S556" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54769,7 +54769,7 @@
       </c>
       <c r="S557" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54866,7 +54866,7 @@
       </c>
       <c r="S558" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -54963,7 +54963,7 @@
       </c>
       <c r="S559" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55060,7 +55060,7 @@
       </c>
       <c r="S560" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55157,7 +55157,7 @@
       </c>
       <c r="S561" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55254,7 +55254,7 @@
       </c>
       <c r="S562" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55351,7 +55351,7 @@
       </c>
       <c r="S563" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55448,7 +55448,7 @@
       </c>
       <c r="S564" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55545,7 +55545,7 @@
       </c>
       <c r="S565" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55642,7 +55642,7 @@
       </c>
       <c r="S566" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55739,7 +55739,7 @@
       </c>
       <c r="S567" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55836,7 +55836,7 @@
       </c>
       <c r="S568" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -55933,7 +55933,7 @@
       </c>
       <c r="S569" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56030,7 +56030,7 @@
       </c>
       <c r="S570" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56127,7 +56127,7 @@
       </c>
       <c r="S571" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56224,7 +56224,7 @@
       </c>
       <c r="S572" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56321,7 +56321,7 @@
       </c>
       <c r="S573" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56418,7 +56418,7 @@
       </c>
       <c r="S574" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56515,7 +56515,7 @@
       </c>
       <c r="S575" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56612,7 +56612,7 @@
       </c>
       <c r="S576" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56709,7 +56709,7 @@
       </c>
       <c r="S577" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S578" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -56903,7 +56903,7 @@
       </c>
       <c r="S579" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57000,7 +57000,7 @@
       </c>
       <c r="S580" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="S581" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57194,7 +57194,7 @@
       </c>
       <c r="S582" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57291,7 +57291,7 @@
       </c>
       <c r="S583" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="S584" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57485,7 +57485,7 @@
       </c>
       <c r="S585" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57582,7 +57582,7 @@
       </c>
       <c r="S586" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57679,7 +57679,7 @@
       </c>
       <c r="S587" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57776,7 +57776,7 @@
       </c>
       <c r="S588" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57873,7 +57873,7 @@
       </c>
       <c r="S589" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -57970,7 +57970,7 @@
       </c>
       <c r="S590" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58067,7 +58067,7 @@
       </c>
       <c r="S591" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58164,7 +58164,7 @@
       </c>
       <c r="S592" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58261,7 +58261,7 @@
       </c>
       <c r="S593" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58358,7 +58358,7 @@
       </c>
       <c r="S594" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58455,7 +58455,7 @@
       </c>
       <c r="S595" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58552,7 +58552,7 @@
       </c>
       <c r="S596" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58649,7 +58649,7 @@
       </c>
       <c r="S597" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58746,7 +58746,7 @@
       </c>
       <c r="S598" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58843,7 +58843,7 @@
       </c>
       <c r="S599" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -58940,7 +58940,7 @@
       </c>
       <c r="S600" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59037,7 +59037,7 @@
       </c>
       <c r="S601" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59134,7 +59134,7 @@
       </c>
       <c r="S602" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59231,7 +59231,7 @@
       </c>
       <c r="S603" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59328,7 +59328,7 @@
       </c>
       <c r="S604" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59425,7 +59425,7 @@
       </c>
       <c r="S605" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="S606" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S607" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59716,7 +59716,7 @@
       </c>
       <c r="S608" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59813,7 +59813,7 @@
       </c>
       <c r="S609" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -59910,7 +59910,7 @@
       </c>
       <c r="S610" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60007,7 +60007,7 @@
       </c>
       <c r="S611" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60104,7 +60104,7 @@
       </c>
       <c r="S612" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60201,7 +60201,7 @@
       </c>
       <c r="S613" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S614" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60395,7 +60395,7 @@
       </c>
       <c r="S615" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60492,7 +60492,7 @@
       </c>
       <c r="S616" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60589,7 +60589,7 @@
       </c>
       <c r="S617" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60686,7 +60686,7 @@
       </c>
       <c r="S618" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60783,7 +60783,7 @@
       </c>
       <c r="S619" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60880,7 +60880,7 @@
       </c>
       <c r="S620" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -60977,7 +60977,7 @@
       </c>
       <c r="S621" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61074,7 +61074,7 @@
       </c>
       <c r="S622" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61171,7 +61171,7 @@
       </c>
       <c r="S623" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61268,7 +61268,7 @@
       </c>
       <c r="S624" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61365,7 +61365,7 @@
       </c>
       <c r="S625" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61462,7 +61462,7 @@
       </c>
       <c r="S626" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61559,7 +61559,7 @@
       </c>
       <c r="S627" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61656,7 +61656,7 @@
       </c>
       <c r="S628" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61753,7 +61753,7 @@
       </c>
       <c r="S629" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61850,7 +61850,7 @@
       </c>
       <c r="S630" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -61947,7 +61947,7 @@
       </c>
       <c r="S631" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62044,7 +62044,7 @@
       </c>
       <c r="S632" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62141,7 +62141,7 @@
       </c>
       <c r="S633" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62238,7 +62238,7 @@
       </c>
       <c r="S634" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62335,7 +62335,7 @@
       </c>
       <c r="S635" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62432,7 +62432,7 @@
       </c>
       <c r="S636" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62529,7 +62529,7 @@
       </c>
       <c r="S637" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62626,7 +62626,7 @@
       </c>
       <c r="S638" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62723,7 +62723,7 @@
       </c>
       <c r="S639" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62820,7 +62820,7 @@
       </c>
       <c r="S640" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -62917,7 +62917,7 @@
       </c>
       <c r="S641" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63014,7 +63014,7 @@
       </c>
       <c r="S642" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63111,7 +63111,7 @@
       </c>
       <c r="S643" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63208,7 +63208,7 @@
       </c>
       <c r="S644" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63305,7 +63305,7 @@
       </c>
       <c r="S645" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63402,7 +63402,7 @@
       </c>
       <c r="S646" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63499,7 +63499,7 @@
       </c>
       <c r="S647" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="S648" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63693,7 +63693,7 @@
       </c>
       <c r="S649" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63790,7 +63790,7 @@
       </c>
       <c r="S650" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63887,7 +63887,7 @@
       </c>
       <c r="S651" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -63984,7 +63984,7 @@
       </c>
       <c r="S652" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -64081,7 +64081,7 @@
       </c>
       <c r="S653" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -64178,7 +64178,7 @@
       </c>
       <c r="S654" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -64275,7 +64275,7 @@
       </c>
       <c r="S655" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -64372,7 +64372,7 @@
       </c>
       <c r="S656" s="15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -39960,27 +39960,27 @@
       </c>
       <c r="F405" s="14" t="inlineStr">
         <is>
-          <t>A playful blend of "king" + 받다 ("to receive/feel"), meaning something is really irritating.</t>
+          <t>A playful blend of English "king" + 열받다 ("to get mad") — something is SO annoying, usually in a funny way rather than real anger.</t>
         </is>
       </c>
       <c r="G405" s="14" t="inlineStr">
         <is>
-          <t>Una mezcla juguetona de "rey" + "recibir", que significa que algo es muy irritante.</t>
+          <t>Una mezcla juguetona del inglés "king" + 열받다 ("enojarse"): algo que molesta muchísimo, normalmente de forma graciosa más que con enojo real.</t>
         </is>
       </c>
       <c r="H405" s="14" t="inlineStr">
         <is>
-          <t>「king」加上「받다」（受到、感覺到）的結合，形容某件事真的很惹怒人。</t>
+          <t>英文「king」加上「열받다」（生氣）的組合，表示某件事超級讓人火大——通常是好笑的那種氣，而不是真的發怒。</t>
         </is>
       </c>
       <c r="I405" s="14" t="inlineStr">
         <is>
-          <t>“king”加上“받다”（受到、感觉到）的结合，形容某件事真的很惹怒人。</t>
+          <t>英文“king”加上“열받다”（生气）的组合，表示某件事超级让人火大——通常是好笑的那种气，而不是真的发怒。</t>
         </is>
       </c>
       <c r="J405" s="14" t="inlineStr">
         <is>
-          <t>「king」と받다（受け取る）を組み合わせた言葉で、すごくイライラすることを表す。</t>
+          <t>英語の「king」と열받다（腹が立つ）を組み合わせた言葉。めちゃくちゃイラッとすることを表すが、本気の怒りより「笑えるイラつき」に使うことが多い。</t>
         </is>
       </c>
       <c r="K405" s="14" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="R405" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S405" s="13" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -26925,7 +26925,7 @@
       </c>
       <c r="R270" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S270" s="11" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$656</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="S73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="S92" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="S93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="S94" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="S95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="S98" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="S102" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="S103" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="S106" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="S110" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="S111" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S113" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="S114" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="S117" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="S118" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S119" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="S120" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="S121" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="S122" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="S123" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="S126" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="S127" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="S128" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S129" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="S130" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="S131" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="S132" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="S133" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="S134" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="S135" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S136" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="S137" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="S138" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="S139" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="S140" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="S141" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="S142" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="S143" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="S144" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="S145" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="S146" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="S147" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="S148" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="S149" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="S150" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="S151" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S152" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="S153" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="S154" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="S155" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="S156" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="S157" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="S158" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="S159" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="S160" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="S161" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="S162" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="S163" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="S164" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="S165" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="S166" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="S167" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="S168" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="S169" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="S170" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="S171" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="S172" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="S173" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="S174" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="S175" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="S176" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="S177" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="S178" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
       </c>
       <c r="S179" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="S180" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="S181" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="S182" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="S183" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="S184" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="S185" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="S186" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="S187" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="S188" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19073,7 +19073,7 @@
       </c>
       <c r="S189" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="S190" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="S191" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="S192" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="S193" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="S194" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="S195" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="S196" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="S197" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="S198" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="S199" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="S200" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="S201" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="S202" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S203" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="S204" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="S205" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="S206" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S207" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S208" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="S209" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="S210" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="S211" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="S212" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="S213" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21498,7 @@
       </c>
       <c r="S214" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="S215" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="S216" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="S217" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="S218" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="S219" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="S220" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="S221" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="S222" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="S223" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="S224" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22565,7 +22565,7 @@
       </c>
       <c r="S225" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22662,7 +22662,7 @@
       </c>
       <c r="S226" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="S227" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="S228" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -22953,7 +22953,7 @@
       </c>
       <c r="S229" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="S230" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="S231" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="S232" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="S233" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23438,7 +23438,7 @@
       </c>
       <c r="S234" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="S235" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="S236" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="S237" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="S238" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
       </c>
       <c r="S239" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S240" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="S241" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="S242" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S243" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="S244" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="S245" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
       </c>
       <c r="S246" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24699,7 +24699,7 @@
       </c>
       <c r="S247" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24796,7 @@
       </c>
       <c r="S248" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24893,7 +24893,7 @@
       </c>
       <c r="S249" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="S250" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="S251" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25184,7 +25184,7 @@
       </c>
       <c r="S252" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="S253" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="S254" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25475,7 @@
       </c>
       <c r="S255" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="S256" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="S257" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="S258" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="S259" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="S260" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="S261" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="S262" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="S263" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="S264" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="S265" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
       </c>
       <c r="S266" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="S267" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
       </c>
       <c r="S268" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26833,7 +26833,7 @@
       </c>
       <c r="S269" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -26930,7 +26930,7 @@
       </c>
       <c r="S270" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27027,7 @@
       </c>
       <c r="S271" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="S272" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="S273" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27318,7 +27318,7 @@
       </c>
       <c r="S274" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="S275" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27512,7 @@
       </c>
       <c r="S276" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="S277" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="S278" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="S279" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27900,7 @@
       </c>
       <c r="S280" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="S281" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="S282" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28191,7 +28191,7 @@
       </c>
       <c r="S283" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="S284" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="S285" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="S286" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28579,7 +28579,7 @@
       </c>
       <c r="S287" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="S288" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,7 @@
       </c>
       <c r="S289" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S290" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="S291" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="S292" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29161,7 @@
       </c>
       <c r="S293" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="S294" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
       </c>
       <c r="S295" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29452,7 +29452,7 @@
       </c>
       <c r="S296" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="S297" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="S298" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29743,7 +29743,7 @@
       </c>
       <c r="S299" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="S300" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="S301" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30034,7 @@
       </c>
       <c r="S302" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="S303" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30228,7 +30228,7 @@
       </c>
       <c r="S304" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30325,7 @@
       </c>
       <c r="S305" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="S306" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S307" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="S308" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="S309" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="S310" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -30907,7 +30907,7 @@
       </c>
       <c r="S311" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31004,7 +31004,7 @@
       </c>
       <c r="S312" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31101,7 +31101,7 @@
       </c>
       <c r="S313" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31198,7 +31198,7 @@
       </c>
       <c r="S314" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31295,7 @@
       </c>
       <c r="S315" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="S316" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="S317" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31586,7 @@
       </c>
       <c r="S318" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="S319" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="S320" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="S321" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -31974,7 +31974,7 @@
       </c>
       <c r="S322" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="S323" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32168,7 +32168,7 @@
       </c>
       <c r="S324" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32265,7 +32265,7 @@
       </c>
       <c r="S325" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="S326" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32459,7 @@
       </c>
       <c r="S327" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="S328" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="S329" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
       </c>
       <c r="S330" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32847,7 +32847,7 @@
       </c>
       <c r="S331" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="S332" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="S333" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S334" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="S335" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="S336" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
       </c>
       <c r="S337" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="S338" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33623,7 +33623,7 @@
       </c>
       <c r="S339" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="S340" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33817,7 @@
       </c>
       <c r="S341" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="S342" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
       </c>
       <c r="S343" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34108,7 @@
       </c>
       <c r="S344" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="S345" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="S346" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34399,7 +34399,7 @@
       </c>
       <c r="S347" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="S348" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34593,7 +34593,7 @@
       </c>
       <c r="S349" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34690,7 +34690,7 @@
       </c>
       <c r="S350" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="S351" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="S352" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -34981,7 +34981,7 @@
       </c>
       <c r="S353" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="S354" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="S355" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35272,7 +35272,7 @@
       </c>
       <c r="S356" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="S357" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35466,7 +35466,7 @@
       </c>
       <c r="S358" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35563,7 +35563,7 @@
       </c>
       <c r="S359" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35660,7 @@
       </c>
       <c r="S360" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35757,7 +35757,7 @@
       </c>
       <c r="S361" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35854,7 +35854,7 @@
       </c>
       <c r="S362" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="S363" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36048,7 +36048,7 @@
       </c>
       <c r="S364" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36145,7 +36145,7 @@
       </c>
       <c r="S365" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="S366" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36339,7 +36339,7 @@
       </c>
       <c r="S367" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="S368" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="S369" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36630,7 +36630,7 @@
       </c>
       <c r="S370" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36727,7 +36727,7 @@
       </c>
       <c r="S371" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36824,7 +36824,7 @@
       </c>
       <c r="S372" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="S373" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37018,7 +37018,7 @@
       </c>
       <c r="S374" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="S375" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="S376" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37309,7 @@
       </c>
       <c r="S377" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S378" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="S379" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="S380" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="S381" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37794,7 +37794,7 @@
       </c>
       <c r="S382" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37891,7 +37891,7 @@
       </c>
       <c r="S383" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -37988,7 +37988,7 @@
       </c>
       <c r="S384" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38085,7 +38085,7 @@
       </c>
       <c r="S385" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38182,7 +38182,7 @@
       </c>
       <c r="S386" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="S387" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38376,7 +38376,7 @@
       </c>
       <c r="S388" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38473,7 +38473,7 @@
       </c>
       <c r="S389" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38570,7 +38570,7 @@
       </c>
       <c r="S390" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38667,7 +38667,7 @@
       </c>
       <c r="S391" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38764,7 +38764,7 @@
       </c>
       <c r="S392" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="S393" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -38958,7 +38958,7 @@
       </c>
       <c r="S394" s="11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39055,7 +39055,7 @@
       </c>
       <c r="S395" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39152,7 +39152,7 @@
       </c>
       <c r="S396" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39249,7 @@
       </c>
       <c r="S397" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39346,7 +39346,7 @@
       </c>
       <c r="S398" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39443,7 +39443,7 @@
       </c>
       <c r="S399" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="S400" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39637,7 +39637,7 @@
       </c>
       <c r="S401" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39734,7 +39734,7 @@
       </c>
       <c r="S402" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39831,7 +39831,7 @@
       </c>
       <c r="S403" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -39928,7 +39928,7 @@
       </c>
       <c r="S404" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40025,7 +40025,7 @@
       </c>
       <c r="S405" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="S406" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40219,7 +40219,7 @@
       </c>
       <c r="S407" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40316,7 +40316,7 @@
       </c>
       <c r="S408" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40413,7 +40413,7 @@
       </c>
       <c r="S409" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40510,7 +40510,7 @@
       </c>
       <c r="S410" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40607,7 +40607,7 @@
       </c>
       <c r="S411" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40704,7 +40704,7 @@
       </c>
       <c r="S412" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S413" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="S414" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -40995,7 +40995,7 @@
       </c>
       <c r="S415" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41092,7 +41092,7 @@
       </c>
       <c r="S416" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="S417" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41286,7 +41286,7 @@
       </c>
       <c r="S418" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41383,7 +41383,7 @@
       </c>
       <c r="S419" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41480,7 +41480,7 @@
       </c>
       <c r="S420" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41577,7 +41577,7 @@
       </c>
       <c r="S421" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41674,7 +41674,7 @@
       </c>
       <c r="S422" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41771,7 +41771,7 @@
       </c>
       <c r="S423" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41868,7 +41868,7 @@
       </c>
       <c r="S424" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S425" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="S426" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="S427" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="S428" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42353,7 +42353,7 @@
       </c>
       <c r="S429" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42450,7 +42450,7 @@
       </c>
       <c r="S430" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42547,7 +42547,7 @@
       </c>
       <c r="S431" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42644,7 +42644,7 @@
       </c>
       <c r="S432" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42741,7 +42741,7 @@
       </c>
       <c r="S433" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42838,7 +42838,7 @@
       </c>
       <c r="S434" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -42935,7 +42935,7 @@
       </c>
       <c r="S435" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43032,7 +43032,7 @@
       </c>
       <c r="S436" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="S437" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="S438" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="S439" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43420,7 +43420,7 @@
       </c>
       <c r="S440" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43517,7 +43517,7 @@
       </c>
       <c r="S441" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="S442" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43711,7 @@
       </c>
       <c r="S443" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43808,7 +43808,7 @@
       </c>
       <c r="S444" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -43905,7 +43905,7 @@
       </c>
       <c r="S445" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44002,7 +44002,7 @@
       </c>
       <c r="S446" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44099,7 +44099,7 @@
       </c>
       <c r="S447" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44196,7 +44196,7 @@
       </c>
       <c r="S448" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44293,7 +44293,7 @@
       </c>
       <c r="S449" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44390,7 +44390,7 @@
       </c>
       <c r="S450" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="S451" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="S452" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44681,7 +44681,7 @@
       </c>
       <c r="S453" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44778,7 +44778,7 @@
       </c>
       <c r="S454" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44875,7 +44875,7 @@
       </c>
       <c r="S455" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -44972,7 +44972,7 @@
       </c>
       <c r="S456" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
       </c>
       <c r="S457" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45166,7 +45166,7 @@
       </c>
       <c r="S458" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45263,7 +45263,7 @@
       </c>
       <c r="S459" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45360,7 +45360,7 @@
       </c>
       <c r="S460" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45457,7 +45457,7 @@
       </c>
       <c r="S461" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45554,7 +45554,7 @@
       </c>
       <c r="S462" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="S463" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="S464" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45845,7 +45845,7 @@
       </c>
       <c r="S465" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -45942,7 +45942,7 @@
       </c>
       <c r="S466" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46039,7 +46039,7 @@
       </c>
       <c r="S467" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46136,7 +46136,7 @@
       </c>
       <c r="S468" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="S469" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46330,7 +46330,7 @@
       </c>
       <c r="S470" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="S471" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46524,7 +46524,7 @@
       </c>
       <c r="S472" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46621,7 +46621,7 @@
       </c>
       <c r="S473" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46718,7 +46718,7 @@
       </c>
       <c r="S474" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46815,7 +46815,7 @@
       </c>
       <c r="S475" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -46912,7 +46912,7 @@
       </c>
       <c r="S476" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47009,7 +47009,7 @@
       </c>
       <c r="S477" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47106,7 +47106,7 @@
       </c>
       <c r="S478" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47203,7 +47203,7 @@
       </c>
       <c r="S479" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S480" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="S481" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47494,7 +47494,7 @@
       </c>
       <c r="S482" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47591,7 +47591,7 @@
       </c>
       <c r="S483" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47688,7 +47688,7 @@
       </c>
       <c r="S484" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47785,7 +47785,7 @@
       </c>
       <c r="S485" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47882,7 +47882,7 @@
       </c>
       <c r="S486" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47979,7 +47979,7 @@
       </c>
       <c r="S487" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48076,7 +48076,7 @@
       </c>
       <c r="S488" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48173,7 +48173,7 @@
       </c>
       <c r="S489" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48270,7 +48270,7 @@
       </c>
       <c r="S490" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48367,7 +48367,7 @@
       </c>
       <c r="S491" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48464,7 +48464,7 @@
       </c>
       <c r="S492" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="S493" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48658,7 +48658,7 @@
       </c>
       <c r="S494" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="S495" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48852,7 +48852,7 @@
       </c>
       <c r="S496" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -48949,7 +48949,7 @@
       </c>
       <c r="S497" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49046,7 +49046,7 @@
       </c>
       <c r="S498" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49143,7 +49143,7 @@
       </c>
       <c r="S499" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49240,7 +49240,7 @@
       </c>
       <c r="S500" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49337,7 +49337,7 @@
       </c>
       <c r="S501" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49434,7 +49434,7 @@
       </c>
       <c r="S502" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49531,7 +49531,7 @@
       </c>
       <c r="S503" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49628,7 +49628,7 @@
       </c>
       <c r="S504" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49725,7 +49725,7 @@
       </c>
       <c r="S505" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49822,7 +49822,7 @@
       </c>
       <c r="S506" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -49919,7 +49919,7 @@
       </c>
       <c r="S507" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50016,7 +50016,7 @@
       </c>
       <c r="S508" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50113,7 +50113,7 @@
       </c>
       <c r="S509" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50210,7 +50210,7 @@
       </c>
       <c r="S510" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50307,7 +50307,7 @@
       </c>
       <c r="S511" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50404,7 +50404,7 @@
       </c>
       <c r="S512" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50501,7 +50501,7 @@
       </c>
       <c r="S513" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50598,7 +50598,7 @@
       </c>
       <c r="S514" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50695,7 +50695,7 @@
       </c>
       <c r="S515" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S516" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50889,7 +50889,7 @@
       </c>
       <c r="S517" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -50986,7 +50986,7 @@
       </c>
       <c r="S518" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51083,7 +51083,7 @@
       </c>
       <c r="S519" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51180,7 +51180,7 @@
       </c>
       <c r="S520" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51277,7 +51277,7 @@
       </c>
       <c r="S521" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="S522" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="S523" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51568,7 +51568,7 @@
       </c>
       <c r="S524" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51665,7 +51665,7 @@
       </c>
       <c r="S525" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51762,7 +51762,7 @@
       </c>
       <c r="S526" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51859,7 +51859,7 @@
       </c>
       <c r="S527" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -51956,7 +51956,7 @@
       </c>
       <c r="S528" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="S529" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52150,7 +52150,7 @@
       </c>
       <c r="S530" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="S531" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52344,7 +52344,7 @@
       </c>
       <c r="S532" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52441,7 +52441,7 @@
       </c>
       <c r="S533" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52538,7 +52538,7 @@
       </c>
       <c r="S534" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="S535" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52732,7 +52732,7 @@
       </c>
       <c r="S536" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52829,7 +52829,7 @@
       </c>
       <c r="S537" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -52926,7 +52926,7 @@
       </c>
       <c r="S538" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53023,7 +53023,7 @@
       </c>
       <c r="S539" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53120,7 +53120,7 @@
       </c>
       <c r="S540" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53217,7 +53217,7 @@
       </c>
       <c r="S541" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53314,7 +53314,7 @@
       </c>
       <c r="S542" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53411,7 +53411,7 @@
       </c>
       <c r="S543" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53508,7 +53508,7 @@
       </c>
       <c r="S544" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53605,7 +53605,7 @@
       </c>
       <c r="S545" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53702,7 +53702,7 @@
       </c>
       <c r="S546" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53799,7 +53799,7 @@
       </c>
       <c r="S547" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53896,7 +53896,7 @@
       </c>
       <c r="S548" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -53993,7 +53993,7 @@
       </c>
       <c r="S549" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54090,7 +54090,7 @@
       </c>
       <c r="S550" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54187,7 +54187,7 @@
       </c>
       <c r="S551" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54284,7 +54284,7 @@
       </c>
       <c r="S552" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54381,7 +54381,7 @@
       </c>
       <c r="S553" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54478,7 +54478,7 @@
       </c>
       <c r="S554" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54575,7 +54575,7 @@
       </c>
       <c r="S555" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54672,7 +54672,7 @@
       </c>
       <c r="S556" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54769,7 +54769,7 @@
       </c>
       <c r="S557" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54866,7 +54866,7 @@
       </c>
       <c r="S558" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -54963,7 +54963,7 @@
       </c>
       <c r="S559" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55060,7 +55060,7 @@
       </c>
       <c r="S560" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55157,7 +55157,7 @@
       </c>
       <c r="S561" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55254,7 +55254,7 @@
       </c>
       <c r="S562" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55351,7 +55351,7 @@
       </c>
       <c r="S563" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55448,7 +55448,7 @@
       </c>
       <c r="S564" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55545,7 +55545,7 @@
       </c>
       <c r="S565" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55642,7 +55642,7 @@
       </c>
       <c r="S566" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55739,7 +55739,7 @@
       </c>
       <c r="S567" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55836,7 +55836,7 @@
       </c>
       <c r="S568" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -55933,7 +55933,7 @@
       </c>
       <c r="S569" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56030,7 +56030,7 @@
       </c>
       <c r="S570" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56127,7 +56127,7 @@
       </c>
       <c r="S571" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56224,7 +56224,7 @@
       </c>
       <c r="S572" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56321,7 +56321,7 @@
       </c>
       <c r="S573" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56418,7 +56418,7 @@
       </c>
       <c r="S574" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56515,7 +56515,7 @@
       </c>
       <c r="S575" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56612,7 +56612,7 @@
       </c>
       <c r="S576" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56709,7 +56709,7 @@
       </c>
       <c r="S577" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S578" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -56903,7 +56903,7 @@
       </c>
       <c r="S579" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57000,7 +57000,7 @@
       </c>
       <c r="S580" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="S581" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57194,7 +57194,7 @@
       </c>
       <c r="S582" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57291,7 +57291,7 @@
       </c>
       <c r="S583" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="S584" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57485,7 +57485,7 @@
       </c>
       <c r="S585" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57582,7 +57582,7 @@
       </c>
       <c r="S586" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57679,7 +57679,7 @@
       </c>
       <c r="S587" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57776,7 +57776,7 @@
       </c>
       <c r="S588" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57873,7 +57873,7 @@
       </c>
       <c r="S589" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -57970,7 +57970,7 @@
       </c>
       <c r="S590" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58067,7 +58067,7 @@
       </c>
       <c r="S591" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58164,7 +58164,7 @@
       </c>
       <c r="S592" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58261,7 +58261,7 @@
       </c>
       <c r="S593" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58358,7 +58358,7 @@
       </c>
       <c r="S594" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58455,7 +58455,7 @@
       </c>
       <c r="S595" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58552,7 +58552,7 @@
       </c>
       <c r="S596" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58649,7 +58649,7 @@
       </c>
       <c r="S597" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58746,7 +58746,7 @@
       </c>
       <c r="S598" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58843,7 +58843,7 @@
       </c>
       <c r="S599" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -58940,7 +58940,7 @@
       </c>
       <c r="S600" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59037,7 +59037,7 @@
       </c>
       <c r="S601" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59134,7 +59134,7 @@
       </c>
       <c r="S602" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59231,7 +59231,7 @@
       </c>
       <c r="S603" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59328,7 +59328,7 @@
       </c>
       <c r="S604" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59425,7 +59425,7 @@
       </c>
       <c r="S605" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="S606" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S607" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59716,7 +59716,7 @@
       </c>
       <c r="S608" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59813,7 +59813,7 @@
       </c>
       <c r="S609" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -59910,7 +59910,7 @@
       </c>
       <c r="S610" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60007,7 +60007,7 @@
       </c>
       <c r="S611" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60104,7 +60104,7 @@
       </c>
       <c r="S612" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60201,7 +60201,7 @@
       </c>
       <c r="S613" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S614" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60395,7 +60395,7 @@
       </c>
       <c r="S615" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60492,7 +60492,7 @@
       </c>
       <c r="S616" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60589,7 +60589,7 @@
       </c>
       <c r="S617" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60686,7 +60686,7 @@
       </c>
       <c r="S618" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60783,7 +60783,7 @@
       </c>
       <c r="S619" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60880,7 +60880,7 @@
       </c>
       <c r="S620" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -60977,7 +60977,7 @@
       </c>
       <c r="S621" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61074,7 +61074,7 @@
       </c>
       <c r="S622" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61171,7 +61171,7 @@
       </c>
       <c r="S623" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61268,7 +61268,7 @@
       </c>
       <c r="S624" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61365,7 +61365,7 @@
       </c>
       <c r="S625" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61462,7 +61462,7 @@
       </c>
       <c r="S626" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61559,7 +61559,7 @@
       </c>
       <c r="S627" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61656,7 +61656,7 @@
       </c>
       <c r="S628" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61753,7 +61753,7 @@
       </c>
       <c r="S629" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61850,7 +61850,7 @@
       </c>
       <c r="S630" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -61947,7 +61947,7 @@
       </c>
       <c r="S631" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62044,7 +62044,7 @@
       </c>
       <c r="S632" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62141,7 +62141,7 @@
       </c>
       <c r="S633" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62238,7 +62238,7 @@
       </c>
       <c r="S634" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62335,7 +62335,7 @@
       </c>
       <c r="S635" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62432,7 +62432,7 @@
       </c>
       <c r="S636" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62529,7 +62529,7 @@
       </c>
       <c r="S637" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62626,7 +62626,7 @@
       </c>
       <c r="S638" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62723,7 +62723,7 @@
       </c>
       <c r="S639" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62820,7 +62820,7 @@
       </c>
       <c r="S640" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -62917,7 +62917,7 @@
       </c>
       <c r="S641" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63014,7 +63014,7 @@
       </c>
       <c r="S642" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63111,7 +63111,7 @@
       </c>
       <c r="S643" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63208,7 +63208,7 @@
       </c>
       <c r="S644" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63305,7 +63305,7 @@
       </c>
       <c r="S645" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63402,7 +63402,7 @@
       </c>
       <c r="S646" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63499,7 +63499,7 @@
       </c>
       <c r="S647" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="S648" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63693,7 +63693,7 @@
       </c>
       <c r="S649" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63790,7 +63790,7 @@
       </c>
       <c r="S650" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63887,7 +63887,7 @@
       </c>
       <c r="S651" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -63984,7 +63984,7 @@
       </c>
       <c r="S652" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -64081,7 +64081,7 @@
       </c>
       <c r="S653" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -64178,7 +64178,7 @@
       </c>
       <c r="S654" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -64275,7 +64275,7 @@
       </c>
       <c r="S655" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -64372,7 +64372,7 @@
       </c>
       <c r="S656" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$656</definedName>
@@ -60427,27 +60427,27 @@
       </c>
       <c r="F616" s="16" t="inlineStr">
         <is>
-          <t>Short for "paired-off guy" — the guy someone has a crush on.</t>
+          <t>Short for 짝사랑하는 남자 ("the guy I have a one-sided crush on") — your crush.</t>
         </is>
       </c>
       <c r="G616" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "chico emparejado": el chico del que alguien está enamorado.</t>
+          <t>Abreviatura de 짝사랑하는 남자 ("el chico del que estoy enamorada en secreto"): tu crush.</t>
         </is>
       </c>
       <c r="H616" s="16" t="inlineStr">
         <is>
-          <t>「配對男」的簡稱——某人暗戀、有好感的男生。</t>
+          <t>짝사랑하는 남자（暗戀的男生）的縮寫——你暗戀的對象。</t>
         </is>
       </c>
       <c r="I616" s="16" t="inlineStr">
         <is>
-          <t>“配对男”的简称——某人暗恋、有好感的男生。</t>
+          <t>짝사랑하는 남자（暗恋的男生）的缩写——你暗恋的对象。</t>
         </is>
       </c>
       <c r="J616" s="16" t="inlineStr">
         <is>
-          <t>「相手の男」の略——誰かが片思いしている男性。</t>
+          <t>짝사랑하는 남자（片思いしている男性）の略——片思いの相手。</t>
         </is>
       </c>
       <c r="K616" s="16" t="inlineStr">
@@ -60487,7 +60487,7 @@
       </c>
       <c r="R616" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S616" s="15" t="inlineStr">
@@ -60524,27 +60524,27 @@
       </c>
       <c r="F617" s="16" t="inlineStr">
         <is>
-          <t>Short for "paired-off girl" — the girl someone has a crush on.</t>
+          <t>Short for 짝사랑하는 여자 ("the girl I have a one-sided crush on") — your crush.</t>
         </is>
       </c>
       <c r="G617" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "chica emparejada": la chica de la que alguien está enamorado.</t>
+          <t>Abreviatura de 짝사랑하는 여자 ("la chica de la que estoy enamorado en secreto"): tu crush.</t>
         </is>
       </c>
       <c r="H617" s="16" t="inlineStr">
         <is>
-          <t>「配對女」的簡稱——某人暗戀、有好感的女生。</t>
+          <t>짝사랑하는 여자（暗戀的女生）的縮寫——你暗戀的對象。</t>
         </is>
       </c>
       <c r="I617" s="16" t="inlineStr">
         <is>
-          <t>“配对女”的简称——某人暗恋、有好感的女生。</t>
+          <t>짝사랑하는 여자（暗恋的女生）的缩写——你暗恋的对象。</t>
         </is>
       </c>
       <c r="J617" s="16" t="inlineStr">
         <is>
-          <t>「相手の女」の略——誰かが片思いしている女性。</t>
+          <t>짝사랑하는 여자（片思いしている女性）の略——片思いの相手。</t>
         </is>
       </c>
       <c r="K617" s="16" t="inlineStr">
@@ -60584,7 +60584,7 @@
       </c>
       <c r="R617" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S617" s="15" t="inlineStr">
@@ -61106,27 +61106,27 @@
       </c>
       <c r="F623" s="16" t="inlineStr">
         <is>
-          <t>"Bear + girlfriend," a term for a girlfriend patiently waiting for her boyfriend to complete mandatory military service.</t>
+          <t>Short for 고무신 (traditional rubber shoes) — a girlfriend patiently waiting for her boyfriend to finish mandatory military service.</t>
         </is>
       </c>
       <c r="G623" s="16" t="inlineStr">
         <is>
-          <t>"Oso + novia", un término para una novia que espera pacientemente a que su novio complete el servicio militar obligatorio.</t>
+          <t>Abreviatura de 고무신 (zapatos tradicionales de goma): una novia que espera pacientemente a que su novio termine el servicio militar obligatorio.</t>
         </is>
       </c>
       <c r="H623" s="16" t="inlineStr">
         <is>
-          <t>「熊＋女友」——耐心等待男友服完兵役的女友暱稱。</t>
+          <t>고무신（傳統膠鞋）的縮寫——耐心等待男友服完兵役的女友。</t>
         </is>
       </c>
       <c r="I623" s="16" t="inlineStr">
         <is>
-          <t>“熊＋女友”——耐心等待男友服完兵役的女友暱称。</t>
+          <t>고무신（传统胶鞋）的缩写——耐心等待男友服完兵役的女友。</t>
         </is>
       </c>
       <c r="J623" s="16" t="inlineStr">
         <is>
-          <t>「熊＋彼女」——兵役を終えるのを我慢強く待つ彼女を指す言葉。</t>
+          <t>고무신（伝統的なゴム靴）の略——兵役を終えるのを待つ彼女のこと。</t>
         </is>
       </c>
       <c r="K623" s="16" t="inlineStr">
@@ -61146,17 +61146,17 @@
       </c>
       <c r="N623" s="16" t="inlineStr">
         <is>
-          <t>熊女友生活還剩六個月了。</t>
+          <t>等男友退伍的日子只剩六個月了。</t>
         </is>
       </c>
       <c r="O623" s="16" t="inlineStr">
         <is>
-          <t>熊女友生活还剩六个月了。</t>
+          <t>等男友退伍的日子只剩六个月了。</t>
         </is>
       </c>
       <c r="P623" s="16" t="inlineStr">
         <is>
-          <t>熊彼女生活、あと6ヶ月残ってる。</t>
+          <t>彼の除隊を待つ生活も、あと6ヶ月。</t>
         </is>
       </c>
       <c r="Q623" s="16" t="inlineStr">
@@ -61166,7 +61166,7 @@
       </c>
       <c r="R623" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S623" s="15" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$656</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$655</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S656"/>
+  <dimension ref="A1:S655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8144,67 +8144,67 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>"Public broadcast" — a casual, personal livestream an idol does directly for fans.</t>
+          <t>Short for 공개방송 ("open broadcast") — going in person to a music show's pre-recording or live broadcast to watch and cheer for your idol.</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>"Transmisión pública": una transmisión en vivo casual y personal que un ídolo hace directamente para los fans.</t>
+          <t>Abreviatura de 공개방송 ("emisión abierta"): ir en persona a la pregrabación o la emisión en vivo de un programa musical para ver y animar a tu idol.</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>「公開放送」——偶像直接為粉絲進行的輕鬆個人直播。</t>
+          <t>공개방송（公開放送）的縮寫——親自到音樂節目的事前錄影或直播現場，為偶像應援。</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>“公开放送”——偶像直接为粉丝进行的轻松个人直播。</t>
+          <t>공개방송（公开放送）的缩写——亲自到音乐节目的预录或直播现场，为偶像应援。</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>「公開放送」の略——アイドルがファンのために直接行う気軽な個人配信。</t>
+          <t>공개방송（公開放送）の略——音楽番組の事前収録や生放送の現場に直接行って、推しを応援すること。</t>
         </is>
       </c>
       <c r="K77" s="8" t="inlineStr">
         <is>
-          <t>갑자기 공방 켰어, 빨리 들어가!</t>
+          <t>이번 주 음방 공방 당첨됐어!</t>
         </is>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
-          <t>They suddenly started a livestream, get in quick!</t>
+          <t>I got picked to attend this week's music show taping!</t>
         </is>
       </c>
       <c r="M77" s="8" t="inlineStr">
         <is>
-          <t>¡De repente empezó una transmisión en vivo, entra rápido!</t>
+          <t>¡Me eligieron para ir a la grabación del programa musical de esta semana!</t>
         </is>
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>突然開了個人直播，快進去！</t>
+          <t>這週音樂節目的公開放送我抽中了！</t>
         </is>
       </c>
       <c r="O77" s="8" t="inlineStr">
         <is>
-          <t>突然开了个人直播，快进去！</t>
+          <t>这周音乐节目的公开放送我抽中了！</t>
         </is>
       </c>
       <c r="P77" s="8" t="inlineStr">
         <is>
-          <t>突然配信始めた、早く入って！</t>
+          <t>今週の音楽番組の公開放送、当選した！</t>
         </is>
       </c>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>Livestreaming platforms</t>
+          <t>Music show fan culture</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S77" s="7" t="inlineStr">
@@ -64190,12 +64190,12 @@
       </c>
       <c r="B655" s="15" t="inlineStr">
         <is>
-          <t>불소</t>
+          <t>패완얼</t>
         </is>
       </c>
       <c r="C655" s="15" t="inlineStr">
         <is>
-          <t>bul-so</t>
+          <t>pae-wan-eol</t>
         </is>
       </c>
       <c r="D655" s="15" t="inlineStr">
@@ -64210,62 +64210,62 @@
       </c>
       <c r="F655" s="16" t="inlineStr">
         <is>
-          <t>"Burning blind date" — a blind date with intense, immediate chemistry or spark.</t>
+          <t>Short for "fashion is completed by the face" — a saying that a good-looking face elevates any outfit, no matter how simple.</t>
         </is>
       </c>
       <c r="G655" s="16" t="inlineStr">
         <is>
-          <t>"Cita a ciegas ardiente": una cita a ciegas con química o chispa intensa e inmediata.</t>
+          <t>Abreviatura de "la moda se completa con la cara": un dicho que dice que una cara atractiva mejora cualquier atuendo, sin importar lo simple que sea.</t>
         </is>
       </c>
       <c r="H655" s="16" t="inlineStr">
         <is>
-          <t>「燃燒的相親」——雙方一見面就火花四射、氣氛熱烈的相親。</t>
+          <t>「時尚的完成是臉」的簡稱——意指帥氣或漂亮的長相能撐起任何穿搭。</t>
         </is>
       </c>
       <c r="I655" s="16" t="inlineStr">
         <is>
-          <t>“燃烧的相亲”——双方一见面就火花四射、气氛热烈的相亲。</t>
+          <t>“时尚的完成是脸”的简称——意指帅气或漂亮的长相能撑起任何穿搭。</t>
         </is>
       </c>
       <c r="J655" s="16" t="inlineStr">
         <is>
-          <t>「燃える合コン」——一瞬で強い相性や火花が生まれる合コン。</t>
+          <t>「ファッションの完成は顔」の略——どんなにシンプルな服でも、整った顔立ちが引き立てるという言葉。</t>
         </is>
       </c>
       <c r="K655" s="16" t="inlineStr">
         <is>
-          <t>이번 주 불소 잡혔다는데 기대돼.</t>
+          <t>역시 패완얼이야, 뭘 입어도 잘 어울려.</t>
         </is>
       </c>
       <c r="L655" s="16" t="inlineStr">
         <is>
-          <t>I heard there's a fiery blind date lined up this week, I'm excited.</t>
+          <t>It's true, fashion's finished by the face — they look good in anything.</t>
         </is>
       </c>
       <c r="M655" s="16" t="inlineStr">
         <is>
-          <t>Escuché que hay una cita a ciegas con mucha química esta semana, estoy emocionada.</t>
+          <t>Es cierto, la cara lo completa todo — se le ve bien cualquier cosa.</t>
         </is>
       </c>
       <c r="N655" s="16" t="inlineStr">
         <is>
-          <t>聽說這禮拜安排了火花四射的相親，好期待。</t>
+          <t>果然臉才是關鍵，穿什麼都好看。</t>
         </is>
       </c>
       <c r="O655" s="16" t="inlineStr">
         <is>
-          <t>听说这礼拜安排了火花四射的相亲，好期待。</t>
+          <t>果然脸才是关键，穿什么都好看。</t>
         </is>
       </c>
       <c r="P655" s="16" t="inlineStr">
         <is>
-          <t>今週火花散る合コンがセッティングされたって、楽しみ。</t>
+          <t>やっぱり顔が全て、何着ても似合う。</t>
         </is>
       </c>
       <c r="Q655" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Fashion/beauty banter</t>
         </is>
       </c>
       <c r="R655" s="15" t="inlineStr">
@@ -64279,105 +64279,8 @@
         </is>
       </c>
     </row>
-    <row r="656" ht="46" customHeight="1">
-      <c r="A656" s="15" t="inlineStr">
-        <is>
-          <t>DAT-082</t>
-        </is>
-      </c>
-      <c r="B656" s="15" t="inlineStr">
-        <is>
-          <t>패완얼</t>
-        </is>
-      </c>
-      <c r="C656" s="15" t="inlineStr">
-        <is>
-          <t>pae-wan-eol</t>
-        </is>
-      </c>
-      <c r="D656" s="15" t="inlineStr">
-        <is>
-          <t>연애 · 썸 표현</t>
-        </is>
-      </c>
-      <c r="E656" s="15" t="inlineStr">
-        <is>
-          <t>Dating &amp; Romance</t>
-        </is>
-      </c>
-      <c r="F656" s="16" t="inlineStr">
-        <is>
-          <t>Short for "fashion is completed by the face" — a saying that a good-looking face elevates any outfit, no matter how simple.</t>
-        </is>
-      </c>
-      <c r="G656" s="16" t="inlineStr">
-        <is>
-          <t>Abreviatura de "la moda se completa con la cara": un dicho que dice que una cara atractiva mejora cualquier atuendo, sin importar lo simple que sea.</t>
-        </is>
-      </c>
-      <c r="H656" s="16" t="inlineStr">
-        <is>
-          <t>「時尚的完成是臉」的簡稱——意指帥氣或漂亮的長相能撐起任何穿搭。</t>
-        </is>
-      </c>
-      <c r="I656" s="16" t="inlineStr">
-        <is>
-          <t>“时尚的完成是脸”的简称——意指帅气或漂亮的长相能撑起任何穿搭。</t>
-        </is>
-      </c>
-      <c r="J656" s="16" t="inlineStr">
-        <is>
-          <t>「ファッションの完成は顔」の略——どんなにシンプルな服でも、整った顔立ちが引き立てるという言葉。</t>
-        </is>
-      </c>
-      <c r="K656" s="16" t="inlineStr">
-        <is>
-          <t>역시 패완얼이야, 뭘 입어도 잘 어울려.</t>
-        </is>
-      </c>
-      <c r="L656" s="16" t="inlineStr">
-        <is>
-          <t>It's true, fashion's finished by the face — they look good in anything.</t>
-        </is>
-      </c>
-      <c r="M656" s="16" t="inlineStr">
-        <is>
-          <t>Es cierto, la cara lo completa todo — se le ve bien cualquier cosa.</t>
-        </is>
-      </c>
-      <c r="N656" s="16" t="inlineStr">
-        <is>
-          <t>果然臉才是關鍵，穿什麼都好看。</t>
-        </is>
-      </c>
-      <c r="O656" s="16" t="inlineStr">
-        <is>
-          <t>果然脸才是关键，穿什么都好看。</t>
-        </is>
-      </c>
-      <c r="P656" s="16" t="inlineStr">
-        <is>
-          <t>やっぱり顔が全て、何着ても似合う。</t>
-        </is>
-      </c>
-      <c r="Q656" s="16" t="inlineStr">
-        <is>
-          <t>Fashion/beauty banter</t>
-        </is>
-      </c>
-      <c r="R656" s="15" t="inlineStr">
-        <is>
-          <t>Draft — please double-check</t>
-        </is>
-      </c>
-      <c r="S656" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S656"/>
+  <autoFilter ref="A1:S655"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$655</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$655</definedName>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>사이트석</t>
+          <t>사이드석</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>sa-i-teu-seok</t>
+          <t>sa-i-deu-seok</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="K111" s="8" t="inlineStr">
         <is>
-          <t>사이트석이라 무대 반쪽만 보였어.</t>
+          <t>사이드석이라 무대 반쪽만 보였어.</t>
         </is>
       </c>
       <c r="L111" s="8" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$655</definedName>
@@ -25216,62 +25216,62 @@
       </c>
       <c r="F253" s="10" t="inlineStr">
         <is>
-          <t>"Love call" — an idol affectionately reaching out or calling out to fans during a broadcast.</t>
+          <t>Short for 러브콜 ("love call") — openly saying you want to work with, meet or invite someone: a casting offer, a collab wish, or fans begging for an appearance.</t>
         </is>
       </c>
       <c r="G253" s="10" t="inlineStr">
         <is>
-          <t>"Llamada de amor": un ídolo que se dirige o llama afectuosamente a los fans durante una transmisión.</t>
+          <t>Abreviatura de 러브콜 ("llamada de amor"): decir abiertamente que quieres trabajar con alguien, conocerlo o invitarlo; una oferta de casting, un deseo de colaborar o fans pidiendo una aparición.</t>
         </is>
       </c>
       <c r="H253" s="10" t="inlineStr">
         <is>
-          <t>「愛的呼喚」——偶像在直播中親切地呼喚、招呼粉絲。</t>
+          <t>러브콜（Love call）的縮寫——公開表達想合作、想見面或想邀請某人：選角邀約、合作意願，或粉絲喊話要求上節目。</t>
         </is>
       </c>
       <c r="I253" s="10" t="inlineStr">
         <is>
-          <t>“爱的呼唤”——偶像在直播中亲切地呼唤、招呼粉丝。</t>
+          <t>러브콜（Love call）的缩写——公开表达想合作、想见面或想邀请某人：选角邀约、合作意愿，或粉丝喊话要求上节目。</t>
         </is>
       </c>
       <c r="J253" s="10" t="inlineStr">
         <is>
-          <t>「愛の呼びかけ」——配信中にアイドルが愛情を込めてファンに呼びかけること。</t>
+          <t>러브콜（ラブコール）の略——一緒に仕事したい、会いたい、招きたいと公に伝えること。キャスティングのオファー、コラボの希望、ファンの出演リクエストなど。</t>
         </is>
       </c>
       <c r="K253" s="10" t="inlineStr">
         <is>
-          <t>럽콜 해줄 때마다 심장 터질 것 같아.</t>
+          <t>그 예능에서 계속 럽콜 보내는 중이래.</t>
         </is>
       </c>
       <c r="L253" s="10" t="inlineStr">
         <is>
-          <t>My heart feels like it'll burst every time they do a love call.</t>
+          <t>I heard that variety show keeps sending her love calls to appear.</t>
         </is>
       </c>
       <c r="M253" s="10" t="inlineStr">
         <is>
-          <t>Siento que mi corazón va a estallar cada vez que hace una llamada de cariño.</t>
+          <t>Dicen que ese programa de variedades no deja de invitarla.</t>
         </is>
       </c>
       <c r="N253" s="10" t="inlineStr">
         <is>
-          <t>每次做愛的呼喚我的心都要跳出來了。</t>
+          <t>聽說那個綜藝一直向她發出邀約。</t>
         </is>
       </c>
       <c r="O253" s="10" t="inlineStr">
         <is>
-          <t>每次做爱的呼唤我的心都要跳出来了。</t>
+          <t>听说那个综艺一直向她发出邀约。</t>
         </is>
       </c>
       <c r="P253" s="10" t="inlineStr">
         <is>
-          <t>ラブコールしてくれるたびに、心臓が爆発しそう。</t>
+          <t>あのバラエティ番組がずっと彼女にラブコールを送ってるらしい。</t>
         </is>
       </c>
       <c r="Q253" s="10" t="inlineStr">
         <is>
-          <t>Livestream fan reactions</t>
+          <t>Collab and casting news</t>
         </is>
       </c>
       <c r="R253" s="9" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="Q268" s="10" t="inlineStr">
         <is>
-          <t>K-pop fan messaging app culture, 2026 slang</t>
+          <t>K-pop fan messaging app culture, 2025 meme</t>
         </is>
       </c>
       <c r="R268" s="9" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$655</definedName>
@@ -17727,12 +17727,12 @@
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>배댓</t>
+          <t>베댓</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>bae-daet</t>
+          <t>be-daet</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
@@ -17747,42 +17747,42 @@
       </c>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>A "belly comment" — a witty first comment posted right under an official account's post.</t>
+          <t>Short for 베스트 댓글 ("best comment"): the top-ranked, most-liked comment shown first under a post or article.</t>
         </is>
       </c>
       <c r="G176" s="10" t="inlineStr">
         <is>
-          <t>Un "comentario de vientre": un comentario ingenioso publicado justo debajo de una publicación de una cuenta oficial.</t>
+          <t>Abreviatura de 베스트 댓글 ("mejor comentario"): el comentario con más likes, que aparece primero bajo una publicación o noticia.</t>
         </is>
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>「肚子留言」——搶在官方帳號貼文下第一時間發的機智留言。</t>
+          <t>베스트 댓글（最佳留言）的縮寫：貼文或新聞下按讚最多、排在最上面的留言。</t>
         </is>
       </c>
       <c r="I176" s="10" t="inlineStr">
         <is>
-          <t>“肚子留言”——抢在官方帐号贴文下第一时间发的机智留言。</t>
+          <t>베스트 댓글（最佳留言）的缩写：帖子或新闻下点赞最多、排在最上面的留言。</t>
         </is>
       </c>
       <c r="J176" s="10" t="inlineStr">
         <is>
-          <t>公式アカウントの投稿の下に一番乗りで書かれる気の利いたコメント。</t>
+          <t>베스트 댓글（ベストコメント）の略——投稿や記事の下で一番いいねが多く、上に表示されるコメント。</t>
         </is>
       </c>
       <c r="K176" s="10" t="inlineStr">
         <is>
-          <t>배댓 진짜 웃겨서 캡처했어.</t>
+          <t>베댓 진짜 웃겨서 캡처했어.</t>
         </is>
       </c>
       <c r="L176" s="10" t="inlineStr">
         <is>
-          <t>The belly comment was so funny I took a screenshot.</t>
+          <t>The top comment was so funny I took a screenshot.</t>
         </is>
       </c>
       <c r="M176" s="10" t="inlineStr">
         <is>
-          <t>El primer comentario fue tan gracioso que le tomé captura.</t>
+          <t>El comentario destacado fue tan gracioso que le tomé captura.</t>
         </is>
       </c>
       <c r="N176" s="10" t="inlineStr">
@@ -17792,17 +17792,17 @@
       </c>
       <c r="O176" s="10" t="inlineStr">
         <is>
-          <t>那则神留言太好笑了，我截屏了。</t>
+          <t>那条神评论太好笑了，我截屏了。</t>
         </is>
       </c>
       <c r="P176" s="10" t="inlineStr">
         <is>
-          <t>神コメント面白すぎてスクショした。</t>
+          <t>ベストコメントが面白すぎてスクショした。</t>
         </is>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
-          <t>Official social posts</t>
+          <t>Comment sections</t>
         </is>
       </c>
       <c r="R176" s="9" t="inlineStr">
@@ -22015,62 +22015,62 @@
       </c>
       <c r="F220" s="10" t="inlineStr">
         <is>
-          <t>"Domestic half" — the portion of a fandom based within Korea, as opposed to overseas.</t>
+          <t>국내 + 盤 ("record, edition"): the Korean domestic release of an album, as opposed to overseas editions like the Japanese one.</t>
         </is>
       </c>
       <c r="G220" s="10" t="inlineStr">
         <is>
-          <t>"Mitad doméstica": la parte del fandom que reside dentro de Corea, en contraste con el extranjero.</t>
+          <t>국내 + 盤 ("disco, edición"): la edición coreana nacional de un álbum, frente a las ediciones extranjeras como la japonesa.</t>
         </is>
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>「國內組」——粉絲圈中位於韓國國內的部分，相對於海外組。</t>
+          <t>國內盤——專輯在韓國國內發行的版本，相對於日本盤等海外版本。</t>
         </is>
       </c>
       <c r="I220" s="10" t="inlineStr">
         <is>
-          <t>“国内组”——粉丝圈中位于韩国国内的部分，相对于海外组。</t>
+          <t>国内盘——专辑在韩国国内发行的版本，相对于日本盘等海外版本。</t>
         </is>
       </c>
       <c r="J220" s="10" t="inlineStr">
         <is>
-          <t>「国内組」——海外ではなく、韓国国内を拠点とするファンダムの部分。</t>
+          <t>国内盤——アルバムの韓国国内リリース版。日本盤など海外版との対比で使う。</t>
         </is>
       </c>
       <c r="K220" s="10" t="inlineStr">
         <is>
-          <t>국내반이랑 해외반이랑 반응이 다르네.</t>
+          <t>국내반이랑 일본반 구성이 달라.</t>
         </is>
       </c>
       <c r="L220" s="10" t="inlineStr">
         <is>
-          <t>The domestic and overseas fandoms are reacting differently.</t>
+          <t>The Korean edition and the Japanese edition have different contents.</t>
         </is>
       </c>
       <c r="M220" s="10" t="inlineStr">
         <is>
-          <t>El fandom nacional y el internacional están reaccionando distinto.</t>
+          <t>La edición coreana y la japonesa traen contenidos distintos.</t>
         </is>
       </c>
       <c r="N220" s="10" t="inlineStr">
         <is>
-          <t>國內飯跟海外飯反應不太一樣。</t>
+          <t>韓國盤和日本盤的內容不一樣。</t>
         </is>
       </c>
       <c r="O220" s="10" t="inlineStr">
         <is>
-          <t>国内饭跟海外饭反应不太一样。</t>
+          <t>韩国盘和日本盘的内容不一样。</t>
         </is>
       </c>
       <c r="P220" s="10" t="inlineStr">
         <is>
-          <t>国内担と海外担で反応が違うね。</t>
+          <t>韓国盤と日本盤は構成が違う。</t>
         </is>
       </c>
       <c r="Q220" s="10" t="inlineStr">
         <is>
-          <t>Fandom comparison talk</t>
+          <t>Album collecting talk</t>
         </is>
       </c>
       <c r="R220" s="9" t="inlineStr">
@@ -22112,62 +22112,62 @@
       </c>
       <c r="F221" s="10" t="inlineStr">
         <is>
-          <t>"Overseas half" — the portion of a fandom based outside Korea.</t>
+          <t>해외 + 盤 ("record, edition"): an album version released outside Korea — such as a Japanese or US edition — often with different photos, photocards or tracks.</t>
         </is>
       </c>
       <c r="G221" s="10" t="inlineStr">
         <is>
-          <t>"Mitad extranjera": la parte del fandom que reside fuera de Corea.</t>
+          <t>해외 + 盤 ("disco, edición"): una versión del álbum lanzada fuera de Corea, como la edición japonesa o estadounidense, a menudo con fotos, photocards o canciones distintas.</t>
         </is>
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>「海外組」——粉絲圈中位於韓國以外地區的部分。</t>
+          <t>海外盤——在韓國以外發行的專輯版本（如日本盤、美國版），照片、小卡或收錄曲常不同。</t>
         </is>
       </c>
       <c r="I221" s="10" t="inlineStr">
         <is>
-          <t>“海外组”——粉丝圈中位于韩国以外地区的部分。</t>
+          <t>海外盘——在韩国以外发行的专辑版本（如日本盘、美国版），照片、小卡或收录曲常不同。</t>
         </is>
       </c>
       <c r="J221" s="10" t="inlineStr">
         <is>
-          <t>「海外組」——韓国以外を拠点とするファンダムの部分。</t>
+          <t>海外盤——韓国以外でリリースされるアルバムの版（日本盤や米国盤など）。写真やトレカ、収録曲が違うことも多い。</t>
         </is>
       </c>
       <c r="K221" s="10" t="inlineStr">
         <is>
-          <t>해외반이 스밍을 진짜 열심히 해.</t>
+          <t>해외반에만 들어 있는 포카가 따로 있대.</t>
         </is>
       </c>
       <c r="L221" s="10" t="inlineStr">
         <is>
-          <t>The overseas fandom streams really hard.</t>
+          <t>I heard there are photocards that only come in the overseas edition.</t>
         </is>
       </c>
       <c r="M221" s="10" t="inlineStr">
         <is>
-          <t>El fandom internacional hace streaming con muchísimo esfuerzo.</t>
+          <t>Dicen que hay photocards que solo vienen en la edición internacional.</t>
         </is>
       </c>
       <c r="N221" s="10" t="inlineStr">
         <is>
-          <t>海外飯刷榜真的很認真。</t>
+          <t>聽說有只放在海外盤裡的小卡。</t>
         </is>
       </c>
       <c r="O221" s="10" t="inlineStr">
         <is>
-          <t>海外饭刷榜真的很认真。</t>
+          <t>听说有只放在海外盘里的小卡。</t>
         </is>
       </c>
       <c r="P221" s="10" t="inlineStr">
         <is>
-          <t>海外担のストリーミング、本当に頑張ってる。</t>
+          <t>海外盤にしか入っていないトレカがあるらしい。</t>
         </is>
       </c>
       <c r="Q221" s="10" t="inlineStr">
         <is>
-          <t>Fandom comparison talk</t>
+          <t>Album collecting talk</t>
         </is>
       </c>
       <c r="R221" s="9" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$655</definedName>
@@ -45780,27 +45780,27 @@
       </c>
       <c r="F465" s="14" t="inlineStr">
         <is>
-          <t>"Hyeja-like" — describes a generous portion or great value, named after a historical figure known for generosity.</t>
+          <t>"Hyeja-like" — generous portions or great value for the price. It comes from a convenience-store lunch box launched in 2010 with actress Kim Hye-ja, famous for packing a lot in for little money.</t>
         </is>
       </c>
       <c r="G465" s="14" t="inlineStr">
         <is>
-          <t>"Como Hyeja": describe una porción generosa o un gran valor, en honor a una figura histórica conocida por su generosidad.</t>
+          <t>"Como Hyeja": porciones generosas o gran relación calidad-precio. Viene de una lonchera de tienda de conveniencia lanzada en 2010 con la actriz Kim Hye-ja, famosa por traer mucho por poco dinero.</t>
         </is>
       </c>
       <c r="H465" s="14" t="inlineStr">
         <is>
-          <t>「惠子式的」——形容份量大方、CP值高，源自一位以慷慨聞名的歷史人物名字。</t>
+          <t>「惠子式的」——形容份量大方、CP值高。源自2010年與演員金惠子合作推出、以便宜又豐盛聞名的便利商店便當。</t>
         </is>
       </c>
       <c r="I465" s="14" t="inlineStr">
         <is>
-          <t>“惠子式的”——形容份量大方、CP值高，源自一位以慷慨闻名的历史人物名字。</t>
+          <t>“惠子式的”——形容份量大方、性价比高。源自2010年与演员金惠子合作推出、以便宜又丰盛闻名的便利店便当。</t>
         </is>
       </c>
       <c r="J465" s="14" t="inlineStr">
         <is>
-          <t>気前が良く、コスパが良いことを表す——寛大さで知られた歴史上の人物の名前から来ている。</t>
+          <t>「ヘジャっぽい」——量が多くてコスパが良いこと。2010年に女優キム・ヘジャさんと発売された、安くてボリューム満点のコンビニ弁当が由来。</t>
         </is>
       </c>
       <c r="K465" s="14" t="inlineStr">
@@ -45825,12 +45825,12 @@
       </c>
       <c r="O465" s="14" t="inlineStr">
         <is>
-          <t>这家餐厅份量真的很佛心。</t>
+          <t>这家餐厅份量真的很良心。</t>
         </is>
       </c>
       <c r="P465" s="14" t="inlineStr">
         <is>
-          <t>このお店、マジで太っ腹だよね。</t>
+          <t>このお店、マジでボリュームたっぷり。</t>
         </is>
       </c>
       <c r="Q465" s="14" t="inlineStr">
@@ -45840,7 +45840,7 @@
       </c>
       <c r="R465" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S465" s="13" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$759</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$760</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S759"/>
+  <dimension ref="A1:S760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -66414,97 +66414,97 @@
       </c>
     </row>
     <row r="678" ht="46" customHeight="1">
-      <c r="A678" s="15" t="inlineStr">
-        <is>
-          <t>DAT-001</t>
-        </is>
-      </c>
-      <c r="B678" s="15" t="inlineStr">
-        <is>
-          <t>썸</t>
-        </is>
-      </c>
-      <c r="C678" s="15" t="inlineStr">
-        <is>
-          <t>sseom</t>
-        </is>
-      </c>
-      <c r="D678" s="15" t="inlineStr">
-        <is>
-          <t>연애 · 썸 표현</t>
-        </is>
-      </c>
-      <c r="E678" s="15" t="inlineStr">
-        <is>
-          <t>Dating &amp; Romance</t>
-        </is>
-      </c>
-      <c r="F678" s="16" t="inlineStr">
-        <is>
-          <t>The ambiguous stage of mutual interest before officially dating, from English "something."</t>
-        </is>
-      </c>
-      <c r="G678" s="16" t="inlineStr">
-        <is>
-          <t>La etapa ambigua de interés mutuo antes de salir oficialmente, del inglés "something".</t>
-        </is>
-      </c>
-      <c r="H678" s="16" t="inlineStr">
-        <is>
-          <t>正式交往前彼此有好感、關係曖昧不明的階段，源自英文「something」。</t>
-        </is>
-      </c>
-      <c r="I678" s="16" t="inlineStr">
-        <is>
-          <t>正式交往前彼此有好感、关系暧昧不明的阶段，源自英文“something”。</t>
-        </is>
-      </c>
-      <c r="J678" s="16" t="inlineStr">
-        <is>
-          <t>正式に付き合う前の、お互いに気がある曖昧な段階——英語の「something」から。</t>
-        </is>
-      </c>
-      <c r="K678" s="16" t="inlineStr">
-        <is>
-          <t>저 둘이 요즘 썸 타는 것 같아.</t>
-        </is>
-      </c>
-      <c r="L678" s="16" t="inlineStr">
-        <is>
-          <t>I think those two are in the talking stage lately.</t>
-        </is>
-      </c>
-      <c r="M678" s="16" t="inlineStr">
-        <is>
-          <t>Creo que esos dos están en la etapa de "algo más que amigos" últimamente.</t>
-        </is>
-      </c>
-      <c r="N678" s="16" t="inlineStr">
-        <is>
-          <t>那兩個人最近好像在曖昧。</t>
-        </is>
-      </c>
-      <c r="O678" s="16" t="inlineStr">
-        <is>
-          <t>那两个人最近好像在暧昧。</t>
-        </is>
-      </c>
-      <c r="P678" s="16" t="inlineStr">
-        <is>
-          <t>あの二人、最近曖昧な関係みたい。</t>
-        </is>
-      </c>
-      <c r="Q678" s="16" t="inlineStr">
-        <is>
-          <t>Casual relationship talk, dramas</t>
-        </is>
-      </c>
-      <c r="R678" s="15" t="inlineStr">
+      <c r="A678" s="13" t="inlineStr">
+        <is>
+          <t>MEM-245</t>
+        </is>
+      </c>
+      <c r="B678" s="13" t="inlineStr">
+        <is>
+          <t>원영적사고</t>
+        </is>
+      </c>
+      <c r="C678" s="13" t="inlineStr">
+        <is>
+          <t>won-yeong-jeok-sa-go</t>
+        </is>
+      </c>
+      <c r="D678" s="13" t="inlineStr">
+        <is>
+          <t>온라인 밈</t>
+        </is>
+      </c>
+      <c r="E678" s="13" t="inlineStr">
+        <is>
+          <t>Online Memes</t>
+        </is>
+      </c>
+      <c r="F678" s="14" t="inlineStr">
+        <is>
+          <t>"Wonyoung-style thinking" — ultra-positive thinking that turns any bad luck into good luck. Named after IVE member Jang Won-young.</t>
+        </is>
+      </c>
+      <c r="G678" s="14" t="inlineStr">
+        <is>
+          <t>"Pensamiento al estilo Wonyoung": pensamiento ultrapositivo que convierte cualquier mala suerte en buena. Se llama así por Jang Won-young, miembro de IVE.</t>
+        </is>
+      </c>
+      <c r="H678" s="14" t="inlineStr">
+        <is>
+          <t>「元英式思考」：把任何壞運都轉成好運的超正向思考。名稱來自IVE成員張員瑛。</t>
+        </is>
+      </c>
+      <c r="I678" s="14" t="inlineStr">
+        <is>
+          <t>“元英式思考”：把任何坏运都转成好运的超正向思考。名称来自IVE成员张员瑛。</t>
+        </is>
+      </c>
+      <c r="J678" s="14" t="inlineStr">
+        <is>
+          <t>「ウォニョン的思考」。どんな不運も幸運に変える超ポジティブ思考。IVEのチャン・ウォニョンにちなむ。</t>
+        </is>
+      </c>
+      <c r="K678" s="14" t="inlineStr">
+        <is>
+          <t>우산 잃어버렸는데 새 거 사니까 오히려 좋아, 완전 원영적 사고야.</t>
+        </is>
+      </c>
+      <c r="L678" s="14" t="inlineStr">
+        <is>
+          <t>I lost my umbrella, but now I get a new one — total Wonyoung-style thinking.</t>
+        </is>
+      </c>
+      <c r="M678" s="14" t="inlineStr">
+        <is>
+          <t>Perdí mi paraguas, pero ahora me compro uno nuevo: puro pensamiento al estilo Wonyoung.</t>
+        </is>
+      </c>
+      <c r="N678" s="14" t="inlineStr">
+        <is>
+          <t>雨傘弄丟了，但可以買新的反而更好，完全是元英式思考。</t>
+        </is>
+      </c>
+      <c r="O678" s="14" t="inlineStr">
+        <is>
+          <t>雨伞弄丢了，但可以买新的反而更好，完全是元英式思考。</t>
+        </is>
+      </c>
+      <c r="P678" s="14" t="inlineStr">
+        <is>
+          <t>傘をなくしたけど新しいのを買えるからむしろ良い、完全にウォニョン的思考。</t>
+        </is>
+      </c>
+      <c r="Q678" s="14" t="inlineStr">
+        <is>
+          <t>Positive-thinking memes, fandom</t>
+        </is>
+      </c>
+      <c r="R678" s="13" t="inlineStr">
         <is>
           <t>Verified (web-checked)</t>
         </is>
       </c>
-      <c r="S678" s="15" t="inlineStr">
+      <c r="S678" s="13" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
@@ -66513,17 +66513,17 @@
     <row r="679" ht="46" customHeight="1">
       <c r="A679" s="15" t="inlineStr">
         <is>
-          <t>DAT-002</t>
+          <t>DAT-001</t>
         </is>
       </c>
       <c r="B679" s="15" t="inlineStr">
         <is>
-          <t>썸타다</t>
+          <t>썸</t>
         </is>
       </c>
       <c r="C679" s="15" t="inlineStr">
         <is>
-          <t>sseom-ta-da</t>
+          <t>sseom</t>
         </is>
       </c>
       <c r="D679" s="15" t="inlineStr">
@@ -66538,62 +66538,62 @@
       </c>
       <c r="F679" s="16" t="inlineStr">
         <is>
-          <t>To be in that ambiguous, pre-dating phase of mutual interest with someone.</t>
+          <t>The ambiguous stage of mutual interest before officially dating, from English "something."</t>
         </is>
       </c>
       <c r="G679" s="16" t="inlineStr">
         <is>
-          <t>Estar en esa fase ambigua y previa a salir formalmente con alguien.</t>
+          <t>La etapa ambigua de interés mutuo antes de salir oficialmente, del inglés "something".</t>
         </is>
       </c>
       <c r="H679" s="16" t="inlineStr">
         <is>
-          <t>正式交往前，彼此有好感、關係曖昧不明的階段。</t>
+          <t>正式交往前彼此有好感、關係曖昧不明的階段，源自英文「something」。</t>
         </is>
       </c>
       <c r="I679" s="16" t="inlineStr">
         <is>
-          <t>正式交往前，彼此有好感、关系暧昧不明的阶段。</t>
+          <t>正式交往前彼此有好感、关系暧昧不明的阶段，源自英文“something”。</t>
         </is>
       </c>
       <c r="J679" s="16" t="inlineStr">
         <is>
-          <t>誰かと正式に付き合う前の、お互いに気がある曖昧な段階にいること。</t>
+          <t>正式に付き合う前の、お互いに気がある曖昧な段階——英語の「something」から。</t>
         </is>
       </c>
       <c r="K679" s="16" t="inlineStr">
         <is>
-          <t>우리 썸탄 지 한 달 됐어.</t>
+          <t>저 둘이 요즘 썸 타는 것 같아.</t>
         </is>
       </c>
       <c r="L679" s="16" t="inlineStr">
         <is>
-          <t>We've been in the talking stage for a month.</t>
+          <t>I think those two are in the talking stage lately.</t>
         </is>
       </c>
       <c r="M679" s="16" t="inlineStr">
         <is>
-          <t>Llevamos un mes en la etapa de "algo más que amigos".</t>
+          <t>Creo que esos dos están en la etapa de "algo más que amigos" últimamente.</t>
         </is>
       </c>
       <c r="N679" s="16" t="inlineStr">
         <is>
-          <t>我們曖昧一個月了。</t>
+          <t>那兩個人最近好像在曖昧。</t>
         </is>
       </c>
       <c r="O679" s="16" t="inlineStr">
         <is>
-          <t>我们暧昧一个月了。</t>
+          <t>那两个人最近好像在暧昧。</t>
         </is>
       </c>
       <c r="P679" s="16" t="inlineStr">
         <is>
-          <t>私たち、曖昧な関係になって1ヶ月経った。</t>
+          <t>あの二人、最近曖昧な関係みたい。</t>
         </is>
       </c>
       <c r="Q679" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>Casual relationship talk, dramas</t>
         </is>
       </c>
       <c r="R679" s="15" t="inlineStr">
@@ -66610,17 +66610,17 @@
     <row r="680" ht="46" customHeight="1">
       <c r="A680" s="15" t="inlineStr">
         <is>
-          <t>DAT-003</t>
+          <t>DAT-002</t>
         </is>
       </c>
       <c r="B680" s="15" t="inlineStr">
         <is>
-          <t>밀당</t>
+          <t>썸타다</t>
         </is>
       </c>
       <c r="C680" s="15" t="inlineStr">
         <is>
-          <t>mil-dang</t>
+          <t>sseom-ta-da</t>
         </is>
       </c>
       <c r="D680" s="15" t="inlineStr">
@@ -66635,62 +66635,62 @@
       </c>
       <c r="F680" s="16" t="inlineStr">
         <is>
-          <t>Short for "pushing and pulling" — playing a little hard to get in a relationship.</t>
+          <t>To be in that ambiguous, pre-dating phase of mutual interest with someone.</t>
         </is>
       </c>
       <c r="G680" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "empujar y jalar": hacerse un poco el difícil en una relación.</t>
+          <t>Estar en esa fase ambigua y previa a salir formalmente con alguien.</t>
         </is>
       </c>
       <c r="H680" s="16" t="inlineStr">
         <is>
-          <t>「推拉」的簡稱——在感情中欲擒故縱、若即若離。</t>
+          <t>正式交往前，彼此有好感、關係曖昧不明的階段。</t>
         </is>
       </c>
       <c r="I680" s="16" t="inlineStr">
         <is>
-          <t>“推拉”的简称——在感情中欲擒故纵、若即若离。</t>
+          <t>正式交往前，彼此有好感、关系暧昧不明的阶段。</t>
         </is>
       </c>
       <c r="J680" s="16" t="inlineStr">
         <is>
-          <t>「押し引き」の略——恋愛でわざと簡単に落ちないようにすること。</t>
+          <t>誰かと正式に付き合う前の、お互いに気がある曖昧な段階にいること。</t>
         </is>
       </c>
       <c r="K680" s="16" t="inlineStr">
         <is>
-          <t>밀당 좀 그만하고 솔직하게 말해.</t>
+          <t>우리 썸탄 지 한 달 됐어.</t>
         </is>
       </c>
       <c r="L680" s="16" t="inlineStr">
         <is>
-          <t>Stop playing push-and-pull and just be honest.</t>
+          <t>We've been in the talking stage for a month.</t>
         </is>
       </c>
       <c r="M680" s="16" t="inlineStr">
         <is>
-          <t>Deja de jugar a hacerte el difícil y sé honesto.</t>
+          <t>Llevamos un mes en la etapa de "algo más que amigos".</t>
         </is>
       </c>
       <c r="N680" s="16" t="inlineStr">
         <is>
-          <t>別再欲擒故縱了，老實說吧。</t>
+          <t>我們曖昧一個月了。</t>
         </is>
       </c>
       <c r="O680" s="16" t="inlineStr">
         <is>
-          <t>别再欲擒故纵了，老实说吧。</t>
+          <t>我们暧昧一个月了。</t>
         </is>
       </c>
       <c r="P680" s="16" t="inlineStr">
         <is>
-          <t>駆け引きはもうやめて、正直に言って。</t>
+          <t>私たち、曖昧な関係になって1ヶ月経った。</t>
         </is>
       </c>
       <c r="Q680" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk, dramas</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R680" s="15" t="inlineStr">
@@ -66707,17 +66707,17 @@
     <row r="681" ht="46" customHeight="1">
       <c r="A681" s="15" t="inlineStr">
         <is>
-          <t>DAT-004</t>
+          <t>DAT-003</t>
         </is>
       </c>
       <c r="B681" s="15" t="inlineStr">
         <is>
-          <t>어장관리</t>
+          <t>밀당</t>
         </is>
       </c>
       <c r="C681" s="15" t="inlineStr">
         <is>
-          <t>eo-jang-gwal-li</t>
+          <t>mil-dang</t>
         </is>
       </c>
       <c r="D681" s="15" t="inlineStr">
@@ -66732,57 +66732,57 @@
       </c>
       <c r="F681" s="16" t="inlineStr">
         <is>
-          <t>"Fish-tank management" — keeping multiple romantic prospects on the line at once without committing.</t>
+          <t>Short for "pushing and pulling" — playing a little hard to get in a relationship.</t>
         </is>
       </c>
       <c r="G681" s="16" t="inlineStr">
         <is>
-          <t>"Manejo de pecera": mantener a varios interesados románticos a la espera sin comprometerse con ninguno.</t>
+          <t>Abreviatura de "empujar y jalar": hacerse un poco el difícil en una relación.</t>
         </is>
       </c>
       <c r="H681" s="16" t="inlineStr">
         <is>
-          <t>「魚缸管理」——同時吊著好幾個對象、不做出承諾，養魚。</t>
+          <t>「推拉」的簡稱——在感情中欲擒故縱、若即若離。</t>
         </is>
       </c>
       <c r="I681" s="16" t="inlineStr">
         <is>
-          <t>“鱼缸管理”——同时吊着好几个对象、不做出承诺，养鱼。</t>
+          <t>“推拉”的简称——在感情中欲擒故纵、若即若离。</t>
         </is>
       </c>
       <c r="J681" s="16" t="inlineStr">
         <is>
-          <t>「養殖場管理」——複数の恋愛候補を、コミットせずに引き止めておくこと。</t>
+          <t>「押し引き」の略——恋愛でわざと簡単に落ちないようにすること。</t>
         </is>
       </c>
       <c r="K681" s="16" t="inlineStr">
         <is>
-          <t>걔 완전 어장관리하는 것 같아, 조심해.</t>
+          <t>밀당 좀 그만하고 솔직하게 말해.</t>
         </is>
       </c>
       <c r="L681" s="16" t="inlineStr">
         <is>
-          <t>I think they're totally fish-tanking people, be careful.</t>
+          <t>Stop playing push-and-pull and just be honest.</t>
         </is>
       </c>
       <c r="M681" s="16" t="inlineStr">
         <is>
-          <t>Creo que esa persona está jugando con varios a la vez, ten cuidado.</t>
+          <t>Deja de jugar a hacerte el difícil y sé honesto.</t>
         </is>
       </c>
       <c r="N681" s="16" t="inlineStr">
         <is>
-          <t>我覺得他在養魚，小心點。</t>
+          <t>別再欲擒故縱了，老實說吧。</t>
         </is>
       </c>
       <c r="O681" s="16" t="inlineStr">
         <is>
-          <t>我觉得他在养鱼，小心点。</t>
+          <t>别再欲擒故纵了，老实说吧。</t>
         </is>
       </c>
       <c r="P681" s="16" t="inlineStr">
         <is>
-          <t>あの人、完全に複数キープしてる感じ、気をつけて。</t>
+          <t>駆け引きはもうやめて、正直に言って。</t>
         </is>
       </c>
       <c r="Q681" s="16" t="inlineStr">
@@ -66804,17 +66804,17 @@
     <row r="682" ht="46" customHeight="1">
       <c r="A682" s="15" t="inlineStr">
         <is>
-          <t>DAT-005</t>
+          <t>DAT-004</t>
         </is>
       </c>
       <c r="B682" s="15" t="inlineStr">
         <is>
-          <t>삼귀다</t>
+          <t>어장관리</t>
         </is>
       </c>
       <c r="C682" s="15" t="inlineStr">
         <is>
-          <t>sam-gwi-da</t>
+          <t>eo-jang-gwal-li</t>
         </is>
       </c>
       <c r="D682" s="15" t="inlineStr">
@@ -66829,62 +66829,62 @@
       </c>
       <c r="F682" s="16" t="inlineStr">
         <is>
-          <t>A playful pun using "3" (삼) as a step before 사귀다 ("to date," which starts with 사=4) — the talking stage.</t>
+          <t>"Fish-tank management" — keeping multiple romantic prospects on the line at once without committing.</t>
         </is>
       </c>
       <c r="G682" s="16" t="inlineStr">
         <is>
-          <t>Un juego de palabras usando "3" (삼) como un paso antes de 사귀다 ("salir", que empieza con 사=4): la etapa previa.</t>
+          <t>"Manejo de pecera": mantener a varios interesados románticos a la espera sin comprometerse con ninguno.</t>
         </is>
       </c>
       <c r="H682" s="16" t="inlineStr">
         <is>
-          <t>用數字「3」取代「사귀다」（交往，以4開頭）玩的雙關語，指正式交往前的曖昧階段。</t>
+          <t>「魚缸管理」——同時吊著好幾個對象、不做出承諾，養魚。</t>
         </is>
       </c>
       <c r="I682" s="16" t="inlineStr">
         <is>
-          <t>用数字“3”取代“사귀다”（交往，以4开头）玩的双关语，指正式交往前的暧昧阶段。</t>
+          <t>“鱼缸管理”——同时吊着好几个对象、不做出承诺，养鱼。</t>
         </is>
       </c>
       <c r="J682" s="16" t="inlineStr">
         <is>
-          <t>「3」（삼）を사귀다（付き合う、「4」＝사で始まる）の前段階として使った言葉遊びで、付き合う前の曖昧な段階を表す。</t>
+          <t>「養殖場管理」——複数の恋愛候補を、コミットせずに引き止めておくこと。</t>
         </is>
       </c>
       <c r="K682" s="16" t="inlineStr">
         <is>
-          <t>우리 지금 삼귀는 사이야.</t>
+          <t>걔 완전 어장관리하는 것 같아, 조심해.</t>
         </is>
       </c>
       <c r="L682" s="16" t="inlineStr">
         <is>
-          <t>We're in that pre-dating stage right now.</t>
+          <t>I think they're totally fish-tanking people, be careful.</t>
         </is>
       </c>
       <c r="M682" s="16" t="inlineStr">
         <is>
-          <t>Ahorita estamos en esa etapa previa a ser novios.</t>
+          <t>Creo que esa persona está jugando con varios a la vez, ten cuidado.</t>
         </is>
       </c>
       <c r="N682" s="16" t="inlineStr">
         <is>
-          <t>我們現在算是曖昧中的關係。</t>
+          <t>我覺得他在養魚，小心點。</t>
         </is>
       </c>
       <c r="O682" s="16" t="inlineStr">
         <is>
-          <t>我们现在算是暧昧中的关系。</t>
+          <t>我觉得他在养鱼，小心点。</t>
         </is>
       </c>
       <c r="P682" s="16" t="inlineStr">
         <is>
-          <t>私たち、今そういう段階にいるの。</t>
+          <t>あの人、完全に複数キープしてる感じ、気をつけて。</t>
         </is>
       </c>
       <c r="Q682" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>Relationship talk, dramas</t>
         </is>
       </c>
       <c r="R682" s="15" t="inlineStr">
@@ -66901,17 +66901,17 @@
     <row r="683" ht="46" customHeight="1">
       <c r="A683" s="15" t="inlineStr">
         <is>
-          <t>DAT-006</t>
+          <t>DAT-005</t>
         </is>
       </c>
       <c r="B683" s="15" t="inlineStr">
         <is>
-          <t>환승연애</t>
+          <t>삼귀다</t>
         </is>
       </c>
       <c r="C683" s="15" t="inlineStr">
         <is>
-          <t>hwan-seung-yeon-ae</t>
+          <t>sam-gwi-da</t>
         </is>
       </c>
       <c r="D683" s="15" t="inlineStr">
@@ -66926,67 +66926,67 @@
       </c>
       <c r="F683" s="16" t="inlineStr">
         <is>
-          <t>"Transfer love" — starting a new relationship right after a breakup, popularized by a reality show of the same name.</t>
+          <t>A playful pun using "3" (삼) as a step before 사귀다 ("to date," which starts with 사=4) — the talking stage.</t>
         </is>
       </c>
       <c r="G683" s="16" t="inlineStr">
         <is>
-          <t>"Amor de transbordo": empezar una nueva relación justo después de una ruptura, popularizado por un reality show del mismo nombre.</t>
+          <t>Un juego de palabras usando "3" (삼) como un paso antes de 사귀다 ("salir", que empieza con 사=4): la etapa previa.</t>
         </is>
       </c>
       <c r="H683" s="16" t="inlineStr">
         <is>
-          <t>「轉乘戀愛」——分手後立刻投入新戀情，因同名實境節目而爆紅。</t>
+          <t>用數字「3」取代「사귀다」（交往，以4開頭）玩的雙關語，指正式交往前的曖昧階段。</t>
         </is>
       </c>
       <c r="I683" s="16" t="inlineStr">
         <is>
-          <t>“转乘恋爱”——分手后立刻投入新恋情，因同名实境节目而爆红。</t>
+          <t>用数字“3”取代“사귀다”（交往，以4开头）玩的双关语，指正式交往前的暧昧阶段。</t>
         </is>
       </c>
       <c r="J683" s="16" t="inlineStr">
         <is>
-          <t>「乗り換え恋愛」——別れた直後にすぐ新しい恋愛を始めること、同名のリアリティ番組で話題になった。</t>
+          <t>「3」（삼）を사귀다（付き合う、「4」＝사で始まる）の前段階として使った言葉遊びで、付き合う前の曖昧な段階を表す。</t>
         </is>
       </c>
       <c r="K683" s="16" t="inlineStr">
         <is>
-          <t>그 커플 완전 환승연애 아니야?</t>
+          <t>우리 지금 삼귀는 사이야.</t>
         </is>
       </c>
       <c r="L683" s="16" t="inlineStr">
         <is>
-          <t>Isn't that couple a total transfer-love situation?</t>
+          <t>We're in that pre-dating stage right now.</t>
         </is>
       </c>
       <c r="M683" s="16" t="inlineStr">
         <is>
-          <t>¿Esa pareja no es un caso típico de "amor de transbordo"?</t>
+          <t>Ahorita estamos en esa etapa previa a ser novios.</t>
         </is>
       </c>
       <c r="N683" s="16" t="inlineStr">
         <is>
-          <t>那對情侶根本是轉乘戀愛吧？</t>
+          <t>我們現在算是曖昧中的關係。</t>
         </is>
       </c>
       <c r="O683" s="16" t="inlineStr">
         <is>
-          <t>那对情侣根本是转乘恋爱吧？</t>
+          <t>我们现在算是暧昧中的关系。</t>
         </is>
       </c>
       <c r="P683" s="16" t="inlineStr">
         <is>
-          <t>あのカップル、完全に乗り換え恋愛じゃない？</t>
+          <t>私たち、今そういう段階にいるの。</t>
         </is>
       </c>
       <c r="Q683" s="16" t="inlineStr">
         <is>
-          <t>Reality show fandom, gossip</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R683" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S683" s="15" t="inlineStr">
@@ -66998,17 +66998,17 @@
     <row r="684" ht="46" customHeight="1">
       <c r="A684" s="15" t="inlineStr">
         <is>
-          <t>DAT-007</t>
+          <t>DAT-006</t>
         </is>
       </c>
       <c r="B684" s="15" t="inlineStr">
         <is>
-          <t>잠수이별</t>
+          <t>환승연애</t>
         </is>
       </c>
       <c r="C684" s="15" t="inlineStr">
         <is>
-          <t>jam-su-i-byeol</t>
+          <t>hwan-seung-yeon-ae</t>
         </is>
       </c>
       <c r="D684" s="15" t="inlineStr">
@@ -67023,62 +67023,62 @@
       </c>
       <c r="F684" s="16" t="inlineStr">
         <is>
-          <t>"Diving breakup" — ending a relationship by disappearing without explanation, i.e. ghosting.</t>
+          <t>"Transfer love" — starting a new relationship right after a breakup, popularized by a reality show of the same name.</t>
         </is>
       </c>
       <c r="G684" s="16" t="inlineStr">
         <is>
-          <t>"Ruptura de buceo": terminar una relación desapareciendo sin explicación, es decir, ghosting.</t>
+          <t>"Amor de transbordo": empezar una nueva relación justo después de una ruptura, popularizado por un reality show del mismo nombre.</t>
         </is>
       </c>
       <c r="H684" s="16" t="inlineStr">
         <is>
-          <t>「潛水式分手」——不做任何說明就人間蒸發結束關係。</t>
+          <t>「轉乘戀愛」——分手後立刻投入新戀情，因同名實境節目而爆紅。</t>
         </is>
       </c>
       <c r="I684" s="16" t="inlineStr">
         <is>
-          <t>“潜水式分手”——不做任何说明就人间蒸发结束关系。</t>
+          <t>“转乘恋爱”——分手后立刻投入新恋情，因同名实境节目而爆红。</t>
         </is>
       </c>
       <c r="J684" s="16" t="inlineStr">
         <is>
-          <t>「潜水別れ」——説明もなく姿を消して関係を終わらせること、つまり音信不通。</t>
+          <t>「乗り換え恋愛」——別れた直後にすぐ新しい恋愛を始めること、同名のリアリティ番組で話題になった。</t>
         </is>
       </c>
       <c r="K684" s="16" t="inlineStr">
         <is>
-          <t>연락도 없이 잠수이별당했어.</t>
+          <t>그 커플 완전 환승연애 아니야?</t>
         </is>
       </c>
       <c r="L684" s="16" t="inlineStr">
         <is>
-          <t>I got ghosted with no explanation at all.</t>
+          <t>Isn't that couple a total transfer-love situation?</t>
         </is>
       </c>
       <c r="M684" s="16" t="inlineStr">
         <is>
-          <t>Me hicieron ghosting sin ninguna explicación.</t>
+          <t>¿Esa pareja no es un caso típico de "amor de transbordo"?</t>
         </is>
       </c>
       <c r="N684" s="16" t="inlineStr">
         <is>
-          <t>毫無音訊就被人間蒸發式分手了。</t>
+          <t>那對情侶根本是轉乘戀愛吧？</t>
         </is>
       </c>
       <c r="O684" s="16" t="inlineStr">
         <is>
-          <t>毫无音频就被人间蒸发式分手了。</t>
+          <t>那对情侣根本是转乘恋爱吧？</t>
         </is>
       </c>
       <c r="P684" s="16" t="inlineStr">
         <is>
-          <t>連絡もなく自然消滅させられた。</t>
+          <t>あのカップル、完全に乗り換え恋愛じゃない？</t>
         </is>
       </c>
       <c r="Q684" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk</t>
+          <t>Reality show fandom, gossip</t>
         </is>
       </c>
       <c r="R684" s="15" t="inlineStr">
@@ -67095,17 +67095,17 @@
     <row r="685" ht="46" customHeight="1">
       <c r="A685" s="15" t="inlineStr">
         <is>
-          <t>DAT-008</t>
+          <t>DAT-007</t>
         </is>
       </c>
       <c r="B685" s="15" t="inlineStr">
         <is>
-          <t>계약연애</t>
+          <t>잠수이별</t>
         </is>
       </c>
       <c r="C685" s="15" t="inlineStr">
         <is>
-          <t>gye-yak-yeon-ae</t>
+          <t>jam-su-i-byeol</t>
         </is>
       </c>
       <c r="D685" s="15" t="inlineStr">
@@ -67120,62 +67120,62 @@
       </c>
       <c r="F685" s="16" t="inlineStr">
         <is>
-          <t>A fake "contract relationship" arranged for practical reasons — a very common K-drama plot device.</t>
+          <t>"Diving breakup" — ending a relationship by disappearing without explanation, i.e. ghosting.</t>
         </is>
       </c>
       <c r="G685" s="16" t="inlineStr">
         <is>
-          <t>Una falsa "relación por contrato" arreglada por razones prácticas, un recurso argumental muy común en K-dramas.</t>
+          <t>"Ruptura de buceo": terminar una relación desapareciendo sin explicación, es decir, ghosting.</t>
         </is>
       </c>
       <c r="H685" s="16" t="inlineStr">
         <is>
-          <t>因現實考量而假裝交往的「契約戀愛」，是韓劇非常常見的劇情設定。</t>
+          <t>「潛水式分手」——不做任何說明就人間蒸發結束關係。</t>
         </is>
       </c>
       <c r="I685" s="16" t="inlineStr">
         <is>
-          <t>因现实考量而假装交往的“契约恋爱”，是韩剧非常常见的剧情设置。</t>
+          <t>“潜水式分手”——不做任何说明就人间蒸发结束关系。</t>
         </is>
       </c>
       <c r="J685" s="16" t="inlineStr">
         <is>
-          <t>現実的な理由で仕組まれた偽の「契約恋愛」——韓国ドラマで非常によくある設定。</t>
+          <t>「潜水別れ」——説明もなく姿を消して関係を終わらせること、つまり音信不通。</t>
         </is>
       </c>
       <c r="K685" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 계약연애물이야.</t>
+          <t>연락도 없이 잠수이별당했어.</t>
         </is>
       </c>
       <c r="L685" s="16" t="inlineStr">
         <is>
-          <t>This drama is a contract-relationship story.</t>
+          <t>I got ghosted with no explanation at all.</t>
         </is>
       </c>
       <c r="M685" s="16" t="inlineStr">
         <is>
-          <t>Este drama es de esos con relación por contrato.</t>
+          <t>Me hicieron ghosting sin ninguna explicación.</t>
         </is>
       </c>
       <c r="N685" s="16" t="inlineStr">
         <is>
-          <t>這部劇是契約戀愛劇情。</t>
+          <t>毫無音訊就被人間蒸發式分手了。</t>
         </is>
       </c>
       <c r="O685" s="16" t="inlineStr">
         <is>
-          <t>这部剧是契约恋爱剧情。</t>
+          <t>毫无音频就被人间蒸发式分手了。</t>
         </is>
       </c>
       <c r="P685" s="16" t="inlineStr">
         <is>
-          <t>このドラマ、契約恋愛ものだよ。</t>
+          <t>連絡もなく自然消滅させられた。</t>
         </is>
       </c>
       <c r="Q685" s="16" t="inlineStr">
         <is>
-          <t>K-drama genre talk</t>
+          <t>Relationship talk</t>
         </is>
       </c>
       <c r="R685" s="15" t="inlineStr">
@@ -67192,17 +67192,17 @@
     <row r="686" ht="46" customHeight="1">
       <c r="A686" s="15" t="inlineStr">
         <is>
-          <t>DAT-009</t>
+          <t>DAT-008</t>
         </is>
       </c>
       <c r="B686" s="15" t="inlineStr">
         <is>
-          <t>재벌</t>
+          <t>계약연애</t>
         </is>
       </c>
       <c r="C686" s="15" t="inlineStr">
         <is>
-          <t>jae-beol</t>
+          <t>gye-yak-yeon-ae</t>
         </is>
       </c>
       <c r="D686" s="15" t="inlineStr">
@@ -67217,62 +67217,62 @@
       </c>
       <c r="F686" s="16" t="inlineStr">
         <is>
-          <t>A chaebol — a large, family-controlled business conglomerate, often a K-drama love interest's background.</t>
+          <t>A fake "contract relationship" arranged for practical reasons — a very common K-drama plot device.</t>
         </is>
       </c>
       <c r="G686" s="16" t="inlineStr">
         <is>
-          <t>Un chaebol: un gran conglomerado empresarial controlado por una familia, a menudo el trasfondo de un interés romántico en K-dramas.</t>
+          <t>Una falsa "relación por contrato" arreglada por razones prácticas, un recurso argumental muy común en K-dramas.</t>
         </is>
       </c>
       <c r="H686" s="16" t="inlineStr">
         <is>
-          <t>財閥——大型家族控制的企業集團，常是韓劇男女主角的家世背景設定。</t>
+          <t>因現實考量而假裝交往的「契約戀愛」，是韓劇非常常見的劇情設定。</t>
         </is>
       </c>
       <c r="I686" s="16" t="inlineStr">
         <is>
-          <t>财阀——大型家族控制的企业集团，常是韩剧男女主角的家世背景设置。</t>
+          <t>因现实考量而假装交往的“契约恋爱”，是韩剧非常常见的剧情设置。</t>
         </is>
       </c>
       <c r="J686" s="16" t="inlineStr">
         <is>
-          <t>家族経営の大規模企業グループ——韓国ドラマの恋愛相手の設定によく使われる。</t>
+          <t>現実的な理由で仕組まれた偽の「契約恋愛」——韓国ドラマで非常によくある設定。</t>
         </is>
       </c>
       <c r="K686" s="16" t="inlineStr">
         <is>
-          <t>이번 드라마 남주는 재벌 3세래.</t>
+          <t>이 드라마 계약연애물이야.</t>
         </is>
       </c>
       <c r="L686" s="16" t="inlineStr">
         <is>
-          <t>I heard this drama's male lead is a third-generation chaebol heir.</t>
+          <t>This drama is a contract-relationship story.</t>
         </is>
       </c>
       <c r="M686" s="16" t="inlineStr">
         <is>
-          <t>Escuché que el protagonista de este drama es heredero de tercera generación de un chaebol.</t>
+          <t>Este drama es de esos con relación por contrato.</t>
         </is>
       </c>
       <c r="N686" s="16" t="inlineStr">
         <is>
-          <t>聽說這次男主角是財閥三代。</t>
+          <t>這部劇是契約戀愛劇情。</t>
         </is>
       </c>
       <c r="O686" s="16" t="inlineStr">
         <is>
-          <t>听说这次男主角是财阀三代。</t>
+          <t>这部剧是契约恋爱剧情。</t>
         </is>
       </c>
       <c r="P686" s="16" t="inlineStr">
         <is>
-          <t>今回のドラマの男主人公は財閥三世らしい。</t>
+          <t>このドラマ、契約恋愛ものだよ。</t>
         </is>
       </c>
       <c r="Q686" s="16" t="inlineStr">
         <is>
-          <t>K-drama plot talk</t>
+          <t>K-drama genre talk</t>
         </is>
       </c>
       <c r="R686" s="15" t="inlineStr">
@@ -67289,17 +67289,17 @@
     <row r="687" ht="46" customHeight="1">
       <c r="A687" s="15" t="inlineStr">
         <is>
-          <t>DAT-010</t>
+          <t>DAT-009</t>
         </is>
       </c>
       <c r="B687" s="15" t="inlineStr">
         <is>
-          <t>막장</t>
+          <t>재벌</t>
         </is>
       </c>
       <c r="C687" s="15" t="inlineStr">
         <is>
-          <t>mak-jang</t>
+          <t>jae-beol</t>
         </is>
       </c>
       <c r="D687" s="15" t="inlineStr">
@@ -67314,62 +67314,62 @@
       </c>
       <c r="F687" s="16" t="inlineStr">
         <is>
-          <t>"End of the mine shaft" — describes an extreme, over-the-top dramatic plot twist.</t>
+          <t>A chaebol — a large, family-controlled business conglomerate, often a K-drama love interest's background.</t>
         </is>
       </c>
       <c r="G687" s="16" t="inlineStr">
         <is>
-          <t>"Final del pozo de la mina": describe un giro argumental extremo y exagerado.</t>
+          <t>Un chaebol: un gran conglomerado empresarial controlado por una familia, a menudo el trasfondo de un interés romántico en K-dramas.</t>
         </is>
       </c>
       <c r="H687" s="16" t="inlineStr">
         <is>
-          <t>字面意思是「礦坑盡頭」——形容誇張、狗血到極點的劇情轉折。</t>
+          <t>財閥——大型家族控制的企業集團，常是韓劇男女主角的家世背景設定。</t>
         </is>
       </c>
       <c r="I687" s="16" t="inlineStr">
         <is>
-          <t>字面意思是“矿坑尽头”——形容夸张、狗血到极点的剧情转折。</t>
+          <t>财阀——大型家族控制的企业集团，常是韩剧男女主角的家世背景设置。</t>
         </is>
       </c>
       <c r="J687" s="16" t="inlineStr">
         <is>
-          <t>「坑道の奥」——極端で、行き過ぎたドラマチックな展開を表す。</t>
+          <t>家族経営の大規模企業グループ——韓国ドラマの恋愛相手の設定によく使われる。</t>
         </is>
       </c>
       <c r="K687" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 완전 막장 전개야.</t>
+          <t>이번 드라마 남주는 재벌 3세래.</t>
         </is>
       </c>
       <c r="L687" s="16" t="inlineStr">
         <is>
-          <t>This drama's plot has gone completely over the top.</t>
+          <t>I heard this drama's male lead is a third-generation chaebol heir.</t>
         </is>
       </c>
       <c r="M687" s="16" t="inlineStr">
         <is>
-          <t>La trama de este drama se volvió totalmente exagerada.</t>
+          <t>Escuché que el protagonista de este drama es heredero de tercera generación de un chaebol.</t>
         </is>
       </c>
       <c r="N687" s="16" t="inlineStr">
         <is>
-          <t>這部劇劇情完全狗血。</t>
+          <t>聽說這次男主角是財閥三代。</t>
         </is>
       </c>
       <c r="O687" s="16" t="inlineStr">
         <is>
-          <t>这部剧剧情完全狗血。</t>
+          <t>听说这次男主角是财阀三代。</t>
         </is>
       </c>
       <c r="P687" s="16" t="inlineStr">
         <is>
-          <t>このドラマ、完全にどろどろ展開になってる。</t>
+          <t>今回のドラマの男主人公は財閥三世らしい。</t>
         </is>
       </c>
       <c r="Q687" s="16" t="inlineStr">
         <is>
-          <t>K-drama genre talk</t>
+          <t>K-drama plot talk</t>
         </is>
       </c>
       <c r="R687" s="15" t="inlineStr">
@@ -67386,17 +67386,17 @@
     <row r="688" ht="46" customHeight="1">
       <c r="A688" s="15" t="inlineStr">
         <is>
-          <t>DAT-011</t>
+          <t>DAT-010</t>
         </is>
       </c>
       <c r="B688" s="15" t="inlineStr">
         <is>
-          <t>누나</t>
+          <t>막장</t>
         </is>
       </c>
       <c r="C688" s="15" t="inlineStr">
         <is>
-          <t>nu-na</t>
+          <t>mak-jang</t>
         </is>
       </c>
       <c r="D688" s="15" t="inlineStr">
@@ -67411,57 +67411,57 @@
       </c>
       <c r="F688" s="16" t="inlineStr">
         <is>
-          <t>What a man calls an older woman — also names the popular "noona romance" drama trope.</t>
+          <t>"End of the mine shaft" — describes an extreme, over-the-top dramatic plot twist.</t>
         </is>
       </c>
       <c r="G688" s="16" t="inlineStr">
         <is>
-          <t>Cómo un hombre llama a una mujer mayor; también nombra el popular recurso de "romance con noona" en los dramas.</t>
+          <t>"Final del pozo de la mina": describe un giro argumental extremo y exagerado.</t>
         </is>
       </c>
       <c r="H688" s="16" t="inlineStr">
         <is>
-          <t>男性稱呼年長女性的用語，也用來指稱流行的「姊弟戀」劇情套路。</t>
+          <t>字面意思是「礦坑盡頭」——形容誇張、狗血到極點的劇情轉折。</t>
         </is>
       </c>
       <c r="I688" s="16" t="inlineStr">
         <is>
-          <t>男性称呼年长女性的用语，也用来指称流行的“姊弟恋”剧情套路。</t>
+          <t>字面意思是“矿坑尽头”——形容夸张、狗血到极点的剧情转折。</t>
         </is>
       </c>
       <c r="J688" s="16" t="inlineStr">
         <is>
-          <t>男性が年上の女性を呼ぶ言葉——人気の「姉さん年上ロマンス」というドラマのトロープの名前でもある。</t>
+          <t>「坑道の奥」——極端で、行き過ぎたドラマチックな展開を表す。</t>
         </is>
       </c>
       <c r="K688" s="16" t="inlineStr">
         <is>
-          <t>이 드라마는 누나 로맨스야.</t>
+          <t>이 드라마 완전 막장 전개야.</t>
         </is>
       </c>
       <c r="L688" s="16" t="inlineStr">
         <is>
-          <t>This drama is a noona romance.</t>
+          <t>This drama's plot has gone completely over the top.</t>
         </is>
       </c>
       <c r="M688" s="16" t="inlineStr">
         <is>
-          <t>Este drama es un romance con una "noona" (mujer mayor).</t>
+          <t>La trama de este drama se volvió totalmente exagerada.</t>
         </is>
       </c>
       <c r="N688" s="16" t="inlineStr">
         <is>
-          <t>這部劇是姊弟戀劇情。</t>
+          <t>這部劇劇情完全狗血。</t>
         </is>
       </c>
       <c r="O688" s="16" t="inlineStr">
         <is>
-          <t>这部剧是姊弟恋剧情。</t>
+          <t>这部剧剧情完全狗血。</t>
         </is>
       </c>
       <c r="P688" s="16" t="inlineStr">
         <is>
-          <t>このドラマは年上女性ロマンスだよ。</t>
+          <t>このドラマ、完全にどろどろ展開になってる。</t>
         </is>
       </c>
       <c r="Q688" s="16" t="inlineStr">
@@ -67483,17 +67483,17 @@
     <row r="689" ht="46" customHeight="1">
       <c r="A689" s="15" t="inlineStr">
         <is>
-          <t>DAT-012</t>
+          <t>DAT-011</t>
         </is>
       </c>
       <c r="B689" s="15" t="inlineStr">
         <is>
-          <t>츤데레</t>
+          <t>누나</t>
         </is>
       </c>
       <c r="C689" s="15" t="inlineStr">
         <is>
-          <t>cheun-de-re</t>
+          <t>nu-na</t>
         </is>
       </c>
       <c r="D689" s="15" t="inlineStr">
@@ -67508,62 +67508,62 @@
       </c>
       <c r="F689" s="16" t="inlineStr">
         <is>
-          <t>A cold-and-prickly-on-the-outside, warm-on-the-inside personality type (originally Japanese, widely used in Korean too).</t>
+          <t>What a man calls an older woman — also names the popular "noona romance" drama trope.</t>
         </is>
       </c>
       <c r="G689" s="16" t="inlineStr">
         <is>
-          <t>Un tipo de personalidad fría por fuera pero cálida por dentro (de origen japonés, muy usado también en coreano).</t>
+          <t>Cómo un hombre llama a una mujer mayor; también nombra el popular recurso de "romance con noona" en los dramas.</t>
         </is>
       </c>
       <c r="H689" s="16" t="inlineStr">
         <is>
-          <t>外表冷淡尖銳、內心溫暖的性格類型，傲嬌，原為日文用語，在韓國也廣泛使用。</t>
+          <t>男性稱呼年長女性的用語，也用來指稱流行的「姊弟戀」劇情套路。</t>
         </is>
       </c>
       <c r="I689" s="16" t="inlineStr">
         <is>
-          <t>外表冷淡尖锐、内心温暖的性格类型，傲娇，原为日文用语，在韩国也广泛使用。</t>
+          <t>男性称呼年长女性的用语，也用来指称流行的“姊弟恋”剧情套路。</t>
         </is>
       </c>
       <c r="J689" s="16" t="inlineStr">
         <is>
-          <t>外見は冷たくてトゲトゲしいけど、内面は温かい性格タイプ（元々日本語で、韓国でも広く使われている）。</t>
+          <t>男性が年上の女性を呼ぶ言葉——人気の「姉さん年上ロマンス」というドラマのトロープの名前でもある。</t>
         </is>
       </c>
       <c r="K689" s="16" t="inlineStr">
         <is>
-          <t>저 캐릭터 완전 츤데레야.</t>
+          <t>이 드라마는 누나 로맨스야.</t>
         </is>
       </c>
       <c r="L689" s="16" t="inlineStr">
         <is>
-          <t>That character is a total tsundere.</t>
+          <t>This drama is a noona romance.</t>
         </is>
       </c>
       <c r="M689" s="16" t="inlineStr">
         <is>
-          <t>Ese personaje es un tsundere total.</t>
+          <t>Este drama es un romance con una "noona" (mujer mayor).</t>
         </is>
       </c>
       <c r="N689" s="16" t="inlineStr">
         <is>
-          <t>那個角色完全是傲嬌。</t>
+          <t>這部劇是姊弟戀劇情。</t>
         </is>
       </c>
       <c r="O689" s="16" t="inlineStr">
         <is>
-          <t>那个角色完全是傲娇。</t>
+          <t>这部剧是姊弟恋剧情。</t>
         </is>
       </c>
       <c r="P689" s="16" t="inlineStr">
         <is>
-          <t>あのキャラ、完全にツンデレだよね。</t>
+          <t>このドラマは年上女性ロマンスだよ。</t>
         </is>
       </c>
       <c r="Q689" s="16" t="inlineStr">
         <is>
-          <t>Drama/anime fan talk</t>
+          <t>K-drama genre talk</t>
         </is>
       </c>
       <c r="R689" s="15" t="inlineStr">
@@ -67580,17 +67580,17 @@
     <row r="690" ht="46" customHeight="1">
       <c r="A690" s="15" t="inlineStr">
         <is>
-          <t>DAT-013</t>
+          <t>DAT-012</t>
         </is>
       </c>
       <c r="B690" s="15" t="inlineStr">
         <is>
-          <t>재회</t>
+          <t>츤데레</t>
         </is>
       </c>
       <c r="C690" s="15" t="inlineStr">
         <is>
-          <t>jae-hoe</t>
+          <t>cheun-de-re</t>
         </is>
       </c>
       <c r="D690" s="15" t="inlineStr">
@@ -67605,62 +67605,62 @@
       </c>
       <c r="F690" s="16" t="inlineStr">
         <is>
-          <t>Reuniting with an ex-partner.</t>
+          <t>A cold-and-prickly-on-the-outside, warm-on-the-inside personality type (originally Japanese, widely used in Korean too).</t>
         </is>
       </c>
       <c r="G690" s="16" t="inlineStr">
         <is>
-          <t>Reencontrarse con una expareja.</t>
+          <t>Un tipo de personalidad fría por fuera pero cálida por dentro (de origen japonés, muy usado también en coreano).</t>
         </is>
       </c>
       <c r="H690" s="16" t="inlineStr">
         <is>
-          <t>與前任重新復合。</t>
+          <t>外表冷淡尖銳、內心溫暖的性格類型，傲嬌，原為日文用語，在韓國也廣泛使用。</t>
         </is>
       </c>
       <c r="I690" s="16" t="inlineStr">
         <is>
-          <t>与前任重新复合。</t>
+          <t>外表冷淡尖锐、内心温暖的性格类型，傲娇，原为日文用语，在韩国也广泛使用。</t>
         </is>
       </c>
       <c r="J690" s="16" t="inlineStr">
         <is>
-          <t>元恋人とよりを戻すこと。</t>
+          <t>外見は冷たくてトゲトゲしいけど、内面は温かい性格タイプ（元々日本語で、韓国でも広く使われている）。</t>
         </is>
       </c>
       <c r="K690" s="16" t="inlineStr">
         <is>
-          <t>그 커플 결국 재회했대.</t>
+          <t>저 캐릭터 완전 츤데레야.</t>
         </is>
       </c>
       <c r="L690" s="16" t="inlineStr">
         <is>
-          <t>I heard that couple got back together in the end.</t>
+          <t>That character is a total tsundere.</t>
         </is>
       </c>
       <c r="M690" s="16" t="inlineStr">
         <is>
-          <t>Escuché que esa pareja al final volvió.</t>
+          <t>Ese personaje es un tsundere total.</t>
         </is>
       </c>
       <c r="N690" s="16" t="inlineStr">
         <is>
-          <t>聽說那對情侶最後復合了。</t>
+          <t>那個角色完全是傲嬌。</t>
         </is>
       </c>
       <c r="O690" s="16" t="inlineStr">
         <is>
-          <t>听说那对情侣最后复合了。</t>
+          <t>那个角色完全是傲娇。</t>
         </is>
       </c>
       <c r="P690" s="16" t="inlineStr">
         <is>
-          <t>あのカップル、結局復縁したらしい。</t>
+          <t>あのキャラ、完全にツンデレだよね。</t>
         </is>
       </c>
       <c r="Q690" s="16" t="inlineStr">
         <is>
-          <t>K-drama plot talk, gossip</t>
+          <t>Drama/anime fan talk</t>
         </is>
       </c>
       <c r="R690" s="15" t="inlineStr">
@@ -67677,17 +67677,17 @@
     <row r="691" ht="46" customHeight="1">
       <c r="A691" s="15" t="inlineStr">
         <is>
-          <t>DAT-014</t>
+          <t>DAT-013</t>
         </is>
       </c>
       <c r="B691" s="15" t="inlineStr">
         <is>
-          <t>짝사랑</t>
+          <t>재회</t>
         </is>
       </c>
       <c r="C691" s="15" t="inlineStr">
         <is>
-          <t>jjak-sa-rang</t>
+          <t>jae-hoe</t>
         </is>
       </c>
       <c r="D691" s="15" t="inlineStr">
@@ -67702,62 +67702,62 @@
       </c>
       <c r="F691" s="16" t="inlineStr">
         <is>
-          <t>Unrequited, one-sided love.</t>
+          <t>Reuniting with an ex-partner.</t>
         </is>
       </c>
       <c r="G691" s="16" t="inlineStr">
         <is>
-          <t>Amor no correspondido, unilateral.</t>
+          <t>Reencontrarse con una expareja.</t>
         </is>
       </c>
       <c r="H691" s="16" t="inlineStr">
         <is>
-          <t>得不到回應的單方面愛戀。</t>
+          <t>與前任重新復合。</t>
         </is>
       </c>
       <c r="I691" s="16" t="inlineStr">
         <is>
-          <t>得不到回应的单方面爱恋。</t>
+          <t>与前任重新复合。</t>
         </is>
       </c>
       <c r="J691" s="16" t="inlineStr">
         <is>
-          <t>報われない、一方的な恋。</t>
+          <t>元恋人とよりを戻すこと。</t>
         </is>
       </c>
       <c r="K691" s="16" t="inlineStr">
         <is>
-          <t>고등학생 때 짝사랑했던 애 기억나.</t>
+          <t>그 커플 결국 재회했대.</t>
         </is>
       </c>
       <c r="L691" s="16" t="inlineStr">
         <is>
-          <t>I remember the person I had a one-sided crush on in high school.</t>
+          <t>I heard that couple got back together in the end.</t>
         </is>
       </c>
       <c r="M691" s="16" t="inlineStr">
         <is>
-          <t>Recuerdo a la persona de la que estuve enamorado sin ser correspondido en la prepa.</t>
+          <t>Escuché que esa pareja al final volvió.</t>
         </is>
       </c>
       <c r="N691" s="16" t="inlineStr">
         <is>
-          <t>我還記得高中時單戀過的那個人。</t>
+          <t>聽說那對情侶最後復合了。</t>
         </is>
       </c>
       <c r="O691" s="16" t="inlineStr">
         <is>
-          <t>我还记得高中时单恋过的那个人。</t>
+          <t>听说那对情侣最后复合了。</t>
         </is>
       </c>
       <c r="P691" s="16" t="inlineStr">
         <is>
-          <t>高校生の時に片思いしてた人のこと覚えてる。</t>
+          <t>あのカップル、結局復縁したらしい。</t>
         </is>
       </c>
       <c r="Q691" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>K-drama plot talk, gossip</t>
         </is>
       </c>
       <c r="R691" s="15" t="inlineStr">
@@ -67774,17 +67774,17 @@
     <row r="692" ht="46" customHeight="1">
       <c r="A692" s="15" t="inlineStr">
         <is>
-          <t>DAT-015</t>
+          <t>DAT-014</t>
         </is>
       </c>
       <c r="B692" s="15" t="inlineStr">
         <is>
-          <t>애정촌</t>
+          <t>짝사랑</t>
         </is>
       </c>
       <c r="C692" s="15" t="inlineStr">
         <is>
-          <t>ae-jeong-chon</t>
+          <t>jjak-sa-rang</t>
         </is>
       </c>
       <c r="D692" s="15" t="inlineStr">
@@ -67799,62 +67799,62 @@
       </c>
       <c r="F692" s="16" t="inlineStr">
         <is>
-          <t>"Love village" — the classic setting/format used in Korean dating reality shows.</t>
+          <t>Unrequited, one-sided love.</t>
         </is>
       </c>
       <c r="G692" s="16" t="inlineStr">
         <is>
-          <t>"Pueblo del amor": el escenario o formato clásico usado en los reality shows de citas coreanos.</t>
+          <t>Amor no correspondido, unilateral.</t>
         </is>
       </c>
       <c r="H692" s="16" t="inlineStr">
         <is>
-          <t>「愛情村」——韓國戀愛實境節目經典的場景設定與節目形式。</t>
+          <t>得不到回應的單方面愛戀。</t>
         </is>
       </c>
       <c r="I692" s="16" t="inlineStr">
         <is>
-          <t>“爱情村”——韩国恋爱实境节目经典的场景设置与节目形式。</t>
+          <t>得不到回应的单方面爱恋。</t>
         </is>
       </c>
       <c r="J692" s="16" t="inlineStr">
         <is>
-          <t>「愛の村」——韓国の恋愛リアリティ番組の定番の舞台設定・フォーマット。</t>
+          <t>報われない、一方的な恋。</t>
         </is>
       </c>
       <c r="K692" s="16" t="inlineStr">
         <is>
-          <t>애정촌 나온 커플 아직도 만나?</t>
+          <t>고등학생 때 짝사랑했던 애 기억나.</t>
         </is>
       </c>
       <c r="L692" s="16" t="inlineStr">
         <is>
-          <t>Is that couple from the love-village show still together?</t>
+          <t>I remember the person I had a one-sided crush on in high school.</t>
         </is>
       </c>
       <c r="M692" s="16" t="inlineStr">
         <is>
-          <t>¿Esa pareja del show de citas todavía sigue junta?</t>
+          <t>Recuerdo a la persona de la que estuve enamorado sin ser correspondido en la prepa.</t>
         </is>
       </c>
       <c r="N692" s="16" t="inlineStr">
         <is>
-          <t>那對從愛情村出來的情侶還在一起嗎？</t>
+          <t>我還記得高中時單戀過的那個人。</t>
         </is>
       </c>
       <c r="O692" s="16" t="inlineStr">
         <is>
-          <t>那对从爱情村出来的情侣还在一起吗？</t>
+          <t>我还记得高中时单恋过的那个人。</t>
         </is>
       </c>
       <c r="P692" s="16" t="inlineStr">
         <is>
-          <t>あの恋の村から出てきたカップル、まだ付き合ってる？</t>
+          <t>高校生の時に片思いしてた人のこと覚えてる。</t>
         </is>
       </c>
       <c r="Q692" s="16" t="inlineStr">
         <is>
-          <t>Dating reality shows</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R692" s="15" t="inlineStr">
@@ -67871,17 +67871,17 @@
     <row r="693" ht="46" customHeight="1">
       <c r="A693" s="15" t="inlineStr">
         <is>
-          <t>DAT-016</t>
+          <t>DAT-015</t>
         </is>
       </c>
       <c r="B693" s="15" t="inlineStr">
         <is>
-          <t>심쿵</t>
+          <t>애정촌</t>
         </is>
       </c>
       <c r="C693" s="15" t="inlineStr">
         <is>
-          <t>sim-kung</t>
+          <t>ae-jeong-chon</t>
         </is>
       </c>
       <c r="D693" s="15" t="inlineStr">
@@ -67896,62 +67896,62 @@
       </c>
       <c r="F693" s="16" t="inlineStr">
         <is>
-          <t>"Heart-thump" — a swoon-worthy, heart-fluttering moment.</t>
+          <t>"Love village" — the classic setting/format used in Korean dating reality shows.</t>
         </is>
       </c>
       <c r="G693" s="16" t="inlineStr">
         <is>
-          <t>"Latido de corazón": un momento que hace suspirar y acelera el corazón.</t>
+          <t>"Pueblo del amor": el escenario o formato clásico usado en los reality shows de citas coreanos.</t>
         </is>
       </c>
       <c r="H693" s="16" t="inlineStr">
         <is>
-          <t>「心臟砰咚」——令人心動、心跳加速的瞬間。</t>
+          <t>「愛情村」——韓國戀愛實境節目經典的場景設定與節目形式。</t>
         </is>
       </c>
       <c r="I693" s="16" t="inlineStr">
         <is>
-          <t>“心脏砰咚”——令人心动、心跳加速的瞬间。</t>
+          <t>“爱情村”——韩国恋爱实境节目经典的场景设置与节目形式。</t>
         </is>
       </c>
       <c r="J693" s="16" t="inlineStr">
         <is>
-          <t>「心臓ドキン」——胸きゅんする瞬間。</t>
+          <t>「愛の村」——韓国の恋愛リアリティ番組の定番の舞台設定・フォーマット。</t>
         </is>
       </c>
       <c r="K693" s="16" t="inlineStr">
         <is>
-          <t>그 장면 완전 심쿵이었어.</t>
+          <t>애정촌 나온 커플 아직도 만나?</t>
         </is>
       </c>
       <c r="L693" s="16" t="inlineStr">
         <is>
-          <t>That scene was such a heart-flutter moment.</t>
+          <t>Is that couple from the love-village show still together?</t>
         </is>
       </c>
       <c r="M693" s="16" t="inlineStr">
         <is>
-          <t>Esa escena fue un momento que hizo latir el corazón muy fuerte.</t>
+          <t>¿Esa pareja del show de citas todavía sigue junta?</t>
         </is>
       </c>
       <c r="N693" s="16" t="inlineStr">
         <is>
-          <t>那個畫面完全讓人心動。</t>
+          <t>那對從愛情村出來的情侶還在一起嗎？</t>
         </is>
       </c>
       <c r="O693" s="16" t="inlineStr">
         <is>
-          <t>那个画面完全让人心动。</t>
+          <t>那对从爱情村出来的情侣还在一起吗？</t>
         </is>
       </c>
       <c r="P693" s="16" t="inlineStr">
         <is>
-          <t>あのシーン、完全にキュンとした。</t>
+          <t>あの恋の村から出てきたカップル、まだ付き合ってる？</t>
         </is>
       </c>
       <c r="Q693" s="16" t="inlineStr">
         <is>
-          <t>K-drama reactions</t>
+          <t>Dating reality shows</t>
         </is>
       </c>
       <c r="R693" s="15" t="inlineStr">
@@ -67968,17 +67968,17 @@
     <row r="694" ht="46" customHeight="1">
       <c r="A694" s="15" t="inlineStr">
         <is>
-          <t>DAT-017</t>
+          <t>DAT-016</t>
         </is>
       </c>
       <c r="B694" s="15" t="inlineStr">
         <is>
-          <t>첫사랑</t>
+          <t>심쿵</t>
         </is>
       </c>
       <c r="C694" s="15" t="inlineStr">
         <is>
-          <t>cheot-sa-rang</t>
+          <t>sim-kung</t>
         </is>
       </c>
       <c r="D694" s="15" t="inlineStr">
@@ -67993,62 +67993,62 @@
       </c>
       <c r="F694" s="16" t="inlineStr">
         <is>
-          <t>One's very first love.</t>
+          <t>"Heart-thump" — a swoon-worthy, heart-fluttering moment.</t>
         </is>
       </c>
       <c r="G694" s="16" t="inlineStr">
         <is>
-          <t>El primer amor de una persona.</t>
+          <t>"Latido de corazón": un momento que hace suspirar y acelera el corazón.</t>
         </is>
       </c>
       <c r="H694" s="16" t="inlineStr">
         <is>
-          <t>一個人生命中最初的戀愛對象，初戀。</t>
+          <t>「心臟砰咚」——令人心動、心跳加速的瞬間。</t>
         </is>
       </c>
       <c r="I694" s="16" t="inlineStr">
         <is>
-          <t>一个人生命中最初的恋爱对象，初恋。</t>
+          <t>“心脏砰咚”——令人心动、心跳加速的瞬间。</t>
         </is>
       </c>
       <c r="J694" s="16" t="inlineStr">
         <is>
-          <t>人生で最初の恋。</t>
+          <t>「心臓ドキン」——胸きゅんする瞬間。</t>
         </is>
       </c>
       <c r="K694" s="16" t="inlineStr">
         <is>
-          <t>그 드라마 보니까 첫사랑 생각나더라.</t>
+          <t>그 장면 완전 심쿵이었어.</t>
         </is>
       </c>
       <c r="L694" s="16" t="inlineStr">
         <is>
-          <t>Watching that drama made me think of my first love.</t>
+          <t>That scene was such a heart-flutter moment.</t>
         </is>
       </c>
       <c r="M694" s="16" t="inlineStr">
         <is>
-          <t>Ver ese drama me hizo pensar en mi primer amor.</t>
+          <t>Esa escena fue un momento que hizo latir el corazón muy fuerte.</t>
         </is>
       </c>
       <c r="N694" s="16" t="inlineStr">
         <is>
-          <t>看那部劇讓我想起初戀。</t>
+          <t>那個畫面完全讓人心動。</t>
         </is>
       </c>
       <c r="O694" s="16" t="inlineStr">
         <is>
-          <t>看那部剧让我想起初恋。</t>
+          <t>那个画面完全让人心动。</t>
         </is>
       </c>
       <c r="P694" s="16" t="inlineStr">
         <is>
-          <t>あのドラマ見てたら初恋を思い出した。</t>
+          <t>あのシーン、完全にキュンとした。</t>
         </is>
       </c>
       <c r="Q694" s="16" t="inlineStr">
         <is>
-          <t>Casual nostalgia talk</t>
+          <t>K-drama reactions</t>
         </is>
       </c>
       <c r="R694" s="15" t="inlineStr">
@@ -68065,17 +68065,17 @@
     <row r="695" ht="46" customHeight="1">
       <c r="A695" s="15" t="inlineStr">
         <is>
-          <t>DAT-018</t>
+          <t>DAT-017</t>
         </is>
       </c>
       <c r="B695" s="15" t="inlineStr">
         <is>
-          <t>국민첫사랑</t>
+          <t>첫사랑</t>
         </is>
       </c>
       <c r="C695" s="15" t="inlineStr">
         <is>
-          <t>guk-min-cheot-sa-rang</t>
+          <t>cheot-sa-rang</t>
         </is>
       </c>
       <c r="D695" s="15" t="inlineStr">
@@ -68090,62 +68090,62 @@
       </c>
       <c r="F695" s="16" t="inlineStr">
         <is>
-          <t>"Nation's first love" — an actress or idol seen as an idealized, universally beloved first-love figure.</t>
+          <t>One's very first love.</t>
         </is>
       </c>
       <c r="G695" s="16" t="inlineStr">
         <is>
-          <t>"Primer amor de la nación": una actriz o ídolo vista como una figura idealizada de primer amor querida por todos.</t>
+          <t>El primer amor de una persona.</t>
         </is>
       </c>
       <c r="H695" s="16" t="inlineStr">
         <is>
-          <t>「國民初戀」——被視為理想化、全民共同初戀形象的女演員或偶像。</t>
+          <t>一個人生命中最初的戀愛對象，初戀。</t>
         </is>
       </c>
       <c r="I695" s="16" t="inlineStr">
         <is>
-          <t>“国民初恋”——被视为理想化、全民共同初恋形象的女演员或偶像。</t>
+          <t>一个人生命中最初的恋爱对象，初恋。</t>
         </is>
       </c>
       <c r="J695" s="16" t="inlineStr">
         <is>
-          <t>「国民の初恋」——理想化された、国民全員に愛される初恋の象徴とされる女優やアイドル。</t>
+          <t>人生で最初の恋。</t>
         </is>
       </c>
       <c r="K695" s="16" t="inlineStr">
         <is>
-          <t>그 배우는 국민첫사랑으로 불려.</t>
+          <t>그 드라마 보니까 첫사랑 생각나더라.</t>
         </is>
       </c>
       <c r="L695" s="16" t="inlineStr">
         <is>
-          <t>That actress is called the nation's first love.</t>
+          <t>Watching that drama made me think of my first love.</t>
         </is>
       </c>
       <c r="M695" s="16" t="inlineStr">
         <is>
-          <t>A esa actriz la llaman el primer amor de la nación.</t>
+          <t>Ver ese drama me hizo pensar en mi primer amor.</t>
         </is>
       </c>
       <c r="N695" s="16" t="inlineStr">
         <is>
-          <t>那位演員被稱為國民初戀。</t>
+          <t>看那部劇讓我想起初戀。</t>
         </is>
       </c>
       <c r="O695" s="16" t="inlineStr">
         <is>
-          <t>那位演员被称为国民初恋。</t>
+          <t>看那部剧让我想起初恋。</t>
         </is>
       </c>
       <c r="P695" s="16" t="inlineStr">
         <is>
-          <t>あの女優は国民的初恋と呼ばれてる。</t>
+          <t>あのドラマ見てたら初恋を思い出した。</t>
         </is>
       </c>
       <c r="Q695" s="16" t="inlineStr">
         <is>
-          <t>Media coverage, fan talk</t>
+          <t>Casual nostalgia talk</t>
         </is>
       </c>
       <c r="R695" s="15" t="inlineStr">
@@ -68162,17 +68162,17 @@
     <row r="696" ht="46" customHeight="1">
       <c r="A696" s="15" t="inlineStr">
         <is>
-          <t>DAT-019</t>
+          <t>DAT-018</t>
         </is>
       </c>
       <c r="B696" s="15" t="inlineStr">
         <is>
-          <t>훈남</t>
+          <t>국민첫사랑</t>
         </is>
       </c>
       <c r="C696" s="15" t="inlineStr">
         <is>
-          <t>hun-nam</t>
+          <t>guk-min-cheot-sa-rang</t>
         </is>
       </c>
       <c r="D696" s="15" t="inlineStr">
@@ -68187,62 +68187,62 @@
       </c>
       <c r="F696" s="16" t="inlineStr">
         <is>
-          <t>A warm, wholesome, good-looking man — approachable rather than intimidating.</t>
+          <t>"Nation's first love" — an actress or idol seen as an idealized, universally beloved first-love figure.</t>
         </is>
       </c>
       <c r="G696" s="16" t="inlineStr">
         <is>
-          <t>Un hombre cálido, agradable y atractivo — cercano en lugar de intimidante.</t>
+          <t>"Primer amor de la nación": una actriz o ídolo vista como una figura idealizada de primer amor querida por todos.</t>
         </is>
       </c>
       <c r="H696" s="16" t="inlineStr">
         <is>
-          <t>溫暖、樸實、外表出眾的男性，給人親切而非有距離感的印象，暖男。</t>
+          <t>「國民初戀」——被視為理想化、全民共同初戀形象的女演員或偶像。</t>
         </is>
       </c>
       <c r="I696" s="16" t="inlineStr">
         <is>
-          <t>温暖、朴实、外表出众的男性，给人亲切而非有距离感的印象，暖男。</t>
+          <t>“国民初恋”——被视为理想化、全民共同初恋形象的女演员或偶像。</t>
         </is>
       </c>
       <c r="J696" s="16" t="inlineStr">
         <is>
-          <t>温かく、素朴で、見た目の良い男性——威圧感がなく親しみやすい。</t>
+          <t>「国民の初恋」——理想化された、国民全員に愛される初恋の象徴とされる女優やアイドル。</t>
         </is>
       </c>
       <c r="K696" s="16" t="inlineStr">
         <is>
-          <t>저 남주 완전 훈남 스타일이야.</t>
+          <t>그 배우는 국민첫사랑으로 불려.</t>
         </is>
       </c>
       <c r="L696" s="16" t="inlineStr">
         <is>
-          <t>That male lead is totally the wholesome good-looking type.</t>
+          <t>That actress is called the nation's first love.</t>
         </is>
       </c>
       <c r="M696" s="16" t="inlineStr">
         <is>
-          <t>Ese protagonista es totalmente del tipo agradable y atractivo.</t>
+          <t>A esa actriz la llaman el primer amor de la nación.</t>
         </is>
       </c>
       <c r="N696" s="16" t="inlineStr">
         <is>
-          <t>那個男主角完全是暖男型。</t>
+          <t>那位演員被稱為國民初戀。</t>
         </is>
       </c>
       <c r="O696" s="16" t="inlineStr">
         <is>
-          <t>那个男主角完全是暖男型。</t>
+          <t>那位演员被称为国民初恋。</t>
         </is>
       </c>
       <c r="P696" s="16" t="inlineStr">
         <is>
-          <t>あの男主人公、完全に好青年タイプだよね。</t>
+          <t>あの女優は国民的初恋と呼ばれてる。</t>
         </is>
       </c>
       <c r="Q696" s="16" t="inlineStr">
         <is>
-          <t>K-drama casting talk</t>
+          <t>Media coverage, fan talk</t>
         </is>
       </c>
       <c r="R696" s="15" t="inlineStr">
@@ -68259,17 +68259,17 @@
     <row r="697" ht="46" customHeight="1">
       <c r="A697" s="15" t="inlineStr">
         <is>
-          <t>DAT-020</t>
+          <t>DAT-019</t>
         </is>
       </c>
       <c r="B697" s="15" t="inlineStr">
         <is>
-          <t>훈녀</t>
+          <t>훈남</t>
         </is>
       </c>
       <c r="C697" s="15" t="inlineStr">
         <is>
-          <t>hun-nyeo</t>
+          <t>hun-nam</t>
         </is>
       </c>
       <c r="D697" s="15" t="inlineStr">
@@ -68284,57 +68284,57 @@
       </c>
       <c r="F697" s="16" t="inlineStr">
         <is>
-          <t>The female equivalent of 훈남 — warm, approachable, and good-looking.</t>
+          <t>A warm, wholesome, good-looking man — approachable rather than intimidating.</t>
         </is>
       </c>
       <c r="G697" s="16" t="inlineStr">
         <is>
-          <t>El equivalente femenino de 훈남: cálida, cercana y atractiva.</t>
+          <t>Un hombre cálido, agradable y atractivo — cercano en lugar de intimidante.</t>
         </is>
       </c>
       <c r="H697" s="16" t="inlineStr">
         <is>
-          <t>훈남的女性版本——溫暖、親切又好看的女性。</t>
+          <t>溫暖、樸實、外表出眾的男性，給人親切而非有距離感的印象，暖男。</t>
         </is>
       </c>
       <c r="I697" s="16" t="inlineStr">
         <is>
-          <t>훈남的女性版本——温暖、亲切又好看的女性。</t>
+          <t>温暖、朴实、外表出众的男性，给人亲切而非有距离感的印象，暖男。</t>
         </is>
       </c>
       <c r="J697" s="16" t="inlineStr">
         <is>
-          <t>훈남の女性版——温かく、親しみやすくて、見た目の良い女性。</t>
+          <t>温かく、素朴で、見た目の良い男性——威圧感がなく親しみやすい。</t>
         </is>
       </c>
       <c r="K697" s="16" t="inlineStr">
         <is>
-          <t>그 여배우는 훈녀 이미지로 유명해.</t>
+          <t>저 남주 완전 훈남 스타일이야.</t>
         </is>
       </c>
       <c r="L697" s="16" t="inlineStr">
         <is>
-          <t>That actress is known for her wholesome good-looking image.</t>
+          <t>That male lead is totally the wholesome good-looking type.</t>
         </is>
       </c>
       <c r="M697" s="16" t="inlineStr">
         <is>
-          <t>Esa actriz es conocida por su imagen cálida y atractiva.</t>
+          <t>Ese protagonista es totalmente del tipo agradable y atractivo.</t>
         </is>
       </c>
       <c r="N697" s="16" t="inlineStr">
         <is>
-          <t>那位女演員以暖女形象聞名。</t>
+          <t>那個男主角完全是暖男型。</t>
         </is>
       </c>
       <c r="O697" s="16" t="inlineStr">
         <is>
-          <t>那位女演员以暖女形象闻名。</t>
+          <t>那个男主角完全是暖男型。</t>
         </is>
       </c>
       <c r="P697" s="16" t="inlineStr">
         <is>
-          <t>あの女優、好感度高い美人イメージで有名。</t>
+          <t>あの男主人公、完全に好青年タイプだよね。</t>
         </is>
       </c>
       <c r="Q697" s="16" t="inlineStr">
@@ -68356,17 +68356,17 @@
     <row r="698" ht="46" customHeight="1">
       <c r="A698" s="15" t="inlineStr">
         <is>
-          <t>DAT-021</t>
+          <t>DAT-020</t>
         </is>
       </c>
       <c r="B698" s="15" t="inlineStr">
         <is>
-          <t>나쁜남자</t>
+          <t>훈녀</t>
         </is>
       </c>
       <c r="C698" s="15" t="inlineStr">
         <is>
-          <t>na-ppeun-nam-ja</t>
+          <t>hun-nyeo</t>
         </is>
       </c>
       <c r="D698" s="15" t="inlineStr">
@@ -68381,62 +68381,62 @@
       </c>
       <c r="F698" s="16" t="inlineStr">
         <is>
-          <t>The "bad boy" trope — a cold, dangerous-seeming male lead who softens for the heroine.</t>
+          <t>The female equivalent of 훈남 — warm, approachable, and good-looking.</t>
         </is>
       </c>
       <c r="G698" s="16" t="inlineStr">
         <is>
-          <t>El arquetipo del "chico malo": un protagonista frío y de apariencia peligrosa que se enternece por la protagonista.</t>
+          <t>El equivalente femenino de 훈남: cálida, cercana y atractiva.</t>
         </is>
       </c>
       <c r="H698" s="16" t="inlineStr">
         <is>
-          <t>「壞男人」套路——外表冷酷、帶點危險氣息，卻在女主角面前逐漸軟化的男主角類型。</t>
+          <t>훈남的女性版本——溫暖、親切又好看的女性。</t>
         </is>
       </c>
       <c r="I698" s="16" t="inlineStr">
         <is>
-          <t>“坏男人”套路——外表冷酷、带点危险气息，却在女主角面前逐渐软化的男主角类型。</t>
+          <t>훈남的女性版本——温暖、亲切又好看的女性。</t>
         </is>
       </c>
       <c r="J698" s="16" t="inlineStr">
         <is>
-          <t>「悪い男」トロープ——冷たくて危険に見えるが、ヒロインの前で心を開いていく男性主人公。</t>
+          <t>훈남の女性版——温かく、親しみやすくて、見た目の良い女性。</t>
         </is>
       </c>
       <c r="K698" s="16" t="inlineStr">
         <is>
-          <t>나쁜남자 클리셰인데도 계속 보게 돼.</t>
+          <t>그 여배우는 훈녀 이미지로 유명해.</t>
         </is>
       </c>
       <c r="L698" s="16" t="inlineStr">
         <is>
-          <t>Even though it's the bad-boy cliché, I keep watching anyway.</t>
+          <t>That actress is known for her wholesome good-looking image.</t>
         </is>
       </c>
       <c r="M698" s="16" t="inlineStr">
         <is>
-          <t>Aunque es el cliché del chico malo, sigo viéndolo de todas formas.</t>
+          <t>Esa actriz es conocida por su imagen cálida y atractiva.</t>
         </is>
       </c>
       <c r="N698" s="16" t="inlineStr">
         <is>
-          <t>雖然是壞男人的老梗，還是會一直看下去。</t>
+          <t>那位女演員以暖女形象聞名。</t>
         </is>
       </c>
       <c r="O698" s="16" t="inlineStr">
         <is>
-          <t>虽然是坏男人的老梗，还是会一直看下去。</t>
+          <t>那位女演员以暖女形象闻名。</t>
         </is>
       </c>
       <c r="P698" s="16" t="inlineStr">
         <is>
-          <t>ワルの魅力系クリシェなのに、つい見ちゃう。</t>
+          <t>あの女優、好感度高い美人イメージで有名。</t>
         </is>
       </c>
       <c r="Q698" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>K-drama casting talk</t>
         </is>
       </c>
       <c r="R698" s="15" t="inlineStr">
@@ -68453,17 +68453,17 @@
     <row r="699" ht="46" customHeight="1">
       <c r="A699" s="15" t="inlineStr">
         <is>
-          <t>DAT-022</t>
+          <t>DAT-021</t>
         </is>
       </c>
       <c r="B699" s="15" t="inlineStr">
         <is>
-          <t>소개팅</t>
+          <t>나쁜남자</t>
         </is>
       </c>
       <c r="C699" s="15" t="inlineStr">
         <is>
-          <t>so-gae-ting</t>
+          <t>na-ppeun-nam-ja</t>
         </is>
       </c>
       <c r="D699" s="15" t="inlineStr">
@@ -68478,62 +68478,62 @@
       </c>
       <c r="F699" s="16" t="inlineStr">
         <is>
-          <t>A blind date, typically set up by a mutual friend.</t>
+          <t>The "bad boy" trope — a cold, dangerous-seeming male lead who softens for the heroine.</t>
         </is>
       </c>
       <c r="G699" s="16" t="inlineStr">
         <is>
-          <t>Una cita a ciegas, generalmente organizada por un amigo en común.</t>
+          <t>El arquetipo del "chico malo": un protagonista frío y de apariencia peligrosa que se enternece por la protagonista.</t>
         </is>
       </c>
       <c r="H699" s="16" t="inlineStr">
         <is>
-          <t>通常由共同朋友安排的相親約會。</t>
+          <t>「壞男人」套路——外表冷酷、帶點危險氣息，卻在女主角面前逐漸軟化的男主角類型。</t>
         </is>
       </c>
       <c r="I699" s="16" t="inlineStr">
         <is>
-          <t>通常由共同朋友安排的相亲约会。</t>
+          <t>“坏男人”套路——外表冷酷、带点危险气息，却在女主角面前逐渐软化的男主角类型。</t>
         </is>
       </c>
       <c r="J699" s="16" t="inlineStr">
         <is>
-          <t>友人が仲介する、一対一の紹介デート。</t>
+          <t>「悪い男」トロープ——冷たくて危険に見えるが、ヒロインの前で心を開いていく男性主人公。</t>
         </is>
       </c>
       <c r="K699" s="16" t="inlineStr">
         <is>
-          <t>친구가 소개팅 시켜준대.</t>
+          <t>나쁜남자 클리셰인데도 계속 보게 돼.</t>
         </is>
       </c>
       <c r="L699" s="16" t="inlineStr">
         <is>
-          <t>My friend is setting me up on a blind date.</t>
+          <t>Even though it's the bad-boy cliché, I keep watching anyway.</t>
         </is>
       </c>
       <c r="M699" s="16" t="inlineStr">
         <is>
-          <t>Mi amiga me va a organizar una cita a ciegas.</t>
+          <t>Aunque es el cliché del chico malo, sigo viéndolo de todas formas.</t>
         </is>
       </c>
       <c r="N699" s="16" t="inlineStr">
         <is>
-          <t>朋友要幫我安排相親。</t>
+          <t>雖然是壞男人的老梗，還是會一直看下去。</t>
         </is>
       </c>
       <c r="O699" s="16" t="inlineStr">
         <is>
-          <t>朋友要帮我安排相亲。</t>
+          <t>虽然是坏男人的老梗，还是会一直看下去。</t>
         </is>
       </c>
       <c r="P699" s="16" t="inlineStr">
         <is>
-          <t>友達が紹介デートセッティングしてくれるって。</t>
+          <t>ワルの魅力系クリシェなのに、つい見ちゃう。</t>
         </is>
       </c>
       <c r="Q699" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R699" s="15" t="inlineStr">
@@ -68550,17 +68550,17 @@
     <row r="700" ht="46" customHeight="1">
       <c r="A700" s="15" t="inlineStr">
         <is>
-          <t>DAT-023</t>
+          <t>DAT-022</t>
         </is>
       </c>
       <c r="B700" s="15" t="inlineStr">
         <is>
-          <t>모솔</t>
+          <t>소개팅</t>
         </is>
       </c>
       <c r="C700" s="15" t="inlineStr">
         <is>
-          <t>mo-sol</t>
+          <t>so-gae-ting</t>
         </is>
       </c>
       <c r="D700" s="15" t="inlineStr">
@@ -68575,62 +68575,62 @@
       </c>
       <c r="F700" s="16" t="inlineStr">
         <is>
-          <t>Short for "solo since birth" — someone who has never dated anyone.</t>
+          <t>A blind date, typically set up by a mutual friend.</t>
         </is>
       </c>
       <c r="G700" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "soltero de nacimiento": alguien que nunca ha salido con nadie.</t>
+          <t>Una cita a ciegas, generalmente organizada por un amigo en común.</t>
         </is>
       </c>
       <c r="H700" s="16" t="inlineStr">
         <is>
-          <t>「從娘胎開始就單身」的簡稱——從來沒有交往過的人，母胎單身。</t>
+          <t>通常由共同朋友安排的相親約會。</t>
         </is>
       </c>
       <c r="I700" s="16" t="inlineStr">
         <is>
-          <t>“从娘胎开始就单身”的简称——从来没有交往过的人，母胎单身。</t>
+          <t>通常由共同朋友安排的相亲约会。</t>
         </is>
       </c>
       <c r="J700" s="16" t="inlineStr">
         <is>
-          <t>「生まれてからずっとソロ」の略——今まで誰とも付き合ったことがない人。</t>
+          <t>友人が仲介する、一対一の紹介デート。</t>
         </is>
       </c>
       <c r="K700" s="16" t="inlineStr">
         <is>
-          <t>나 아직도 모솔이야.</t>
+          <t>친구가 소개팅 시켜준대.</t>
         </is>
       </c>
       <c r="L700" s="16" t="inlineStr">
         <is>
-          <t>I'm still someone who's never dated.</t>
+          <t>My friend is setting me up on a blind date.</t>
         </is>
       </c>
       <c r="M700" s="16" t="inlineStr">
         <is>
-          <t>Todavía soy alguien que nunca ha salido con nadie.</t>
+          <t>Mi amiga me va a organizar una cita a ciegas.</t>
         </is>
       </c>
       <c r="N700" s="16" t="inlineStr">
         <is>
-          <t>我還是母胎單身。</t>
+          <t>朋友要幫我安排相親。</t>
         </is>
       </c>
       <c r="O700" s="16" t="inlineStr">
         <is>
-          <t>我还是母胎单身。</t>
+          <t>朋友要帮我安排相亲。</t>
         </is>
       </c>
       <c r="P700" s="16" t="inlineStr">
         <is>
-          <t>私はまだ恋愛経験ゼロだよ。</t>
+          <t>友達が紹介デートセッティングしてくれるって。</t>
         </is>
       </c>
       <c r="Q700" s="16" t="inlineStr">
         <is>
-          <t>Casual self-description</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R700" s="15" t="inlineStr">
@@ -68647,17 +68647,17 @@
     <row r="701" ht="46" customHeight="1">
       <c r="A701" s="15" t="inlineStr">
         <is>
-          <t>DAT-024</t>
+          <t>DAT-023</t>
         </is>
       </c>
       <c r="B701" s="15" t="inlineStr">
         <is>
-          <t>자만추</t>
+          <t>모솔</t>
         </is>
       </c>
       <c r="C701" s="15" t="inlineStr">
         <is>
-          <t>ja-man-chu</t>
+          <t>mo-sol</t>
         </is>
       </c>
       <c r="D701" s="15" t="inlineStr">
@@ -68672,62 +68672,62 @@
       </c>
       <c r="F701" s="16" t="inlineStr">
         <is>
-          <t>Short for "seeking a natural meeting" — wanting to meet a partner organically rather than through a setup.</t>
+          <t>Short for "solo since birth" — someone who has never dated anyone.</t>
         </is>
       </c>
       <c r="G701" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "buscar un encuentro natural": querer conocer a una pareja de forma orgánica en lugar de por una cita arreglada.</t>
+          <t>Abreviatura de "soltero de nacimiento": alguien que nunca ha salido con nadie.</t>
         </is>
       </c>
       <c r="H701" s="16" t="inlineStr">
         <is>
-          <t>「追求自然相遇」的簡稱——希望自然而然認識對象，而非透過相親介紹。</t>
+          <t>「從娘胎開始就單身」的簡稱——從來沒有交往過的人，母胎單身。</t>
         </is>
       </c>
       <c r="I701" s="16" t="inlineStr">
         <is>
-          <t>“追求自然相遇”的简称——希望自然而然认识对象，而非通过相亲介绍。</t>
+          <t>“从娘胎开始就单身”的简称——从来没有交往过的人，母胎单身。</t>
         </is>
       </c>
       <c r="J701" s="16" t="inlineStr">
         <is>
-          <t>「自然な出会いを求める」の略——紹介ではなく、自然に相手と出会いたいという願望。</t>
+          <t>「生まれてからずっとソロ」の略——今まで誰とも付き合ったことがない人。</t>
         </is>
       </c>
       <c r="K701" s="16" t="inlineStr">
         <is>
-          <t>나는 자만추 스타일이라 소개팅은 안 해.</t>
+          <t>나 아직도 모솔이야.</t>
         </is>
       </c>
       <c r="L701" s="16" t="inlineStr">
         <is>
-          <t>I'm the natural-encounter type, so I don't do blind dates.</t>
+          <t>I'm still someone who's never dated.</t>
         </is>
       </c>
       <c r="M701" s="16" t="inlineStr">
         <is>
-          <t>Soy del tipo que prefiere encuentros naturales, así que no hago citas a ciegas.</t>
+          <t>Todavía soy alguien que nunca ha salido con nadie.</t>
         </is>
       </c>
       <c r="N701" s="16" t="inlineStr">
         <is>
-          <t>我是喜歡自然認識的類型，不太相親。</t>
+          <t>我還是母胎單身。</t>
         </is>
       </c>
       <c r="O701" s="16" t="inlineStr">
         <is>
-          <t>我是喜欢自然认识的类型，不太相亲。</t>
+          <t>我还是母胎单身。</t>
         </is>
       </c>
       <c r="P701" s="16" t="inlineStr">
         <is>
-          <t>私は自然な出会い派だから、合コンはしない。</t>
+          <t>私はまだ恋愛経験ゼロだよ。</t>
         </is>
       </c>
       <c r="Q701" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Casual self-description</t>
         </is>
       </c>
       <c r="R701" s="15" t="inlineStr">
@@ -68744,17 +68744,17 @@
     <row r="702" ht="46" customHeight="1">
       <c r="A702" s="15" t="inlineStr">
         <is>
-          <t>DAT-025</t>
+          <t>DAT-024</t>
         </is>
       </c>
       <c r="B702" s="15" t="inlineStr">
         <is>
-          <t>여사친</t>
+          <t>자만추</t>
         </is>
       </c>
       <c r="C702" s="15" t="inlineStr">
         <is>
-          <t>yeo-sa-chin</t>
+          <t>ja-man-chu</t>
         </is>
       </c>
       <c r="D702" s="15" t="inlineStr">
@@ -68769,62 +68769,62 @@
       </c>
       <c r="F702" s="16" t="inlineStr">
         <is>
-          <t>Short for "female friend" — used to clarify a woman is just a friend, not a romantic interest.</t>
+          <t>Short for "seeking a natural meeting" — wanting to meet a partner organically rather than through a setup.</t>
         </is>
       </c>
       <c r="G702" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "amiga mujer": se usa para aclarar que una mujer es solo una amiga, no un interés romántico.</t>
+          <t>Abreviatura de "buscar un encuentro natural": querer conocer a una pareja de forma orgánica en lugar de por una cita arreglada.</t>
         </is>
       </c>
       <c r="H702" s="16" t="inlineStr">
         <is>
-          <t>「女性朋友」的簡稱——用來澄清某位女性只是朋友、並非戀愛對象。</t>
+          <t>「追求自然相遇」的簡稱——希望自然而然認識對象，而非透過相親介紹。</t>
         </is>
       </c>
       <c r="I702" s="16" t="inlineStr">
         <is>
-          <t>“女性朋友”的简称——用来澄清某位女性只是朋友、并非恋爱对象。</t>
+          <t>“追求自然相遇”的简称——希望自然而然认识对象，而非通过相亲介绍。</t>
         </is>
       </c>
       <c r="J702" s="16" t="inlineStr">
         <is>
-          <t>「女性の友達」の略——恋愛対象ではなく、ただの友達であることを明確にする時に使う。</t>
+          <t>「自然な出会いを求める」の略——紹介ではなく、自然に相手と出会いたいという願望。</t>
         </is>
       </c>
       <c r="K702" s="16" t="inlineStr">
         <is>
-          <t>그냥 여사친이야, 오해하지 마.</t>
+          <t>나는 자만추 스타일이라 소개팅은 안 해.</t>
         </is>
       </c>
       <c r="L702" s="16" t="inlineStr">
         <is>
-          <t>She's just a female friend, don't get the wrong idea.</t>
+          <t>I'm the natural-encounter type, so I don't do blind dates.</t>
         </is>
       </c>
       <c r="M702" s="16" t="inlineStr">
         <is>
-          <t>Es solo mi amiga, no te confundas.</t>
+          <t>Soy del tipo que prefiere encuentros naturales, así que no hago citas a ciegas.</t>
         </is>
       </c>
       <c r="N702" s="16" t="inlineStr">
         <is>
-          <t>只是女性朋友而已，別誤會。</t>
+          <t>我是喜歡自然認識的類型，不太相親。</t>
         </is>
       </c>
       <c r="O702" s="16" t="inlineStr">
         <is>
-          <t>只是女性朋友而已，别误会。</t>
+          <t>我是喜欢自然认识的类型，不太相亲。</t>
         </is>
       </c>
       <c r="P702" s="16" t="inlineStr">
         <is>
-          <t>ただの女友達だよ、誤解しないで。</t>
+          <t>私は自然な出会い派だから、合コンはしない。</t>
         </is>
       </c>
       <c r="Q702" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship clarifications</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R702" s="15" t="inlineStr">
@@ -68841,17 +68841,17 @@
     <row r="703" ht="46" customHeight="1">
       <c r="A703" s="15" t="inlineStr">
         <is>
-          <t>DAT-026</t>
+          <t>DAT-025</t>
         </is>
       </c>
       <c r="B703" s="15" t="inlineStr">
         <is>
-          <t>남사친</t>
+          <t>여사친</t>
         </is>
       </c>
       <c r="C703" s="15" t="inlineStr">
         <is>
-          <t>nam-sa-chin</t>
+          <t>yeo-sa-chin</t>
         </is>
       </c>
       <c r="D703" s="15" t="inlineStr">
@@ -68866,57 +68866,57 @@
       </c>
       <c r="F703" s="16" t="inlineStr">
         <is>
-          <t>Short for "male friend" — used to clarify a man is just a friend, not a romantic interest.</t>
+          <t>Short for "female friend" — used to clarify a woman is just a friend, not a romantic interest.</t>
         </is>
       </c>
       <c r="G703" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "amigo hombre": se usa para aclarar que un hombre es solo un amigo, no un interés romántico.</t>
+          <t>Abreviatura de "amiga mujer": se usa para aclarar que una mujer es solo una amiga, no un interés romántico.</t>
         </is>
       </c>
       <c r="H703" s="16" t="inlineStr">
         <is>
-          <t>「男性朋友」的簡稱——用來澄清某位男性只是朋友、並非戀愛對象。</t>
+          <t>「女性朋友」的簡稱——用來澄清某位女性只是朋友、並非戀愛對象。</t>
         </is>
       </c>
       <c r="I703" s="16" t="inlineStr">
         <is>
-          <t>“男性朋友”的简称——用来澄清某位男性只是朋友、并非恋爱对象。</t>
+          <t>“女性朋友”的简称——用来澄清某位女性只是朋友、并非恋爱对象。</t>
         </is>
       </c>
       <c r="J703" s="16" t="inlineStr">
         <is>
-          <t>「男性の友達」の略——恋愛対象ではなく、ただの友達であることを明確にする時に使う。</t>
+          <t>「女性の友達」の略——恋愛対象ではなく、ただの友達であることを明確にする時に使う。</t>
         </is>
       </c>
       <c r="K703" s="16" t="inlineStr">
         <is>
-          <t>남사친이랑 영화 보러 갔어.</t>
+          <t>그냥 여사친이야, 오해하지 마.</t>
         </is>
       </c>
       <c r="L703" s="16" t="inlineStr">
         <is>
-          <t>I went to see a movie with my guy friend.</t>
+          <t>She's just a female friend, don't get the wrong idea.</t>
         </is>
       </c>
       <c r="M703" s="16" t="inlineStr">
         <is>
-          <t>Fui al cine con mi amigo (no es nada romántico).</t>
+          <t>Es solo mi amiga, no te confundas.</t>
         </is>
       </c>
       <c r="N703" s="16" t="inlineStr">
         <is>
-          <t>跟男性朋友去看電影了。</t>
+          <t>只是女性朋友而已，別誤會。</t>
         </is>
       </c>
       <c r="O703" s="16" t="inlineStr">
         <is>
-          <t>跟男性朋友去看电影了。</t>
+          <t>只是女性朋友而已，别误会。</t>
         </is>
       </c>
       <c r="P703" s="16" t="inlineStr">
         <is>
-          <t>男友達と映画見に行った。</t>
+          <t>ただの女友達だよ、誤解しないで。</t>
         </is>
       </c>
       <c r="Q703" s="16" t="inlineStr">
@@ -68938,17 +68938,17 @@
     <row r="704" ht="46" customHeight="1">
       <c r="A704" s="15" t="inlineStr">
         <is>
-          <t>DAT-027</t>
+          <t>DAT-026</t>
         </is>
       </c>
       <c r="B704" s="15" t="inlineStr">
         <is>
-          <t>애칭</t>
+          <t>남사친</t>
         </is>
       </c>
       <c r="C704" s="15" t="inlineStr">
         <is>
-          <t>ae-ching</t>
+          <t>nam-sa-chin</t>
         </is>
       </c>
       <c r="D704" s="15" t="inlineStr">
@@ -68963,62 +68963,62 @@
       </c>
       <c r="F704" s="16" t="inlineStr">
         <is>
-          <t>A cute nickname used between romantic partners.</t>
+          <t>Short for "male friend" — used to clarify a man is just a friend, not a romantic interest.</t>
         </is>
       </c>
       <c r="G704" s="16" t="inlineStr">
         <is>
-          <t>Un apodo tierno usado entre parejas románticas.</t>
+          <t>Abreviatura de "amigo hombre": se usa para aclarar que un hombre es solo un amigo, no un interés romántico.</t>
         </is>
       </c>
       <c r="H704" s="16" t="inlineStr">
         <is>
-          <t>情侶之間使用的可愛暱稱。</t>
+          <t>「男性朋友」的簡稱——用來澄清某位男性只是朋友、並非戀愛對象。</t>
         </is>
       </c>
       <c r="I704" s="16" t="inlineStr">
         <is>
-          <t>情侣之间使用的可爱暱称。</t>
+          <t>“男性朋友”的简称——用来澄清某位男性只是朋友、并非恋爱对象。</t>
         </is>
       </c>
       <c r="J704" s="16" t="inlineStr">
         <is>
-          <t>恋人同士で使う可愛いニックネーム。</t>
+          <t>「男性の友達」の略——恋愛対象ではなく、ただの友達であることを明確にする時に使う。</t>
         </is>
       </c>
       <c r="K704" s="16" t="inlineStr">
         <is>
-          <t>둘이 애칭까지 있는 거 보니 진짜 사귀나 봐.</t>
+          <t>남사친이랑 영화 보러 갔어.</t>
         </is>
       </c>
       <c r="L704" s="16" t="inlineStr">
         <is>
-          <t>Seeing they even have pet names for each other, they must really be dating.</t>
+          <t>I went to see a movie with my guy friend.</t>
         </is>
       </c>
       <c r="M704" s="16" t="inlineStr">
         <is>
-          <t>Al ver que tienen apodos cariñosos entre ellos, seguro que sí están saliendo.</t>
+          <t>Fui al cine con mi amigo (no es nada romántico).</t>
         </is>
       </c>
       <c r="N704" s="16" t="inlineStr">
         <is>
-          <t>看到兩個人連暱稱都有了，看來真的在交往。</t>
+          <t>跟男性朋友去看電影了。</t>
         </is>
       </c>
       <c r="O704" s="16" t="inlineStr">
         <is>
-          <t>看到两个人连暱称都有了，看来真的在交往。</t>
+          <t>跟男性朋友去看电影了。</t>
         </is>
       </c>
       <c r="P704" s="16" t="inlineStr">
         <is>
-          <t>二人とも愛称まであるなんて、本当に付き合ってるみたいだね。</t>
+          <t>男友達と映画見に行った。</t>
         </is>
       </c>
       <c r="Q704" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, dramas</t>
+          <t>Casual relationship clarifications</t>
         </is>
       </c>
       <c r="R704" s="15" t="inlineStr">
@@ -69035,17 +69035,17 @@
     <row r="705" ht="46" customHeight="1">
       <c r="A705" s="15" t="inlineStr">
         <is>
-          <t>DAT-028</t>
+          <t>DAT-027</t>
         </is>
       </c>
       <c r="B705" s="15" t="inlineStr">
         <is>
-          <t>럽스타그램</t>
+          <t>애칭</t>
         </is>
       </c>
       <c r="C705" s="15" t="inlineStr">
         <is>
-          <t>leob-seu-ta-geu-raem</t>
+          <t>ae-ching</t>
         </is>
       </c>
       <c r="D705" s="15" t="inlineStr">
@@ -69060,62 +69060,62 @@
       </c>
       <c r="F705" s="16" t="inlineStr">
         <is>
-          <t>"Love + Instagram" — social media posts where a couple shows off their relationship.</t>
+          <t>A cute nickname used between romantic partners.</t>
         </is>
       </c>
       <c r="G705" s="16" t="inlineStr">
         <is>
-          <t>"Amor + Instagram": publicaciones en redes sociales donde una pareja muestra su relación.</t>
+          <t>Un apodo tierno usado entre parejas románticas.</t>
         </is>
       </c>
       <c r="H705" s="16" t="inlineStr">
         <is>
-          <t>「愛情＋Instagram」——情侶在社群媒體上曬恩愛的貼文。</t>
+          <t>情侶之間使用的可愛暱稱。</t>
         </is>
       </c>
       <c r="I705" s="16" t="inlineStr">
         <is>
-          <t>“爱情＋Instagram”——情侣在社群媒体上晒恩爱的贴文。</t>
+          <t>情侣之间使用的可爱暱称。</t>
         </is>
       </c>
       <c r="J705" s="16" t="inlineStr">
         <is>
-          <t>「愛＋Instagram」——カップルが交際をアピールするSNS投稿。</t>
+          <t>恋人同士で使う可愛いニックネーム。</t>
         </is>
       </c>
       <c r="K705" s="16" t="inlineStr">
         <is>
-          <t>럽스타그램 보니까 진짜 좋아 보인다.</t>
+          <t>둘이 애칭까지 있는 거 보니 진짜 사귀나 봐.</t>
         </is>
       </c>
       <c r="L705" s="16" t="inlineStr">
         <is>
-          <t>Seeing their couple posts, they really look happy together.</t>
+          <t>Seeing they even have pet names for each other, they must really be dating.</t>
         </is>
       </c>
       <c r="M705" s="16" t="inlineStr">
         <is>
-          <t>Al ver sus publicaciones de pareja, de verdad se ven felices juntos.</t>
+          <t>Al ver que tienen apodos cariñosos entre ellos, seguro que sí están saliendo.</t>
         </is>
       </c>
       <c r="N705" s="16" t="inlineStr">
         <is>
-          <t>看他們曬恩愛，感覺真的很幸福。</t>
+          <t>看到兩個人連暱稱都有了，看來真的在交往。</t>
         </is>
       </c>
       <c r="O705" s="16" t="inlineStr">
         <is>
-          <t>看他们晒恩爱，感觉真的很幸福。</t>
+          <t>看到两个人连暱称都有了，看来真的在交往。</t>
         </is>
       </c>
       <c r="P705" s="16" t="inlineStr">
         <is>
-          <t>ラブグラム見てたら、本当に幸せそうだった。</t>
+          <t>二人とも愛称まであるなんて、本当に付き合ってるみたいだね。</t>
         </is>
       </c>
       <c r="Q705" s="16" t="inlineStr">
         <is>
-          <t>Instagram couple culture</t>
+          <t>Couple culture, dramas</t>
         </is>
       </c>
       <c r="R705" s="15" t="inlineStr">
@@ -69132,17 +69132,17 @@
     <row r="706" ht="46" customHeight="1">
       <c r="A706" s="15" t="inlineStr">
         <is>
-          <t>DAT-029</t>
+          <t>DAT-028</t>
         </is>
       </c>
       <c r="B706" s="15" t="inlineStr">
         <is>
-          <t>캔디</t>
+          <t>럽스타그램</t>
         </is>
       </c>
       <c r="C706" s="15" t="inlineStr">
         <is>
-          <t>kaen-di</t>
+          <t>leob-seu-ta-geu-raem</t>
         </is>
       </c>
       <c r="D706" s="15" t="inlineStr">
@@ -69157,62 +69157,62 @@
       </c>
       <c r="F706" s="16" t="inlineStr">
         <is>
-          <t>A plucky, resilient, kind female lead trope who stays positive despite hardship, named after the classic character Candy Candy.</t>
+          <t>"Love + Instagram" — social media posts where a couple shows off their relationship.</t>
         </is>
       </c>
       <c r="G706" s="16" t="inlineStr">
         <is>
-          <t>Un arquetipo de protagonista femenina animosa, resiliente y bondadosa que se mantiene positiva a pesar de las dificultades, en honor al clásico personaje Candy Candy.</t>
+          <t>"Amor + Instagram": publicaciones en redes sociales donde una pareja muestra su relación.</t>
         </is>
       </c>
       <c r="H706" s="16" t="inlineStr">
         <is>
-          <t>堅強樂觀、即使歷經困境仍保持正向的女主角類型，源自經典角色《小甜甜》。</t>
+          <t>「愛情＋Instagram」——情侶在社群媒體上曬恩愛的貼文。</t>
         </is>
       </c>
       <c r="I706" s="16" t="inlineStr">
         <is>
-          <t>坚强乐观、即使历经困境仍保持正向的女主角类型，源自经典角色《小甜甜》。</t>
+          <t>“爱情＋Instagram”——情侣在社群媒体上晒恩爱的贴文。</t>
         </is>
       </c>
       <c r="J706" s="16" t="inlineStr">
         <is>
-          <t>逆境にもめげず前向きな、芯の強いヒロインのトロープ——古典キャラクター「キャンディキャンディ」に由来。</t>
+          <t>「愛＋Instagram」——カップルが交際をアピールするSNS投稿。</t>
         </is>
       </c>
       <c r="K706" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 여주 완전 캔디형이야.</t>
+          <t>럽스타그램 보니까 진짜 좋아 보인다.</t>
         </is>
       </c>
       <c r="L706" s="16" t="inlineStr">
         <is>
-          <t>This drama's female lead is a total Candy-type heroine.</t>
+          <t>Seeing their couple posts, they really look happy together.</t>
         </is>
       </c>
       <c r="M706" s="16" t="inlineStr">
         <is>
-          <t>La protagonista de este drama es totalmente del tipo Candy.</t>
+          <t>Al ver sus publicaciones de pareja, de verdad se ven felices juntos.</t>
         </is>
       </c>
       <c r="N706" s="16" t="inlineStr">
         <is>
-          <t>這部劇女主角完全是小甜甜類型。</t>
+          <t>看他們曬恩愛，感覺真的很幸福。</t>
         </is>
       </c>
       <c r="O706" s="16" t="inlineStr">
         <is>
-          <t>这部剧女主角完全是小甜甜类型。</t>
+          <t>看他们晒恩爱，感觉真的很幸福。</t>
         </is>
       </c>
       <c r="P706" s="16" t="inlineStr">
         <is>
-          <t>このドラマのヒロイン、完全にキャンディ型だよね。</t>
+          <t>ラブグラム見てたら、本当に幸せそうだった。</t>
         </is>
       </c>
       <c r="Q706" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>Instagram couple culture</t>
         </is>
       </c>
       <c r="R706" s="15" t="inlineStr">
@@ -69229,17 +69229,17 @@
     <row r="707" ht="46" customHeight="1">
       <c r="A707" s="15" t="inlineStr">
         <is>
-          <t>DAT-030</t>
+          <t>DAT-029</t>
         </is>
       </c>
       <c r="B707" s="15" t="inlineStr">
         <is>
-          <t>출생의 비밀</t>
+          <t>캔디</t>
         </is>
       </c>
       <c r="C707" s="15" t="inlineStr">
         <is>
-          <t>chul-saeng-ui bi-mil</t>
+          <t>kaen-di</t>
         </is>
       </c>
       <c r="D707" s="15" t="inlineStr">
@@ -69254,57 +69254,57 @@
       </c>
       <c r="F707" s="16" t="inlineStr">
         <is>
-          <t>A classic K-drama plot device where a character's true parentage or origin is secretly hidden and later revealed.</t>
+          <t>A plucky, resilient, kind female lead trope who stays positive despite hardship, named after the classic character Candy Candy.</t>
         </is>
       </c>
       <c r="G707" s="16" t="inlineStr">
         <is>
-          <t>Un clásico recurso argumental de los K-dramas donde el verdadero origen o parentesco de un personaje se oculta en secreto y se revela después.</t>
+          <t>Un arquetipo de protagonista femenina animosa, resiliente y bondadosa que se mantiene positiva a pesar de las dificultades, en honor al clásico personaje Candy Candy.</t>
         </is>
       </c>
       <c r="H707" s="16" t="inlineStr">
         <is>
-          <t>韓劇經典劇情套路——角色真實身世或血緣被隱藏、後來才揭曉的設定，出生之謎。</t>
+          <t>堅強樂觀、即使歷經困境仍保持正向的女主角類型，源自經典角色《小甜甜》。</t>
         </is>
       </c>
       <c r="I707" s="16" t="inlineStr">
         <is>
-          <t>韩剧经典剧情套路——角色真实身世或血缘被隐藏、后来才揭晓的设置，出生之谜。</t>
+          <t>坚强乐观、即使历经困境仍保持正向的女主角类型，源自经典角色《小甜甜》。</t>
         </is>
       </c>
       <c r="J707" s="16" t="inlineStr">
         <is>
-          <t>韓国ドラマの定番展開で、キャラクターの本当の親や出自が隠されていて、後で明かされるというもの。</t>
+          <t>逆境にもめげず前向きな、芯の強いヒロインのトロープ——古典キャラクター「キャンディキャンディ」に由来。</t>
         </is>
       </c>
       <c r="K707" s="16" t="inlineStr">
         <is>
-          <t>이 드라마도 결국 출생의 비밀이 나왔어.</t>
+          <t>이 드라마 여주 완전 캔디형이야.</t>
         </is>
       </c>
       <c r="L707" s="16" t="inlineStr">
         <is>
-          <t>This drama ended up having a secret-birth twist too.</t>
+          <t>This drama's female lead is a total Candy-type heroine.</t>
         </is>
       </c>
       <c r="M707" s="16" t="inlineStr">
         <is>
-          <t>Este drama también terminó teniendo el giro del secreto de nacimiento.</t>
+          <t>La protagonista de este drama es totalmente del tipo Candy.</t>
         </is>
       </c>
       <c r="N707" s="16" t="inlineStr">
         <is>
-          <t>這部劇最後也出現了出生之謎的劇情。</t>
+          <t>這部劇女主角完全是小甜甜類型。</t>
         </is>
       </c>
       <c r="O707" s="16" t="inlineStr">
         <is>
-          <t>这部剧最后也出现了出生之谜的剧情。</t>
+          <t>这部剧女主角完全是小甜甜类型。</t>
         </is>
       </c>
       <c r="P707" s="16" t="inlineStr">
         <is>
-          <t>このドラマも結局出生の秘密が出てきた。</t>
+          <t>このドラマのヒロイン、完全にキャンディ型だよね。</t>
         </is>
       </c>
       <c r="Q707" s="16" t="inlineStr">
@@ -69326,17 +69326,17 @@
     <row r="708" ht="46" customHeight="1">
       <c r="A708" s="15" t="inlineStr">
         <is>
-          <t>DAT-031</t>
+          <t>DAT-030</t>
         </is>
       </c>
       <c r="B708" s="15" t="inlineStr">
         <is>
-          <t>고부갈등</t>
+          <t>출생의 비밀</t>
         </is>
       </c>
       <c r="C708" s="15" t="inlineStr">
         <is>
-          <t>go-bu-gal-deung</t>
+          <t>chul-saeng-ui bi-mil</t>
         </is>
       </c>
       <c r="D708" s="15" t="inlineStr">
@@ -69351,57 +69351,57 @@
       </c>
       <c r="F708" s="16" t="inlineStr">
         <is>
-          <t>Tension and conflict between a wife and her mother-in-law, a very common drama theme.</t>
+          <t>A classic K-drama plot device where a character's true parentage or origin is secretly hidden and later revealed.</t>
         </is>
       </c>
       <c r="G708" s="16" t="inlineStr">
         <is>
-          <t>Tensión y conflicto entre una esposa y su suegra, un tema muy común en los dramas.</t>
+          <t>Un clásico recurso argumental de los K-dramas donde el verdadero origen o parentesco de un personaje se oculta en secreto y se revela después.</t>
         </is>
       </c>
       <c r="H708" s="16" t="inlineStr">
         <is>
-          <t>妻子與婆婆之間的緊張與衝突，是韓劇非常常見的題材，婆媳問題。</t>
+          <t>韓劇經典劇情套路——角色真實身世或血緣被隱藏、後來才揭曉的設定，出生之謎。</t>
         </is>
       </c>
       <c r="I708" s="16" t="inlineStr">
         <is>
-          <t>妻子与婆婆之间的紧张与冲突，是韩剧非常常见的题材，婆媳问题。</t>
+          <t>韩剧经典剧情套路——角色真实身世或血缘被隐藏、后来才揭晓的设置，出生之谜。</t>
         </is>
       </c>
       <c r="J708" s="16" t="inlineStr">
         <is>
-          <t>妻と姑の間の緊張と対立——ドラマの非常によくあるテーマ。</t>
+          <t>韓国ドラマの定番展開で、キャラクターの本当の親や出自が隠されていて、後で明かされるというもの。</t>
         </is>
       </c>
       <c r="K708" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 고부갈등이 너무 스트레스야.</t>
+          <t>이 드라마도 결국 출생의 비밀이 나왔어.</t>
         </is>
       </c>
       <c r="L708" s="16" t="inlineStr">
         <is>
-          <t>This drama's mother-in-law conflict is so stressful to watch.</t>
+          <t>This drama ended up having a secret-birth twist too.</t>
         </is>
       </c>
       <c r="M708" s="16" t="inlineStr">
         <is>
-          <t>El conflicto con la suegra en este drama da mucho estrés de ver.</t>
+          <t>Este drama también terminó teniendo el giro del secreto de nacimiento.</t>
         </is>
       </c>
       <c r="N708" s="16" t="inlineStr">
         <is>
-          <t>這部劇的婆媳問題看得好有壓力。</t>
+          <t>這部劇最後也出現了出生之謎的劇情。</t>
         </is>
       </c>
       <c r="O708" s="16" t="inlineStr">
         <is>
-          <t>这部剧的婆媳问题看得好有压力。</t>
+          <t>这部剧最后也出现了出生之谜的剧情。</t>
         </is>
       </c>
       <c r="P708" s="16" t="inlineStr">
         <is>
-          <t>このドラマの嫁姑問題、見てて本当にストレス溜まる。</t>
+          <t>このドラマも結局出生の秘密が出てきた。</t>
         </is>
       </c>
       <c r="Q708" s="16" t="inlineStr">
@@ -69423,17 +69423,17 @@
     <row r="709" ht="46" customHeight="1">
       <c r="A709" s="15" t="inlineStr">
         <is>
-          <t>DAT-032</t>
+          <t>DAT-031</t>
         </is>
       </c>
       <c r="B709" s="15" t="inlineStr">
         <is>
-          <t>삼각관계</t>
+          <t>고부갈등</t>
         </is>
       </c>
       <c r="C709" s="15" t="inlineStr">
         <is>
-          <t>sam-gak-gwan-gye</t>
+          <t>go-bu-gal-deung</t>
         </is>
       </c>
       <c r="D709" s="15" t="inlineStr">
@@ -69448,57 +69448,57 @@
       </c>
       <c r="F709" s="16" t="inlineStr">
         <is>
-          <t>A romantic storyline involving three people with overlapping feelings for each other.</t>
+          <t>Tension and conflict between a wife and her mother-in-law, a very common drama theme.</t>
         </is>
       </c>
       <c r="G709" s="16" t="inlineStr">
         <is>
-          <t>Una trama romántica que involucra a tres personas con sentimientos cruzados entre ellas.</t>
+          <t>Tensión y conflicto entre una esposa y su suegra, un tema muy común en los dramas.</t>
         </is>
       </c>
       <c r="H709" s="16" t="inlineStr">
         <is>
-          <t>三個人之間互有情愫、糾葛交織的戀愛劇情，三角關係。</t>
+          <t>妻子與婆婆之間的緊張與衝突，是韓劇非常常見的題材，婆媳問題。</t>
         </is>
       </c>
       <c r="I709" s="16" t="inlineStr">
         <is>
-          <t>三个人之间互有情愫、纠葛交织的恋爱剧情，三角关系。</t>
+          <t>妻子与婆婆之间的紧张与冲突，是韩剧非常常见的题材，婆媳问题。</t>
         </is>
       </c>
       <c r="J709" s="16" t="inlineStr">
         <is>
-          <t>三人が互いに感情を抱き合う恋愛ストーリーライン。</t>
+          <t>妻と姑の間の緊張と対立——ドラマの非常によくあるテーマ。</t>
         </is>
       </c>
       <c r="K709" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 삼각관계 너무 답답해.</t>
+          <t>이 드라마 고부갈등이 너무 스트레스야.</t>
         </is>
       </c>
       <c r="L709" s="16" t="inlineStr">
         <is>
-          <t>This drama's love triangle is so frustrating.</t>
+          <t>This drama's mother-in-law conflict is so stressful to watch.</t>
         </is>
       </c>
       <c r="M709" s="16" t="inlineStr">
         <is>
-          <t>El triángulo amoroso de este drama es muy frustrante.</t>
+          <t>El conflicto con la suegra en este drama da mucho estrés de ver.</t>
         </is>
       </c>
       <c r="N709" s="16" t="inlineStr">
         <is>
-          <t>這部劇的三角關係讓人好鬱悶。</t>
+          <t>這部劇的婆媳問題看得好有壓力。</t>
         </is>
       </c>
       <c r="O709" s="16" t="inlineStr">
         <is>
-          <t>这部剧的三角关系让人好郁闷。</t>
+          <t>这部剧的婆媳问题看得好有压力。</t>
         </is>
       </c>
       <c r="P709" s="16" t="inlineStr">
         <is>
-          <t>このドラマの三角関係、本当にもどかしい。</t>
+          <t>このドラマの嫁姑問題、見てて本当にストレス溜まる。</t>
         </is>
       </c>
       <c r="Q709" s="16" t="inlineStr">
@@ -69520,17 +69520,17 @@
     <row r="710" ht="46" customHeight="1">
       <c r="A710" s="15" t="inlineStr">
         <is>
-          <t>DAT-033</t>
+          <t>DAT-032</t>
         </is>
       </c>
       <c r="B710" s="15" t="inlineStr">
         <is>
-          <t>시한부</t>
+          <t>삼각관계</t>
         </is>
       </c>
       <c r="C710" s="15" t="inlineStr">
         <is>
-          <t>si-han-bu</t>
+          <t>sam-gak-gwan-gye</t>
         </is>
       </c>
       <c r="D710" s="15" t="inlineStr">
@@ -69545,57 +69545,57 @@
       </c>
       <c r="F710" s="16" t="inlineStr">
         <is>
-          <t>A drama plot device where a character has a terminal illness, often driving the emotional storyline.</t>
+          <t>A romantic storyline involving three people with overlapping feelings for each other.</t>
         </is>
       </c>
       <c r="G710" s="16" t="inlineStr">
         <is>
-          <t>Un recurso argumental donde un personaje tiene una enfermedad terminal, a menudo impulsando la trama emocional.</t>
+          <t>Una trama romántica que involucra a tres personas con sentimientos cruzados entre ellas.</t>
         </is>
       </c>
       <c r="H710" s="16" t="inlineStr">
         <is>
-          <t>角色罹患絕症的劇情設定，常用來推動情感張力，絕症設定。</t>
+          <t>三個人之間互有情愫、糾葛交織的戀愛劇情，三角關係。</t>
         </is>
       </c>
       <c r="I710" s="16" t="inlineStr">
         <is>
-          <t>角色罹患绝症的剧情设置，常用来推动情感张力，绝症设置。</t>
+          <t>三个人之间互有情愫、纠葛交织的恋爱剧情，三角关系。</t>
         </is>
       </c>
       <c r="J710" s="16" t="inlineStr">
         <is>
-          <t>キャラクターが不治の病を患うドラマの設定で、感情的なストーリーラインを引っ張ることが多い。</t>
+          <t>三人が互いに感情を抱き合う恋愛ストーリーライン。</t>
         </is>
       </c>
       <c r="K710" s="16" t="inlineStr">
         <is>
-          <t>시한부 설정인 거 알고 나서 더 슬프게 봤어.</t>
+          <t>이 드라마 삼각관계 너무 답답해.</t>
         </is>
       </c>
       <c r="L710" s="16" t="inlineStr">
         <is>
-          <t>Once I found out about the terminal illness twist, I watched it even more sadly.</t>
+          <t>This drama's love triangle is so frustrating.</t>
         </is>
       </c>
       <c r="M710" s="16" t="inlineStr">
         <is>
-          <t>Después de saber del giro de la enfermedad terminal, lo vi con más tristeza.</t>
+          <t>El triángulo amoroso de este drama es muy frustrante.</t>
         </is>
       </c>
       <c r="N710" s="16" t="inlineStr">
         <is>
-          <t>知道是絕症設定之後看得更難過了。</t>
+          <t>這部劇的三角關係讓人好鬱悶。</t>
         </is>
       </c>
       <c r="O710" s="16" t="inlineStr">
         <is>
-          <t>知道是绝症设置之后看得更难过了。</t>
+          <t>这部剧的三角关系让人好郁闷。</t>
         </is>
       </c>
       <c r="P710" s="16" t="inlineStr">
         <is>
-          <t>余命宣告の設定だと知ってから、もっと悲しく見てしまった。</t>
+          <t>このドラマの三角関係、本当にもどかしい。</t>
         </is>
       </c>
       <c r="Q710" s="16" t="inlineStr">
@@ -69617,17 +69617,17 @@
     <row r="711" ht="46" customHeight="1">
       <c r="A711" s="15" t="inlineStr">
         <is>
-          <t>DAT-034</t>
+          <t>DAT-033</t>
         </is>
       </c>
       <c r="B711" s="15" t="inlineStr">
         <is>
-          <t>정략결혼</t>
+          <t>시한부</t>
         </is>
       </c>
       <c r="C711" s="15" t="inlineStr">
         <is>
-          <t>jeong-ryak-gyeol-hon</t>
+          <t>si-han-bu</t>
         </is>
       </c>
       <c r="D711" s="15" t="inlineStr">
@@ -69642,57 +69642,57 @@
       </c>
       <c r="F711" s="16" t="inlineStr">
         <is>
-          <t>A marriage arranged for business, family, or political reasons rather than love — a common drama setup.</t>
+          <t>A drama plot device where a character has a terminal illness, often driving the emotional storyline.</t>
         </is>
       </c>
       <c r="G711" s="16" t="inlineStr">
         <is>
-          <t>Un matrimonio arreglado por razones de negocios, familia o política en lugar de amor; un montaje común en los dramas.</t>
+          <t>Un recurso argumental donde un personaje tiene una enfermedad terminal, a menudo impulsando la trama emocional.</t>
         </is>
       </c>
       <c r="H711" s="16" t="inlineStr">
         <is>
-          <t>因商業、家族或政治因素而非愛情所安排的婚姻，是韓劇常見的設定，利益聯姻。</t>
+          <t>角色罹患絕症的劇情設定，常用來推動情感張力，絕症設定。</t>
         </is>
       </c>
       <c r="I711" s="16" t="inlineStr">
         <is>
-          <t>因商业、家族或政治因素而非爱情所安排的婚姻，是韩剧常见的设置，利益联姻。</t>
+          <t>角色罹患绝症的剧情设置，常用来推动情感张力，绝症设置。</t>
         </is>
       </c>
       <c r="J711" s="16" t="inlineStr">
         <is>
-          <t>恋愛ではなく、ビジネスや家族、政治的な理由で決められた結婚——ドラマによくある設定。</t>
+          <t>キャラクターが不治の病を患うドラマの設定で、感情的なストーリーラインを引っ張ることが多い。</t>
         </is>
       </c>
       <c r="K711" s="16" t="inlineStr">
         <is>
-          <t>정략결혼으로 시작했는데 진짜 사랑에 빠졌어.</t>
+          <t>시한부 설정인 거 알고 나서 더 슬프게 봤어.</t>
         </is>
       </c>
       <c r="L711" s="16" t="inlineStr">
         <is>
-          <t>It started as an arranged marriage, but they really fell in love.</t>
+          <t>Once I found out about the terminal illness twist, I watched it even more sadly.</t>
         </is>
       </c>
       <c r="M711" s="16" t="inlineStr">
         <is>
-          <t>Empezó como un matrimonio arreglado, pero de verdad se enamoraron.</t>
+          <t>Después de saber del giro de la enfermedad terminal, lo vi con más tristeza.</t>
         </is>
       </c>
       <c r="N711" s="16" t="inlineStr">
         <is>
-          <t>雖然是利益聯姻開始的，但真的墜入愛河了。</t>
+          <t>知道是絕症設定之後看得更難過了。</t>
         </is>
       </c>
       <c r="O711" s="16" t="inlineStr">
         <is>
-          <t>虽然是利益联姻开始的，但真的坠入爱河了。</t>
+          <t>知道是绝症设置之后看得更难过了。</t>
         </is>
       </c>
       <c r="P711" s="16" t="inlineStr">
         <is>
-          <t>政略結婚で始まったのに、本当に恋に落ちた。</t>
+          <t>余命宣告の設定だと知ってから、もっと悲しく見てしまった。</t>
         </is>
       </c>
       <c r="Q711" s="16" t="inlineStr">
@@ -69714,17 +69714,17 @@
     <row r="712" ht="46" customHeight="1">
       <c r="A712" s="15" t="inlineStr">
         <is>
-          <t>DAT-035</t>
+          <t>DAT-034</t>
         </is>
       </c>
       <c r="B712" s="15" t="inlineStr">
         <is>
-          <t>신데렐라</t>
+          <t>정략결혼</t>
         </is>
       </c>
       <c r="C712" s="15" t="inlineStr">
         <is>
-          <t>sin-de-rel-la</t>
+          <t>jeong-ryak-gyeol-hon</t>
         </is>
       </c>
       <c r="D712" s="15" t="inlineStr">
@@ -69739,57 +69739,57 @@
       </c>
       <c r="F712" s="16" t="inlineStr">
         <is>
-          <t>A story trope where an ordinary or poor character rises into a wealthy or elite world, often through romance.</t>
+          <t>A marriage arranged for business, family, or political reasons rather than love — a common drama setup.</t>
         </is>
       </c>
       <c r="G712" s="16" t="inlineStr">
         <is>
-          <t>Un arquetipo narrativo donde un personaje común o pobre asciende a un mundo rico o de élite, a menudo a través del romance.</t>
+          <t>Un matrimonio arreglado por razones de negocios, familia o política en lugar de amor; un montaje común en los dramas.</t>
         </is>
       </c>
       <c r="H712" s="16" t="inlineStr">
         <is>
-          <t>平凡或貧窮的角色透過戀愛躍升進入富裕上流世界的劇情套路，灰姑娘故事。</t>
+          <t>因商業、家族或政治因素而非愛情所安排的婚姻，是韓劇常見的設定，利益聯姻。</t>
         </is>
       </c>
       <c r="I712" s="16" t="inlineStr">
         <is>
-          <t>平凡或贫穷的角色通过恋爱跃升进入富裕上流世界的剧情套路，灰姑娘故事。</t>
+          <t>因商业、家族或政治因素而非爱情所安排的婚姻，是韩剧常见的设置，利益联姻。</t>
         </is>
       </c>
       <c r="J712" s="16" t="inlineStr">
         <is>
-          <t>平凡または貧しいキャラクターが、恋愛を通じて裕福またはエリートの世界に上り詰めるストーリートロープ。</t>
+          <t>恋愛ではなく、ビジネスや家族、政治的な理由で決められた結婚——ドラマによくある設定。</t>
         </is>
       </c>
       <c r="K712" s="16" t="inlineStr">
         <is>
-          <t>완전 신데렐라 스토리다.</t>
+          <t>정략결혼으로 시작했는데 진짜 사랑에 빠졌어.</t>
         </is>
       </c>
       <c r="L712" s="16" t="inlineStr">
         <is>
-          <t>It's a total Cinderella story.</t>
+          <t>It started as an arranged marriage, but they really fell in love.</t>
         </is>
       </c>
       <c r="M712" s="16" t="inlineStr">
         <is>
-          <t>Es una historia de Cenicienta total.</t>
+          <t>Empezó como un matrimonio arreglado, pero de verdad se enamoraron.</t>
         </is>
       </c>
       <c r="N712" s="16" t="inlineStr">
         <is>
-          <t>完全是灰姑娘的故事。</t>
+          <t>雖然是利益聯姻開始的，但真的墜入愛河了。</t>
         </is>
       </c>
       <c r="O712" s="16" t="inlineStr">
         <is>
-          <t>完全是灰姑娘的故事。</t>
+          <t>虽然是利益联姻开始的，但真的坠入爱河了。</t>
         </is>
       </c>
       <c r="P712" s="16" t="inlineStr">
         <is>
-          <t>完全にシンデレラストーリーだね。</t>
+          <t>政略結婚で始まったのに、本当に恋に落ちた。</t>
         </is>
       </c>
       <c r="Q712" s="16" t="inlineStr">
@@ -69811,17 +69811,17 @@
     <row r="713" ht="46" customHeight="1">
       <c r="A713" s="15" t="inlineStr">
         <is>
-          <t>DAT-036</t>
+          <t>DAT-035</t>
         </is>
       </c>
       <c r="B713" s="15" t="inlineStr">
         <is>
-          <t>소울메이트</t>
+          <t>신데렐라</t>
         </is>
       </c>
       <c r="C713" s="15" t="inlineStr">
         <is>
-          <t>so-ul-me-i-teu</t>
+          <t>sin-de-rel-la</t>
         </is>
       </c>
       <c r="D713" s="15" t="inlineStr">
@@ -69836,62 +69836,62 @@
       </c>
       <c r="F713" s="16" t="inlineStr">
         <is>
-          <t>A person who feels like a perfect emotional match, a soulmate.</t>
+          <t>A story trope where an ordinary or poor character rises into a wealthy or elite world, often through romance.</t>
         </is>
       </c>
       <c r="G713" s="16" t="inlineStr">
         <is>
-          <t>Una persona que se siente como una pareja emocional perfecta, un alma gemela.</t>
+          <t>Un arquetipo narrativo donde un personaje común o pobre asciende a un mundo rico o de élite, a menudo a través del romance.</t>
         </is>
       </c>
       <c r="H713" s="16" t="inlineStr">
         <is>
-          <t>感覺與自己完美契合的靈魂伴侶。</t>
+          <t>平凡或貧窮的角色透過戀愛躍升進入富裕上流世界的劇情套路，灰姑娘故事。</t>
         </is>
       </c>
       <c r="I713" s="16" t="inlineStr">
         <is>
-          <t>感觉与自己完美契合的灵魂伴侣。</t>
+          <t>平凡或贫穷的角色通过恋爱跃升进入富裕上流世界的剧情套路，灰姑娘故事。</t>
         </is>
       </c>
       <c r="J713" s="16" t="inlineStr">
         <is>
-          <t>完璧な心の相性を感じさせる人——魂の伴侶。</t>
+          <t>平凡または貧しいキャラクターが、恋愛を通じて裕福またはエリートの世界に上り詰めるストーリートロープ。</t>
         </is>
       </c>
       <c r="K713" s="16" t="inlineStr">
         <is>
-          <t>둘이 완전 소울메이트 같아.</t>
+          <t>완전 신데렐라 스토리다.</t>
         </is>
       </c>
       <c r="L713" s="16" t="inlineStr">
         <is>
-          <t>Those two seem like total soulmates.</t>
+          <t>It's a total Cinderella story.</t>
         </is>
       </c>
       <c r="M713" s="16" t="inlineStr">
         <is>
-          <t>Esos dos parecen almas gemelas totales.</t>
+          <t>Es una historia de Cenicienta total.</t>
         </is>
       </c>
       <c r="N713" s="16" t="inlineStr">
         <is>
-          <t>那兩個人真的像靈魂伴侶。</t>
+          <t>完全是灰姑娘的故事。</t>
         </is>
       </c>
       <c r="O713" s="16" t="inlineStr">
         <is>
-          <t>那两个人真的像灵魂伴侣。</t>
+          <t>完全是灰姑娘的故事。</t>
         </is>
       </c>
       <c r="P713" s="16" t="inlineStr">
         <is>
-          <t>あの二人、完全にソウルメイトみたい。</t>
+          <t>完全にシンデレラストーリーだね。</t>
         </is>
       </c>
       <c r="Q713" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R713" s="15" t="inlineStr">
@@ -69908,17 +69908,17 @@
     <row r="714" ht="46" customHeight="1">
       <c r="A714" s="15" t="inlineStr">
         <is>
-          <t>DAT-037</t>
+          <t>DAT-036</t>
         </is>
       </c>
       <c r="B714" s="15" t="inlineStr">
         <is>
-          <t>이상형</t>
+          <t>소울메이트</t>
         </is>
       </c>
       <c r="C714" s="15" t="inlineStr">
         <is>
-          <t>i-sang-hyeong</t>
+          <t>so-ul-me-i-teu</t>
         </is>
       </c>
       <c r="D714" s="15" t="inlineStr">
@@ -69933,62 +69933,62 @@
       </c>
       <c r="F714" s="16" t="inlineStr">
         <is>
-          <t>A person's ideal type or preferred qualities in a romantic partner.</t>
+          <t>A person who feels like a perfect emotional match, a soulmate.</t>
         </is>
       </c>
       <c r="G714" s="16" t="inlineStr">
         <is>
-          <t>El tipo ideal o las cualidades preferidas de una persona en una pareja romántica.</t>
+          <t>Una persona que se siente como una pareja emocional perfecta, un alma gemela.</t>
         </is>
       </c>
       <c r="H714" s="16" t="inlineStr">
         <is>
-          <t>一個人心目中理想的戀愛對象條件或類型，理想型。</t>
+          <t>感覺與自己完美契合的靈魂伴侶。</t>
         </is>
       </c>
       <c r="I714" s="16" t="inlineStr">
         <is>
-          <t>一个人心目中理想的恋爱对象条件或类型，理想型。</t>
+          <t>感觉与自己完美契合的灵魂伴侣。</t>
         </is>
       </c>
       <c r="J714" s="16" t="inlineStr">
         <is>
-          <t>恋愛相手に求める理想のタイプや条件。</t>
+          <t>完璧な心の相性を感じさせる人——魂の伴侶。</t>
         </is>
       </c>
       <c r="K714" s="16" t="inlineStr">
         <is>
-          <t>내 이상형은 웃음이 많은 사람이야.</t>
+          <t>둘이 완전 소울메이트 같아.</t>
         </is>
       </c>
       <c r="L714" s="16" t="inlineStr">
         <is>
-          <t>My ideal type is someone who laughs a lot.</t>
+          <t>Those two seem like total soulmates.</t>
         </is>
       </c>
       <c r="M714" s="16" t="inlineStr">
         <is>
-          <t>Mi tipo ideal es alguien que se ríe mucho.</t>
+          <t>Esos dos parecen almas gemelas totales.</t>
         </is>
       </c>
       <c r="N714" s="16" t="inlineStr">
         <is>
-          <t>我的理想型是很愛笑的人。</t>
+          <t>那兩個人真的像靈魂伴侶。</t>
         </is>
       </c>
       <c r="O714" s="16" t="inlineStr">
         <is>
-          <t>我的理想型是很爱笑的人。</t>
+          <t>那两个人真的像灵魂伴侣。</t>
         </is>
       </c>
       <c r="P714" s="16" t="inlineStr">
         <is>
-          <t>私の理想のタイプは、よく笑う人。</t>
+          <t>あの二人、完全にソウルメイトみたい。</t>
         </is>
       </c>
       <c r="Q714" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R714" s="15" t="inlineStr">
@@ -70005,17 +70005,17 @@
     <row r="715" ht="46" customHeight="1">
       <c r="A715" s="15" t="inlineStr">
         <is>
-          <t>DAT-038</t>
+          <t>DAT-037</t>
         </is>
       </c>
       <c r="B715" s="15" t="inlineStr">
         <is>
-          <t>이상형월드컵</t>
+          <t>이상형</t>
         </is>
       </c>
       <c r="C715" s="15" t="inlineStr">
         <is>
-          <t>i-sang-hyeong-wol-deu-keop</t>
+          <t>i-sang-hyeong</t>
         </is>
       </c>
       <c r="D715" s="15" t="inlineStr">
@@ -70030,62 +70030,62 @@
       </c>
       <c r="F715" s="16" t="inlineStr">
         <is>
-          <t>"Ideal type World Cup" — a bracket-style elimination game where you repeatedly pick a favorite between two options.</t>
+          <t>A person's ideal type or preferred qualities in a romantic partner.</t>
         </is>
       </c>
       <c r="G715" s="16" t="inlineStr">
         <is>
-          <t>"Mundial de tipo ideal": un juego de eliminación en formato de llaves donde eliges repetidamente a tu favorito entre dos opciones.</t>
+          <t>El tipo ideal o las cualidades preferidas de una persona en una pareja romántica.</t>
         </is>
       </c>
       <c r="H715" s="16" t="inlineStr">
         <is>
-          <t>「理想型世界盃」——透過兩兩淘汰的方式反覆選出最愛的錦標賽形式小遊戲。</t>
+          <t>一個人心目中理想的戀愛對象條件或類型，理想型。</t>
         </is>
       </c>
       <c r="I715" s="16" t="inlineStr">
         <is>
-          <t>“理想型世界杯”——通过两两淘汰的方式反复选出最爱的锦标赛形式小游戏。</t>
+          <t>一个人心目中理想的恋爱对象条件或类型，理想型。</t>
         </is>
       </c>
       <c r="J715" s="16" t="inlineStr">
         <is>
-          <t>「理想のタイプワールドカップ」——二択を繰り返してお気に入りを選ぶ、トーナメント形式のゲーム。</t>
+          <t>恋愛相手に求める理想のタイプや条件。</t>
         </is>
       </c>
       <c r="K715" s="16" t="inlineStr">
         <is>
-          <t>최애 이상형월드컵 했는데 결승까지 갔어.</t>
+          <t>내 이상형은 웃음이 많은 사람이야.</t>
         </is>
       </c>
       <c r="L715" s="16" t="inlineStr">
         <is>
-          <t>I did the ideal-type bracket for my bias and they made it to the finals.</t>
+          <t>My ideal type is someone who laughs a lot.</t>
         </is>
       </c>
       <c r="M715" s="16" t="inlineStr">
         <is>
-          <t>Hice el torneo de tipo ideal de mi bias y llegó hasta la final.</t>
+          <t>Mi tipo ideal es alguien que se ríe mucho.</t>
         </is>
       </c>
       <c r="N715" s="16" t="inlineStr">
         <is>
-          <t>玩了本命的理想型世界盃，結果進到決賽了。</t>
+          <t>我的理想型是很愛笑的人。</t>
         </is>
       </c>
       <c r="O715" s="16" t="inlineStr">
         <is>
-          <t>玩了本命的理想型世界杯，结果进到决赛了。</t>
+          <t>我的理想型是很爱笑的人。</t>
         </is>
       </c>
       <c r="P715" s="16" t="inlineStr">
         <is>
-          <t>推しの理想のタイプワールドカップやったら、決勝まで行った。</t>
+          <t>私の理想のタイプは、よく笑う人。</t>
         </is>
       </c>
       <c r="Q715" s="16" t="inlineStr">
         <is>
-          <t>Online games, fan content</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R715" s="15" t="inlineStr">
@@ -70102,17 +70102,17 @@
     <row r="716" ht="46" customHeight="1">
       <c r="A716" s="15" t="inlineStr">
         <is>
-          <t>DAT-039</t>
+          <t>DAT-038</t>
         </is>
       </c>
       <c r="B716" s="15" t="inlineStr">
         <is>
-          <t>열애설</t>
+          <t>이상형월드컵</t>
         </is>
       </c>
       <c r="C716" s="15" t="inlineStr">
         <is>
-          <t>yeol-ae-seol</t>
+          <t>i-sang-hyeong-wol-deu-keop</t>
         </is>
       </c>
       <c r="D716" s="15" t="inlineStr">
@@ -70127,62 +70127,62 @@
       </c>
       <c r="F716" s="16" t="inlineStr">
         <is>
-          <t>"Hot romance rumor" — a rumor or report that a celebrity is secretly dating someone.</t>
+          <t>"Ideal type World Cup" — a bracket-style elimination game where you repeatedly pick a favorite between two options.</t>
         </is>
       </c>
       <c r="G716" s="16" t="inlineStr">
         <is>
-          <t>"Rumor de romance ardiente": un rumor o reporte de que una celebridad está saliendo en secreto con alguien.</t>
+          <t>"Mundial de tipo ideal": un juego de eliminación en formato de llaves donde eliges repetidamente a tu favorito entre dos opciones.</t>
         </is>
       </c>
       <c r="H716" s="16" t="inlineStr">
         <is>
-          <t>「熱戀傳聞」——傳出藝人正在秘密交往的緋聞或報導。</t>
+          <t>「理想型世界盃」——透過兩兩淘汰的方式反覆選出最愛的錦標賽形式小遊戲。</t>
         </is>
       </c>
       <c r="I716" s="16" t="inlineStr">
         <is>
-          <t>“热恋传闻”——传出艺人正在秘密交往的绯闻或报导。</t>
+          <t>“理想型世界杯”——通过两两淘汰的方式反复选出最爱的锦标赛形式小游戏。</t>
         </is>
       </c>
       <c r="J716" s="16" t="inlineStr">
         <is>
-          <t>「熱い恋の噂」——芸能人が密かに誰かと付き合っているという噂や報道。</t>
+          <t>「理想のタイプワールドカップ」——二択を繰り返してお気に入りを選ぶ、トーナメント形式のゲーム。</t>
         </is>
       </c>
       <c r="K716" s="16" t="inlineStr">
         <is>
-          <t>열애설 터졌다는 기사 봤어?</t>
+          <t>최애 이상형월드컵 했는데 결승까지 갔어.</t>
         </is>
       </c>
       <c r="L716" s="16" t="inlineStr">
         <is>
-          <t>Did you see the article about the dating rumor breaking?</t>
+          <t>I did the ideal-type bracket for my bias and they made it to the finals.</t>
         </is>
       </c>
       <c r="M716" s="16" t="inlineStr">
         <is>
-          <t>¿Viste el artículo sobre el rumor de romance que salió?</t>
+          <t>Hice el torneo de tipo ideal de mi bias y llegó hasta la final.</t>
         </is>
       </c>
       <c r="N716" s="16" t="inlineStr">
         <is>
-          <t>你看到那則戀愛緋聞爆出的新聞了嗎？</t>
+          <t>玩了本命的理想型世界盃，結果進到決賽了。</t>
         </is>
       </c>
       <c r="O716" s="16" t="inlineStr">
         <is>
-          <t>你看到那则恋爱绯闻爆出的新闻了吗？</t>
+          <t>玩了本命的理想型世界杯，结果进到决赛了。</t>
         </is>
       </c>
       <c r="P716" s="16" t="inlineStr">
         <is>
-          <t>熱愛報道出たってニュース見た？</t>
+          <t>推しの理想のタイプワールドカップやったら、決勝まで行った。</t>
         </is>
       </c>
       <c r="Q716" s="16" t="inlineStr">
         <is>
-          <t>Entertainment news</t>
+          <t>Online games, fan content</t>
         </is>
       </c>
       <c r="R716" s="15" t="inlineStr">
@@ -70199,17 +70199,17 @@
     <row r="717" ht="46" customHeight="1">
       <c r="A717" s="15" t="inlineStr">
         <is>
-          <t>DAT-040</t>
+          <t>DAT-039</t>
         </is>
       </c>
       <c r="B717" s="15" t="inlineStr">
         <is>
-          <t>럽라인</t>
+          <t>열애설</t>
         </is>
       </c>
       <c r="C717" s="15" t="inlineStr">
         <is>
-          <t>leob-la-in</t>
+          <t>yeol-ae-seol</t>
         </is>
       </c>
       <c r="D717" s="15" t="inlineStr">
@@ -70224,62 +70224,62 @@
       </c>
       <c r="F717" s="16" t="inlineStr">
         <is>
-          <t>"Love line" — the romantic pairing or storyline within a show.</t>
+          <t>"Hot romance rumor" — a rumor or report that a celebrity is secretly dating someone.</t>
         </is>
       </c>
       <c r="G717" s="16" t="inlineStr">
         <is>
-          <t>"Línea de amor": la pareja romántica o trama dentro de un programa.</t>
+          <t>"Rumor de romance ardiente": un rumor o reporte de que una celebridad está saliendo en secreto con alguien.</t>
         </is>
       </c>
       <c r="H717" s="16" t="inlineStr">
         <is>
-          <t>「愛情線」——一部作品中的戀愛配對或感情發展劇情線。</t>
+          <t>「熱戀傳聞」——傳出藝人正在秘密交往的緋聞或報導。</t>
         </is>
       </c>
       <c r="I717" s="16" t="inlineStr">
         <is>
-          <t>“爱情线”——一部作品中的恋爱配对或感情发展剧情线。</t>
+          <t>“热恋传闻”——传出艺人正在秘密交往的绯闻或报导。</t>
         </is>
       </c>
       <c r="J717" s="16" t="inlineStr">
         <is>
-          <t>「恋愛ライン」——番組内の恋愛カップリングやストーリーライン。</t>
+          <t>「熱い恋の噂」——芸能人が密かに誰かと付き合っているという噂や報道。</t>
         </is>
       </c>
       <c r="K717" s="16" t="inlineStr">
         <is>
-          <t>이번 시즌 럽라인이 제일 기대돼.</t>
+          <t>열애설 터졌다는 기사 봤어?</t>
         </is>
       </c>
       <c r="L717" s="16" t="inlineStr">
         <is>
-          <t>This season's romance storyline is what I'm most excited for.</t>
+          <t>Did you see the article about the dating rumor breaking?</t>
         </is>
       </c>
       <c r="M717" s="16" t="inlineStr">
         <is>
-          <t>La línea romántica de esta temporada es lo que más me emociona.</t>
+          <t>¿Viste el artículo sobre el rumor de romance que salió?</t>
         </is>
       </c>
       <c r="N717" s="16" t="inlineStr">
         <is>
-          <t>這季最期待的就是感情線發展。</t>
+          <t>你看到那則戀愛緋聞爆出的新聞了嗎？</t>
         </is>
       </c>
       <c r="O717" s="16" t="inlineStr">
         <is>
-          <t>这季最期待的就是感情线发展。</t>
+          <t>你看到那则恋爱绯闻爆出的新闻了吗？</t>
         </is>
       </c>
       <c r="P717" s="16" t="inlineStr">
         <is>
-          <t>今シーズンのラブラインが一番楽しみ。</t>
+          <t>熱愛報道出たってニュース見た？</t>
         </is>
       </c>
       <c r="Q717" s="16" t="inlineStr">
         <is>
-          <t>Drama discussion threads</t>
+          <t>Entertainment news</t>
         </is>
       </c>
       <c r="R717" s="15" t="inlineStr">
@@ -70296,17 +70296,17 @@
     <row r="718" ht="46" customHeight="1">
       <c r="A718" s="15" t="inlineStr">
         <is>
-          <t>DAT-041</t>
+          <t>DAT-040</t>
         </is>
       </c>
       <c r="B718" s="15" t="inlineStr">
         <is>
-          <t>커플링</t>
+          <t>럽라인</t>
         </is>
       </c>
       <c r="C718" s="15" t="inlineStr">
         <is>
-          <t>keo-peul-ling</t>
+          <t>leob-la-in</t>
         </is>
       </c>
       <c r="D718" s="15" t="inlineStr">
@@ -70321,62 +70321,62 @@
       </c>
       <c r="F718" s="16" t="inlineStr">
         <is>
-          <t>"Coupling" — fans pairing up two characters or idols as a romantic match, whether canon or imagined.</t>
+          <t>"Love line" — the romantic pairing or storyline within a show.</t>
         </is>
       </c>
       <c r="G718" s="16" t="inlineStr">
         <is>
-          <t>"Emparejamiento": los fans emparejando a dos personajes o ídolos como pareja romántica, sea canónica o imaginada.</t>
+          <t>"Línea de amor": la pareja romántica o trama dentro de un programa.</t>
         </is>
       </c>
       <c r="H718" s="16" t="inlineStr">
         <is>
-          <t>粉絲將兩個角色或偶像配成一對的戀愛想像，無論是官方認證還是純粉絲腦補。</t>
+          <t>「愛情線」——一部作品中的戀愛配對或感情發展劇情線。</t>
         </is>
       </c>
       <c r="I718" s="16" t="inlineStr">
         <is>
-          <t>粉丝将两个角色或偶像配成一对的恋爱想像，无论是官方认证还是纯粉丝脑补。</t>
+          <t>“爱情线”——一部作品中的恋爱配对或感情发展剧情线。</t>
         </is>
       </c>
       <c r="J718" s="16" t="inlineStr">
         <is>
-          <t>ファンが二人のキャラクターやアイドルを恋愛の組み合わせとして見ること、公式でも妄想でも。</t>
+          <t>「恋愛ライン」——番組内の恋愛カップリングやストーリーライン。</t>
         </is>
       </c>
       <c r="K718" s="16" t="inlineStr">
         <is>
-          <t>이 둘 커플링 진짜 인기 많아.</t>
+          <t>이번 시즌 럽라인이 제일 기대돼.</t>
         </is>
       </c>
       <c r="L718" s="16" t="inlineStr">
         <is>
-          <t>This pairing is really popular among fans.</t>
+          <t>This season's romance storyline is what I'm most excited for.</t>
         </is>
       </c>
       <c r="M718" s="16" t="inlineStr">
         <is>
-          <t>Esta pareja (shippeada) es muy popular entre los fans.</t>
+          <t>La línea romántica de esta temporada es lo que más me emociona.</t>
         </is>
       </c>
       <c r="N718" s="16" t="inlineStr">
         <is>
-          <t>這對CP真的超受歡迎。</t>
+          <t>這季最期待的就是感情線發展。</t>
         </is>
       </c>
       <c r="O718" s="16" t="inlineStr">
         <is>
-          <t>这对CP真的超受欢迎。</t>
+          <t>这季最期待的就是感情线发展。</t>
         </is>
       </c>
       <c r="P718" s="16" t="inlineStr">
         <is>
-          <t>このカップリング、本当に人気ある。</t>
+          <t>今シーズンのラブラインが一番楽しみ。</t>
         </is>
       </c>
       <c r="Q718" s="16" t="inlineStr">
         <is>
-          <t>Fan fiction, shipping culture</t>
+          <t>Drama discussion threads</t>
         </is>
       </c>
       <c r="R718" s="15" t="inlineStr">
@@ -70393,17 +70393,17 @@
     <row r="719" ht="46" customHeight="1">
       <c r="A719" s="15" t="inlineStr">
         <is>
-          <t>DAT-042</t>
+          <t>DAT-041</t>
         </is>
       </c>
       <c r="B719" s="15" t="inlineStr">
         <is>
-          <t>짝남</t>
+          <t>커플링</t>
         </is>
       </c>
       <c r="C719" s="15" t="inlineStr">
         <is>
-          <t>jjak-nam</t>
+          <t>keo-peul-ling</t>
         </is>
       </c>
       <c r="D719" s="15" t="inlineStr">
@@ -70418,67 +70418,67 @@
       </c>
       <c r="F719" s="16" t="inlineStr">
         <is>
-          <t>Short for 짝사랑하는 남자 ("the guy I have a one-sided crush on") — your crush.</t>
+          <t>"Coupling" — fans pairing up two characters or idols as a romantic match, whether canon or imagined.</t>
         </is>
       </c>
       <c r="G719" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 짝사랑하는 남자 ("el chico del que estoy enamorada en secreto"): tu crush.</t>
+          <t>"Emparejamiento": los fans emparejando a dos personajes o ídolos como pareja romántica, sea canónica o imaginada.</t>
         </is>
       </c>
       <c r="H719" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 남자（暗戀的男生）的縮寫——你暗戀的對象。</t>
+          <t>粉絲將兩個角色或偶像配成一對的戀愛想像，無論是官方認證還是純粉絲腦補。</t>
         </is>
       </c>
       <c r="I719" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 남자（暗恋的男生）的缩写——你暗恋的对象。</t>
+          <t>粉丝将两个角色或偶像配成一对的恋爱想像，无论是官方认证还是纯粉丝脑补。</t>
         </is>
       </c>
       <c r="J719" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 남자（片思いしている男性）の略——片思いの相手。</t>
+          <t>ファンが二人のキャラクターやアイドルを恋愛の組み合わせとして見ること、公式でも妄想でも。</t>
         </is>
       </c>
       <c r="K719" s="16" t="inlineStr">
         <is>
-          <t>짝남 앞에서 완전 얼음 됐어.</t>
+          <t>이 둘 커플링 진짜 인기 많아.</t>
         </is>
       </c>
       <c r="L719" s="16" t="inlineStr">
         <is>
-          <t>I totally froze up in front of my crush.</t>
+          <t>This pairing is really popular among fans.</t>
         </is>
       </c>
       <c r="M719" s="16" t="inlineStr">
         <is>
-          <t>Me quedé completamente congelada frente a mi crush.</t>
+          <t>Esta pareja (shippeada) es muy popular entre los fans.</t>
         </is>
       </c>
       <c r="N719" s="16" t="inlineStr">
         <is>
-          <t>在喜歡的男生面前完全僵住了。</t>
+          <t>這對CP真的超受歡迎。</t>
         </is>
       </c>
       <c r="O719" s="16" t="inlineStr">
         <is>
-          <t>在喜欢的男生面前完全僵住了。</t>
+          <t>这对CP真的超受欢迎。</t>
         </is>
       </c>
       <c r="P719" s="16" t="inlineStr">
         <is>
-          <t>好きな人の前で完全に固まっちゃった。</t>
+          <t>このカップリング、本当に人気ある。</t>
         </is>
       </c>
       <c r="Q719" s="16" t="inlineStr">
         <is>
-          <t>Casual crush talk</t>
+          <t>Fan fiction, shipping culture</t>
         </is>
       </c>
       <c r="R719" s="15" t="inlineStr">
         <is>
-          <t>Verified (web-checked)</t>
+          <t>Draft — please double-check</t>
         </is>
       </c>
       <c r="S719" s="15" t="inlineStr">
@@ -70490,17 +70490,17 @@
     <row r="720" ht="46" customHeight="1">
       <c r="A720" s="15" t="inlineStr">
         <is>
-          <t>DAT-043</t>
+          <t>DAT-042</t>
         </is>
       </c>
       <c r="B720" s="15" t="inlineStr">
         <is>
-          <t>짝녀</t>
+          <t>짝남</t>
         </is>
       </c>
       <c r="C720" s="15" t="inlineStr">
         <is>
-          <t>jjak-nyeo</t>
+          <t>jjak-nam</t>
         </is>
       </c>
       <c r="D720" s="15" t="inlineStr">
@@ -70515,57 +70515,57 @@
       </c>
       <c r="F720" s="16" t="inlineStr">
         <is>
-          <t>Short for 짝사랑하는 여자 ("the girl I have a one-sided crush on") — your crush.</t>
+          <t>Short for 짝사랑하는 남자 ("the guy I have a one-sided crush on") — your crush.</t>
         </is>
       </c>
       <c r="G720" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 짝사랑하는 여자 ("la chica de la que estoy enamorado en secreto"): tu crush.</t>
+          <t>Abreviatura de 짝사랑하는 남자 ("el chico del que estoy enamorada en secreto"): tu crush.</t>
         </is>
       </c>
       <c r="H720" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 여자（暗戀的女生）的縮寫——你暗戀的對象。</t>
+          <t>짝사랑하는 남자（暗戀的男生）的縮寫——你暗戀的對象。</t>
         </is>
       </c>
       <c r="I720" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 여자（暗恋的女生）的缩写——你暗恋的对象。</t>
+          <t>짝사랑하는 남자（暗恋的男生）的缩写——你暗恋的对象。</t>
         </is>
       </c>
       <c r="J720" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 여자（片思いしている女性）の略——片思いの相手。</t>
+          <t>짝사랑하는 남자（片思いしている男性）の略——片思いの相手。</t>
         </is>
       </c>
       <c r="K720" s="16" t="inlineStr">
         <is>
-          <t>짝녀한테 어떻게 말 걸지 고민이야.</t>
+          <t>짝남 앞에서 완전 얼음 됐어.</t>
         </is>
       </c>
       <c r="L720" s="16" t="inlineStr">
         <is>
-          <t>I'm stressing over how to talk to my crush.</t>
+          <t>I totally froze up in front of my crush.</t>
         </is>
       </c>
       <c r="M720" s="16" t="inlineStr">
         <is>
-          <t>Estoy preocupado por cómo hablarle a mi crush.</t>
+          <t>Me quedé completamente congelada frente a mi crush.</t>
         </is>
       </c>
       <c r="N720" s="16" t="inlineStr">
         <is>
-          <t>煩惱要怎麼跟喜歡的女生搭話。</t>
+          <t>在喜歡的男生面前完全僵住了。</t>
         </is>
       </c>
       <c r="O720" s="16" t="inlineStr">
         <is>
-          <t>烦恼要怎么跟喜欢的女生搭话。</t>
+          <t>在喜欢的男生面前完全僵住了。</t>
         </is>
       </c>
       <c r="P720" s="16" t="inlineStr">
         <is>
-          <t>好きな人にどう話しかけるか悩んでる。</t>
+          <t>好きな人の前で完全に固まっちゃった。</t>
         </is>
       </c>
       <c r="Q720" s="16" t="inlineStr">
@@ -70587,17 +70587,17 @@
     <row r="721" ht="46" customHeight="1">
       <c r="A721" s="15" t="inlineStr">
         <is>
-          <t>DAT-044</t>
+          <t>DAT-043</t>
         </is>
       </c>
       <c r="B721" s="15" t="inlineStr">
         <is>
-          <t>대시</t>
+          <t>짝녀</t>
         </is>
       </c>
       <c r="C721" s="15" t="inlineStr">
         <is>
-          <t>dae-si</t>
+          <t>jjak-nyeo</t>
         </is>
       </c>
       <c r="D721" s="15" t="inlineStr">
@@ -70612,67 +70612,67 @@
       </c>
       <c r="F721" s="16" t="inlineStr">
         <is>
-          <t>"Dash" — making a romantic move on someone, like asking them out.</t>
+          <t>Short for 짝사랑하는 여자 ("the girl I have a one-sided crush on") — your crush.</t>
         </is>
       </c>
       <c r="G721" s="16" t="inlineStr">
         <is>
-          <t>"Dash": hacer un movimiento romántico hacia alguien, como invitarlo a salir.</t>
+          <t>Abreviatura de 짝사랑하는 여자 ("la chica de la que estoy enamorado en secreto"): tu crush.</t>
         </is>
       </c>
       <c r="H721" s="16" t="inlineStr">
         <is>
-          <t>主動採取行動追求某人，例如開口邀約，主動出擊。</t>
+          <t>짝사랑하는 여자（暗戀的女生）的縮寫——你暗戀的對象。</t>
         </is>
       </c>
       <c r="I721" s="16" t="inlineStr">
         <is>
-          <t>主动采取行动追求某人，例如开口邀约，主动出击。</t>
+          <t>짝사랑하는 여자（暗恋的女生）的缩写——你暗恋的对象。</t>
         </is>
       </c>
       <c r="J721" s="16" t="inlineStr">
         <is>
-          <t>「ダッシュ」——デートに誘うなど、恋愛的なアクションを起こすこと。</t>
+          <t>짝사랑하는 여자（片思いしている女性）の略——片思いの相手。</t>
         </is>
       </c>
       <c r="K721" s="16" t="inlineStr">
         <is>
-          <t>드디어 대시했어!</t>
+          <t>짝녀한테 어떻게 말 걸지 고민이야.</t>
         </is>
       </c>
       <c r="L721" s="16" t="inlineStr">
         <is>
-          <t>I finally made a move!</t>
+          <t>I'm stressing over how to talk to my crush.</t>
         </is>
       </c>
       <c r="M721" s="16" t="inlineStr">
         <is>
-          <t>¡Por fin di el paso!</t>
+          <t>Estoy preocupado por cómo hablarle a mi crush.</t>
         </is>
       </c>
       <c r="N721" s="16" t="inlineStr">
         <is>
-          <t>終於主動出擊了！</t>
+          <t>煩惱要怎麼跟喜歡的女生搭話。</t>
         </is>
       </c>
       <c r="O721" s="16" t="inlineStr">
         <is>
-          <t>终于主动出击了！</t>
+          <t>烦恼要怎么跟喜欢的女生搭话。</t>
         </is>
       </c>
       <c r="P721" s="16" t="inlineStr">
         <is>
-          <t>ついにアタックした！</t>
+          <t>好きな人にどう話しかけるか悩んでる。</t>
         </is>
       </c>
       <c r="Q721" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Casual crush talk</t>
         </is>
       </c>
       <c r="R721" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S721" s="15" t="inlineStr">
@@ -70684,17 +70684,17 @@
     <row r="722" ht="46" customHeight="1">
       <c r="A722" s="15" t="inlineStr">
         <is>
-          <t>DAT-045</t>
+          <t>DAT-044</t>
         </is>
       </c>
       <c r="B722" s="15" t="inlineStr">
         <is>
-          <t>애프터</t>
+          <t>대시</t>
         </is>
       </c>
       <c r="C722" s="15" t="inlineStr">
         <is>
-          <t>ae-peu-teo</t>
+          <t>dae-si</t>
         </is>
       </c>
       <c r="D722" s="15" t="inlineStr">
@@ -70709,57 +70709,57 @@
       </c>
       <c r="F722" s="16" t="inlineStr">
         <is>
-          <t>"After" — a follow-up date arranged after an initial blind date.</t>
+          <t>"Dash" — making a romantic move on someone, like asking them out.</t>
         </is>
       </c>
       <c r="G722" s="16" t="inlineStr">
         <is>
-          <t>"After": una cita de seguimiento organizada después de una cita a ciegas inicial.</t>
+          <t>"Dash": hacer un movimiento romántico hacia alguien, como invitarlo a salir.</t>
         </is>
       </c>
       <c r="H722" s="16" t="inlineStr">
         <is>
-          <t>相親後安排的後續約會。</t>
+          <t>主動採取行動追求某人，例如開口邀約，主動出擊。</t>
         </is>
       </c>
       <c r="I722" s="16" t="inlineStr">
         <is>
-          <t>相亲后安排的后续约会。</t>
+          <t>主动采取行动追求某人，例如开口邀约，主动出击。</t>
         </is>
       </c>
       <c r="J722" s="16" t="inlineStr">
         <is>
-          <t>最初の合コンの後に設定される、フォローアップのデート——「アフター」。</t>
+          <t>「ダッシュ」——デートに誘うなど、恋愛的なアクションを起こすこと。</t>
         </is>
       </c>
       <c r="K722" s="16" t="inlineStr">
         <is>
-          <t>소개팅 애프터 신청 받았어.</t>
+          <t>드디어 대시했어!</t>
         </is>
       </c>
       <c r="L722" s="16" t="inlineStr">
         <is>
-          <t>I got asked for a follow-up date after the blind date.</t>
+          <t>I finally made a move!</t>
         </is>
       </c>
       <c r="M722" s="16" t="inlineStr">
         <is>
-          <t>Me pidieron una segunda cita después de la cita a ciegas.</t>
+          <t>¡Por fin di el paso!</t>
         </is>
       </c>
       <c r="N722" s="16" t="inlineStr">
         <is>
-          <t>相親後收到了續攤約會的邀約。</t>
+          <t>終於主動出擊了！</t>
         </is>
       </c>
       <c r="O722" s="16" t="inlineStr">
         <is>
-          <t>相亲后收到了续摊约会的邀约。</t>
+          <t>终于主动出击了！</t>
         </is>
       </c>
       <c r="P722" s="16" t="inlineStr">
         <is>
-          <t>合コンのアフターに誘われた。</t>
+          <t>ついにアタックした！</t>
         </is>
       </c>
       <c r="Q722" s="16" t="inlineStr">
@@ -70781,17 +70781,17 @@
     <row r="723" ht="46" customHeight="1">
       <c r="A723" s="15" t="inlineStr">
         <is>
-          <t>DAT-046</t>
+          <t>DAT-045</t>
         </is>
       </c>
       <c r="B723" s="15" t="inlineStr">
         <is>
-          <t>그린라이트</t>
+          <t>애프터</t>
         </is>
       </c>
       <c r="C723" s="15" t="inlineStr">
         <is>
-          <t>geu-rin-la-i-teu</t>
+          <t>ae-peu-teo</t>
         </is>
       </c>
       <c r="D723" s="15" t="inlineStr">
@@ -70806,57 +70806,57 @@
       </c>
       <c r="F723" s="16" t="inlineStr">
         <is>
-          <t>"Green light" — a signal that someone is romantically interested and open to being pursued.</t>
+          <t>"After" — a follow-up date arranged after an initial blind date.</t>
         </is>
       </c>
       <c r="G723" s="16" t="inlineStr">
         <is>
-          <t>"Luz verde": una señal de que alguien está interesado románticamente y abierto a ser conquistado.</t>
+          <t>"After": una cita de seguimiento organizada después de una cita a ciegas inicial.</t>
         </is>
       </c>
       <c r="H723" s="16" t="inlineStr">
         <is>
-          <t>「綠燈」——表示對方對你有意思、可以繼續追求的訊號。</t>
+          <t>相親後安排的後續約會。</t>
         </is>
       </c>
       <c r="I723" s="16" t="inlineStr">
         <is>
-          <t>“绿灯”——表示对方对你有意思、可以继续追求的信号。</t>
+          <t>相亲后安排的后续约会。</t>
         </is>
       </c>
       <c r="J723" s="16" t="inlineStr">
         <is>
-          <t>「青信号」——相手が恋愛的に興味を持っていて、アプローチを受け入れる準備があるというサイン。</t>
+          <t>最初の合コンの後に設定される、フォローアップのデート——「アフター」。</t>
         </is>
       </c>
       <c r="K723" s="16" t="inlineStr">
         <is>
-          <t>그거 완전 그린라이트 아니야?</t>
+          <t>소개팅 애프터 신청 받았어.</t>
         </is>
       </c>
       <c r="L723" s="16" t="inlineStr">
         <is>
-          <t>Isn't that a total green light?</t>
+          <t>I got asked for a follow-up date after the blind date.</t>
         </is>
       </c>
       <c r="M723" s="16" t="inlineStr">
         <is>
-          <t>¿Eso no es una luz verde total?</t>
+          <t>Me pidieron una segunda cita después de la cita a ciegas.</t>
         </is>
       </c>
       <c r="N723" s="16" t="inlineStr">
         <is>
-          <t>那不完全是綠燈訊號嗎？</t>
+          <t>相親後收到了續攤約會的邀約。</t>
         </is>
       </c>
       <c r="O723" s="16" t="inlineStr">
         <is>
-          <t>那不完全是绿灯信号吗？</t>
+          <t>相亲后收到了续摊约会的邀约。</t>
         </is>
       </c>
       <c r="P723" s="16" t="inlineStr">
         <is>
-          <t>それって完全にグリーンライトじゃない？</t>
+          <t>合コンのアフターに誘われた。</t>
         </is>
       </c>
       <c r="Q723" s="16" t="inlineStr">
@@ -70878,17 +70878,17 @@
     <row r="724" ht="46" customHeight="1">
       <c r="A724" s="15" t="inlineStr">
         <is>
-          <t>DAT-047</t>
+          <t>DAT-046</t>
         </is>
       </c>
       <c r="B724" s="15" t="inlineStr">
         <is>
-          <t>훈훈하다</t>
+          <t>그린라이트</t>
         </is>
       </c>
       <c r="C724" s="15" t="inlineStr">
         <is>
-          <t>hun-hun-ha-da</t>
+          <t>geu-rin-la-i-teu</t>
         </is>
       </c>
       <c r="D724" s="15" t="inlineStr">
@@ -70903,62 +70903,62 @@
       </c>
       <c r="F724" s="16" t="inlineStr">
         <is>
-          <t>Describes a warm, wholesome, feel-good atmosphere or moment — or a warmly attractive appearance.</t>
+          <t>"Green light" — a signal that someone is romantically interested and open to being pursued.</t>
         </is>
       </c>
       <c r="G724" s="16" t="inlineStr">
         <is>
-          <t>Describe un ambiente o momento cálido, agradable y de buen sentir — o una apariencia cálidamente atractiva.</t>
+          <t>"Luz verde": una señal de que alguien está interesado románticamente y abierto a ser conquistado.</t>
         </is>
       </c>
       <c r="H724" s="16" t="inlineStr">
         <is>
-          <t>形容溫暖、樸實、讓人感覺舒服的氛圍或瞬間，也可形容外表溫暖有魅力。</t>
+          <t>「綠燈」——表示對方對你有意思、可以繼續追求的訊號。</t>
         </is>
       </c>
       <c r="I724" s="16" t="inlineStr">
         <is>
-          <t>形容温暖、朴实、让人感觉舒服的氛围或瞬间，也可形容外表温暖有魅力。</t>
+          <t>“绿灯”——表示对方对你有意思、可以继续追求的信号。</t>
         </is>
       </c>
       <c r="J724" s="16" t="inlineStr">
         <is>
-          <t>温かく、素朴で、心地よい雰囲気や瞬間——または温かみのある魅力的な外見を表す。</t>
+          <t>「青信号」——相手が恋愛的に興味を持っていて、アプローチを受け入れる準備があるというサイン。</t>
         </is>
       </c>
       <c r="K724" s="16" t="inlineStr">
         <is>
-          <t>이 훈훈한 미담 봐봐.</t>
+          <t>그거 완전 그린라이트 아니야?</t>
         </is>
       </c>
       <c r="L724" s="16" t="inlineStr">
         <is>
-          <t>Check out this warm, feel-good story.</t>
+          <t>Isn't that a total green light?</t>
         </is>
       </c>
       <c r="M724" s="16" t="inlineStr">
         <is>
-          <t>Mira esta historia tan cálida y conmovedora.</t>
+          <t>¿Eso no es una luz verde total?</t>
         </is>
       </c>
       <c r="N724" s="16" t="inlineStr">
         <is>
-          <t>看看這則暖心的故事。</t>
+          <t>那不完全是綠燈訊號嗎？</t>
         </is>
       </c>
       <c r="O724" s="16" t="inlineStr">
         <is>
-          <t>看看这则暖心的故事。</t>
+          <t>那不完全是绿灯信号吗？</t>
         </is>
       </c>
       <c r="P724" s="16" t="inlineStr">
         <is>
-          <t>このほのぼのする美談見て。</t>
+          <t>それって完全にグリーンライトじゃない？</t>
         </is>
       </c>
       <c r="Q724" s="16" t="inlineStr">
         <is>
-          <t>Feel-good news, casual compliments</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R724" s="15" t="inlineStr">
@@ -70975,17 +70975,17 @@
     <row r="725" ht="46" customHeight="1">
       <c r="A725" s="15" t="inlineStr">
         <is>
-          <t>DAT-048</t>
+          <t>DAT-047</t>
         </is>
       </c>
       <c r="B725" s="15" t="inlineStr">
         <is>
-          <t>이별</t>
+          <t>훈훈하다</t>
         </is>
       </c>
       <c r="C725" s="15" t="inlineStr">
         <is>
-          <t>i-byeol</t>
+          <t>hun-hun-ha-da</t>
         </is>
       </c>
       <c r="D725" s="15" t="inlineStr">
@@ -71000,62 +71000,62 @@
       </c>
       <c r="F725" s="16" t="inlineStr">
         <is>
-          <t>The ending of a romantic relationship.</t>
+          <t>Describes a warm, wholesome, feel-good atmosphere or moment — or a warmly attractive appearance.</t>
         </is>
       </c>
       <c r="G725" s="16" t="inlineStr">
         <is>
-          <t>El fin de una relación romántica.</t>
+          <t>Describe un ambiente o momento cálido, agradable y de buen sentir — o una apariencia cálidamente atractiva.</t>
         </is>
       </c>
       <c r="H725" s="16" t="inlineStr">
         <is>
-          <t>一段戀愛關係的結束，分手。</t>
+          <t>形容溫暖、樸實、讓人感覺舒服的氛圍或瞬間，也可形容外表溫暖有魅力。</t>
         </is>
       </c>
       <c r="I725" s="16" t="inlineStr">
         <is>
-          <t>一段恋爱关系的结束，分手。</t>
+          <t>形容温暖、朴实、让人感觉舒服的氛围或瞬间，也可形容外表温暖有魅力。</t>
         </is>
       </c>
       <c r="J725" s="16" t="inlineStr">
         <is>
-          <t>恋愛関係の終わり。</t>
+          <t>温かく、素朴で、心地よい雰囲気や瞬間——または温かみのある魅力的な外見を表す。</t>
         </is>
       </c>
       <c r="K725" s="16" t="inlineStr">
         <is>
-          <t>이별 후에 한동안 힘들었어.</t>
+          <t>이 훈훈한 미담 봐봐.</t>
         </is>
       </c>
       <c r="L725" s="16" t="inlineStr">
         <is>
-          <t>I had a hard time for a while after the breakup.</t>
+          <t>Check out this warm, feel-good story.</t>
         </is>
       </c>
       <c r="M725" s="16" t="inlineStr">
         <is>
-          <t>La pasé mal por un tiempo después de la ruptura.</t>
+          <t>Mira esta historia tan cálida y conmovedora.</t>
         </is>
       </c>
       <c r="N725" s="16" t="inlineStr">
         <is>
-          <t>分手後有一陣子過得很辛苦。</t>
+          <t>看看這則暖心的故事。</t>
         </is>
       </c>
       <c r="O725" s="16" t="inlineStr">
         <is>
-          <t>分手后有一阵子过得很辛苦。</t>
+          <t>看看这则暖心的故事。</t>
         </is>
       </c>
       <c r="P725" s="16" t="inlineStr">
         <is>
-          <t>別れた後、しばらく辛かった。</t>
+          <t>このほのぼのする美談見て。</t>
         </is>
       </c>
       <c r="Q725" s="16" t="inlineStr">
         <is>
-          <t>K-drama plot talk, casual speech</t>
+          <t>Feel-good news, casual compliments</t>
         </is>
       </c>
       <c r="R725" s="15" t="inlineStr">
@@ -71072,17 +71072,17 @@
     <row r="726" ht="46" customHeight="1">
       <c r="A726" s="15" t="inlineStr">
         <is>
-          <t>DAT-049</t>
+          <t>DAT-048</t>
         </is>
       </c>
       <c r="B726" s="15" t="inlineStr">
         <is>
-          <t>곰신</t>
+          <t>이별</t>
         </is>
       </c>
       <c r="C726" s="15" t="inlineStr">
         <is>
-          <t>gom-sin</t>
+          <t>i-byeol</t>
         </is>
       </c>
       <c r="D726" s="15" t="inlineStr">
@@ -71097,67 +71097,67 @@
       </c>
       <c r="F726" s="16" t="inlineStr">
         <is>
-          <t>Short for 고무신 (traditional rubber shoes) — a girlfriend patiently waiting for her boyfriend to finish mandatory military service.</t>
+          <t>The ending of a romantic relationship.</t>
         </is>
       </c>
       <c r="G726" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 고무신 (zapatos tradicionales de goma): una novia que espera pacientemente a que su novio termine el servicio militar obligatorio.</t>
+          <t>El fin de una relación romántica.</t>
         </is>
       </c>
       <c r="H726" s="16" t="inlineStr">
         <is>
-          <t>고무신（傳統膠鞋）的縮寫——耐心等待男友服完兵役的女友。</t>
+          <t>一段戀愛關係的結束，分手。</t>
         </is>
       </c>
       <c r="I726" s="16" t="inlineStr">
         <is>
-          <t>고무신（传统胶鞋）的缩写——耐心等待男友服完兵役的女友。</t>
+          <t>一段恋爱关系的结束，分手。</t>
         </is>
       </c>
       <c r="J726" s="16" t="inlineStr">
         <is>
-          <t>고무신（伝統的なゴム靴）の略——兵役を終えるのを待つ彼女のこと。</t>
+          <t>恋愛関係の終わり。</t>
         </is>
       </c>
       <c r="K726" s="16" t="inlineStr">
         <is>
-          <t>곰신 생활 이제 6개월 남았어.</t>
+          <t>이별 후에 한동안 힘들었어.</t>
         </is>
       </c>
       <c r="L726" s="16" t="inlineStr">
         <is>
-          <t>I only have six months left of being a waiting girlfriend.</t>
+          <t>I had a hard time for a while after the breakup.</t>
         </is>
       </c>
       <c r="M726" s="16" t="inlineStr">
         <is>
-          <t>Solo me quedan seis meses esperando a que termine el servicio militar.</t>
+          <t>La pasé mal por un tiempo después de la ruptura.</t>
         </is>
       </c>
       <c r="N726" s="16" t="inlineStr">
         <is>
-          <t>等男友退伍的日子只剩六個月了。</t>
+          <t>分手後有一陣子過得很辛苦。</t>
         </is>
       </c>
       <c r="O726" s="16" t="inlineStr">
         <is>
-          <t>等男友退伍的日子只剩六个月了。</t>
+          <t>分手后有一阵子过得很辛苦。</t>
         </is>
       </c>
       <c r="P726" s="16" t="inlineStr">
         <is>
-          <t>彼の除隊を待つ生活も、あと6ヶ月。</t>
+          <t>別れた後、しばらく辛かった。</t>
         </is>
       </c>
       <c r="Q726" s="16" t="inlineStr">
         <is>
-          <t>Military service relationship talk</t>
+          <t>K-drama plot talk, casual speech</t>
         </is>
       </c>
       <c r="R726" s="15" t="inlineStr">
         <is>
-          <t>Verified (web-checked)</t>
+          <t>Draft — please double-check</t>
         </is>
       </c>
       <c r="S726" s="15" t="inlineStr">
@@ -71169,17 +71169,17 @@
     <row r="727" ht="46" customHeight="1">
       <c r="A727" s="15" t="inlineStr">
         <is>
-          <t>DAT-050</t>
+          <t>DAT-049</t>
         </is>
       </c>
       <c r="B727" s="15" t="inlineStr">
         <is>
-          <t>장거리연애</t>
+          <t>곰신</t>
         </is>
       </c>
       <c r="C727" s="15" t="inlineStr">
         <is>
-          <t>jang-geo-ri-yeon-ae</t>
+          <t>gom-sin</t>
         </is>
       </c>
       <c r="D727" s="15" t="inlineStr">
@@ -71194,67 +71194,67 @@
       </c>
       <c r="F727" s="16" t="inlineStr">
         <is>
-          <t>A romantic relationship where the couple lives far apart from each other.</t>
+          <t>Short for 고무신 (traditional rubber shoes) — a girlfriend patiently waiting for her boyfriend to finish mandatory military service.</t>
         </is>
       </c>
       <c r="G727" s="16" t="inlineStr">
         <is>
-          <t>Una relación romántica donde la pareja vive lejos el uno del otro.</t>
+          <t>Abreviatura de 고무신 (zapatos tradicionales de goma): una novia que espera pacientemente a que su novio termine el servicio militar obligatorio.</t>
         </is>
       </c>
       <c r="H727" s="16" t="inlineStr">
         <is>
-          <t>情侶分隔兩地、住得很遠的戀愛關係，遠距離戀愛。</t>
+          <t>고무신（傳統膠鞋）的縮寫——耐心等待男友服完兵役的女友。</t>
         </is>
       </c>
       <c r="I727" s="16" t="inlineStr">
         <is>
-          <t>情侣分隔两地、住得很远的恋爱关系，远距离恋爱。</t>
+          <t>고무신（传统胶鞋）的缩写——耐心等待男友服完兵役的女友。</t>
         </is>
       </c>
       <c r="J727" s="16" t="inlineStr">
         <is>
-          <t>カップルが離れて暮らす恋愛関係。</t>
+          <t>고무신（伝統的なゴム靴）の略——兵役を終えるのを待つ彼女のこと。</t>
         </is>
       </c>
       <c r="K727" s="16" t="inlineStr">
         <is>
-          <t>장거리연애 힘들지만 잘 버티고 있어.</t>
+          <t>곰신 생활 이제 6개월 남았어.</t>
         </is>
       </c>
       <c r="L727" s="16" t="inlineStr">
         <is>
-          <t>Long-distance is hard, but we're holding up well.</t>
+          <t>I only have six months left of being a waiting girlfriend.</t>
         </is>
       </c>
       <c r="M727" s="16" t="inlineStr">
         <is>
-          <t>La distancia es difícil, pero lo estamos llevando bien.</t>
+          <t>Solo me quedan seis meses esperando a que termine el servicio militar.</t>
         </is>
       </c>
       <c r="N727" s="16" t="inlineStr">
         <is>
-          <t>遠距離戀愛雖然辛苦，但撐得很好。</t>
+          <t>等男友退伍的日子只剩六個月了。</t>
         </is>
       </c>
       <c r="O727" s="16" t="inlineStr">
         <is>
-          <t>远距离恋爱虽然辛苦，但撑得很好。</t>
+          <t>等男友退伍的日子只剩六个月了。</t>
         </is>
       </c>
       <c r="P727" s="16" t="inlineStr">
         <is>
-          <t>遠距離恋愛は大変だけど、うまくやってる。</t>
+          <t>彼の除隊を待つ生活も、あと6ヶ月。</t>
         </is>
       </c>
       <c r="Q727" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk</t>
+          <t>Military service relationship talk</t>
         </is>
       </c>
       <c r="R727" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S727" s="15" t="inlineStr">
@@ -71266,17 +71266,17 @@
     <row r="728" ht="46" customHeight="1">
       <c r="A728" s="15" t="inlineStr">
         <is>
-          <t>DAT-051</t>
+          <t>DAT-050</t>
         </is>
       </c>
       <c r="B728" s="15" t="inlineStr">
         <is>
-          <t>권태기</t>
+          <t>장거리연애</t>
         </is>
       </c>
       <c r="C728" s="15" t="inlineStr">
         <is>
-          <t>gwon-tae-gi</t>
+          <t>jang-geo-ri-yeon-ae</t>
         </is>
       </c>
       <c r="D728" s="15" t="inlineStr">
@@ -71291,62 +71291,62 @@
       </c>
       <c r="F728" s="16" t="inlineStr">
         <is>
-          <t>A phase in a relationship marked by boredom or waning excitement.</t>
+          <t>A romantic relationship where the couple lives far apart from each other.</t>
         </is>
       </c>
       <c r="G728" s="16" t="inlineStr">
         <is>
-          <t>Una fase en una relación marcada por el aburrimiento o la disminución del entusiasmo.</t>
+          <t>Una relación romántica donde la pareja vive lejos el uno del otro.</t>
         </is>
       </c>
       <c r="H728" s="16" t="inlineStr">
         <is>
-          <t>感情中出現無聊感或熱情消退的階段，倦怠期。</t>
+          <t>情侶分隔兩地、住得很遠的戀愛關係，遠距離戀愛。</t>
         </is>
       </c>
       <c r="I728" s="16" t="inlineStr">
         <is>
-          <t>感情中出现无聊感或热情消退的阶段，倦怠期。</t>
+          <t>情侣分隔两地、住得很远的恋爱关系，远距离恋爱。</t>
         </is>
       </c>
       <c r="J728" s="16" t="inlineStr">
         <is>
-          <t>退屈さや情熱の低下が見られる、関係の一時期。</t>
+          <t>カップルが離れて暮らす恋愛関係。</t>
         </is>
       </c>
       <c r="K728" s="16" t="inlineStr">
         <is>
-          <t>우리 요즘 권태기인 것 같아.</t>
+          <t>장거리연애 힘들지만 잘 버티고 있어.</t>
         </is>
       </c>
       <c r="L728" s="16" t="inlineStr">
         <is>
-          <t>I think we're going through a relationship rut lately.</t>
+          <t>Long-distance is hard, but we're holding up well.</t>
         </is>
       </c>
       <c r="M728" s="16" t="inlineStr">
         <is>
-          <t>Creo que estamos pasando por una etapa de aburrimiento últimamente.</t>
+          <t>La distancia es difícil, pero lo estamos llevando bien.</t>
         </is>
       </c>
       <c r="N728" s="16" t="inlineStr">
         <is>
-          <t>我們最近好像進入倦怠期了。</t>
+          <t>遠距離戀愛雖然辛苦，但撐得很好。</t>
         </is>
       </c>
       <c r="O728" s="16" t="inlineStr">
         <is>
-          <t>我们最近好像进入倦怠期了。</t>
+          <t>远距离恋爱虽然辛苦，但撑得很好。</t>
         </is>
       </c>
       <c r="P728" s="16" t="inlineStr">
         <is>
-          <t>最近倦怠期っぽい気がする。</t>
+          <t>遠距離恋愛は大変だけど、うまくやってる。</t>
         </is>
       </c>
       <c r="Q728" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk, dramas</t>
+          <t>Relationship talk</t>
         </is>
       </c>
       <c r="R728" s="15" t="inlineStr">
@@ -71363,17 +71363,17 @@
     <row r="729" ht="46" customHeight="1">
       <c r="A729" s="15" t="inlineStr">
         <is>
-          <t>DAT-052</t>
+          <t>DAT-051</t>
         </is>
       </c>
       <c r="B729" s="15" t="inlineStr">
         <is>
-          <t>연상연하</t>
+          <t>권태기</t>
         </is>
       </c>
       <c r="C729" s="15" t="inlineStr">
         <is>
-          <t>yeon-sang-yeon-ha</t>
+          <t>gwon-tae-gi</t>
         </is>
       </c>
       <c r="D729" s="15" t="inlineStr">
@@ -71388,62 +71388,62 @@
       </c>
       <c r="F729" s="16" t="inlineStr">
         <is>
-          <t>A relationship where one partner is noticeably older (연상) and the other younger (연하) — a common K-drama dynamic.</t>
+          <t>A phase in a relationship marked by boredom or waning excitement.</t>
         </is>
       </c>
       <c r="G729" s="16" t="inlineStr">
         <is>
-          <t>Una relación donde una pareja es notablemente mayor (연상) y la otra más joven (연하), una dinámica común en los K-dramas.</t>
+          <t>Una fase en una relación marcada por el aburrimiento o la disminución del entusiasmo.</t>
         </is>
       </c>
       <c r="H729" s="16" t="inlineStr">
         <is>
-          <t>一方明顯年長（연상）、另一方較年輕（연하）的戀愛關係——韓劇常見的組合。</t>
+          <t>感情中出現無聊感或熱情消退的階段，倦怠期。</t>
         </is>
       </c>
       <c r="I729" s="16" t="inlineStr">
         <is>
-          <t>一方明显年长（연상）、另一方较年轻（연하）的恋爱关系——韩剧常见的组合。</t>
+          <t>感情中出现无聊感或热情消退的阶段，倦怠期。</t>
         </is>
       </c>
       <c r="J729" s="16" t="inlineStr">
         <is>
-          <t>一方が明らかに年上（연상）、もう一方が年下（연하）の恋愛関係——韓国ドラマによくある組み合わせ。</t>
+          <t>退屈さや情熱の低下が見られる、関係の一時期。</t>
         </is>
       </c>
       <c r="K729" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 연상연하 커플이야.</t>
+          <t>우리 요즘 권태기인 것 같아.</t>
         </is>
       </c>
       <c r="L729" s="16" t="inlineStr">
         <is>
-          <t>This drama has an age-gap couple.</t>
+          <t>I think we're going through a relationship rut lately.</t>
         </is>
       </c>
       <c r="M729" s="16" t="inlineStr">
         <is>
-          <t>Este drama tiene una pareja con diferencia de edad.</t>
+          <t>Creo que estamos pasando por una etapa de aburrimiento últimamente.</t>
         </is>
       </c>
       <c r="N729" s="16" t="inlineStr">
         <is>
-          <t>這部劇是姊弟戀組合。</t>
+          <t>我們最近好像進入倦怠期了。</t>
         </is>
       </c>
       <c r="O729" s="16" t="inlineStr">
         <is>
-          <t>这部剧是姊弟恋组合。</t>
+          <t>我们最近好像进入倦怠期了。</t>
         </is>
       </c>
       <c r="P729" s="16" t="inlineStr">
         <is>
-          <t>このドラマ、年上年下カップルだよ。</t>
+          <t>最近倦怠期っぽい気がする。</t>
         </is>
       </c>
       <c r="Q729" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>Relationship talk, dramas</t>
         </is>
       </c>
       <c r="R729" s="15" t="inlineStr">
@@ -71460,17 +71460,17 @@
     <row r="730" ht="46" customHeight="1">
       <c r="A730" s="15" t="inlineStr">
         <is>
-          <t>DAT-053</t>
+          <t>DAT-052</t>
         </is>
       </c>
       <c r="B730" s="15" t="inlineStr">
         <is>
-          <t>로맨스판타지</t>
+          <t>연상연하</t>
         </is>
       </c>
       <c r="C730" s="15" t="inlineStr">
         <is>
-          <t>ro-maen-seu-pan-ta-ji</t>
+          <t>yeon-sang-yeon-ha</t>
         </is>
       </c>
       <c r="D730" s="15" t="inlineStr">
@@ -71485,62 +71485,62 @@
       </c>
       <c r="F730" s="16" t="inlineStr">
         <is>
-          <t>"Romantasy" — a hugely popular web novel and webtoon genre blending romance with a fantasy setting, often featuring reincarnation.</t>
+          <t>A relationship where one partner is noticeably older (연상) and the other younger (연하) — a common K-drama dynamic.</t>
         </is>
       </c>
       <c r="G730" s="16" t="inlineStr">
         <is>
-          <t>"Romantasía": un género de novelas web y webtoons muy popular que combina romance con un escenario de fantasía, a menudo con reencarnación.</t>
+          <t>Una relación donde una pareja es notablemente mayor (연상) y la otra más joven (연하), una dinámica común en los K-dramas.</t>
         </is>
       </c>
       <c r="H730" s="16" t="inlineStr">
         <is>
-          <t>「浪漫奇幻」——結合戀愛與奇幻背景設定、常帶有轉生元素的超人氣網路小說與網漫類型。</t>
+          <t>一方明顯年長（연상）、另一方較年輕（연하）的戀愛關係——韓劇常見的組合。</t>
         </is>
       </c>
       <c r="I730" s="16" t="inlineStr">
         <is>
-          <t>“浪漫奇幻”——结合恋爱与奇幻背景设置、常带有转生元素的超人气网络小说与网漫类型。</t>
+          <t>一方明显年长（연상）、另一方较年轻（연하）的恋爱关系——韩剧常见的组合。</t>
         </is>
       </c>
       <c r="J730" s="16" t="inlineStr">
         <is>
-          <t>「ロマンタジー」——恋愛とファンタジー設定を組み合わせた、ウェブ小説とウェブトゥーンで大人気のジャンルで、転生要素を含むことが多い。</t>
+          <t>一方が明らかに年上（연상）、もう一方が年下（연하）の恋愛関係——韓国ドラマによくある組み合わせ。</t>
         </is>
       </c>
       <c r="K730" s="16" t="inlineStr">
         <is>
-          <t>요즘 로맨스판타지 웹툰에 완전 빠졌어.</t>
+          <t>이 드라마 연상연하 커플이야.</t>
         </is>
       </c>
       <c r="L730" s="16" t="inlineStr">
         <is>
-          <t>I've totally fallen into romance-fantasy webtoons lately.</t>
+          <t>This drama has an age-gap couple.</t>
         </is>
       </c>
       <c r="M730" s="16" t="inlineStr">
         <is>
-          <t>Últimamente estoy súper metida en los webtoons de romance y fantasía.</t>
+          <t>Este drama tiene una pareja con diferencia de edad.</t>
         </is>
       </c>
       <c r="N730" s="16" t="inlineStr">
         <is>
-          <t>最近完全沉迷浪漫奇幻網漫。</t>
+          <t>這部劇是姊弟戀組合。</t>
         </is>
       </c>
       <c r="O730" s="16" t="inlineStr">
         <is>
-          <t>最近完全沉迷浪漫奇幻网漫。</t>
+          <t>这部剧是姊弟恋组合。</t>
         </is>
       </c>
       <c r="P730" s="16" t="inlineStr">
         <is>
-          <t>最近ロマンスファンタジーのウェブトゥーンにハマってる。</t>
+          <t>このドラマ、年上年下カップルだよ。</t>
         </is>
       </c>
       <c r="Q730" s="16" t="inlineStr">
         <is>
-          <t>Webtoon/web novel genre talk</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R730" s="15" t="inlineStr">
@@ -71557,17 +71557,17 @@
     <row r="731" ht="46" customHeight="1">
       <c r="A731" s="15" t="inlineStr">
         <is>
-          <t>DAT-054</t>
+          <t>DAT-053</t>
         </is>
       </c>
       <c r="B731" s="15" t="inlineStr">
         <is>
-          <t>상사병</t>
+          <t>로맨스판타지</t>
         </is>
       </c>
       <c r="C731" s="15" t="inlineStr">
         <is>
-          <t>sang-sa-byeong</t>
+          <t>ro-maen-seu-pan-ta-ji</t>
         </is>
       </c>
       <c r="D731" s="15" t="inlineStr">
@@ -71582,62 +71582,62 @@
       </c>
       <c r="F731" s="16" t="inlineStr">
         <is>
-          <t>"Longing illness" — being so consumed by romantic longing for someone that it feels like a sickness.</t>
+          <t>"Romantasy" — a hugely popular web novel and webtoon genre blending romance with a fantasy setting, often featuring reincarnation.</t>
         </is>
       </c>
       <c r="G731" s="16" t="inlineStr">
         <is>
-          <t>"Enfermedad de anhelo": estar tan consumido por el anhelo romántico por alguien que se siente como una enfermedad.</t>
+          <t>"Romantasía": un género de novelas web y webtoons muy popular que combina romance con un escenario de fantasía, a menudo con reencarnación.</t>
         </is>
       </c>
       <c r="H731" s="16" t="inlineStr">
         <is>
-          <t>「思念之病」——被對某人的思念淹沒到彷彿生病一般，相思病。</t>
+          <t>「浪漫奇幻」——結合戀愛與奇幻背景設定、常帶有轉生元素的超人氣網路小說與網漫類型。</t>
         </is>
       </c>
       <c r="I731" s="16" t="inlineStr">
         <is>
-          <t>“思念之病”——被对某人的思念淹没到仿佛生病一般，相思病。</t>
+          <t>“浪漫奇幻”——结合恋爱与奇幻背景设置、常带有转生元素的超人气网络小说与网漫类型。</t>
         </is>
       </c>
       <c r="J731" s="16" t="inlineStr">
         <is>
-          <t>「恋しさの病」——誰かへの恋しさに完全にとらわれて、まるで病気のように感じること。</t>
+          <t>「ロマンタジー」——恋愛とファンタジー設定を組み合わせた、ウェブ小説とウェブトゥーンで大人気のジャンルで、転生要素を含むことが多い。</t>
         </is>
       </c>
       <c r="K731" s="16" t="inlineStr">
         <is>
-          <t>완전 상사병 걸린 것 같아.</t>
+          <t>요즘 로맨스판타지 웹툰에 완전 빠졌어.</t>
         </is>
       </c>
       <c r="L731" s="16" t="inlineStr">
         <is>
-          <t>I think I've totally caught lovesickness.</t>
+          <t>I've totally fallen into romance-fantasy webtoons lately.</t>
         </is>
       </c>
       <c r="M731" s="16" t="inlineStr">
         <is>
-          <t>Creo que me dio mal de amores por completo.</t>
+          <t>Últimamente estoy súper metida en los webtoons de romance y fantasía.</t>
         </is>
       </c>
       <c r="N731" s="16" t="inlineStr">
         <is>
-          <t>我好像得了相思病。</t>
+          <t>最近完全沉迷浪漫奇幻網漫。</t>
         </is>
       </c>
       <c r="O731" s="16" t="inlineStr">
         <is>
-          <t>我好像得了相思病。</t>
+          <t>最近完全沉迷浪漫奇幻网漫。</t>
         </is>
       </c>
       <c r="P731" s="16" t="inlineStr">
         <is>
-          <t>完全に恋煩いにかかったみたい。</t>
+          <t>最近ロマンスファンタジーのウェブトゥーンにハマってる。</t>
         </is>
       </c>
       <c r="Q731" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk, casual speech</t>
+          <t>Webtoon/web novel genre talk</t>
         </is>
       </c>
       <c r="R731" s="15" t="inlineStr">
@@ -71654,17 +71654,17 @@
     <row r="732" ht="46" customHeight="1">
       <c r="A732" s="15" t="inlineStr">
         <is>
-          <t>DAT-055</t>
+          <t>DAT-054</t>
         </is>
       </c>
       <c r="B732" s="15" t="inlineStr">
         <is>
-          <t>첫눈에반하다</t>
+          <t>상사병</t>
         </is>
       </c>
       <c r="C732" s="15" t="inlineStr">
         <is>
-          <t>cheot-nun-e-ban-ha-da</t>
+          <t>sang-sa-byeong</t>
         </is>
       </c>
       <c r="D732" s="15" t="inlineStr">
@@ -71679,62 +71679,62 @@
       </c>
       <c r="F732" s="16" t="inlineStr">
         <is>
-          <t>Falling in love with someone the very first moment you see them.</t>
+          <t>"Longing illness" — being so consumed by romantic longing for someone that it feels like a sickness.</t>
         </is>
       </c>
       <c r="G732" s="16" t="inlineStr">
         <is>
-          <t>Enamorarse de alguien desde el primer momento en que lo ves.</t>
+          <t>"Enfermedad de anhelo": estar tan consumido por el anhelo romántico por alguien que se siente como una enfermedad.</t>
         </is>
       </c>
       <c r="H732" s="16" t="inlineStr">
         <is>
-          <t>第一眼看到某人就墜入愛河，一見鍾情。</t>
+          <t>「思念之病」——被對某人的思念淹沒到彷彿生病一般，相思病。</t>
         </is>
       </c>
       <c r="I732" s="16" t="inlineStr">
         <is>
-          <t>第一眼看到某人就坠入爱河，一见钟情。</t>
+          <t>“思念之病”——被对某人的思念淹没到仿佛生病一般，相思病。</t>
         </is>
       </c>
       <c r="J732" s="16" t="inlineStr">
         <is>
-          <t>相手を初めて見た瞬間に恋に落ちること。</t>
+          <t>「恋しさの病」——誰かへの恋しさに完全にとらわれて、まるで病気のように感じること。</t>
         </is>
       </c>
       <c r="K732" s="16" t="inlineStr">
         <is>
-          <t>첫눈에반했다는 게 무슨 느낌인지 이제 알겠어.</t>
+          <t>완전 상사병 걸린 것 같아.</t>
         </is>
       </c>
       <c r="L732" s="16" t="inlineStr">
         <is>
-          <t>I finally understand what love at first sight feels like.</t>
+          <t>I think I've totally caught lovesickness.</t>
         </is>
       </c>
       <c r="M732" s="16" t="inlineStr">
         <is>
-          <t>Por fin entiendo qué se siente el amor a primera vista.</t>
+          <t>Creo que me dio mal de amores por completo.</t>
         </is>
       </c>
       <c r="N732" s="16" t="inlineStr">
         <is>
-          <t>現在終於懂一見鍾情是什麼感覺了。</t>
+          <t>我好像得了相思病。</t>
         </is>
       </c>
       <c r="O732" s="16" t="inlineStr">
         <is>
-          <t>现在终于懂一见钟情是什么感觉了。</t>
+          <t>我好像得了相思病。</t>
         </is>
       </c>
       <c r="P732" s="16" t="inlineStr">
         <is>
-          <t>一目惚れってどんな感じかやっとわかった。</t>
+          <t>完全に恋煩いにかかったみたい。</t>
         </is>
       </c>
       <c r="Q732" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>K-drama trope talk, casual speech</t>
         </is>
       </c>
       <c r="R732" s="15" t="inlineStr">
@@ -71751,17 +71751,17 @@
     <row r="733" ht="46" customHeight="1">
       <c r="A733" s="15" t="inlineStr">
         <is>
-          <t>DAT-056</t>
+          <t>DAT-055</t>
         </is>
       </c>
       <c r="B733" s="15" t="inlineStr">
         <is>
-          <t>고백</t>
+          <t>첫눈에반하다</t>
         </is>
       </c>
       <c r="C733" s="15" t="inlineStr">
         <is>
-          <t>go-baek</t>
+          <t>cheot-nun-e-ban-ha-da</t>
         </is>
       </c>
       <c r="D733" s="15" t="inlineStr">
@@ -71776,62 +71776,62 @@
       </c>
       <c r="F733" s="16" t="inlineStr">
         <is>
-          <t>Confessing romantic feelings to someone.</t>
+          <t>Falling in love with someone the very first moment you see them.</t>
         </is>
       </c>
       <c r="G733" s="16" t="inlineStr">
         <is>
-          <t>Confesar sentimientos románticos a alguien.</t>
+          <t>Enamorarse de alguien desde el primer momento en que lo ves.</t>
         </is>
       </c>
       <c r="H733" s="16" t="inlineStr">
         <is>
-          <t>向某人表白自己的戀愛心意，告白。</t>
+          <t>第一眼看到某人就墜入愛河，一見鍾情。</t>
         </is>
       </c>
       <c r="I733" s="16" t="inlineStr">
         <is>
-          <t>向某人表白自己的恋爱心意，告白。</t>
+          <t>第一眼看到某人就坠入爱河，一见钟情。</t>
         </is>
       </c>
       <c r="J733" s="16" t="inlineStr">
         <is>
-          <t>相手に恋愛感情を打ち明けること。</t>
+          <t>相手を初めて見た瞬間に恋に落ちること。</t>
         </is>
       </c>
       <c r="K733" s="16" t="inlineStr">
         <is>
-          <t>드디어 고백했어!</t>
+          <t>첫눈에반했다는 게 무슨 느낌인지 이제 알겠어.</t>
         </is>
       </c>
       <c r="L733" s="16" t="inlineStr">
         <is>
-          <t>I finally confessed my feelings!</t>
+          <t>I finally understand what love at first sight feels like.</t>
         </is>
       </c>
       <c r="M733" s="16" t="inlineStr">
         <is>
-          <t>¡Por fin confesé mis sentimientos!</t>
+          <t>Por fin entiendo qué se siente el amor a primera vista.</t>
         </is>
       </c>
       <c r="N733" s="16" t="inlineStr">
         <is>
-          <t>終於告白了！</t>
+          <t>現在終於懂一見鍾情是什麼感覺了。</t>
         </is>
       </c>
       <c r="O733" s="16" t="inlineStr">
         <is>
-          <t>终于告白了！</t>
+          <t>现在终于懂一见钟情是什么感觉了。</t>
         </is>
       </c>
       <c r="P733" s="16" t="inlineStr">
         <is>
-          <t>ついに告白した！</t>
+          <t>一目惚れってどんな感じかやっとわかった。</t>
         </is>
       </c>
       <c r="Q733" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk, casual dating talk</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R733" s="15" t="inlineStr">
@@ -71848,17 +71848,17 @@
     <row r="734" ht="46" customHeight="1">
       <c r="A734" s="15" t="inlineStr">
         <is>
-          <t>DAT-057</t>
+          <t>DAT-056</t>
         </is>
       </c>
       <c r="B734" s="15" t="inlineStr">
         <is>
-          <t>데이트코스</t>
+          <t>고백</t>
         </is>
       </c>
       <c r="C734" s="15" t="inlineStr">
         <is>
-          <t>de-i-teu-ko-seu</t>
+          <t>go-baek</t>
         </is>
       </c>
       <c r="D734" s="15" t="inlineStr">
@@ -71873,62 +71873,62 @@
       </c>
       <c r="F734" s="16" t="inlineStr">
         <is>
-          <t>"Date course" — a planned sequence of activities and locations for a date.</t>
+          <t>Confessing romantic feelings to someone.</t>
         </is>
       </c>
       <c r="G734" s="16" t="inlineStr">
         <is>
-          <t>"Curso de cita": una secuencia planeada de actividades y lugares para una cita.</t>
+          <t>Confesar sentimientos románticos a alguien.</t>
         </is>
       </c>
       <c r="H734" s="16" t="inlineStr">
         <is>
-          <t>事先規劃好的約會活動與地點行程，約會行程。</t>
+          <t>向某人表白自己的戀愛心意，告白。</t>
         </is>
       </c>
       <c r="I734" s="16" t="inlineStr">
         <is>
-          <t>事先规划好的约会活动与地点行程，约会行程。</t>
+          <t>向某人表白自己的恋爱心意，告白。</t>
         </is>
       </c>
       <c r="J734" s="16" t="inlineStr">
         <is>
-          <t>「デートコース」——事前に計画されたデートの活動や場所の順序。</t>
+          <t>相手に恋愛感情を打ち明けること。</t>
         </is>
       </c>
       <c r="K734" s="16" t="inlineStr">
         <is>
-          <t>데이트코스 다 짜놨어.</t>
+          <t>드디어 고백했어!</t>
         </is>
       </c>
       <c r="L734" s="16" t="inlineStr">
         <is>
-          <t>I already planned out the whole date itinerary.</t>
+          <t>I finally confessed my feelings!</t>
         </is>
       </c>
       <c r="M734" s="16" t="inlineStr">
         <is>
-          <t>Ya planeé todo el itinerario de la cita.</t>
+          <t>¡Por fin confesé mis sentimientos!</t>
         </is>
       </c>
       <c r="N734" s="16" t="inlineStr">
         <is>
-          <t>已經規劃好整個約會行程了。</t>
+          <t>終於告白了！</t>
         </is>
       </c>
       <c r="O734" s="16" t="inlineStr">
         <is>
-          <t>已经规划好整个约会行程了。</t>
+          <t>终于告白了！</t>
         </is>
       </c>
       <c r="P734" s="16" t="inlineStr">
         <is>
-          <t>デートコース、全部計画済み。</t>
+          <t>ついに告白した！</t>
         </is>
       </c>
       <c r="Q734" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>K-drama trope talk, casual dating talk</t>
         </is>
       </c>
       <c r="R734" s="15" t="inlineStr">
@@ -71945,17 +71945,17 @@
     <row r="735" ht="46" customHeight="1">
       <c r="A735" s="15" t="inlineStr">
         <is>
-          <t>DAT-058</t>
+          <t>DAT-057</t>
         </is>
       </c>
       <c r="B735" s="15" t="inlineStr">
         <is>
-          <t>백일</t>
+          <t>데이트코스</t>
         </is>
       </c>
       <c r="C735" s="15" t="inlineStr">
         <is>
-          <t>baek-il</t>
+          <t>de-i-teu-ko-seu</t>
         </is>
       </c>
       <c r="D735" s="15" t="inlineStr">
@@ -71970,62 +71970,62 @@
       </c>
       <c r="F735" s="16" t="inlineStr">
         <is>
-          <t>The 100-day relationship milestone, commonly celebrated by Korean couples.</t>
+          <t>"Date course" — a planned sequence of activities and locations for a date.</t>
         </is>
       </c>
       <c r="G735" s="16" t="inlineStr">
         <is>
-          <t>El hito de los 100 días de relación, comúnmente celebrado por las parejas coreanas.</t>
+          <t>"Curso de cita": una secuencia planeada de actividades y lugares para una cita.</t>
         </is>
       </c>
       <c r="H735" s="16" t="inlineStr">
         <is>
-          <t>韓國情侶常慶祝的交往一百天紀念日。</t>
+          <t>事先規劃好的約會活動與地點行程，約會行程。</t>
         </is>
       </c>
       <c r="I735" s="16" t="inlineStr">
         <is>
-          <t>韩国情侣常庆祝的交往一百天纪念日。</t>
+          <t>事先规划好的约会活动与地点行程，约会行程。</t>
         </is>
       </c>
       <c r="J735" s="16" t="inlineStr">
         <is>
-          <t>韓国のカップルがよく祝う、交際100日の記念日。</t>
+          <t>「デートコース」——事前に計画されたデートの活動や場所の順序。</t>
         </is>
       </c>
       <c r="K735" s="16" t="inlineStr">
         <is>
-          <t>이번 주 백일이라 선물 준비했어.</t>
+          <t>데이트코스 다 짜놨어.</t>
         </is>
       </c>
       <c r="L735" s="16" t="inlineStr">
         <is>
-          <t>This week is our 100-day anniversary, so I prepared a gift.</t>
+          <t>I already planned out the whole date itinerary.</t>
         </is>
       </c>
       <c r="M735" s="16" t="inlineStr">
         <is>
-          <t>Esta semana cumplimos 100 días, así que preparé un regalo.</t>
+          <t>Ya planeé todo el itinerario de la cita.</t>
         </is>
       </c>
       <c r="N735" s="16" t="inlineStr">
         <is>
-          <t>這禮拜是百日紀念，準備了禮物。</t>
+          <t>已經規劃好整個約會行程了。</t>
         </is>
       </c>
       <c r="O735" s="16" t="inlineStr">
         <is>
-          <t>这礼拜是百日纪念，准备了礼物。</t>
+          <t>已经规划好整个约会行程了。</t>
         </is>
       </c>
       <c r="P735" s="16" t="inlineStr">
         <is>
-          <t>今週100日記念日だから、プレゼント準備した。</t>
+          <t>デートコース、全部計画済み。</t>
         </is>
       </c>
       <c r="Q735" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, casual dating talk</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R735" s="15" t="inlineStr">
@@ -72042,17 +72042,17 @@
     <row r="736" ht="46" customHeight="1">
       <c r="A736" s="15" t="inlineStr">
         <is>
-          <t>DAT-059</t>
+          <t>DAT-058</t>
         </is>
       </c>
       <c r="B736" s="15" t="inlineStr">
         <is>
-          <t>연애세포</t>
+          <t>백일</t>
         </is>
       </c>
       <c r="C736" s="15" t="inlineStr">
         <is>
-          <t>yeon-ae-se-po</t>
+          <t>baek-il</t>
         </is>
       </c>
       <c r="D736" s="15" t="inlineStr">
@@ -72067,62 +72067,62 @@
       </c>
       <c r="F736" s="16" t="inlineStr">
         <is>
-          <t>"Romance cells" — one's inner drive or interest in dating and romance.</t>
+          <t>The 100-day relationship milestone, commonly celebrated by Korean couples.</t>
         </is>
       </c>
       <c r="G736" s="16" t="inlineStr">
         <is>
-          <t>"Células de romance": el impulso o interés interno de alguien por las citas y el romance.</t>
+          <t>El hito de los 100 días de relación, comúnmente celebrado por las parejas coreanas.</t>
         </is>
       </c>
       <c r="H736" s="16" t="inlineStr">
         <is>
-          <t>「戀愛細胞」——一個人對談戀愛、交往的內在動力或興趣。</t>
+          <t>韓國情侶常慶祝的交往一百天紀念日。</t>
         </is>
       </c>
       <c r="I736" s="16" t="inlineStr">
         <is>
-          <t>“恋爱细胞”——一个人对谈恋爱、交往的内在动力或兴趣。</t>
+          <t>韩国情侣常庆祝的交往一百天纪念日。</t>
         </is>
       </c>
       <c r="J736" s="16" t="inlineStr">
         <is>
-          <t>「恋愛の細胞」——恋愛やデートへの内なる意欲や興味。</t>
+          <t>韓国のカップルがよく祝う、交際100日の記念日。</t>
         </is>
       </c>
       <c r="K736" s="16" t="inlineStr">
         <is>
-          <t>연애세포가 다 죽은 것 같아.</t>
+          <t>이번 주 백일이라 선물 준비했어.</t>
         </is>
       </c>
       <c r="L736" s="16" t="inlineStr">
         <is>
-          <t>I feel like my romance drive has completely died.</t>
+          <t>This week is our 100-day anniversary, so I prepared a gift.</t>
         </is>
       </c>
       <c r="M736" s="16" t="inlineStr">
         <is>
-          <t>Siento que mi interés por el romance murió por completo.</t>
+          <t>Esta semana cumplimos 100 días, así que preparé un regalo.</t>
         </is>
       </c>
       <c r="N736" s="16" t="inlineStr">
         <is>
-          <t>感覺我的戀愛細胞都死光了。</t>
+          <t>這禮拜是百日紀念，準備了禮物。</t>
         </is>
       </c>
       <c r="O736" s="16" t="inlineStr">
         <is>
-          <t>感觉我的恋爱细胞都死光了。</t>
+          <t>这礼拜是百日纪念，准备了礼物。</t>
         </is>
       </c>
       <c r="P736" s="16" t="inlineStr">
         <is>
-          <t>恋愛細胞が全部死んだ気がする。</t>
+          <t>今週100日記念日だから、プレゼント準備した。</t>
         </is>
       </c>
       <c r="Q736" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Couple culture, casual dating talk</t>
         </is>
       </c>
       <c r="R736" s="15" t="inlineStr">
@@ -72139,17 +72139,17 @@
     <row r="737" ht="46" customHeight="1">
       <c r="A737" s="15" t="inlineStr">
         <is>
-          <t>DAT-060</t>
+          <t>DAT-059</t>
         </is>
       </c>
       <c r="B737" s="15" t="inlineStr">
         <is>
-          <t>순정만화</t>
+          <t>연애세포</t>
         </is>
       </c>
       <c r="C737" s="15" t="inlineStr">
         <is>
-          <t>sun-jeong-man-hwa</t>
+          <t>yeon-ae-se-po</t>
         </is>
       </c>
       <c r="D737" s="15" t="inlineStr">
@@ -72164,62 +72164,62 @@
       </c>
       <c r="F737" s="16" t="inlineStr">
         <is>
-          <t>"Pure-love comic" — a genre label for sweet, innocent romance stories, often used to describe an idealized real-life romance.</t>
+          <t>"Romance cells" — one's inner drive or interest in dating and romance.</t>
         </is>
       </c>
       <c r="G737" s="16" t="inlineStr">
         <is>
-          <t>"Cómic de amor puro": una etiqueta de género para historias de romance dulces e inocentes, usada a menudo para describir un romance real idealizado.</t>
+          <t>"Células de romance": el impulso o interés interno de alguien por las citas y el romance.</t>
         </is>
       </c>
       <c r="H737" s="16" t="inlineStr">
         <is>
-          <t>「純愛漫畫」——形容甜美、純真的戀愛故事類型，也用來形容如漫畫般理想化的真實戀情。</t>
+          <t>「戀愛細胞」——一個人對談戀愛、交往的內在動力或興趣。</t>
         </is>
       </c>
       <c r="I737" s="16" t="inlineStr">
         <is>
-          <t>“纯爱漫画”——形容甜美、纯真的恋爱故事类型，也用来形容如漫画般理想化的真实恋情。</t>
+          <t>“恋爱细胞”——一个人对谈恋爱、交往的内在动力或兴趣。</t>
         </is>
       </c>
       <c r="J737" s="16" t="inlineStr">
         <is>
-          <t>「純粋な愛の漫画」——甘く純粋な恋愛物語のジャンルラベルで、理想化された現実の恋愛を表現するのにも使われる。</t>
+          <t>「恋愛の細胞」——恋愛やデートへの内なる意欲や興味。</t>
         </is>
       </c>
       <c r="K737" s="16" t="inlineStr">
         <is>
-          <t>저 커플 완전 순정만화 그 자체야.</t>
+          <t>연애세포가 다 죽은 것 같아.</t>
         </is>
       </c>
       <c r="L737" s="16" t="inlineStr">
         <is>
-          <t>That couple is literally a pure-love comic come to life.</t>
+          <t>I feel like my romance drive has completely died.</t>
         </is>
       </c>
       <c r="M737" s="16" t="inlineStr">
         <is>
-          <t>Esa pareja es literalmente un cómic de amor puro hecho realidad.</t>
+          <t>Siento que mi interés por el romance murió por completo.</t>
         </is>
       </c>
       <c r="N737" s="16" t="inlineStr">
         <is>
-          <t>那對情侶完全就是純愛漫畫本人。</t>
+          <t>感覺我的戀愛細胞都死光了。</t>
         </is>
       </c>
       <c r="O737" s="16" t="inlineStr">
         <is>
-          <t>那对情侣完全就是纯爱漫画本人。</t>
+          <t>感觉我的恋爱细胞都死光了。</t>
         </is>
       </c>
       <c r="P737" s="16" t="inlineStr">
         <is>
-          <t>あのカップル、完全に純愛漫画そのものだよ。</t>
+          <t>恋愛細胞が全部死んだ気がする。</t>
         </is>
       </c>
       <c r="Q737" s="16" t="inlineStr">
         <is>
-          <t>K-drama/romance trope talk</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R737" s="15" t="inlineStr">
@@ -72236,17 +72236,17 @@
     <row r="738" ht="46" customHeight="1">
       <c r="A738" s="15" t="inlineStr">
         <is>
-          <t>DAT-061</t>
+          <t>DAT-060</t>
         </is>
       </c>
       <c r="B738" s="15" t="inlineStr">
         <is>
-          <t>심장저격</t>
+          <t>순정만화</t>
         </is>
       </c>
       <c r="C738" s="15" t="inlineStr">
         <is>
-          <t>sim-jang-jeo-gyeok</t>
+          <t>sun-jeong-man-hwa</t>
         </is>
       </c>
       <c r="D738" s="15" t="inlineStr">
@@ -72261,62 +72261,62 @@
       </c>
       <c r="F738" s="16" t="inlineStr">
         <is>
-          <t>"Heart sniper" — something that strikes directly at your heart, usually describing a romantic or swoon-worthy moment.</t>
+          <t>"Pure-love comic" — a genre label for sweet, innocent romance stories, often used to describe an idealized real-life romance.</t>
         </is>
       </c>
       <c r="G738" s="16" t="inlineStr">
         <is>
-          <t>"Francotirador del corazón": algo que golpea directamente tu corazón, generalmente describiendo un momento romántico o que hace suspirar.</t>
+          <t>"Cómic de amor puro": una etiqueta de género para historias de romance dulces e inocentes, usada a menudo para describir un romance real idealizado.</t>
         </is>
       </c>
       <c r="H738" s="16" t="inlineStr">
         <is>
-          <t>「心臟狙擊」——直接命中內心、通常用來形容浪漫或令人心動的瞬間。</t>
+          <t>「純愛漫畫」——形容甜美、純真的戀愛故事類型，也用來形容如漫畫般理想化的真實戀情。</t>
         </is>
       </c>
       <c r="I738" s="16" t="inlineStr">
         <is>
-          <t>“心脏狙击”——直接命中内心、通常用来形容浪漫或令人心动的瞬间。</t>
+          <t>“纯爱漫画”——形容甜美、纯真的恋爱故事类型，也用来形容如漫画般理想化的真实恋情。</t>
         </is>
       </c>
       <c r="J738" s="16" t="inlineStr">
         <is>
-          <t>「心臓狙撃」——ロマンチックで胸きゅんする瞬間を表す時によく使われる、直接心臓を突き刺すようなもの。</t>
+          <t>「純粋な愛の漫画」——甘く純粋な恋愛物語のジャンルラベルで、理想化された現実の恋愛を表現するのにも使われる。</t>
         </is>
       </c>
       <c r="K738" s="16" t="inlineStr">
         <is>
-          <t>그 대사 완전 심장저격이었어.</t>
+          <t>저 커플 완전 순정만화 그 자체야.</t>
         </is>
       </c>
       <c r="L738" s="16" t="inlineStr">
         <is>
-          <t>That line was a total heart sniper.</t>
+          <t>That couple is literally a pure-love comic come to life.</t>
         </is>
       </c>
       <c r="M738" s="16" t="inlineStr">
         <is>
-          <t>Esa frase fue un disparo directo al corazón.</t>
+          <t>Esa pareja es literalmente un cómic de amor puro hecho realidad.</t>
         </is>
       </c>
       <c r="N738" s="16" t="inlineStr">
         <is>
-          <t>那句台詞完全是心臟狙擊。</t>
+          <t>那對情侶完全就是純愛漫畫本人。</t>
         </is>
       </c>
       <c r="O738" s="16" t="inlineStr">
         <is>
-          <t>那句台词完全是心脏狙击。</t>
+          <t>那对情侣完全就是纯爱漫画本人。</t>
         </is>
       </c>
       <c r="P738" s="16" t="inlineStr">
         <is>
-          <t>あのセリフ、完全に心臓狙撃だった。</t>
+          <t>あのカップル、完全に純愛漫画そのものだよ。</t>
         </is>
       </c>
       <c r="Q738" s="16" t="inlineStr">
         <is>
-          <t>K-drama reactions</t>
+          <t>K-drama/romance trope talk</t>
         </is>
       </c>
       <c r="R738" s="15" t="inlineStr">
@@ -72333,17 +72333,17 @@
     <row r="739" ht="46" customHeight="1">
       <c r="A739" s="15" t="inlineStr">
         <is>
-          <t>DAT-062</t>
+          <t>DAT-061</t>
         </is>
       </c>
       <c r="B739" s="15" t="inlineStr">
         <is>
-          <t>애교</t>
+          <t>심장저격</t>
         </is>
       </c>
       <c r="C739" s="15" t="inlineStr">
         <is>
-          <t>ae-gyo</t>
+          <t>sim-jang-jeo-gyeok</t>
         </is>
       </c>
       <c r="D739" s="15" t="inlineStr">
@@ -72358,62 +72358,62 @@
       </c>
       <c r="F739" s="16" t="inlineStr">
         <is>
-          <t>Deliberately cute, affectionate speech or behavior — a cutesy voice, pouty expressions, or playful gestures used to charm someone.</t>
+          <t>"Heart sniper" — something that strikes directly at your heart, usually describing a romantic or swoon-worthy moment.</t>
         </is>
       </c>
       <c r="G739" s="16" t="inlineStr">
         <is>
-          <t>Habla o comportamiento tierno y afectuoso deliberado: una voz melosa, expresiones de puchero o gestos juguetones usados para encantar a alguien.</t>
+          <t>"Francotirador del corazón": algo que golpea directamente tu corazón, generalmente describiendo un momento romántico o que hace suspirar.</t>
         </is>
       </c>
       <c r="H739" s="16" t="inlineStr">
         <is>
-          <t>刻意展現可愛、撒嬌的言行——嗲聲嗲氣、嘟嘴或俏皮動作，用來討人喜歡，撒嬌。</t>
+          <t>「心臟狙擊」——直接命中內心、通常用來形容浪漫或令人心動的瞬間。</t>
         </is>
       </c>
       <c r="I739" s="16" t="inlineStr">
         <is>
-          <t>刻意展现可爱、撒娇的言行——嗲声嗲气、嘟嘴或俏皮动作，用来讨人喜欢，撒娇。</t>
+          <t>“心脏狙击”——直接命中内心、通常用来形容浪漫或令人心动的瞬间。</t>
         </is>
       </c>
       <c r="J739" s="16" t="inlineStr">
         <is>
-          <t>わざと可愛く、愛情を込めた話し方や振る舞い——甘えた声、拗ねた表情、遊び心のあるジェスチャーで相手を魅了すること。</t>
+          <t>「心臓狙撃」——ロマンチックで胸きゅんする瞬間を表す時によく使われる、直接心臓を突き刺すようなもの。</t>
         </is>
       </c>
       <c r="K739" s="16" t="inlineStr">
         <is>
-          <t>애교 좀 부려봐!</t>
+          <t>그 대사 완전 심장저격이었어.</t>
         </is>
       </c>
       <c r="L739" s="16" t="inlineStr">
         <is>
-          <t>Do some aegyo for me!</t>
+          <t>That line was a total heart sniper.</t>
         </is>
       </c>
       <c r="M739" s="16" t="inlineStr">
         <is>
-          <t>¡Hazme un poco de aegyo!</t>
+          <t>Esa frase fue un disparo directo al corazón.</t>
         </is>
       </c>
       <c r="N739" s="16" t="inlineStr">
         <is>
-          <t>撒嬌一下嘛！</t>
+          <t>那句台詞完全是心臟狙擊。</t>
         </is>
       </c>
       <c r="O739" s="16" t="inlineStr">
         <is>
-          <t>撒娇一下嘛！</t>
+          <t>那句台词完全是心脏狙击。</t>
         </is>
       </c>
       <c r="P739" s="16" t="inlineStr">
         <is>
-          <t>愛嬌見せてよ！</t>
+          <t>あのセリフ、完全に心臓狙撃だった。</t>
         </is>
       </c>
       <c r="Q739" s="16" t="inlineStr">
         <is>
-          <t>Variety shows, couple culture</t>
+          <t>K-drama reactions</t>
         </is>
       </c>
       <c r="R739" s="15" t="inlineStr">
@@ -72430,17 +72430,17 @@
     <row r="740" ht="46" customHeight="1">
       <c r="A740" s="15" t="inlineStr">
         <is>
-          <t>DAT-063</t>
+          <t>DAT-062</t>
         </is>
       </c>
       <c r="B740" s="15" t="inlineStr">
         <is>
-          <t>사랑꾼</t>
+          <t>애교</t>
         </is>
       </c>
       <c r="C740" s="15" t="inlineStr">
         <is>
-          <t>sa-rang-kkun</t>
+          <t>ae-gyo</t>
         </is>
       </c>
       <c r="D740" s="15" t="inlineStr">
@@ -72455,62 +72455,62 @@
       </c>
       <c r="F740" s="16" t="inlineStr">
         <is>
-          <t>"Love expert" — someone devotedly romantic who dotes openly on their partner.</t>
+          <t>Deliberately cute, affectionate speech or behavior — a cutesy voice, pouty expressions, or playful gestures used to charm someone.</t>
         </is>
       </c>
       <c r="G740" s="16" t="inlineStr">
         <is>
-          <t>"Experto en amor": alguien devotamente romántico que consiente abiertamente a su pareja.</t>
+          <t>Habla o comportamiento tierno y afectuoso deliberado: una voz melosa, expresiones de puchero o gestos juguetones usados para encantar a alguien.</t>
         </is>
       </c>
       <c r="H740" s="16" t="inlineStr">
         <is>
-          <t>「愛情達人」——全心全意投入戀愛、公開寵愛另一半的人。</t>
+          <t>刻意展現可愛、撒嬌的言行——嗲聲嗲氣、嘟嘴或俏皮動作，用來討人喜歡，撒嬌。</t>
         </is>
       </c>
       <c r="I740" s="16" t="inlineStr">
         <is>
-          <t>“爱情达人”——全心全意投入恋爱、公开宠爱另一半的人。</t>
+          <t>刻意展现可爱、撒娇的言行——嗲声嗲气、嘟嘴或俏皮动作，用来讨人喜欢，撒娇。</t>
         </is>
       </c>
       <c r="J740" s="16" t="inlineStr">
         <is>
-          <t>「愛の達人」——恋人に対して献身的で、公然と甘やかす人。</t>
+          <t>わざと可愛く、愛情を込めた話し方や振る舞い——甘えた声、拗ねた表情、遊び心のあるジェスチャーで相手を魅了すること。</t>
         </is>
       </c>
       <c r="K740" s="16" t="inlineStr">
         <is>
-          <t>저 사람 완전 사랑꾼이야.</t>
+          <t>애교 좀 부려봐!</t>
         </is>
       </c>
       <c r="L740" s="16" t="inlineStr">
         <is>
-          <t>That person is a total devoted romantic.</t>
+          <t>Do some aegyo for me!</t>
         </is>
       </c>
       <c r="M740" s="16" t="inlineStr">
         <is>
-          <t>Esa persona es completamente entregada en el amor.</t>
+          <t>¡Hazme un poco de aegyo!</t>
         </is>
       </c>
       <c r="N740" s="16" t="inlineStr">
         <is>
-          <t>那個人完全是寵愛型戀人。</t>
+          <t>撒嬌一下嘛！</t>
         </is>
       </c>
       <c r="O740" s="16" t="inlineStr">
         <is>
-          <t>那个人完全是宠爱型恋人。</t>
+          <t>撒娇一下嘛！</t>
         </is>
       </c>
       <c r="P740" s="16" t="inlineStr">
         <is>
-          <t>あの人は本当に愛情深いタイプだよ。</t>
+          <t>愛嬌見せてよ！</t>
         </is>
       </c>
       <c r="Q740" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, variety shows</t>
+          <t>Variety shows, couple culture</t>
         </is>
       </c>
       <c r="R740" s="15" t="inlineStr">
@@ -72527,17 +72527,17 @@
     <row r="741" ht="46" customHeight="1">
       <c r="A741" s="15" t="inlineStr">
         <is>
-          <t>DAT-064</t>
+          <t>DAT-063</t>
         </is>
       </c>
       <c r="B741" s="15" t="inlineStr">
         <is>
-          <t>잉꼬부부</t>
+          <t>사랑꾼</t>
         </is>
       </c>
       <c r="C741" s="15" t="inlineStr">
         <is>
-          <t>ing-kko-bu-bu</t>
+          <t>sa-rang-kkun</t>
         </is>
       </c>
       <c r="D741" s="15" t="inlineStr">
@@ -72552,62 +72552,62 @@
       </c>
       <c r="F741" s="16" t="inlineStr">
         <is>
-          <t>"Lovebird couple" — a married couple who are openly and consistently affectionate with each other.</t>
+          <t>"Love expert" — someone devotedly romantic who dotes openly on their partner.</t>
         </is>
       </c>
       <c r="G741" s="16" t="inlineStr">
         <is>
-          <t>"Pareja de pájaros del amor": una pareja casada que es abierta y constantemente cariñosa entre sí.</t>
+          <t>"Experto en amor": alguien devotamente romántico que consiente abiertamente a su pareja.</t>
         </is>
       </c>
       <c r="H741" s="16" t="inlineStr">
         <is>
-          <t>「鴛鴦夫妻」——公開且持續展現親密恩愛的夫妻，恩愛夫妻。</t>
+          <t>「愛情達人」——全心全意投入戀愛、公開寵愛另一半的人。</t>
         </is>
       </c>
       <c r="I741" s="16" t="inlineStr">
         <is>
-          <t>“鸳鸯夫妻”——公开且持续展现亲密恩爱的夫妻，恩爱夫妻。</t>
+          <t>“爱情达人”——全心全意投入恋爱、公开宠爱另一半的人。</t>
         </is>
       </c>
       <c r="J741" s="16" t="inlineStr">
         <is>
-          <t>「インコ夫婦」——常に公然と愛情表現をし合う夫婦。</t>
+          <t>「愛の達人」——恋人に対して献身的で、公然と甘やかす人。</t>
         </is>
       </c>
       <c r="K741" s="16" t="inlineStr">
         <is>
-          <t>저 부부 완전 잉꼬부부야.</t>
+          <t>저 사람 완전 사랑꾼이야.</t>
         </is>
       </c>
       <c r="L741" s="16" t="inlineStr">
         <is>
-          <t>That couple is total lovebirds.</t>
+          <t>That person is a total devoted romantic.</t>
         </is>
       </c>
       <c r="M741" s="16" t="inlineStr">
         <is>
-          <t>Esa pareja es como tortolitos, siempre cariñosos.</t>
+          <t>Esa persona es completamente entregada en el amor.</t>
         </is>
       </c>
       <c r="N741" s="16" t="inlineStr">
         <is>
-          <t>那對夫妻完全是恩愛夫妻。</t>
+          <t>那個人完全是寵愛型戀人。</t>
         </is>
       </c>
       <c r="O741" s="16" t="inlineStr">
         <is>
-          <t>那对夫妻完全是恩爱夫妻。</t>
+          <t>那个人完全是宠爱型恋人。</t>
         </is>
       </c>
       <c r="P741" s="16" t="inlineStr">
         <is>
-          <t>あの夫婦、完全におしどり夫婦だよね。</t>
+          <t>あの人は本当に愛情深いタイプだよ。</t>
         </is>
       </c>
       <c r="Q741" s="16" t="inlineStr">
         <is>
-          <t>Celebrity couple talk</t>
+          <t>Couple culture, variety shows</t>
         </is>
       </c>
       <c r="R741" s="15" t="inlineStr">
@@ -72624,17 +72624,17 @@
     <row r="742" ht="46" customHeight="1">
       <c r="A742" s="15" t="inlineStr">
         <is>
-          <t>DAT-065</t>
+          <t>DAT-064</t>
         </is>
       </c>
       <c r="B742" s="15" t="inlineStr">
         <is>
-          <t>남친룩</t>
+          <t>잉꼬부부</t>
         </is>
       </c>
       <c r="C742" s="15" t="inlineStr">
         <is>
-          <t>nam-chin-ruk</t>
+          <t>ing-kko-bu-bu</t>
         </is>
       </c>
       <c r="D742" s="15" t="inlineStr">
@@ -72649,62 +72649,62 @@
       </c>
       <c r="F742" s="16" t="inlineStr">
         <is>
-          <t>"Boyfriend look" — a fashion style mimicking oversized, borrowed-looking boyfriend clothing.</t>
+          <t>"Lovebird couple" — a married couple who are openly and consistently affectionate with each other.</t>
         </is>
       </c>
       <c r="G742" s="16" t="inlineStr">
         <is>
-          <t>"Look de novio": un estilo de moda que imita ropa holgada, como si fuera prestada por el novio.</t>
+          <t>"Pareja de pájaros del amor": una pareja casada que es abierta y constantemente cariñosa entre sí.</t>
         </is>
       </c>
       <c r="H742" s="16" t="inlineStr">
         <is>
-          <t>「男友風」——模仿男友寬鬆、彷彿借穿男友衣服的穿搭風格。</t>
+          <t>「鴛鴦夫妻」——公開且持續展現親密恩愛的夫妻，恩愛夫妻。</t>
         </is>
       </c>
       <c r="I742" s="16" t="inlineStr">
         <is>
-          <t>“男友风”——模仿男友宽松、仿佛借穿男友衣服的穿搭风格。</t>
+          <t>“鸳鸯夫妻”——公开且持续展现亲密恩爱的夫妻，恩爱夫妻。</t>
         </is>
       </c>
       <c r="J742" s="16" t="inlineStr">
         <is>
-          <t>「彼氏ルック」——彼氏の服を借りたような、オーバーサイズのファッションスタイル。</t>
+          <t>「インコ夫婦」——常に公然と愛情表現をし合う夫婦。</t>
         </is>
       </c>
       <c r="K742" s="16" t="inlineStr">
         <is>
-          <t>오늘 남친룩으로 입어봤어.</t>
+          <t>저 부부 완전 잉꼬부부야.</t>
         </is>
       </c>
       <c r="L742" s="16" t="inlineStr">
         <is>
-          <t>I tried out the boyfriend-look style today.</t>
+          <t>That couple is total lovebirds.</t>
         </is>
       </c>
       <c r="M742" s="16" t="inlineStr">
         <is>
-          <t>Hoy probé el estilo de ropa prestada del novio.</t>
+          <t>Esa pareja es como tortolitos, siempre cariñosos.</t>
         </is>
       </c>
       <c r="N742" s="16" t="inlineStr">
         <is>
-          <t>今天試了男友風穿搭。</t>
+          <t>那對夫妻完全是恩愛夫妻。</t>
         </is>
       </c>
       <c r="O742" s="16" t="inlineStr">
         <is>
-          <t>今天试了男友风穿搭。</t>
+          <t>那对夫妻完全是恩爱夫妻。</t>
         </is>
       </c>
       <c r="P742" s="16" t="inlineStr">
         <is>
-          <t>今日、彼シャツ風の格好してみた。</t>
+          <t>あの夫婦、完全におしどり夫婦だよね。</t>
         </is>
       </c>
       <c r="Q742" s="16" t="inlineStr">
         <is>
-          <t>Fashion talk</t>
+          <t>Celebrity couple talk</t>
         </is>
       </c>
       <c r="R742" s="15" t="inlineStr">
@@ -72721,17 +72721,17 @@
     <row r="743" ht="46" customHeight="1">
       <c r="A743" s="15" t="inlineStr">
         <is>
-          <t>DAT-066</t>
+          <t>DAT-065</t>
         </is>
       </c>
       <c r="B743" s="15" t="inlineStr">
         <is>
-          <t>결혼각</t>
+          <t>남친룩</t>
         </is>
       </c>
       <c r="C743" s="15" t="inlineStr">
         <is>
-          <t>gyeol-hon-gak</t>
+          <t>nam-chin-ruk</t>
         </is>
       </c>
       <c r="D743" s="15" t="inlineStr">
@@ -72746,62 +72746,62 @@
       </c>
       <c r="F743" s="16" t="inlineStr">
         <is>
-          <t>"Marriage angle" — signs or vibes suggesting a couple might be headed toward marriage.</t>
+          <t>"Boyfriend look" — a fashion style mimicking oversized, borrowed-looking boyfriend clothing.</t>
         </is>
       </c>
       <c r="G743" s="16" t="inlineStr">
         <is>
-          <t>"Ángulo de matrimonio": señales o vibra que sugieren que una pareja podría estar encaminada al matrimonio.</t>
+          <t>"Look de novio": un estilo de moda que imita ropa holgada, como si fuera prestada por el novio.</t>
         </is>
       </c>
       <c r="H743" s="16" t="inlineStr">
         <is>
-          <t>「結婚角度」——顯示一對情侶可能正朝向結婚發展的跡象或氛圍。</t>
+          <t>「男友風」——模仿男友寬鬆、彷彿借穿男友衣服的穿搭風格。</t>
         </is>
       </c>
       <c r="I743" s="16" t="inlineStr">
         <is>
-          <t>“结婚角度”——显示一对情侣可能正朝向结婚发展的迹象或氛围。</t>
+          <t>“男友风”——模仿男友宽松、仿佛借穿男友衣服的穿搭风格。</t>
         </is>
       </c>
       <c r="J743" s="16" t="inlineStr">
         <is>
-          <t>「結婚角度」——カップルが結婚に向かっているように見える兆候や雰囲気。</t>
+          <t>「彼氏ルック」——彼氏の服を借りたような、オーバーサイズのファッションスタイル。</t>
         </is>
       </c>
       <c r="K743" s="16" t="inlineStr">
         <is>
-          <t>둘이 완전 결혼각이야.</t>
+          <t>오늘 남친룩으로 입어봤어.</t>
         </is>
       </c>
       <c r="L743" s="16" t="inlineStr">
         <is>
-          <t>Those two have total marriage vibes.</t>
+          <t>I tried out the boyfriend-look style today.</t>
         </is>
       </c>
       <c r="M743" s="16" t="inlineStr">
         <is>
-          <t>Esos dos tienen toda la pinta de ir hacia el matrimonio.</t>
+          <t>Hoy probé el estilo de ropa prestada del novio.</t>
         </is>
       </c>
       <c r="N743" s="16" t="inlineStr">
         <is>
-          <t>兩人完全有結婚跡象。</t>
+          <t>今天試了男友風穿搭。</t>
         </is>
       </c>
       <c r="O743" s="16" t="inlineStr">
         <is>
-          <t>两人完全有结婚迹象。</t>
+          <t>今天试了男友风穿搭。</t>
         </is>
       </c>
       <c r="P743" s="16" t="inlineStr">
         <is>
-          <t>二人とも完全に結婚の気配だよね。</t>
+          <t>今日、彼シャツ風の格好してみた。</t>
         </is>
       </c>
       <c r="Q743" s="16" t="inlineStr">
         <is>
-          <t>Celebrity couple speculation</t>
+          <t>Fashion talk</t>
         </is>
       </c>
       <c r="R743" s="15" t="inlineStr">
@@ -72818,17 +72818,17 @@
     <row r="744" ht="46" customHeight="1">
       <c r="A744" s="15" t="inlineStr">
         <is>
-          <t>DAT-067</t>
+          <t>DAT-066</t>
         </is>
       </c>
       <c r="B744" s="15" t="inlineStr">
         <is>
-          <t>열애중</t>
+          <t>결혼각</t>
         </is>
       </c>
       <c r="C744" s="15" t="inlineStr">
         <is>
-          <t>yeol-ae-jung</t>
+          <t>gyeol-hon-gak</t>
         </is>
       </c>
       <c r="D744" s="15" t="inlineStr">
@@ -72843,62 +72843,62 @@
       </c>
       <c r="F744" s="16" t="inlineStr">
         <is>
-          <t>"Currently in a hot romance" — actively dating someone, often used in celebrity news.</t>
+          <t>"Marriage angle" — signs or vibes suggesting a couple might be headed toward marriage.</t>
         </is>
       </c>
       <c r="G744" s="16" t="inlineStr">
         <is>
-          <t>"Actualmente en un romance ardiente": saliendo activamente con alguien, a menudo usado en noticias de celebridades.</t>
+          <t>"Ángulo de matrimonio": señales o vibra que sugieren que una pareja podría estar encaminada al matrimonio.</t>
         </is>
       </c>
       <c r="H744" s="16" t="inlineStr">
         <is>
-          <t>「熱戀中」——正在積極交往中，常用於藝人新聞報導。</t>
+          <t>「結婚角度」——顯示一對情侶可能正朝向結婚發展的跡象或氛圍。</t>
         </is>
       </c>
       <c r="I744" s="16" t="inlineStr">
         <is>
-          <t>“热恋中”——正在积极交往中，常用于艺人新闻报导。</t>
+          <t>“结婚角度”——显示一对情侣可能正朝向结婚发展的迹象或氛围。</t>
         </is>
       </c>
       <c r="J744" s="16" t="inlineStr">
         <is>
-          <t>「熱い恋の最中」——現在誰かと積極的に交際していること、芸能ニュースでよく使われる。</t>
+          <t>「結婚角度」——カップルが結婚に向かっているように見える兆候や雰囲気。</t>
         </is>
       </c>
       <c r="K744" s="16" t="inlineStr">
         <is>
-          <t>두 사람 열애중이라는 기사 떴어.</t>
+          <t>둘이 완전 결혼각이야.</t>
         </is>
       </c>
       <c r="L744" s="16" t="inlineStr">
         <is>
-          <t>An article came out saying the two of them are dating.</t>
+          <t>Those two have total marriage vibes.</t>
         </is>
       </c>
       <c r="M744" s="16" t="inlineStr">
         <is>
-          <t>Salió un artículo diciendo que esos dos están saliendo.</t>
+          <t>Esos dos tienen toda la pinta de ir hacia el matrimonio.</t>
         </is>
       </c>
       <c r="N744" s="16" t="inlineStr">
         <is>
-          <t>有報導說兩人正在熱戀中。</t>
+          <t>兩人完全有結婚跡象。</t>
         </is>
       </c>
       <c r="O744" s="16" t="inlineStr">
         <is>
-          <t>有报导说两人正在热恋中。</t>
+          <t>两人完全有结婚迹象。</t>
         </is>
       </c>
       <c r="P744" s="16" t="inlineStr">
         <is>
-          <t>二人とも熱愛中だっていう記事出た。</t>
+          <t>二人とも完全に結婚の気配だよね。</t>
         </is>
       </c>
       <c r="Q744" s="16" t="inlineStr">
         <is>
-          <t>Entertainment news</t>
+          <t>Celebrity couple speculation</t>
         </is>
       </c>
       <c r="R744" s="15" t="inlineStr">
@@ -72915,17 +72915,17 @@
     <row r="745" ht="46" customHeight="1">
       <c r="A745" s="15" t="inlineStr">
         <is>
-          <t>DAT-068</t>
+          <t>DAT-067</t>
         </is>
       </c>
       <c r="B745" s="15" t="inlineStr">
         <is>
-          <t>솔로탈출</t>
+          <t>열애중</t>
         </is>
       </c>
       <c r="C745" s="15" t="inlineStr">
         <is>
-          <t>sol-lo-tal-chul</t>
+          <t>yeol-ae-jung</t>
         </is>
       </c>
       <c r="D745" s="15" t="inlineStr">
@@ -72940,62 +72940,62 @@
       </c>
       <c r="F745" s="16" t="inlineStr">
         <is>
-          <t>"Escaping single life" — finally entering a relationship after being single for a while.</t>
+          <t>"Currently in a hot romance" — actively dating someone, often used in celebrity news.</t>
         </is>
       </c>
       <c r="G745" s="16" t="inlineStr">
         <is>
-          <t>"Escapar de la soltería": finalmente entrar en una relación después de haber estado soltero por un tiempo.</t>
+          <t>"Actualmente en un romance ardiente": saliendo activamente con alguien, a menudo usado en noticias de celebridades.</t>
         </is>
       </c>
       <c r="H745" s="16" t="inlineStr">
         <is>
-          <t>「逃離單身」——經過一段單身期後終於進入一段感情，脫單。</t>
+          <t>「熱戀中」——正在積極交往中，常用於藝人新聞報導。</t>
         </is>
       </c>
       <c r="I745" s="16" t="inlineStr">
         <is>
-          <t>“逃离单身”——经过一段单身期后终于进入一段感情，脱单。</t>
+          <t>“热恋中”——正在积极交往中，常用于艺人新闻报导。</t>
         </is>
       </c>
       <c r="J745" s="16" t="inlineStr">
         <is>
-          <t>「シングル生活からの脱出」——しばらく独身だった後、ついに恋愛関係に入ること。</t>
+          <t>「熱い恋の最中」——現在誰かと積極的に交際していること、芸能ニュースでよく使われる。</t>
         </is>
       </c>
       <c r="K745" s="16" t="inlineStr">
         <is>
-          <t>드디어 솔로탈출 했어!</t>
+          <t>두 사람 열애중이라는 기사 떴어.</t>
         </is>
       </c>
       <c r="L745" s="16" t="inlineStr">
         <is>
-          <t>I finally escaped single life!</t>
+          <t>An article came out saying the two of them are dating.</t>
         </is>
       </c>
       <c r="M745" s="16" t="inlineStr">
         <is>
-          <t>¡Por fin dejé de estar soltera!</t>
+          <t>Salió un artículo diciendo que esos dos están saliendo.</t>
         </is>
       </c>
       <c r="N745" s="16" t="inlineStr">
         <is>
-          <t>終於脫單了！</t>
+          <t>有報導說兩人正在熱戀中。</t>
         </is>
       </c>
       <c r="O745" s="16" t="inlineStr">
         <is>
-          <t>终于脱单了！</t>
+          <t>有报导说两人正在热恋中。</t>
         </is>
       </c>
       <c r="P745" s="16" t="inlineStr">
         <is>
-          <t>ついに脱ソロした！</t>
+          <t>二人とも熱愛中だっていう記事出た。</t>
         </is>
       </c>
       <c r="Q745" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Entertainment news</t>
         </is>
       </c>
       <c r="R745" s="15" t="inlineStr">
@@ -73012,17 +73012,17 @@
     <row r="746" ht="46" customHeight="1">
       <c r="A746" s="15" t="inlineStr">
         <is>
-          <t>DAT-069</t>
+          <t>DAT-068</t>
         </is>
       </c>
       <c r="B746" s="15" t="inlineStr">
         <is>
-          <t>연애고수</t>
+          <t>솔로탈출</t>
         </is>
       </c>
       <c r="C746" s="15" t="inlineStr">
         <is>
-          <t>yeon-ae-go-su</t>
+          <t>sol-lo-tal-chul</t>
         </is>
       </c>
       <c r="D746" s="15" t="inlineStr">
@@ -73037,57 +73037,57 @@
       </c>
       <c r="F746" s="16" t="inlineStr">
         <is>
-          <t>Someone skilled and experienced at romance and relationships.</t>
+          <t>"Escaping single life" — finally entering a relationship after being single for a while.</t>
         </is>
       </c>
       <c r="G746" s="16" t="inlineStr">
         <is>
-          <t>Alguien hábil y experimentado en el romance y las relaciones.</t>
+          <t>"Escapar de la soltería": finalmente entrar en una relación después de haber estado soltero por un tiempo.</t>
         </is>
       </c>
       <c r="H746" s="16" t="inlineStr">
         <is>
-          <t>在感情與戀愛方面經驗豐富、技巧熟練的人，戀愛高手。</t>
+          <t>「逃離單身」——經過一段單身期後終於進入一段感情，脫單。</t>
         </is>
       </c>
       <c r="I746" s="16" t="inlineStr">
         <is>
-          <t>在感情与恋爱方面经验丰富、技巧熟练的人，恋爱高手。</t>
+          <t>“逃离单身”——经过一段单身期后终于进入一段感情，脱单。</t>
         </is>
       </c>
       <c r="J746" s="16" t="inlineStr">
         <is>
-          <t>恋愛や交際に長けていて、経験豊富な人。</t>
+          <t>「シングル生活からの脱出」——しばらく独身だった後、ついに恋愛関係に入ること。</t>
         </is>
       </c>
       <c r="K746" s="16" t="inlineStr">
         <is>
-          <t>쟤는 진짜 연애고수야.</t>
+          <t>드디어 솔로탈출 했어!</t>
         </is>
       </c>
       <c r="L746" s="16" t="inlineStr">
         <is>
-          <t>That person is a real dating master.</t>
+          <t>I finally escaped single life!</t>
         </is>
       </c>
       <c r="M746" s="16" t="inlineStr">
         <is>
-          <t>Esa persona es una verdadera maestra del amor.</t>
+          <t>¡Por fin dejé de estar soltera!</t>
         </is>
       </c>
       <c r="N746" s="16" t="inlineStr">
         <is>
-          <t>那個人真的是戀愛高手。</t>
+          <t>終於脫單了！</t>
         </is>
       </c>
       <c r="O746" s="16" t="inlineStr">
         <is>
-          <t>那个人真的是恋爱高手。</t>
+          <t>终于脱单了！</t>
         </is>
       </c>
       <c r="P746" s="16" t="inlineStr">
         <is>
-          <t>あの人は本当に恋愛マスターだよ。</t>
+          <t>ついに脱ソロした！</t>
         </is>
       </c>
       <c r="Q746" s="16" t="inlineStr">
@@ -73109,17 +73109,17 @@
     <row r="747" ht="46" customHeight="1">
       <c r="A747" s="15" t="inlineStr">
         <is>
-          <t>DAT-070</t>
+          <t>DAT-069</t>
         </is>
       </c>
       <c r="B747" s="15" t="inlineStr">
         <is>
-          <t>애정표현</t>
+          <t>연애고수</t>
         </is>
       </c>
       <c r="C747" s="15" t="inlineStr">
         <is>
-          <t>ae-jeong-pyo-hyeon</t>
+          <t>yeon-ae-go-su</t>
         </is>
       </c>
       <c r="D747" s="15" t="inlineStr">
@@ -73134,62 +73134,62 @@
       </c>
       <c r="F747" s="16" t="inlineStr">
         <is>
-          <t>Openly expressing affection toward a partner, whether verbally or physically.</t>
+          <t>Someone skilled and experienced at romance and relationships.</t>
         </is>
       </c>
       <c r="G747" s="16" t="inlineStr">
         <is>
-          <t>Expresar abiertamente afecto hacia una pareja, ya sea verbal o físicamente.</t>
+          <t>Alguien hábil y experimentado en el romance y las relaciones.</t>
         </is>
       </c>
       <c r="H747" s="16" t="inlineStr">
         <is>
-          <t>無論是言語或肢體上，公開向伴侶表達愛意。</t>
+          <t>在感情與戀愛方面經驗豐富、技巧熟練的人，戀愛高手。</t>
         </is>
       </c>
       <c r="I747" s="16" t="inlineStr">
         <is>
-          <t>无论是言语或肢体上，公开向伴侣表达爱意。</t>
+          <t>在感情与恋爱方面经验丰富、技巧熟练的人，恋爱高手。</t>
         </is>
       </c>
       <c r="J747" s="16" t="inlineStr">
         <is>
-          <t>言葉でも身体的にでも、パートナーに対して公然と愛情を表すこと。</t>
+          <t>恋愛や交際に長けていて、経験豊富な人。</t>
         </is>
       </c>
       <c r="K747" s="16" t="inlineStr">
         <is>
-          <t>둘이 애정표현이 진짜 많아.</t>
+          <t>쟤는 진짜 연애고수야.</t>
         </is>
       </c>
       <c r="L747" s="16" t="inlineStr">
         <is>
-          <t>Those two show a lot of affection toward each other.</t>
+          <t>That person is a real dating master.</t>
         </is>
       </c>
       <c r="M747" s="16" t="inlineStr">
         <is>
-          <t>Esos dos se muestran mucho cariño mutuamente.</t>
+          <t>Esa persona es una verdadera maestra del amor.</t>
         </is>
       </c>
       <c r="N747" s="16" t="inlineStr">
         <is>
-          <t>兩個人真的很常表達愛意。</t>
+          <t>那個人真的是戀愛高手。</t>
         </is>
       </c>
       <c r="O747" s="16" t="inlineStr">
         <is>
-          <t>两个人真的很常表达爱意。</t>
+          <t>那个人真的是恋爱高手。</t>
         </is>
       </c>
       <c r="P747" s="16" t="inlineStr">
         <is>
-          <t>二人とも愛情表現が本当に多いよね。</t>
+          <t>あの人は本当に恋愛マスターだよ。</t>
         </is>
       </c>
       <c r="Q747" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, dramas</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R747" s="15" t="inlineStr">
@@ -73206,17 +73206,17 @@
     <row r="748" ht="46" customHeight="1">
       <c r="A748" s="15" t="inlineStr">
         <is>
-          <t>DAT-071</t>
+          <t>DAT-070</t>
         </is>
       </c>
       <c r="B748" s="15" t="inlineStr">
         <is>
-          <t>짝꿍</t>
+          <t>애정표현</t>
         </is>
       </c>
       <c r="C748" s="15" t="inlineStr">
         <is>
-          <t>jjak-kkung</t>
+          <t>ae-jeong-pyo-hyeon</t>
         </is>
       </c>
       <c r="D748" s="15" t="inlineStr">
@@ -73231,62 +73231,62 @@
       </c>
       <c r="F748" s="16" t="inlineStr">
         <is>
-          <t>A cute, informal term for a significant other or a close paired friend.</t>
+          <t>Openly expressing affection toward a partner, whether verbally or physically.</t>
         </is>
       </c>
       <c r="G748" s="16" t="inlineStr">
         <is>
-          <t>Un término tierno e informal para una pareja sentimental o un amigo cercano emparejado.</t>
+          <t>Expresar abiertamente afecto hacia una pareja, ya sea verbal o físicamente.</t>
         </is>
       </c>
       <c r="H748" s="16" t="inlineStr">
         <is>
-          <t>對另一半或親密好友的可愛、非正式稱呼。</t>
+          <t>無論是言語或肢體上，公開向伴侶表達愛意。</t>
         </is>
       </c>
       <c r="I748" s="16" t="inlineStr">
         <is>
-          <t>对另一半或亲密好友的可爱、非正式称呼。</t>
+          <t>无论是言语或肢体上，公开向伴侣表达爱意。</t>
         </is>
       </c>
       <c r="J748" s="16" t="inlineStr">
         <is>
-          <t>恋人や親しい相手を指す、可愛くてカジュアルな呼び方。</t>
+          <t>言葉でも身体的にでも、パートナーに対して公然と愛情を表すこと。</t>
         </is>
       </c>
       <c r="K748" s="16" t="inlineStr">
         <is>
-          <t>내 짝꿍이랑 데이트하고 왔어.</t>
+          <t>둘이 애정표현이 진짜 많아.</t>
         </is>
       </c>
       <c r="L748" s="16" t="inlineStr">
         <is>
-          <t>I just came back from a date with my sweetheart.</t>
+          <t>Those two show a lot of affection toward each other.</t>
         </is>
       </c>
       <c r="M748" s="16" t="inlineStr">
         <is>
-          <t>Acabo de volver de una cita con mi pareja.</t>
+          <t>Esos dos se muestran mucho cariño mutuamente.</t>
         </is>
       </c>
       <c r="N748" s="16" t="inlineStr">
         <is>
-          <t>剛跟我的另一半約會回來。</t>
+          <t>兩個人真的很常表達愛意。</t>
         </is>
       </c>
       <c r="O748" s="16" t="inlineStr">
         <is>
-          <t>刚跟我的另一半约会回来。</t>
+          <t>两个人真的很常表达爱意。</t>
         </is>
       </c>
       <c r="P748" s="16" t="inlineStr">
         <is>
-          <t>相棒とデートしてきた。</t>
+          <t>二人とも愛情表現が本当に多いよね。</t>
         </is>
       </c>
       <c r="Q748" s="16" t="inlineStr">
         <is>
-          <t>Casual couple talk</t>
+          <t>Couple culture, dramas</t>
         </is>
       </c>
       <c r="R748" s="15" t="inlineStr">
@@ -73303,17 +73303,17 @@
     <row r="749" ht="46" customHeight="1">
       <c r="A749" s="15" t="inlineStr">
         <is>
-          <t>DAT-072</t>
+          <t>DAT-071</t>
         </is>
       </c>
       <c r="B749" s="15" t="inlineStr">
         <is>
-          <t>알콩달콩</t>
+          <t>짝꿍</t>
         </is>
       </c>
       <c r="C749" s="15" t="inlineStr">
         <is>
-          <t>al-kong-dal-kong</t>
+          <t>jjak-kkung</t>
         </is>
       </c>
       <c r="D749" s="15" t="inlineStr">
@@ -73328,62 +73328,62 @@
       </c>
       <c r="F749" s="16" t="inlineStr">
         <is>
-          <t>A cute expression describing a couple being sweetly, playfully affectionate together.</t>
+          <t>A cute, informal term for a significant other or a close paired friend.</t>
         </is>
       </c>
       <c r="G749" s="16" t="inlineStr">
         <is>
-          <t>Una expresión tierna que describe a una pareja siendo dulce y juguetonamente cariñosa entre sí.</t>
+          <t>Un término tierno e informal para una pareja sentimental o un amigo cercano emparejado.</t>
         </is>
       </c>
       <c r="H749" s="16" t="inlineStr">
         <is>
-          <t>形容一對情侶甜蜜、俏皮地相處，甜甜蜜蜜。</t>
+          <t>對另一半或親密好友的可愛、非正式稱呼。</t>
         </is>
       </c>
       <c r="I749" s="16" t="inlineStr">
         <is>
-          <t>形容一对情侣甜蜜、俏皮地相处，甜甜蜜蜜。</t>
+          <t>对另一半或亲密好友的可爱、非正式称呼。</t>
         </is>
       </c>
       <c r="J749" s="16" t="inlineStr">
         <is>
-          <t>カップルが甘く、遊び心を持って愛情深く過ごしている様子を表す可愛い表現。</t>
+          <t>恋人や親しい相手を指す、可愛くてカジュアルな呼び方。</t>
         </is>
       </c>
       <c r="K749" s="16" t="inlineStr">
         <is>
-          <t>둘이 알콩달콩 잘 지내고 있어.</t>
+          <t>내 짝꿍이랑 데이트하고 왔어.</t>
         </is>
       </c>
       <c r="L749" s="16" t="inlineStr">
         <is>
-          <t>The two of them are doing well, all sweet and lovey-dovey.</t>
+          <t>I just came back from a date with my sweetheart.</t>
         </is>
       </c>
       <c r="M749" s="16" t="inlineStr">
         <is>
-          <t>Esos dos la están pasando bien, muy dulces y cariñosos.</t>
+          <t>Acabo de volver de una cita con mi pareja.</t>
         </is>
       </c>
       <c r="N749" s="16" t="inlineStr">
         <is>
-          <t>兩個人甜甜蜜蜜地過得很好。</t>
+          <t>剛跟我的另一半約會回來。</t>
         </is>
       </c>
       <c r="O749" s="16" t="inlineStr">
         <is>
-          <t>两个人甜甜蜜蜜地过得很好。</t>
+          <t>刚跟我的另一半约会回来。</t>
         </is>
       </c>
       <c r="P749" s="16" t="inlineStr">
         <is>
-          <t>二人ともラブラブでうまくやってる。</t>
+          <t>相棒とデートしてきた。</t>
         </is>
       </c>
       <c r="Q749" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, dramas</t>
+          <t>Casual couple talk</t>
         </is>
       </c>
       <c r="R749" s="15" t="inlineStr">
@@ -73400,17 +73400,17 @@
     <row r="750" ht="46" customHeight="1">
       <c r="A750" s="15" t="inlineStr">
         <is>
-          <t>DAT-073</t>
+          <t>DAT-072</t>
         </is>
       </c>
       <c r="B750" s="15" t="inlineStr">
         <is>
-          <t>핑크빛</t>
+          <t>알콩달콩</t>
         </is>
       </c>
       <c r="C750" s="15" t="inlineStr">
         <is>
-          <t>ping-keu-bit</t>
+          <t>al-kong-dal-kong</t>
         </is>
       </c>
       <c r="D750" s="15" t="inlineStr">
@@ -73425,62 +73425,62 @@
       </c>
       <c r="F750" s="16" t="inlineStr">
         <is>
-          <t>"Pink-tinted" — describes a romantic, love-filled mood or atmosphere.</t>
+          <t>A cute expression describing a couple being sweetly, playfully affectionate together.</t>
         </is>
       </c>
       <c r="G750" s="16" t="inlineStr">
         <is>
-          <t>"Teñido de rosa": describe un ambiente o estado de ánimo romántico y lleno de amor.</t>
+          <t>Una expresión tierna que describe a una pareja siendo dulce y juguetonamente cariñosa entre sí.</t>
         </is>
       </c>
       <c r="H750" s="16" t="inlineStr">
         <is>
-          <t>「粉紅色調」——形容浪漫、充滿愛意的氛圍或心情。</t>
+          <t>形容一對情侶甜蜜、俏皮地相處，甜甜蜜蜜。</t>
         </is>
       </c>
       <c r="I750" s="16" t="inlineStr">
         <is>
-          <t>“粉红色调”——形容浪漫、充满爱意的氛围或心情。</t>
+          <t>形容一对情侣甜蜜、俏皮地相处，甜甜蜜蜜。</t>
         </is>
       </c>
       <c r="J750" s="16" t="inlineStr">
         <is>
-          <t>「ピンク色」——ロマンチックで愛情に満ちた雰囲気や気分を表す。</t>
+          <t>カップルが甘く、遊び心を持って愛情深く過ごしている様子を表す可愛い表現。</t>
         </is>
       </c>
       <c r="K750" s="16" t="inlineStr">
         <is>
-          <t>둘 사이에 핑크빛 기류가 흘러.</t>
+          <t>둘이 알콩달콩 잘 지내고 있어.</t>
         </is>
       </c>
       <c r="L750" s="16" t="inlineStr">
         <is>
-          <t>There's a rosy romantic vibe flowing between the two of them.</t>
+          <t>The two of them are doing well, all sweet and lovey-dovey.</t>
         </is>
       </c>
       <c r="M750" s="16" t="inlineStr">
         <is>
-          <t>Hay un aire romántico y rosado fluyendo entre esos dos.</t>
+          <t>Esos dos la están pasando bien, muy dulces y cariñosos.</t>
         </is>
       </c>
       <c r="N750" s="16" t="inlineStr">
         <is>
-          <t>兩人之間流動著粉紅氛圍。</t>
+          <t>兩個人甜甜蜜蜜地過得很好。</t>
         </is>
       </c>
       <c r="O750" s="16" t="inlineStr">
         <is>
-          <t>两人之间流动着粉红氛围。</t>
+          <t>两个人甜甜蜜蜜地过得很好。</t>
         </is>
       </c>
       <c r="P750" s="16" t="inlineStr">
         <is>
-          <t>二人の間にバラ色の空気が流れてる。</t>
+          <t>二人ともラブラブでうまくやってる。</t>
         </is>
       </c>
       <c r="Q750" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk, gossip</t>
+          <t>Couple culture, dramas</t>
         </is>
       </c>
       <c r="R750" s="15" t="inlineStr">
@@ -73497,17 +73497,17 @@
     <row r="751" ht="46" customHeight="1">
       <c r="A751" s="15" t="inlineStr">
         <is>
-          <t>DAT-074</t>
+          <t>DAT-073</t>
         </is>
       </c>
       <c r="B751" s="15" t="inlineStr">
         <is>
-          <t>이별후유증</t>
+          <t>핑크빛</t>
         </is>
       </c>
       <c r="C751" s="15" t="inlineStr">
         <is>
-          <t>i-byeol-hu-yu-jeung</t>
+          <t>ping-keu-bit</t>
         </is>
       </c>
       <c r="D751" s="15" t="inlineStr">
@@ -73522,62 +73522,62 @@
       </c>
       <c r="F751" s="16" t="inlineStr">
         <is>
-          <t>The emotional aftereffects that linger after a relationship ends.</t>
+          <t>"Pink-tinted" — describes a romantic, love-filled mood or atmosphere.</t>
         </is>
       </c>
       <c r="G751" s="16" t="inlineStr">
         <is>
-          <t>Los efectos emocionales posteriores que persisten después de que termina una relación.</t>
+          <t>"Teñido de rosa": describe un ambiente o estado de ánimo romántico y lleno de amor.</t>
         </is>
       </c>
       <c r="H751" s="16" t="inlineStr">
         <is>
-          <t>一段感情結束後持續存在的情緒後遺症，分手後遺症。</t>
+          <t>「粉紅色調」——形容浪漫、充滿愛意的氛圍或心情。</t>
         </is>
       </c>
       <c r="I751" s="16" t="inlineStr">
         <is>
-          <t>一段感情结束后持续存在的情绪后遗症，分手后遗症。</t>
+          <t>“粉红色调”——形容浪漫、充满爱意的氛围或心情。</t>
         </is>
       </c>
       <c r="J751" s="16" t="inlineStr">
         <is>
-          <t>恋愛関係が終わった後も続く、感情的な後遺症。</t>
+          <t>「ピンク色」——ロマンチックで愛情に満ちた雰囲気や気分を表す。</t>
         </is>
       </c>
       <c r="K751" s="16" t="inlineStr">
         <is>
-          <t>이별후유증이 생각보다 오래 갔어.</t>
+          <t>둘 사이에 핑크빛 기류가 흘러.</t>
         </is>
       </c>
       <c r="L751" s="16" t="inlineStr">
         <is>
-          <t>The breakup aftermath lasted longer than I expected.</t>
+          <t>There's a rosy romantic vibe flowing between the two of them.</t>
         </is>
       </c>
       <c r="M751" s="16" t="inlineStr">
         <is>
-          <t>Las secuelas de la ruptura duraron más de lo que esperaba.</t>
+          <t>Hay un aire romántico y rosado fluyendo entre esos dos.</t>
         </is>
       </c>
       <c r="N751" s="16" t="inlineStr">
         <is>
-          <t>分手後遺症比想像中持續更久。</t>
+          <t>兩人之間流動著粉紅氛圍。</t>
         </is>
       </c>
       <c r="O751" s="16" t="inlineStr">
         <is>
-          <t>分手后遗症比想像中持续更久。</t>
+          <t>两人之间流动着粉红氛围。</t>
         </is>
       </c>
       <c r="P751" s="16" t="inlineStr">
         <is>
-          <t>失恋の後遺症が思ったより長引いた。</t>
+          <t>二人の間にバラ色の空気が流れてる。</t>
         </is>
       </c>
       <c r="Q751" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>K-drama trope talk, gossip</t>
         </is>
       </c>
       <c r="R751" s="15" t="inlineStr">
@@ -73594,17 +73594,17 @@
     <row r="752" ht="46" customHeight="1">
       <c r="A752" s="15" t="inlineStr">
         <is>
-          <t>DAT-075</t>
+          <t>DAT-074</t>
         </is>
       </c>
       <c r="B752" s="15" t="inlineStr">
         <is>
-          <t>연애전선</t>
+          <t>이별후유증</t>
         </is>
       </c>
       <c r="C752" s="15" t="inlineStr">
         <is>
-          <t>yeon-ae-jeon-seon</t>
+          <t>i-byeol-hu-yu-jeung</t>
         </is>
       </c>
       <c r="D752" s="15" t="inlineStr">
@@ -73619,62 +73619,62 @@
       </c>
       <c r="F752" s="16" t="inlineStr">
         <is>
-          <t>"Romance front line" — a weather-front-style metaphor for the current state of someone's love life.</t>
+          <t>The emotional aftereffects that linger after a relationship ends.</t>
         </is>
       </c>
       <c r="G752" s="16" t="inlineStr">
         <is>
-          <t>"Frente romántico": una metáfora al estilo de un frente meteorológico para el estado actual de la vida amorosa de alguien.</t>
+          <t>Los efectos emocionales posteriores que persisten después de que termina una relación.</t>
         </is>
       </c>
       <c r="H752" s="16" t="inlineStr">
         <is>
-          <t>「戀愛前線」——借用天氣鋒面概念，比喻某人目前的感情狀態。</t>
+          <t>一段感情結束後持續存在的情緒後遺症，分手後遺症。</t>
         </is>
       </c>
       <c r="I752" s="16" t="inlineStr">
         <is>
-          <t>“恋爱前线”——借用天气锋面概念，比喻某人目前的感情状态。</t>
+          <t>一段感情结束后持续存在的情绪后遗症，分手后遗症。</t>
         </is>
       </c>
       <c r="J752" s="16" t="inlineStr">
         <is>
-          <t>「恋愛の前線」——天気の前線に例えて、誰かの恋愛状況の現状を表す言葉。</t>
+          <t>恋愛関係が終わった後も続く、感情的な後遺症。</t>
         </is>
       </c>
       <c r="K752" s="16" t="inlineStr">
         <is>
-          <t>요즘 연애전선 어때?</t>
+          <t>이별후유증이 생각보다 오래 갔어.</t>
         </is>
       </c>
       <c r="L752" s="16" t="inlineStr">
         <is>
-          <t>How's your love life going these days?</t>
+          <t>The breakup aftermath lasted longer than I expected.</t>
         </is>
       </c>
       <c r="M752" s="16" t="inlineStr">
         <is>
-          <t>¿Cómo va tu vida amorosa últimamente?</t>
+          <t>Las secuelas de la ruptura duraron más de lo que esperaba.</t>
         </is>
       </c>
       <c r="N752" s="16" t="inlineStr">
         <is>
-          <t>最近戀愛前線如何？</t>
+          <t>分手後遺症比想像中持續更久。</t>
         </is>
       </c>
       <c r="O752" s="16" t="inlineStr">
         <is>
-          <t>最近恋爱前线如何？</t>
+          <t>分手后遗症比想像中持续更久。</t>
         </is>
       </c>
       <c r="P752" s="16" t="inlineStr">
         <is>
-          <t>最近恋愛前線どう？</t>
+          <t>失恋の後遺症が思ったより長引いた。</t>
         </is>
       </c>
       <c r="Q752" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R752" s="15" t="inlineStr">
@@ -73691,17 +73691,17 @@
     <row r="753" ht="46" customHeight="1">
       <c r="A753" s="15" t="inlineStr">
         <is>
-          <t>DAT-076</t>
+          <t>DAT-075</t>
         </is>
       </c>
       <c r="B753" s="15" t="inlineStr">
         <is>
-          <t>커플브이로그</t>
+          <t>연애전선</t>
         </is>
       </c>
       <c r="C753" s="15" t="inlineStr">
         <is>
-          <t>keo-peul-beu-i-ro-geu</t>
+          <t>yeon-ae-jeon-seon</t>
         </is>
       </c>
       <c r="D753" s="15" t="inlineStr">
@@ -73716,62 +73716,62 @@
       </c>
       <c r="F753" s="16" t="inlineStr">
         <is>
-          <t>Video content a couple makes together documenting their relationship and daily life.</t>
+          <t>"Romance front line" — a weather-front-style metaphor for the current state of someone's love life.</t>
         </is>
       </c>
       <c r="G753" s="16" t="inlineStr">
         <is>
-          <t>Contenido de video que una pareja hace junta documentando su relación y vida diaria.</t>
+          <t>"Frente romántico": una metáfora al estilo de un frente meteorológico para el estado actual de la vida amorosa de alguien.</t>
         </is>
       </c>
       <c r="H753" s="16" t="inlineStr">
         <is>
-          <t>情侶一起拍攝、記錄兩人關係與日常生活的影片內容。</t>
+          <t>「戀愛前線」——借用天氣鋒面概念，比喻某人目前的感情狀態。</t>
         </is>
       </c>
       <c r="I753" s="16" t="inlineStr">
         <is>
-          <t>情侣一起拍摄、记录两人关系与日常生活的视频内容。</t>
+          <t>“恋爱前线”——借用天气锋面概念，比喻某人目前的感情状态。</t>
         </is>
       </c>
       <c r="J753" s="16" t="inlineStr">
         <is>
-          <t>カップルが一緒に作る、二人の関係や日常生活を記録した動画コンテンツ。</t>
+          <t>「恋愛の前線」——天気の前線に例えて、誰かの恋愛状況の現状を表す言葉。</t>
         </is>
       </c>
       <c r="K753" s="16" t="inlineStr">
         <is>
-          <t>이 커플브이로그 보면 나도 연애하고 싶어져.</t>
+          <t>요즘 연애전선 어때?</t>
         </is>
       </c>
       <c r="L753" s="16" t="inlineStr">
         <is>
-          <t>Watching this couple vlog makes me want to date too.</t>
+          <t>How's your love life going these days?</t>
         </is>
       </c>
       <c r="M753" s="16" t="inlineStr">
         <is>
-          <t>Ver este vlog de pareja me dan ganas de tener novio también.</t>
+          <t>¿Cómo va tu vida amorosa últimamente?</t>
         </is>
       </c>
       <c r="N753" s="16" t="inlineStr">
         <is>
-          <t>看這個情侶Vlog會讓人也想談戀愛。</t>
+          <t>最近戀愛前線如何？</t>
         </is>
       </c>
       <c r="O753" s="16" t="inlineStr">
         <is>
-          <t>看这个情侣Vlog会让人也想谈恋爱。</t>
+          <t>最近恋爱前线如何？</t>
         </is>
       </c>
       <c r="P753" s="16" t="inlineStr">
         <is>
-          <t>このカップルVlog見てると、私も恋したくなる。</t>
+          <t>最近恋愛前線どう？</t>
         </is>
       </c>
       <c r="Q753" s="16" t="inlineStr">
         <is>
-          <t>YouTube couple content</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R753" s="15" t="inlineStr">
@@ -73788,17 +73788,17 @@
     <row r="754" ht="46" customHeight="1">
       <c r="A754" s="15" t="inlineStr">
         <is>
-          <t>DAT-077</t>
+          <t>DAT-076</t>
         </is>
       </c>
       <c r="B754" s="15" t="inlineStr">
         <is>
-          <t>심쿵포인트</t>
+          <t>커플브이로그</t>
         </is>
       </c>
       <c r="C754" s="15" t="inlineStr">
         <is>
-          <t>sim-kung-po-in-teu</t>
+          <t>keo-peul-beu-i-ro-geu</t>
         </is>
       </c>
       <c r="D754" s="15" t="inlineStr">
@@ -73813,62 +73813,62 @@
       </c>
       <c r="F754" s="16" t="inlineStr">
         <is>
-          <t>The specific moment or detail that makes you fall for someone or feel butterflies.</t>
+          <t>Video content a couple makes together documenting their relationship and daily life.</t>
         </is>
       </c>
       <c r="G754" s="16" t="inlineStr">
         <is>
-          <t>El momento o detalle específico que te hace enamorarte de alguien o sentir mariposas.</t>
+          <t>Contenido de video que una pareja hace junta documentando su relación y vida diaria.</t>
         </is>
       </c>
       <c r="H754" s="16" t="inlineStr">
         <is>
-          <t>讓你對某人心動、產生小鹿亂撞感覺的特定瞬間或細節，心動點。</t>
+          <t>情侶一起拍攝、記錄兩人關係與日常生活的影片內容。</t>
         </is>
       </c>
       <c r="I754" s="16" t="inlineStr">
         <is>
-          <t>让你对某人心动、产生小鹿乱撞感觉的特定瞬间或细节，心动点。</t>
+          <t>情侣一起拍摄、记录两人关系与日常生活的视频内容。</t>
         </is>
       </c>
       <c r="J754" s="16" t="inlineStr">
         <is>
-          <t>誰かに惹かれたり、胸がときめいたりする特定の瞬間や細部。</t>
+          <t>カップルが一緒に作る、二人の関係や日常生活を記録した動画コンテンツ。</t>
         </is>
       </c>
       <c r="K754" s="16" t="inlineStr">
         <is>
-          <t>그 미소가 내 심쿵포인트였어.</t>
+          <t>이 커플브이로그 보면 나도 연애하고 싶어져.</t>
         </is>
       </c>
       <c r="L754" s="16" t="inlineStr">
         <is>
-          <t>That smile was my heart-flutter moment.</t>
+          <t>Watching this couple vlog makes me want to date too.</t>
         </is>
       </c>
       <c r="M754" s="16" t="inlineStr">
         <is>
-          <t>Esa sonrisa fue mi punto de flechazo.</t>
+          <t>Ver este vlog de pareja me dan ganas de tener novio también.</t>
         </is>
       </c>
       <c r="N754" s="16" t="inlineStr">
         <is>
-          <t>那個微笑就是我的心動點。</t>
+          <t>看這個情侶Vlog會讓人也想談戀愛。</t>
         </is>
       </c>
       <c r="O754" s="16" t="inlineStr">
         <is>
-          <t>那个微笑就是我的心动点。</t>
+          <t>看这个情侣Vlog会让人也想谈恋爱。</t>
         </is>
       </c>
       <c r="P754" s="16" t="inlineStr">
         <is>
-          <t>あの笑顔が私のキュンポイントだった。</t>
+          <t>このカップルVlog見てると、私も恋したくなる。</t>
         </is>
       </c>
       <c r="Q754" s="16" t="inlineStr">
         <is>
-          <t>Casual dating/crush talk</t>
+          <t>YouTube couple content</t>
         </is>
       </c>
       <c r="R754" s="15" t="inlineStr">
@@ -73885,17 +73885,17 @@
     <row r="755" ht="46" customHeight="1">
       <c r="A755" s="15" t="inlineStr">
         <is>
-          <t>DAT-078</t>
+          <t>DAT-077</t>
         </is>
       </c>
       <c r="B755" s="15" t="inlineStr">
         <is>
-          <t>천일</t>
+          <t>심쿵포인트</t>
         </is>
       </c>
       <c r="C755" s="15" t="inlineStr">
         <is>
-          <t>cheon-il</t>
+          <t>sim-kung-po-in-teu</t>
         </is>
       </c>
       <c r="D755" s="15" t="inlineStr">
@@ -73910,62 +73910,62 @@
       </c>
       <c r="F755" s="16" t="inlineStr">
         <is>
-          <t>The 1,000-day relationship milestone, a bigger version of the 100-day celebration.</t>
+          <t>The specific moment or detail that makes you fall for someone or feel butterflies.</t>
         </is>
       </c>
       <c r="G755" s="16" t="inlineStr">
         <is>
-          <t>El hito de los 1,000 días de relación, una versión más grande de la celebración de los 100 días.</t>
+          <t>El momento o detalle específico que te hace enamorarte de alguien o sentir mariposas.</t>
         </is>
       </c>
       <c r="H755" s="16" t="inlineStr">
         <is>
-          <t>交往滿一千天的紀念日，是百日紀念的加強版。</t>
+          <t>讓你對某人心動、產生小鹿亂撞感覺的特定瞬間或細節，心動點。</t>
         </is>
       </c>
       <c r="I755" s="16" t="inlineStr">
         <is>
-          <t>交往满一千天的纪念日，是百日纪念的加强版。</t>
+          <t>让你对某人心动、产生小鹿乱撞感觉的特定瞬间或细节，心动点。</t>
         </is>
       </c>
       <c r="J755" s="16" t="inlineStr">
         <is>
-          <t>100日記念日をさらに大きくした、交際1000日の記念日。</t>
+          <t>誰かに惹かれたり、胸がときめいたりする特定の瞬間や細部。</t>
         </is>
       </c>
       <c r="K755" s="16" t="inlineStr">
         <is>
-          <t>다음 달이 우리 천일이야.</t>
+          <t>그 미소가 내 심쿵포인트였어.</t>
         </is>
       </c>
       <c r="L755" s="16" t="inlineStr">
         <is>
-          <t>Next month is our 1,000-day anniversary.</t>
+          <t>That smile was my heart-flutter moment.</t>
         </is>
       </c>
       <c r="M755" s="16" t="inlineStr">
         <is>
-          <t>El próximo mes cumplimos 1,000 días.</t>
+          <t>Esa sonrisa fue mi punto de flechazo.</t>
         </is>
       </c>
       <c r="N755" s="16" t="inlineStr">
         <is>
-          <t>下個月是我們的千日紀念。</t>
+          <t>那個微笑就是我的心動點。</t>
         </is>
       </c>
       <c r="O755" s="16" t="inlineStr">
         <is>
-          <t>下个月是我们的千日纪念。</t>
+          <t>那个微笑就是我的心动点。</t>
         </is>
       </c>
       <c r="P755" s="16" t="inlineStr">
         <is>
-          <t>来月が私たちの1000日記念日。</t>
+          <t>あの笑顔が私のキュンポイントだった。</t>
         </is>
       </c>
       <c r="Q755" s="16" t="inlineStr">
         <is>
-          <t>Couple culture</t>
+          <t>Casual dating/crush talk</t>
         </is>
       </c>
       <c r="R755" s="15" t="inlineStr">
@@ -73982,17 +73982,17 @@
     <row r="756" ht="46" customHeight="1">
       <c r="A756" s="15" t="inlineStr">
         <is>
-          <t>DAT-079</t>
+          <t>DAT-078</t>
         </is>
       </c>
       <c r="B756" s="15" t="inlineStr">
         <is>
-          <t>열애인정</t>
+          <t>천일</t>
         </is>
       </c>
       <c r="C756" s="15" t="inlineStr">
         <is>
-          <t>yeol-ae-in-jeong</t>
+          <t>cheon-il</t>
         </is>
       </c>
       <c r="D756" s="15" t="inlineStr">
@@ -74007,62 +74007,62 @@
       </c>
       <c r="F756" s="16" t="inlineStr">
         <is>
-          <t>When a celebrity couple officially confirms they're dating, often via their agency.</t>
+          <t>The 1,000-day relationship milestone, a bigger version of the 100-day celebration.</t>
         </is>
       </c>
       <c r="G756" s="16" t="inlineStr">
         <is>
-          <t>Cuando una pareja de celebridades confirma oficialmente que está saliendo, a menudo a través de su agencia.</t>
+          <t>El hito de los 1,000 días de relación, una versión más grande de la celebración de los 100 días.</t>
         </is>
       </c>
       <c r="H756" s="16" t="inlineStr">
         <is>
-          <t>名人情侶（常透過經紀公司）正式承認交往關係，承認戀情。</t>
+          <t>交往滿一千天的紀念日，是百日紀念的加強版。</t>
         </is>
       </c>
       <c r="I756" s="16" t="inlineStr">
         <is>
-          <t>名人情侣（常通过经纪公司）正式承认交往关系，承认恋情。</t>
+          <t>交往满一千天的纪念日，是百日纪念的加强版。</t>
         </is>
       </c>
       <c r="J756" s="16" t="inlineStr">
         <is>
-          <t>芸能人カップルが、事務所を通じてなど正式に交際を認めること。</t>
+          <t>100日記念日をさらに大きくした、交際1000日の記念日。</t>
         </is>
       </c>
       <c r="K756" s="16" t="inlineStr">
         <is>
-          <t>결국 열애인정 했대!</t>
+          <t>다음 달이 우리 천일이야.</t>
         </is>
       </c>
       <c r="L756" s="16" t="inlineStr">
         <is>
-          <t>They finally confirmed the relationship!</t>
+          <t>Next month is our 1,000-day anniversary.</t>
         </is>
       </c>
       <c r="M756" s="16" t="inlineStr">
         <is>
-          <t>¡Al final confirmaron la relación!</t>
+          <t>El próximo mes cumplimos 1,000 días.</t>
         </is>
       </c>
       <c r="N756" s="16" t="inlineStr">
         <is>
-          <t>最後承認戀情了！</t>
+          <t>下個月是我們的千日紀念。</t>
         </is>
       </c>
       <c r="O756" s="16" t="inlineStr">
         <is>
-          <t>最后承认恋情了！</t>
+          <t>下个月是我们的千日纪念。</t>
         </is>
       </c>
       <c r="P756" s="16" t="inlineStr">
         <is>
-          <t>ついに交際を認めたって！</t>
+          <t>来月が私たちの1000日記念日。</t>
         </is>
       </c>
       <c r="Q756" s="16" t="inlineStr">
         <is>
-          <t>Entertainment news</t>
+          <t>Couple culture</t>
         </is>
       </c>
       <c r="R756" s="15" t="inlineStr">
@@ -74079,17 +74079,17 @@
     <row r="757" ht="46" customHeight="1">
       <c r="A757" s="15" t="inlineStr">
         <is>
-          <t>DAT-080</t>
+          <t>DAT-079</t>
         </is>
       </c>
       <c r="B757" s="15" t="inlineStr">
         <is>
-          <t>사내연애</t>
+          <t>열애인정</t>
         </is>
       </c>
       <c r="C757" s="15" t="inlineStr">
         <is>
-          <t>sa-nae-yeon-ae</t>
+          <t>yeol-ae-in-jeong</t>
         </is>
       </c>
       <c r="D757" s="15" t="inlineStr">
@@ -74104,62 +74104,62 @@
       </c>
       <c r="F757" s="16" t="inlineStr">
         <is>
-          <t>Dating a coworker at the same company — a common drama trope.</t>
+          <t>When a celebrity couple officially confirms they're dating, often via their agency.</t>
         </is>
       </c>
       <c r="G757" s="16" t="inlineStr">
         <is>
-          <t>Salir con un compañero de trabajo de la misma empresa; un cliché común en los dramas.</t>
+          <t>Cuando una pareja de celebridades confirma oficialmente que está saliendo, a menudo a través de su agencia.</t>
         </is>
       </c>
       <c r="H757" s="16" t="inlineStr">
         <is>
-          <t>與同公司同事交往，是韓劇常見的劇情套路，辦公室戀情。</t>
+          <t>名人情侶（常透過經紀公司）正式承認交往關係，承認戀情。</t>
         </is>
       </c>
       <c r="I757" s="16" t="inlineStr">
         <is>
-          <t>与同公司同事交往，是韩剧常见的剧情套路，办公室恋情。</t>
+          <t>名人情侣（常通过经纪公司）正式承认交往关系，承认恋情。</t>
         </is>
       </c>
       <c r="J757" s="16" t="inlineStr">
         <is>
-          <t>同じ会社の同僚と付き合うこと——ドラマによくあるトロープ。</t>
+          <t>芸能人カップルが、事務所を通じてなど正式に交際を認めること。</t>
         </is>
       </c>
       <c r="K757" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 사내연애 전개가 진짜 설레.</t>
+          <t>결국 열애인정 했대!</t>
         </is>
       </c>
       <c r="L757" s="16" t="inlineStr">
         <is>
-          <t>This drama's workplace romance storyline is so exciting.</t>
+          <t>They finally confirmed the relationship!</t>
         </is>
       </c>
       <c r="M757" s="16" t="inlineStr">
         <is>
-          <t>La trama de romance de oficina de este drama es muy emocionante.</t>
+          <t>¡Al final confirmaron la relación!</t>
         </is>
       </c>
       <c r="N757" s="16" t="inlineStr">
         <is>
-          <t>這部劇的辦公室戀情發展真的很讓人心動。</t>
+          <t>最後承認戀情了！</t>
         </is>
       </c>
       <c r="O757" s="16" t="inlineStr">
         <is>
-          <t>这部剧的办公室恋情发展真的很让人心动。</t>
+          <t>最后承认恋情了！</t>
         </is>
       </c>
       <c r="P757" s="16" t="inlineStr">
         <is>
-          <t>このドラマの社内恋愛展開、本当にドキドキする。</t>
+          <t>ついに交際を認めたって！</t>
         </is>
       </c>
       <c r="Q757" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>Entertainment news</t>
         </is>
       </c>
       <c r="R757" s="15" t="inlineStr">
@@ -74176,17 +74176,17 @@
     <row r="758" ht="46" customHeight="1">
       <c r="A758" s="15" t="inlineStr">
         <is>
-          <t>DAT-081</t>
+          <t>DAT-080</t>
         </is>
       </c>
       <c r="B758" s="15" t="inlineStr">
         <is>
-          <t>패완얼</t>
+          <t>사내연애</t>
         </is>
       </c>
       <c r="C758" s="15" t="inlineStr">
         <is>
-          <t>pae-wan-eol</t>
+          <t>sa-nae-yeon-ae</t>
         </is>
       </c>
       <c r="D758" s="15" t="inlineStr">
@@ -74201,62 +74201,62 @@
       </c>
       <c r="F758" s="16" t="inlineStr">
         <is>
-          <t>Short for "fashion is completed by the face" — a saying that a good-looking face elevates any outfit, no matter how simple.</t>
+          <t>Dating a coworker at the same company — a common drama trope.</t>
         </is>
       </c>
       <c r="G758" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "la moda se completa con la cara": un dicho que dice que una cara atractiva mejora cualquier atuendo, sin importar lo simple que sea.</t>
+          <t>Salir con un compañero de trabajo de la misma empresa; un cliché común en los dramas.</t>
         </is>
       </c>
       <c r="H758" s="16" t="inlineStr">
         <is>
-          <t>「時尚的完成是臉」的簡稱——意指帥氣或漂亮的長相能撐起任何穿搭。</t>
+          <t>與同公司同事交往，是韓劇常見的劇情套路，辦公室戀情。</t>
         </is>
       </c>
       <c r="I758" s="16" t="inlineStr">
         <is>
-          <t>“时尚的完成是脸”的简称——意指帅气或漂亮的长相能撑起任何穿搭。</t>
+          <t>与同公司同事交往，是韩剧常见的剧情套路，办公室恋情。</t>
         </is>
       </c>
       <c r="J758" s="16" t="inlineStr">
         <is>
-          <t>「ファッションの完成は顔」の略——どんなにシンプルな服でも、整った顔立ちが引き立てるという言葉。</t>
+          <t>同じ会社の同僚と付き合うこと——ドラマによくあるトロープ。</t>
         </is>
       </c>
       <c r="K758" s="16" t="inlineStr">
         <is>
-          <t>역시 패완얼이야, 뭘 입어도 잘 어울려.</t>
+          <t>이 드라마 사내연애 전개가 진짜 설레.</t>
         </is>
       </c>
       <c r="L758" s="16" t="inlineStr">
         <is>
-          <t>It's true, fashion's finished by the face — they look good in anything.</t>
+          <t>This drama's workplace romance storyline is so exciting.</t>
         </is>
       </c>
       <c r="M758" s="16" t="inlineStr">
         <is>
-          <t>Es cierto, la cara lo completa todo — se le ve bien cualquier cosa.</t>
+          <t>La trama de romance de oficina de este drama es muy emocionante.</t>
         </is>
       </c>
       <c r="N758" s="16" t="inlineStr">
         <is>
-          <t>果然臉才是關鍵，穿什麼都好看。</t>
+          <t>這部劇的辦公室戀情發展真的很讓人心動。</t>
         </is>
       </c>
       <c r="O758" s="16" t="inlineStr">
         <is>
-          <t>果然脸才是关键，穿什么都好看。</t>
+          <t>这部剧的办公室恋情发展真的很让人心动。</t>
         </is>
       </c>
       <c r="P758" s="16" t="inlineStr">
         <is>
-          <t>やっぱり顔が全て、何着ても似合う。</t>
+          <t>このドラマの社内恋愛展開、本当にドキドキする。</t>
         </is>
       </c>
       <c r="Q758" s="16" t="inlineStr">
         <is>
-          <t>Fashion/beauty banter</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R758" s="15" t="inlineStr">
@@ -74273,102 +74273,199 @@
     <row r="759" ht="46" customHeight="1">
       <c r="A759" s="15" t="inlineStr">
         <is>
+          <t>DAT-081</t>
+        </is>
+      </c>
+      <c r="B759" s="15" t="inlineStr">
+        <is>
+          <t>패완얼</t>
+        </is>
+      </c>
+      <c r="C759" s="15" t="inlineStr">
+        <is>
+          <t>pae-wan-eol</t>
+        </is>
+      </c>
+      <c r="D759" s="15" t="inlineStr">
+        <is>
+          <t>연애 · 썸 표현</t>
+        </is>
+      </c>
+      <c r="E759" s="15" t="inlineStr">
+        <is>
+          <t>Dating &amp; Romance</t>
+        </is>
+      </c>
+      <c r="F759" s="16" t="inlineStr">
+        <is>
+          <t>Short for "fashion is completed by the face" — a saying that a good-looking face elevates any outfit, no matter how simple.</t>
+        </is>
+      </c>
+      <c r="G759" s="16" t="inlineStr">
+        <is>
+          <t>Abreviatura de "la moda se completa con la cara": un dicho que dice que una cara atractiva mejora cualquier atuendo, sin importar lo simple que sea.</t>
+        </is>
+      </c>
+      <c r="H759" s="16" t="inlineStr">
+        <is>
+          <t>「時尚的完成是臉」的簡稱——意指帥氣或漂亮的長相能撐起任何穿搭。</t>
+        </is>
+      </c>
+      <c r="I759" s="16" t="inlineStr">
+        <is>
+          <t>“时尚的完成是脸”的简称——意指帅气或漂亮的长相能撑起任何穿搭。</t>
+        </is>
+      </c>
+      <c r="J759" s="16" t="inlineStr">
+        <is>
+          <t>「ファッションの完成は顔」の略——どんなにシンプルな服でも、整った顔立ちが引き立てるという言葉。</t>
+        </is>
+      </c>
+      <c r="K759" s="16" t="inlineStr">
+        <is>
+          <t>역시 패완얼이야, 뭘 입어도 잘 어울려.</t>
+        </is>
+      </c>
+      <c r="L759" s="16" t="inlineStr">
+        <is>
+          <t>It's true, fashion's finished by the face — they look good in anything.</t>
+        </is>
+      </c>
+      <c r="M759" s="16" t="inlineStr">
+        <is>
+          <t>Es cierto, la cara lo completa todo — se le ve bien cualquier cosa.</t>
+        </is>
+      </c>
+      <c r="N759" s="16" t="inlineStr">
+        <is>
+          <t>果然臉才是關鍵，穿什麼都好看。</t>
+        </is>
+      </c>
+      <c r="O759" s="16" t="inlineStr">
+        <is>
+          <t>果然脸才是关键，穿什么都好看。</t>
+        </is>
+      </c>
+      <c r="P759" s="16" t="inlineStr">
+        <is>
+          <t>やっぱり顔が全て、何着ても似合う。</t>
+        </is>
+      </c>
+      <c r="Q759" s="16" t="inlineStr">
+        <is>
+          <t>Fashion/beauty banter</t>
+        </is>
+      </c>
+      <c r="R759" s="15" t="inlineStr">
+        <is>
+          <t>Draft — please double-check</t>
+        </is>
+      </c>
+      <c r="S759" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="760" ht="46" customHeight="1">
+      <c r="A760" s="15" t="inlineStr">
+        <is>
           <t>DAT-082</t>
         </is>
       </c>
-      <c r="B759" s="15" t="inlineStr">
+      <c r="B760" s="15" t="inlineStr">
         <is>
           <t>금사빠</t>
         </is>
       </c>
-      <c r="C759" s="15" t="inlineStr">
+      <c r="C760" s="15" t="inlineStr">
         <is>
           <t>geum-sa-ppa</t>
         </is>
       </c>
-      <c r="D759" s="15" t="inlineStr">
+      <c r="D760" s="15" t="inlineStr">
         <is>
           <t>연애 · 썸 표현</t>
         </is>
       </c>
-      <c r="E759" s="15" t="inlineStr">
+      <c r="E760" s="15" t="inlineStr">
         <is>
           <t>Dating &amp; Romance</t>
         </is>
       </c>
-      <c r="F759" s="16" t="inlineStr">
+      <c r="F760" s="16" t="inlineStr">
         <is>
           <t>Short for 금방 사랑에 빠지는 사람 — someone who falls in love super easily.</t>
         </is>
       </c>
-      <c r="G759" s="16" t="inlineStr">
+      <c r="G760" s="16" t="inlineStr">
         <is>
           <t>Abreviatura de 금방 사랑에 빠지는 사람: alguien que se enamora con mucha facilidad.</t>
         </is>
       </c>
-      <c r="H759" s="16" t="inlineStr">
+      <c r="H760" s="16" t="inlineStr">
         <is>
           <t>금방 사랑에 빠지는 사람（很快就墜入愛河的人）的縮寫：超容易動心的人。</t>
         </is>
       </c>
-      <c r="I759" s="16" t="inlineStr">
+      <c r="I760" s="16" t="inlineStr">
         <is>
           <t>금방 사랑에 빠지는 사람（很快就坠入爱河的人）的缩写：超容易动心的人。</t>
         </is>
       </c>
-      <c r="J759" s="16" t="inlineStr">
+      <c r="J760" s="16" t="inlineStr">
         <is>
           <t>금방 사랑에 빠지는 사람（すぐ恋に落ちる人）の略。惚れっぽい人。</t>
         </is>
       </c>
-      <c r="K759" s="16" t="inlineStr">
+      <c r="K760" s="16" t="inlineStr">
         <is>
           <t>나 금사빠라 웃어 주기만 해도 반해.</t>
         </is>
       </c>
-      <c r="L759" s="16" t="inlineStr">
+      <c r="L760" s="16" t="inlineStr">
         <is>
           <t>I fall in love fast — one smile and I'm gone.</t>
         </is>
       </c>
-      <c r="M759" s="16" t="inlineStr">
+      <c r="M760" s="16" t="inlineStr">
         <is>
           <t>Me enamoro rápido, con una sonrisa ya caigo.</t>
         </is>
       </c>
-      <c r="N759" s="16" t="inlineStr">
+      <c r="N760" s="16" t="inlineStr">
         <is>
           <t>我很容易動心，對我笑一下就淪陷了。</t>
         </is>
       </c>
-      <c r="O759" s="16" t="inlineStr">
+      <c r="O760" s="16" t="inlineStr">
         <is>
           <t>我很容易动心，对我笑一下就沦陷了。</t>
         </is>
       </c>
-      <c r="P759" s="16" t="inlineStr">
+      <c r="P760" s="16" t="inlineStr">
         <is>
           <t>惚れっぽいから、笑ってくれただけで好きになる。</t>
         </is>
       </c>
-      <c r="Q759" s="16" t="inlineStr">
+      <c r="Q760" s="16" t="inlineStr">
         <is>
           <t>Dating talk, fandom</t>
         </is>
       </c>
-      <c r="R759" s="15" t="inlineStr">
+      <c r="R760" s="15" t="inlineStr">
         <is>
           <t>Draft — please double-check</t>
         </is>
       </c>
-      <c r="S759" s="15" t="inlineStr">
+      <c r="S760" s="15" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S759"/>
+  <autoFilter ref="A1:S760"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$760</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$760</definedName>
@@ -42736,7 +42736,7 @@
       </c>
       <c r="R433" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S433" s="11" t="inlineStr">
@@ -65531,7 +65531,7 @@
       </c>
       <c r="R668" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S668" s="13" t="inlineStr">
@@ -65919,7 +65919,7 @@
       </c>
       <c r="R672" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S672" s="13" t="inlineStr">
@@ -66016,7 +66016,7 @@
       </c>
       <c r="R673" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S673" s="13" t="inlineStr">
@@ -66113,7 +66113,7 @@
       </c>
       <c r="R674" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S674" s="13" t="inlineStr">
@@ -66307,7 +66307,7 @@
       </c>
       <c r="R676" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S676" s="13" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S63" s="7" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S64" s="7" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S65" s="7" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S82" s="7" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S86" s="7" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S106" s="7" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S150" s="7" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S161" s="7" t="inlineStr">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="R168" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="R170" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S170" s="7" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="R178" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S178" s="9" t="inlineStr">
@@ -18486,7 +18486,7 @@
       </c>
       <c r="R183" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S183" s="9" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="R186" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S186" s="9" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="R189" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S189" s="9" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="R193" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S193" s="9" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="R199" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S199" s="9" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="R201" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S201" s="9" t="inlineStr">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="R214" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S214" s="9" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="R215" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S215" s="9" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="R223" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S223" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="R238" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S238" s="9" t="inlineStr">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="R239" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S239" s="9" t="inlineStr">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="R248" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S248" s="9" t="inlineStr">
@@ -24985,7 +24985,7 @@
       </c>
       <c r="R250" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S250" s="9" t="inlineStr">
@@ -25955,7 +25955,7 @@
       </c>
       <c r="R260" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S260" s="9" t="inlineStr">
@@ -26440,7 +26440,7 @@
       </c>
       <c r="R265" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S265" s="9" t="inlineStr">
@@ -27119,7 +27119,7 @@
       </c>
       <c r="R272" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S272" s="9" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="R292" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S292" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="R308" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S308" s="11" t="inlineStr">
@@ -30708,7 +30708,7 @@
       </c>
       <c r="R309" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S309" s="11" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="R310" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S310" s="11" t="inlineStr">
@@ -30902,7 +30902,7 @@
       </c>
       <c r="R311" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S311" s="11" t="inlineStr">
@@ -31387,7 +31387,7 @@
       </c>
       <c r="R316" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S316" s="11" t="inlineStr">
@@ -31581,7 +31581,7 @@
       </c>
       <c r="R318" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S318" s="11" t="inlineStr">
@@ -31678,7 +31678,7 @@
       </c>
       <c r="R319" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S319" s="11" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="R320" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S320" s="11" t="inlineStr">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="R321" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S321" s="11" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="R322" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S322" s="11" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="R325" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S325" s="11" t="inlineStr">
@@ -32357,7 +32357,7 @@
       </c>
       <c r="R326" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S326" s="11" t="inlineStr">
@@ -32551,7 +32551,7 @@
       </c>
       <c r="R328" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S328" s="11" t="inlineStr">
@@ -32648,7 +32648,7 @@
       </c>
       <c r="R329" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S329" s="11" t="inlineStr">
@@ -32842,7 +32842,7 @@
       </c>
       <c r="R331" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S331" s="11" t="inlineStr">
@@ -33036,7 +33036,7 @@
       </c>
       <c r="R333" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S333" s="11" t="inlineStr">
@@ -33327,7 +33327,7 @@
       </c>
       <c r="R336" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S336" s="11" t="inlineStr">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="R337" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S337" s="11" t="inlineStr">
@@ -33812,7 +33812,7 @@
       </c>
       <c r="R341" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S341" s="11" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="R344" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S344" s="11" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="R357" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S357" s="11" t="inlineStr">
@@ -35558,7 +35558,7 @@
       </c>
       <c r="R359" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S359" s="11" t="inlineStr">
@@ -35655,7 +35655,7 @@
       </c>
       <c r="R360" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S360" s="11" t="inlineStr">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="R363" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S363" s="11" t="inlineStr">
@@ -38759,7 +38759,7 @@
       </c>
       <c r="R392" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S392" s="11" t="inlineStr">
@@ -38856,7 +38856,7 @@
       </c>
       <c r="R393" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S393" s="11" t="inlineStr">
@@ -38953,7 +38953,7 @@
       </c>
       <c r="R394" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S394" s="11" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="R395" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S395" s="11" t="inlineStr">
@@ -39147,7 +39147,7 @@
       </c>
       <c r="R396" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S396" s="11" t="inlineStr">
@@ -39244,7 +39244,7 @@
       </c>
       <c r="R397" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S397" s="11" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="R405" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S405" s="11" t="inlineStr">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="R422" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S422" s="11" t="inlineStr">
@@ -42542,7 +42542,7 @@
       </c>
       <c r="R431" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S431" s="11" t="inlineStr">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="R432" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S432" s="11" t="inlineStr">
@@ -42930,7 +42930,7 @@
       </c>
       <c r="R435" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S435" s="13" t="inlineStr">
@@ -43027,7 +43027,7 @@
       </c>
       <c r="R436" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S436" s="13" t="inlineStr">
@@ -43124,7 +43124,7 @@
       </c>
       <c r="R437" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S437" s="13" t="inlineStr">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="R438" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S438" s="13" t="inlineStr">
@@ -43318,7 +43318,7 @@
       </c>
       <c r="R439" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S439" s="13" t="inlineStr">
@@ -43415,7 +43415,7 @@
       </c>
       <c r="R440" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S440" s="13" t="inlineStr">
@@ -43512,7 +43512,7 @@
       </c>
       <c r="R441" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S441" s="13" t="inlineStr">
@@ -43609,7 +43609,7 @@
       </c>
       <c r="R442" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S442" s="13" t="inlineStr">
@@ -43803,7 +43803,7 @@
       </c>
       <c r="R444" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S444" s="13" t="inlineStr">
@@ -43997,7 +43997,7 @@
       </c>
       <c r="R446" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S446" s="13" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="R447" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S447" s="13" t="inlineStr">
@@ -45452,7 +45452,7 @@
       </c>
       <c r="R461" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S461" s="13" t="inlineStr">
@@ -45549,7 +45549,7 @@
       </c>
       <c r="R462" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S462" s="13" t="inlineStr">
@@ -45743,7 +45743,7 @@
       </c>
       <c r="R464" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S464" s="13" t="inlineStr">
@@ -46422,7 +46422,7 @@
       </c>
       <c r="R471" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S471" s="13" t="inlineStr">
@@ -46519,7 +46519,7 @@
       </c>
       <c r="R472" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S472" s="13" t="inlineStr">
@@ -46616,7 +46616,7 @@
       </c>
       <c r="R473" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S473" s="13" t="inlineStr">
@@ -46713,7 +46713,7 @@
       </c>
       <c r="R474" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S474" s="13" t="inlineStr">
@@ -46810,7 +46810,7 @@
       </c>
       <c r="R475" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S475" s="13" t="inlineStr">
@@ -47004,7 +47004,7 @@
       </c>
       <c r="R477" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S477" s="13" t="inlineStr">
@@ -47101,7 +47101,7 @@
       </c>
       <c r="R478" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S478" s="13" t="inlineStr">
@@ -47198,7 +47198,7 @@
       </c>
       <c r="R479" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S479" s="13" t="inlineStr">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="R481" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S481" s="13" t="inlineStr">
@@ -47489,7 +47489,7 @@
       </c>
       <c r="R482" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S482" s="13" t="inlineStr">
@@ -48168,7 +48168,7 @@
       </c>
       <c r="R489" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S489" s="13" t="inlineStr">
@@ -48265,7 +48265,7 @@
       </c>
       <c r="R490" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S490" s="13" t="inlineStr">
@@ -48362,7 +48362,7 @@
       </c>
       <c r="R491" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S491" s="13" t="inlineStr">
@@ -48459,7 +48459,7 @@
       </c>
       <c r="R492" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S492" s="13" t="inlineStr">
@@ -48556,7 +48556,7 @@
       </c>
       <c r="R493" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S493" s="13" t="inlineStr">
@@ -48653,7 +48653,7 @@
       </c>
       <c r="R494" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S494" s="13" t="inlineStr">
@@ -48750,7 +48750,7 @@
       </c>
       <c r="R495" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S495" s="13" t="inlineStr">
@@ -48847,7 +48847,7 @@
       </c>
       <c r="R496" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S496" s="13" t="inlineStr">
@@ -48944,7 +48944,7 @@
       </c>
       <c r="R497" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S497" s="13" t="inlineStr">
@@ -49041,7 +49041,7 @@
       </c>
       <c r="R498" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S498" s="13" t="inlineStr">
@@ -49526,7 +49526,7 @@
       </c>
       <c r="R503" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S503" s="13" t="inlineStr">
@@ -49817,7 +49817,7 @@
       </c>
       <c r="R506" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S506" s="13" t="inlineStr">
@@ -49914,7 +49914,7 @@
       </c>
       <c r="R507" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S507" s="13" t="inlineStr">
@@ -50011,7 +50011,7 @@
       </c>
       <c r="R508" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S508" s="13" t="inlineStr">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="R509" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S509" s="13" t="inlineStr">
@@ -50302,7 +50302,7 @@
       </c>
       <c r="R511" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S511" s="13" t="inlineStr">
@@ -50690,7 +50690,7 @@
       </c>
       <c r="R515" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S515" s="13" t="inlineStr">
@@ -50884,7 +50884,7 @@
       </c>
       <c r="R517" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S517" s="13" t="inlineStr">
@@ -50981,7 +50981,7 @@
       </c>
       <c r="R518" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S518" s="13" t="inlineStr">
@@ -51757,7 +51757,7 @@
       </c>
       <c r="R526" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S526" s="13" t="inlineStr">
@@ -52048,7 +52048,7 @@
       </c>
       <c r="R529" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S529" s="13" t="inlineStr">
@@ -53212,7 +53212,7 @@
       </c>
       <c r="R541" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S541" s="13" t="inlineStr">
@@ -53406,7 +53406,7 @@
       </c>
       <c r="R543" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S543" s="13" t="inlineStr">
@@ -53503,7 +53503,7 @@
       </c>
       <c r="R544" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S544" s="13" t="inlineStr">
@@ -53600,7 +53600,7 @@
       </c>
       <c r="R545" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S545" s="13" t="inlineStr">
@@ -53794,7 +53794,7 @@
       </c>
       <c r="R547" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S547" s="13" t="inlineStr">
@@ -53891,7 +53891,7 @@
       </c>
       <c r="R548" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S548" s="13" t="inlineStr">
@@ -53988,7 +53988,7 @@
       </c>
       <c r="R549" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S549" s="13" t="inlineStr">
@@ -56316,7 +56316,7 @@
       </c>
       <c r="R573" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S573" s="13" t="inlineStr">
@@ -56413,7 +56413,7 @@
       </c>
       <c r="R574" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S574" s="13" t="inlineStr">
@@ -56607,7 +56607,7 @@
       </c>
       <c r="R576" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S576" s="13" t="inlineStr">
@@ -56704,7 +56704,7 @@
       </c>
       <c r="R577" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S577" s="13" t="inlineStr">
@@ -56898,7 +56898,7 @@
       </c>
       <c r="R579" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S579" s="13" t="inlineStr">
@@ -57092,7 +57092,7 @@
       </c>
       <c r="R581" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S581" s="13" t="inlineStr">
@@ -57189,7 +57189,7 @@
       </c>
       <c r="R582" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S582" s="13" t="inlineStr">
@@ -57286,7 +57286,7 @@
       </c>
       <c r="R583" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S583" s="13" t="inlineStr">
@@ -57868,7 +57868,7 @@
       </c>
       <c r="R589" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S589" s="13" t="inlineStr">
@@ -57965,7 +57965,7 @@
       </c>
       <c r="R590" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S590" s="13" t="inlineStr">
@@ -58256,7 +58256,7 @@
       </c>
       <c r="R593" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S593" s="13" t="inlineStr">
@@ -59420,7 +59420,7 @@
       </c>
       <c r="R605" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S605" s="13" t="inlineStr">
@@ -59517,7 +59517,7 @@
       </c>
       <c r="R606" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S606" s="13" t="inlineStr">
@@ -59808,7 +59808,7 @@
       </c>
       <c r="R609" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S609" s="13" t="inlineStr">
@@ -59905,7 +59905,7 @@
       </c>
       <c r="R610" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S610" s="13" t="inlineStr">
@@ -60002,7 +60002,7 @@
       </c>
       <c r="R611" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S611" s="13" t="inlineStr">
@@ -60390,7 +60390,7 @@
       </c>
       <c r="R615" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S615" s="13" t="inlineStr">
@@ -60584,7 +60584,7 @@
       </c>
       <c r="R617" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S617" s="13" t="inlineStr">
@@ -60875,7 +60875,7 @@
       </c>
       <c r="R620" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S620" s="13" t="inlineStr">
@@ -61166,7 +61166,7 @@
       </c>
       <c r="R623" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S623" s="13" t="inlineStr">
@@ -61203,7 +61203,7 @@
       </c>
       <c r="F624" s="14" t="inlineStr">
         <is>
-          <t>A dialect-flavored "what's going on?" (무슨 일이고) where 일이구 is written as the numbers 129.</t>
+          <t>A dialect-flavored "what's going on?" (무슨 일이고) where 일이고 is written as the numbers 129.</t>
         </is>
       </c>
       <c r="G624" s="14" t="inlineStr">
@@ -61360,7 +61360,7 @@
       </c>
       <c r="R625" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S625" s="13" t="inlineStr">
@@ -61457,7 +61457,7 @@
       </c>
       <c r="R626" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S626" s="13" t="inlineStr">
@@ -61748,7 +61748,7 @@
       </c>
       <c r="R629" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S629" s="13" t="inlineStr">
@@ -61942,7 +61942,7 @@
       </c>
       <c r="R631" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S631" s="13" t="inlineStr">
@@ -62136,7 +62136,7 @@
       </c>
       <c r="R633" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S633" s="13" t="inlineStr">
@@ -62233,7 +62233,7 @@
       </c>
       <c r="R634" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S634" s="13" t="inlineStr">
@@ -62330,7 +62330,7 @@
       </c>
       <c r="R635" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S635" s="13" t="inlineStr">
@@ -62524,7 +62524,7 @@
       </c>
       <c r="R637" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S637" s="13" t="inlineStr">
@@ -62718,7 +62718,7 @@
       </c>
       <c r="R639" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S639" s="13" t="inlineStr">
@@ -62815,7 +62815,7 @@
       </c>
       <c r="R640" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S640" s="13" t="inlineStr">
@@ -63203,7 +63203,7 @@
       </c>
       <c r="R644" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S644" s="13" t="inlineStr">
@@ -63397,7 +63397,7 @@
       </c>
       <c r="R646" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S646" s="13" t="inlineStr">
@@ -63591,7 +63591,7 @@
       </c>
       <c r="R648" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S648" s="13" t="inlineStr">
@@ -63688,7 +63688,7 @@
       </c>
       <c r="R649" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S649" s="13" t="inlineStr">
@@ -64076,7 +64076,7 @@
       </c>
       <c r="R653" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S653" s="13" t="inlineStr">
@@ -64270,7 +64270,7 @@
       </c>
       <c r="R655" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S655" s="13" t="inlineStr">
@@ -64367,7 +64367,7 @@
       </c>
       <c r="R656" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S656" s="13" t="inlineStr">
@@ -64464,7 +64464,7 @@
       </c>
       <c r="R657" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S657" s="13" t="inlineStr">
@@ -64658,7 +64658,7 @@
       </c>
       <c r="R659" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S659" s="13" t="inlineStr">
@@ -64755,7 +64755,7 @@
       </c>
       <c r="R660" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S660" s="13" t="inlineStr">
@@ -64852,7 +64852,7 @@
       </c>
       <c r="R661" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S661" s="13" t="inlineStr">
@@ -64949,7 +64949,7 @@
       </c>
       <c r="R662" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S662" s="13" t="inlineStr">
@@ -65046,7 +65046,7 @@
       </c>
       <c r="R663" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S663" s="13" t="inlineStr">
@@ -65143,7 +65143,7 @@
       </c>
       <c r="R664" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S664" s="13" t="inlineStr">
@@ -65240,7 +65240,7 @@
       </c>
       <c r="R665" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S665" s="13" t="inlineStr">
@@ -65337,7 +65337,7 @@
       </c>
       <c r="R666" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S666" s="13" t="inlineStr">
@@ -65434,7 +65434,7 @@
       </c>
       <c r="R667" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S667" s="13" t="inlineStr">
@@ -65531,7 +65531,7 @@
       </c>
       <c r="R668" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S668" s="13" t="inlineStr">
@@ -65725,7 +65725,7 @@
       </c>
       <c r="R670" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S670" s="13" t="inlineStr">
@@ -65822,7 +65822,7 @@
       </c>
       <c r="R671" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S671" s="13" t="inlineStr">
@@ -67665,7 +67665,7 @@
       </c>
       <c r="R690" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S690" s="15" t="inlineStr">
@@ -67762,7 +67762,7 @@
       </c>
       <c r="R691" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S691" s="15" t="inlineStr">
@@ -67859,7 +67859,7 @@
       </c>
       <c r="R692" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S692" s="15" t="inlineStr">
@@ -68150,7 +68150,7 @@
       </c>
       <c r="R695" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S695" s="15" t="inlineStr">
@@ -68344,7 +68344,7 @@
       </c>
       <c r="R697" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S697" s="15" t="inlineStr">
@@ -68441,7 +68441,7 @@
       </c>
       <c r="R698" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S698" s="15" t="inlineStr">
@@ -68635,7 +68635,7 @@
       </c>
       <c r="R700" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S700" s="15" t="inlineStr">
@@ -68732,7 +68732,7 @@
       </c>
       <c r="R701" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S701" s="15" t="inlineStr">
@@ -68926,7 +68926,7 @@
       </c>
       <c r="R703" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S703" s="15" t="inlineStr">
@@ -69023,7 +69023,7 @@
       </c>
       <c r="R704" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S704" s="15" t="inlineStr">
@@ -69120,7 +69120,7 @@
       </c>
       <c r="R705" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S705" s="15" t="inlineStr">
@@ -69217,7 +69217,7 @@
       </c>
       <c r="R706" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S706" s="15" t="inlineStr">
@@ -69314,7 +69314,7 @@
       </c>
       <c r="R707" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S707" s="15" t="inlineStr">
@@ -69896,7 +69896,7 @@
       </c>
       <c r="R713" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S713" s="15" t="inlineStr">
@@ -71254,7 +71254,7 @@
       </c>
       <c r="R727" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S727" s="15" t="inlineStr">
@@ -72418,7 +72418,7 @@
       </c>
       <c r="R739" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S739" s="15" t="inlineStr">
@@ -72806,7 +72806,7 @@
       </c>
       <c r="R743" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S743" s="15" t="inlineStr">
@@ -72903,7 +72903,7 @@
       </c>
       <c r="R744" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S744" s="15" t="inlineStr">
@@ -74746,7 +74746,7 @@
       </c>
       <c r="R763" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S763" s="15" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
@@ -2033,27 +2033,27 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Casual behind-the-scenes content idols make and post themselves.</t>
+          <t>Short for 자체 콘텐츠 — videos a group's agency plans and produces in-house, like the group's own variety shows, vlogs and behind-the-scenes clips.</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Contenido casual detrás de cámaras que los ídolos crean y publican ellos mismos.</t>
+          <t>Abreviatura de 자체 콘텐츠: videos que la agencia del grupo planea y produce por su cuenta, como sus propios programas de variedades, vlogs y clips detrás de cámaras.</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>偶像自己拍攝並上傳的輕鬆幕後內容。</t>
+          <t>「自體內容」的縮寫——經紀公司自己企劃、自製的偶像影片，例如團體自製綜藝、vlog和幕後花絮。</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>偶像自己拍摄并上传的轻松幕后内容。</t>
+          <t>“自体内容”的缩写——经纪公司自己企划、自制的偶像视频，例如团体自制综艺、vlog和幕后花絮。</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>アイドルが自分で撮影して投稿する気軽な舞台裏コンテンツ。</t>
+          <t>「自体コンテンツ」の略。事務所が自ら企画・制作するアイドルの映像コンテンツで、グループの自主制作バラエティやVlog、舞台裏映像など。</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S68" s="7" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S69" s="7" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S70" s="7" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S71" s="7" t="inlineStr">
@@ -8241,27 +8241,27 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>An "all-rounder idol" skilled across singing, dancing, rapping, and visuals.</t>
+          <t>An "all-rounder idol" — good at everything: on stage, and also in variety shows, acting and more.</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Un "ídolo todoterreno", talentoso en canto, baile, rap y también en apariencia.</t>
+          <t>Un "ídolo todoterreno": bueno en todo, en el escenario y también en programas de variedades, actuación y más.</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>在唱歌、跳舞、饒舌、visual各方面都很全面的「全能偶像」。</t>
+          <t>舞台之外，綜藝、演戲等各方面也都很拿手的「全能偶像」。</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>在唱歌、跳舞、饶舌、visual各方面都很全面的“全能偶像”。</t>
+          <t>舞台之外，综艺、演戏等各方面也都很拿手的“全能偶像”。</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>歌、ダンス、ラップ、ビジュアルすべてに秀でた「万能アイドル」。</t>
+          <t>ステージだけでなく、バラエティや演技などなんでもこなす「万能アイドル」。</t>
         </is>
       </c>
       <c r="K78" s="8" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S88" s="7" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S89" s="7" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>Short for "first-day-and-week sales" — an album's initial sales figures, a key chart metric.</t>
+          <t>Short for 초동 판매량 (initial sales) — an album's sales in its first week from release, a key chart metric.</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Abreviatura de "ventas del primer día y semana": las cifras de ventas iniciales de un álbum, una métrica clave de las listas.</t>
+          <t>Abreviatura de 초동 판매량 (ventas iniciales): las ventas de un álbum en su primera semana desde el lanzamiento, una métrica clave de las listas.</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>“初动”——专辑发行首周的销量数字，是重要的排行指针。</t>
+          <t>“初动”——专辑发行首周的销量数字，是重要的排行指标。</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>「初日・初週の売り上げ」の略——アルバムの初期販売数を示す、重要なチャート指標。</t>
+          <t>「初動販売量」の略——発売から1週間のアルバム販売枚数のことで、重要なチャート指標。</t>
         </is>
       </c>
       <c r="K100" s="8" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S100" s="7" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>美国告示牌音乐排行榜，是K-pop国际成功的重要指针。</t>
+          <t>美国告示牌音乐排行榜，是K-pop国际成功的重要指标。</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -11830,27 +11830,27 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>The finale round of a survival show where the final debut lineup ranking is revealed live.</t>
+          <t>A ranking announcement round on a survival show, where contestants' current ranks are revealed and those below the cutoff are eliminated.</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>La ronda final de un programa de supervivencia donde se revela en vivo el ranking final de la alineación de debut.</t>
+          <t>La ronda de anuncio de posiciones de un programa de supervivencia, donde se revela el puesto actual de cada concursante y quienes quedan por debajo del corte son eliminados.</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>選秀節目最終回中現場公布最終出道排名的環節。</t>
+          <t>選秀節目中公布參賽者當前排名的環節，排名在淘汰線以下的人會被淘汰。</t>
         </is>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>选秀节目最终回中现场公布最终出道排名的环节。</t>
+          <t>选秀节目中公布参赛者当前排名的环节，排名在淘汰线以下的人会被淘汰。</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>サバイバル番組の最終回で、最終的なデビューメンバーの順位がライブで発表される場面。</t>
+          <t>サバイバル番組で参加者の現在の順位が発表され、ボーダー以下の人が脱落する回。</t>
         </is>
       </c>
       <c r="K115" s="8" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>Todos lloramos juntos viendo la ceremonia de revelación del ranking final.</t>
+          <t>Todos lloramos juntos viendo la ceremonia de anuncio de posiciones.</t>
         </is>
       </c>
       <c r="N115" s="8" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="Q115" s="8" t="inlineStr">
         <is>
-          <t>Survival show finales</t>
+          <t>Survival shows</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S115" s="7" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S117" s="7" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S120" s="7" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S121" s="7" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S152" s="7" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S153" s="7" t="inlineStr">
@@ -15867,7 +15867,7 @@
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S156" s="7" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S157" s="7" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S159" s="7" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="R160" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S160" s="7" t="inlineStr">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="R162" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S162" s="7" t="inlineStr">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="R164" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S164" s="7" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="R167" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="R169" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S169" s="7" t="inlineStr">
@@ -19262,7 +19262,7 @@
       </c>
       <c r="R191" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S191" s="9" t="inlineStr">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="R216" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S216" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="R227" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S227" s="9" t="inlineStr">
@@ -23142,7 +23142,7 @@
       </c>
       <c r="R231" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S231" s="9" t="inlineStr">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="R234" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S234" s="9" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="R249" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S249" s="9" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="R256" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S256" s="9" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="R270" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S270" s="9" t="inlineStr">
@@ -27992,7 +27992,7 @@
       </c>
       <c r="R281" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S281" s="9" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="R284" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S284" s="9" t="inlineStr">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="R293" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S293" s="9" t="inlineStr">
@@ -29544,7 +29544,7 @@
       </c>
       <c r="R297" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S297" s="9" t="inlineStr">
@@ -29641,7 +29641,7 @@
       </c>
       <c r="R298" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S298" s="9" t="inlineStr">
@@ -29932,7 +29932,7 @@
       </c>
       <c r="R301" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S301" s="9" t="inlineStr">
@@ -30126,7 +30126,7 @@
       </c>
       <c r="R303" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S303" s="9" t="inlineStr">
@@ -30417,7 +30417,7 @@
       </c>
       <c r="R306" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S306" s="9" t="inlineStr">
@@ -35073,7 +35073,7 @@
       </c>
       <c r="R354" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S354" s="11" t="inlineStr">
@@ -35170,7 +35170,7 @@
       </c>
       <c r="R355" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S355" s="11" t="inlineStr">
@@ -35849,7 +35849,7 @@
       </c>
       <c r="R362" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S362" s="11" t="inlineStr">
@@ -36043,7 +36043,7 @@
       </c>
       <c r="R364" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S364" s="11" t="inlineStr">
@@ -36140,7 +36140,7 @@
       </c>
       <c r="R365" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S365" s="11" t="inlineStr">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="R366" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S366" s="11" t="inlineStr">
@@ -36334,7 +36334,7 @@
       </c>
       <c r="R367" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S367" s="11" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="R371" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S371" s="11" t="inlineStr">
@@ -36819,7 +36819,7 @@
       </c>
       <c r="R372" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S372" s="11" t="inlineStr">
@@ -36916,7 +36916,7 @@
       </c>
       <c r="R373" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S373" s="11" t="inlineStr">
@@ -37013,7 +37013,7 @@
       </c>
       <c r="R374" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S374" s="11" t="inlineStr">
@@ -37110,7 +37110,7 @@
       </c>
       <c r="R375" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S375" s="11" t="inlineStr">
@@ -37207,7 +37207,7 @@
       </c>
       <c r="R376" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S376" s="11" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="R378" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S378" s="11" t="inlineStr">
@@ -37498,7 +37498,7 @@
       </c>
       <c r="R379" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S379" s="11" t="inlineStr">
@@ -37595,7 +37595,7 @@
       </c>
       <c r="R380" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S380" s="11" t="inlineStr">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="R385" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S385" s="11" t="inlineStr">
@@ -38177,7 +38177,7 @@
       </c>
       <c r="R386" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S386" s="11" t="inlineStr">
@@ -39341,7 +39341,7 @@
       </c>
       <c r="R398" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S398" s="11" t="inlineStr">
@@ -39438,7 +39438,7 @@
       </c>
       <c r="R399" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S399" s="11" t="inlineStr">
@@ -39535,7 +39535,7 @@
       </c>
       <c r="R400" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S400" s="11" t="inlineStr">
@@ -39632,7 +39632,7 @@
       </c>
       <c r="R401" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S401" s="11" t="inlineStr">
@@ -39826,7 +39826,7 @@
       </c>
       <c r="R403" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S403" s="11" t="inlineStr">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="R404" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S404" s="11" t="inlineStr">
@@ -40117,7 +40117,7 @@
       </c>
       <c r="R406" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S406" s="11" t="inlineStr">
@@ -40505,7 +40505,7 @@
       </c>
       <c r="R410" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S410" s="11" t="inlineStr">
@@ -40893,7 +40893,7 @@
       </c>
       <c r="R414" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S414" s="11" t="inlineStr">
@@ -41184,7 +41184,7 @@
       </c>
       <c r="R417" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S417" s="11" t="inlineStr">
@@ -67374,7 +67374,7 @@
       </c>
       <c r="R687" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S687" s="15" t="inlineStr">
@@ -67471,7 +67471,7 @@
       </c>
       <c r="R688" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S688" s="15" t="inlineStr">
@@ -67956,7 +67956,7 @@
       </c>
       <c r="R693" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S693" s="15" t="inlineStr">
@@ -68247,7 +68247,7 @@
       </c>
       <c r="R696" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S696" s="15" t="inlineStr">
@@ -68538,7 +68538,7 @@
       </c>
       <c r="R699" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S699" s="15" t="inlineStr">
@@ -69508,7 +69508,7 @@
       </c>
       <c r="R709" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S709" s="15" t="inlineStr">
@@ -69702,7 +69702,7 @@
       </c>
       <c r="R711" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S711" s="15" t="inlineStr">
@@ -70187,7 +70187,7 @@
       </c>
       <c r="R716" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S716" s="15" t="inlineStr">
@@ -71739,7 +71739,7 @@
       </c>
       <c r="R732" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S732" s="15" t="inlineStr">
@@ -71933,7 +71933,7 @@
       </c>
       <c r="R734" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S734" s="15" t="inlineStr">
@@ -72515,7 +72515,7 @@
       </c>
       <c r="R740" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S740" s="15" t="inlineStr">
@@ -74649,7 +74649,7 @@
       </c>
       <c r="R762" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S762" s="15" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S96" s="7" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S102" s="7" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S103" s="7" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S104" s="7" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S108" s="7" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S122" s="7" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S123" s="7" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S126" s="7" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S127" s="7" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S128" s="7" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S129" s="7" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S138" s="7" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="R166" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="R171" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S171" s="7" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="R443" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S443" s="13" t="inlineStr">
@@ -66501,7 +66501,7 @@
       </c>
       <c r="R678" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S678" s="13" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S75" s="7" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S76" s="7" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S79" s="7" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S80" s="7" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S81" s="7" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S83" s="7" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S84" s="7" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S85" s="7" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S90" s="7" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S91" s="7" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S109" s="7" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S113" s="7" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S124" s="7" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S134" s="7" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S147" s="7" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="R155" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S155" s="7" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="R195" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S195" s="9" t="inlineStr">
@@ -19747,7 +19747,7 @@
       </c>
       <c r="R196" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S196" s="9" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="R197" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S197" s="9" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="R228" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S228" s="9" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="R233" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S233" s="9" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="R262" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S262" s="9" t="inlineStr">
@@ -29447,7 +29447,7 @@
       </c>
       <c r="R296" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S296" s="9" t="inlineStr">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="R300" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S300" s="9" t="inlineStr">
@@ -30999,7 +30999,7 @@
       </c>
       <c r="R312" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S312" s="11" t="inlineStr">
@@ -31036,27 +31036,27 @@
       </c>
       <c r="F313" s="12" t="inlineStr">
         <is>
-          <t>Literally "eyes moist" — describes something pitiful or embarrassing.</t>
+          <t>Short for 안구에 습기 ("moisture in the eyes") — something so sad or pitiful it almost brings tears; often used half-jokingly.</t>
         </is>
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
-          <t>Literalmente "ojos húmedos", describe algo lamentable o vergonzoso.</t>
+          <t>Abreviatura de 안구에 습기 ("humedad en los ojos"): algo tan triste o lamentable que casi hace llorar; a menudo se dice medio en broma.</t>
         </is>
       </c>
       <c r="H313" s="12" t="inlineStr">
         <is>
-          <t>字面意思是「眼睛濕了」——形容可憐或尷尬的事，淚目。</t>
+          <t>「안구에 습기」（眼球有濕氣）的縮寫——形容可憐、悲傷到快要流淚的事，常帶點半開玩笑的語氣。</t>
         </is>
       </c>
       <c r="I313" s="12" t="inlineStr">
         <is>
-          <t>字面意思是“眼睛湿了”——形容可怜或尴尬的事，泪目。</t>
+          <t>“안구에 습기”（眼球有湿气）的缩写——形容可怜、悲伤到快要流泪的事，常带点半开玩笑的语气。</t>
         </is>
       </c>
       <c r="J313" s="12" t="inlineStr">
         <is>
-          <t>直訳すると「目が濡れる」——哀れ、または恥ずかしいことを表す。</t>
+          <t>「안구에 습기（眼球に湿気）」の略——涙が出そうなほど哀れ・悲しいことを表す。半分冗談っぽく使うことが多い。</t>
         </is>
       </c>
       <c r="K313" s="12" t="inlineStr">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="R313" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S313" s="11" t="inlineStr">
@@ -31193,7 +31193,7 @@
       </c>
       <c r="R314" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S314" s="11" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="R315" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S315" s="11" t="inlineStr">
@@ -31484,7 +31484,7 @@
       </c>
       <c r="R317" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S317" s="11" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="R330" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S330" s="11" t="inlineStr">
@@ -33521,7 +33521,7 @@
       </c>
       <c r="R338" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S338" s="11" t="inlineStr">
@@ -33618,7 +33618,7 @@
       </c>
       <c r="R339" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S339" s="11" t="inlineStr">
@@ -34006,7 +34006,7 @@
       </c>
       <c r="R343" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S343" s="11" t="inlineStr">
@@ -34685,7 +34685,7 @@
       </c>
       <c r="R350" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S350" s="11" t="inlineStr">
@@ -34976,7 +34976,7 @@
       </c>
       <c r="R353" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S353" s="11" t="inlineStr">
@@ -35752,7 +35752,7 @@
       </c>
       <c r="R361" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S361" s="11" t="inlineStr">
@@ -36625,7 +36625,7 @@
       </c>
       <c r="R370" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S370" s="11" t="inlineStr">
@@ -38468,7 +38468,7 @@
       </c>
       <c r="R389" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S389" s="11" t="inlineStr">
@@ -40602,7 +40602,7 @@
       </c>
       <c r="R411" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S411" s="11" t="inlineStr">
@@ -41281,7 +41281,7 @@
       </c>
       <c r="R418" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S418" s="11" t="inlineStr">
@@ -41766,7 +41766,7 @@
       </c>
       <c r="R423" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S423" s="11" t="inlineStr">
@@ -42154,7 +42154,7 @@
       </c>
       <c r="R427" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S427" s="11" t="inlineStr">
@@ -42348,7 +42348,7 @@
       </c>
       <c r="R429" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S429" s="11" t="inlineStr">
@@ -69411,7 +69411,7 @@
       </c>
       <c r="R708" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S708" s="15" t="inlineStr">
@@ -69605,7 +69605,7 @@
       </c>
       <c r="R710" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S710" s="15" t="inlineStr">
@@ -70284,7 +70284,7 @@
       </c>
       <c r="R717" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S717" s="15" t="inlineStr">
@@ -70575,7 +70575,7 @@
       </c>
       <c r="R720" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S720" s="15" t="inlineStr">
@@ -70769,7 +70769,7 @@
       </c>
       <c r="R722" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S722" s="15" t="inlineStr">
@@ -71448,7 +71448,7 @@
       </c>
       <c r="R729" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S729" s="15" t="inlineStr">
@@ -71642,7 +71642,7 @@
       </c>
       <c r="R731" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S731" s="15" t="inlineStr">
@@ -72030,7 +72030,7 @@
       </c>
       <c r="R735" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S735" s="15" t="inlineStr">
@@ -74552,7 +74552,7 @@
       </c>
       <c r="R761" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S761" s="15" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S66" s="7" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S74" s="7" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S99" s="7" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S101" s="7" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S105" s="7" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S107" s="7" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S137" s="7" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="R141" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S141" s="7" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="R142" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S142" s="7" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S149" s="7" t="inlineStr">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="R158" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S158" s="7" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="R163" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S163" s="7" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="R188" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S188" s="9" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="R235" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S235" s="9" t="inlineStr">
@@ -24500,7 +24500,7 @@
       </c>
       <c r="R245" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S245" s="9" t="inlineStr">
@@ -26537,7 +26537,7 @@
       </c>
       <c r="R266" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S266" s="9" t="inlineStr">
@@ -32454,7 +32454,7 @@
       </c>
       <c r="R327" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S327" s="11" t="inlineStr">
@@ -35461,7 +35461,7 @@
       </c>
       <c r="R358" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S358" s="11" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="R368" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S368" s="11" t="inlineStr">
@@ -36528,7 +36528,7 @@
       </c>
       <c r="R369" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S369" s="11" t="inlineStr">
@@ -40990,7 +40990,7 @@
       </c>
       <c r="R415" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S415" s="11" t="inlineStr">
@@ -41378,7 +41378,7 @@
       </c>
       <c r="R419" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S419" s="11" t="inlineStr">
@@ -42057,7 +42057,7 @@
       </c>
       <c r="R426" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S426" s="11" t="inlineStr">
@@ -49623,7 +49623,7 @@
       </c>
       <c r="R504" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S504" s="13" t="inlineStr">
@@ -52824,7 +52824,7 @@
       </c>
       <c r="R537" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S537" s="13" t="inlineStr">
@@ -53115,7 +53115,7 @@
       </c>
       <c r="R540" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S540" s="13" t="inlineStr">
@@ -60972,7 +60972,7 @@
       </c>
       <c r="R621" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S621" s="13" t="inlineStr">
@@ -63494,7 +63494,7 @@
       </c>
       <c r="R647" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S647" s="13" t="inlineStr">
@@ -70478,7 +70478,7 @@
       </c>
       <c r="R719" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S719" s="15" t="inlineStr">
@@ -71157,7 +71157,7 @@
       </c>
       <c r="R726" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S726" s="15" t="inlineStr">
@@ -73000,7 +73000,7 @@
       </c>
       <c r="R745" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S745" s="15" t="inlineStr">
@@ -73037,57 +73037,57 @@
       </c>
       <c r="F746" s="16" t="inlineStr">
         <is>
-          <t>"Boyfriend look" — a fashion style mimicking oversized, borrowed-looking boyfriend clothing.</t>
+          <t>"Boyfriend look" — a guy's outfit or vibe that makes him look like the ideal boyfriend on a date; fans also use it for idol photos that feel like a date.</t>
         </is>
       </c>
       <c r="G746" s="16" t="inlineStr">
         <is>
-          <t>"Look de novio": un estilo de moda que imita ropa holgada, como si fuera prestada por el novio.</t>
+          <t>"Look de novio": el outfit o la vibra de un chico que lo hace ver como el novio ideal en una cita; los fans también lo usan para fotos de idols que parecen de una cita.</t>
         </is>
       </c>
       <c r="H746" s="16" t="inlineStr">
         <is>
-          <t>「男友風」——模仿男友寬鬆、彷彿借穿男友衣服的穿搭風格。</t>
+          <t>「男友風」——男生看起來像約會中理想男友的穿搭或氛圍；粉絲也用來形容像約會照的偶像照片。</t>
         </is>
       </c>
       <c r="I746" s="16" t="inlineStr">
         <is>
-          <t>“男友风”——模仿男友宽松、仿佛借穿男友衣服的穿搭风格。</t>
+          <t>“男友风”——男生看起来像约会中理想男友的穿搭或氛围；粉丝也用来形容像约会照的偶像照片。</t>
         </is>
       </c>
       <c r="J746" s="16" t="inlineStr">
         <is>
-          <t>「彼氏ルック」——彼氏の服を借りたような、オーバーサイズのファッションスタイル。</t>
+          <t>「彼氏ルック」——デート中の理想の彼氏みたいに見える男性の服装や雰囲気。デートっぽいアイドルの写真にも使う。</t>
         </is>
       </c>
       <c r="K746" s="16" t="inlineStr">
         <is>
-          <t>오늘 남친룩으로 입어봤어.</t>
+          <t>이 사진 완전 남친룩이다.</t>
         </is>
       </c>
       <c r="L746" s="16" t="inlineStr">
         <is>
-          <t>I tried out the boyfriend-look style today.</t>
+          <t>This photo is total boyfriend look.</t>
         </is>
       </c>
       <c r="M746" s="16" t="inlineStr">
         <is>
-          <t>Hoy probé el estilo de ropa prestada del novio.</t>
+          <t>Esta foto es puro look de novio.</t>
         </is>
       </c>
       <c r="N746" s="16" t="inlineStr">
         <is>
-          <t>今天試了男友風穿搭。</t>
+          <t>這張照片完全是男友風。</t>
         </is>
       </c>
       <c r="O746" s="16" t="inlineStr">
         <is>
-          <t>今天试了男友风穿搭。</t>
+          <t>这张照片完全是男友风。</t>
         </is>
       </c>
       <c r="P746" s="16" t="inlineStr">
         <is>
-          <t>今日、彼シャツ風の格好してみた。</t>
+          <t>この写真、完全に彼氏ルックだ。</t>
         </is>
       </c>
       <c r="Q746" s="16" t="inlineStr">
@@ -73097,7 +73097,7 @@
       </c>
       <c r="R746" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S746" s="15" t="inlineStr">
@@ -73388,7 +73388,7 @@
       </c>
       <c r="R749" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S749" s="15" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S131" s="7" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S145" s="7" t="inlineStr">
@@ -19105,57 +19105,57 @@
       </c>
       <c r="F190" s="10" t="inlineStr">
         <is>
-          <t>A "couple item" — matching merch that fans buy to feel paired with their bias or each other.</t>
+          <t>A "couple item" — matching things a couple wears or uses together, like rings, sneakers or phone cases. Fans also joke about having a "couple item" with their bias.</t>
         </is>
       </c>
       <c r="G190" s="10" t="inlineStr">
         <is>
-          <t>Un "artículo de pareja": mercancía a juego que los fans compran para sentirse conectados con su bias u otros fans.</t>
+          <t>Un "artículo de pareja": cosas a juego que una pareja usa junta, como anillos, tenis o fundas de celular. Los fans también bromean con tener un "artículo de pareja" con su bias.</t>
         </is>
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>「情侶物品」——粉絲購買來與本命或彼此配對的周邊商品。</t>
+          <t>「情侶物品」——情侶一起穿戴或使用的同款物品，像戒指、球鞋、手機殼。粉絲也會開玩笑說和本命用同款是「情侶款」。</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr">
         <is>
-          <t>“情侣物品”——粉丝购买来与本命或彼此配对的周边商品。</t>
+          <t>“情侣物品”——情侣一起穿戴或使用的同款物品，像戒指、球鞋、手机壳。粉丝也会开玩笑说和本命用同款是“情侣款”。</t>
         </is>
       </c>
       <c r="J190" s="10" t="inlineStr">
         <is>
-          <t>推しや互いとペアになった気分を味わうためにファンが買う「カップルアイテム」。</t>
+          <t>「カップルアイテム」——恋人同士でおそろいにする指輪やスニーカー、スマホケースなど。推しと同じ物を持つことを冗談でこう呼ぶファンも。</t>
         </is>
       </c>
       <c r="K190" s="10" t="inlineStr">
         <is>
-          <t>최애랑 커플템 맞춰봤어.</t>
+          <t>남친이랑 커플템 맞췄어.</t>
         </is>
       </c>
       <c r="L190" s="10" t="inlineStr">
         <is>
-          <t>I got a matching couple item with my bias.</t>
+          <t>My boyfriend and I got matching couple items.</t>
         </is>
       </c>
       <c r="M190" s="10" t="inlineStr">
         <is>
-          <t>Conseguí un artículo a juego con mi bias.</t>
+          <t>Mi novio y yo compramos artículos de pareja a juego.</t>
         </is>
       </c>
       <c r="N190" s="10" t="inlineStr">
         <is>
-          <t>跟本命買了情侶小物。</t>
+          <t>跟男朋友買了情侶小物。</t>
         </is>
       </c>
       <c r="O190" s="10" t="inlineStr">
         <is>
-          <t>跟本命买了情侣小物。</t>
+          <t>跟男朋友买了情侣小物。</t>
         </is>
       </c>
       <c r="P190" s="10" t="inlineStr">
         <is>
-          <t>推しとお揃いアイテム合わせてみた。</t>
+          <t>彼氏とペアアイテムそろえた。</t>
         </is>
       </c>
       <c r="Q190" s="10" t="inlineStr">
@@ -19165,7 +19165,7 @@
       </c>
       <c r="R190" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S190" s="9" t="inlineStr">
@@ -22560,7 +22560,7 @@
       </c>
       <c r="R225" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S225" s="9" t="inlineStr">
@@ -22657,7 +22657,7 @@
       </c>
       <c r="R226" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S226" s="9" t="inlineStr">
@@ -23045,7 +23045,7 @@
       </c>
       <c r="R230" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S230" s="9" t="inlineStr">
@@ -23239,7 +23239,7 @@
       </c>
       <c r="R232" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S232" s="9" t="inlineStr">
@@ -23627,7 +23627,7 @@
       </c>
       <c r="R236" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S236" s="9" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="R237" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S237" s="9" t="inlineStr">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="R243" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S243" s="9" t="inlineStr">
@@ -25082,7 +25082,7 @@
       </c>
       <c r="R251" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S251" s="9" t="inlineStr">
@@ -25276,7 +25276,7 @@
       </c>
       <c r="R253" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S253" s="9" t="inlineStr">
@@ -25470,7 +25470,7 @@
       </c>
       <c r="R255" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S255" s="9" t="inlineStr">
@@ -25761,7 +25761,7 @@
       </c>
       <c r="R258" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S258" s="9" t="inlineStr">
@@ -28962,7 +28962,7 @@
       </c>
       <c r="R291" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S291" s="9" t="inlineStr">
@@ -34588,7 +34588,7 @@
       </c>
       <c r="R349" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S349" s="11" t="inlineStr">
@@ -34879,7 +34879,7 @@
       </c>
       <c r="R352" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S352" s="11" t="inlineStr">
@@ -38274,7 +38274,7 @@
       </c>
       <c r="R387" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S387" s="11" t="inlineStr">
@@ -38565,7 +38565,7 @@
       </c>
       <c r="R390" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S390" s="11" t="inlineStr">
@@ -39729,7 +39729,7 @@
       </c>
       <c r="R402" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S402" s="11" t="inlineStr">
@@ -40796,7 +40796,7 @@
       </c>
       <c r="R413" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S413" s="11" t="inlineStr">
@@ -41475,7 +41475,7 @@
       </c>
       <c r="R420" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S420" s="11" t="inlineStr">
@@ -41863,7 +41863,7 @@
       </c>
       <c r="R424" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S424" s="11" t="inlineStr">
@@ -51175,7 +51175,7 @@
       </c>
       <c r="R520" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S520" s="13" t="inlineStr">
@@ -61554,7 +61554,7 @@
       </c>
       <c r="R627" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S627" s="13" t="inlineStr">
@@ -63300,7 +63300,7 @@
       </c>
       <c r="R645" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S645" s="13" t="inlineStr">
@@ -67568,7 +67568,7 @@
       </c>
       <c r="R689" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S689" s="15" t="inlineStr">
@@ -68053,7 +68053,7 @@
       </c>
       <c r="R694" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S694" s="15" t="inlineStr">
@@ -68829,7 +68829,7 @@
       </c>
       <c r="R702" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S702" s="15" t="inlineStr">
@@ -69799,7 +69799,7 @@
       </c>
       <c r="R712" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S712" s="15" t="inlineStr">
@@ -69993,7 +69993,7 @@
       </c>
       <c r="R714" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S714" s="15" t="inlineStr">
@@ -70090,7 +70090,7 @@
       </c>
       <c r="R715" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S715" s="15" t="inlineStr">
@@ -70381,7 +70381,7 @@
       </c>
       <c r="R718" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S718" s="15" t="inlineStr">
@@ -70672,7 +70672,7 @@
       </c>
       <c r="R721" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S721" s="15" t="inlineStr">
@@ -71351,7 +71351,7 @@
       </c>
       <c r="R728" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S728" s="15" t="inlineStr">
@@ -72127,7 +72127,7 @@
       </c>
       <c r="R736" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S736" s="15" t="inlineStr">
@@ -72224,7 +72224,7 @@
       </c>
       <c r="R737" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S737" s="15" t="inlineStr">
@@ -73291,7 +73291,7 @@
       </c>
       <c r="R748" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S748" s="15" t="inlineStr">
@@ -73485,7 +73485,7 @@
       </c>
       <c r="R750" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S750" s="15" t="inlineStr">
@@ -73582,7 +73582,7 @@
       </c>
       <c r="R751" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S751" s="15" t="inlineStr">
@@ -73776,7 +73776,7 @@
       </c>
       <c r="R753" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S753" s="15" t="inlineStr">
@@ -73873,7 +73873,7 @@
       </c>
       <c r="R754" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S754" s="15" t="inlineStr">
@@ -74164,7 +74164,7 @@
       </c>
       <c r="R757" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S757" s="15" t="inlineStr">
@@ -74358,7 +74358,7 @@
       </c>
       <c r="R759" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S759" s="15" t="inlineStr">
@@ -74455,7 +74455,7 @@
       </c>
       <c r="R760" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S760" s="15" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S73" s="7" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S87" s="7" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S116" s="7" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S118" s="7" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S119" s="7" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S125" s="7" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S130" s="7" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S144" s="7" t="inlineStr">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="R187" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S187" s="9" t="inlineStr">
@@ -19941,7 +19941,7 @@
       </c>
       <c r="R198" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S198" s="9" t="inlineStr">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="R224" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S224" s="9" t="inlineStr">
@@ -28126,57 +28126,57 @@
       </c>
       <c r="F283" s="10" t="inlineStr">
         <is>
-          <t>Someone's very first time attending a concert for a particular artist — a memorable fan milestone.</t>
+          <t>Short for 첫 콘서트 — the first day of a concert run (the opposite of 막콘). Fans also use it for their own very first concert of an artist.</t>
         </is>
       </c>
       <c r="G283" s="10" t="inlineStr">
         <is>
-          <t>La primera vez que alguien asiste a un concierto de un artista en particular; un hito memorable para un fan.</t>
+          <t>Abreviatura de 첫 콘서트: el primer día de una serie de conciertos (lo contrario de 막콘). Los fans también lo usan para su primer concierto de un artista.</t>
         </is>
       </c>
       <c r="H283" s="10" t="inlineStr">
         <is>
-          <t>某人第一次到現場觀看特定藝人的演唱會，是難忘的追星里程碑。</t>
+          <t>「첫 콘서트」的縮寫——一輪演唱會的首場（相對於막콘）。粉絲也用來指自己第一次去看某藝人的演唱會。</t>
         </is>
       </c>
       <c r="I283" s="10" t="inlineStr">
         <is>
-          <t>某人第一次到现场观看特定艺人的演唱会，是难忘的追星里程碑。</t>
+          <t>“첫 콘서트”的缩写——一轮演唱会的首场（相对于막콘）。粉丝也用来指自己第一次去看某艺人的演唱会。</t>
         </is>
       </c>
       <c r="J283" s="10" t="inlineStr">
         <is>
-          <t>特定のアーティストのコンサートに初めて行くこと——忘れられないファンの節目。</t>
+          <t>첫 콘서트の略——公演期間の初日（막콘の反対）。自分が初めて行くそのアーティストのコンサートの意味でも使う。</t>
         </is>
       </c>
       <c r="K283" s="10" t="inlineStr">
         <is>
-          <t>드디어 첫콘 다녀왔어!</t>
+          <t>첫콘이라 셋리스트 스포 없이 갔어.</t>
         </is>
       </c>
       <c r="L283" s="10" t="inlineStr">
         <is>
-          <t>I finally went to my first concert!</t>
+          <t>It was opening night, so I went in without setlist spoilers.</t>
         </is>
       </c>
       <c r="M283" s="10" t="inlineStr">
         <is>
-          <t>¡Por fin fui a mi primer concierto!</t>
+          <t>Era la primera función, así que fui sin spoilers del setlist.</t>
         </is>
       </c>
       <c r="N283" s="10" t="inlineStr">
         <is>
-          <t>終於去了初次演唱會！</t>
+          <t>因為是首場，沒被歌單劇透就去了。</t>
         </is>
       </c>
       <c r="O283" s="10" t="inlineStr">
         <is>
-          <t>终于去了初次演唱会！</t>
+          <t>因为是首场，没被歌单剧透就去了。</t>
         </is>
       </c>
       <c r="P283" s="10" t="inlineStr">
         <is>
-          <t>ついに初コン行ってきた！</t>
+          <t>初日だからセトリのネタバレなしで行った。</t>
         </is>
       </c>
       <c r="Q283" s="10" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="R283" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S283" s="9" t="inlineStr">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="R305" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S305" s="9" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="R332" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S332" s="11" t="inlineStr">
@@ -33909,7 +33909,7 @@
       </c>
       <c r="R342" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S342" s="11" t="inlineStr">
@@ -34782,7 +34782,7 @@
       </c>
       <c r="R351" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S351" s="11" t="inlineStr">
@@ -35267,7 +35267,7 @@
       </c>
       <c r="R356" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S356" s="11" t="inlineStr">
@@ -38371,7 +38371,7 @@
       </c>
       <c r="R388" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S388" s="11" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="R416" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S416" s="11" t="inlineStr">
@@ -42251,7 +42251,7 @@
       </c>
       <c r="R428" s="11" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S428" s="11" t="inlineStr">
@@ -46325,7 +46325,7 @@
       </c>
       <c r="R470" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S470" s="13" t="inlineStr">
@@ -47780,7 +47780,7 @@
       </c>
       <c r="R485" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S485" s="13" t="inlineStr">
@@ -53309,7 +53309,7 @@
       </c>
       <c r="R542" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S542" s="13" t="inlineStr">
@@ -53697,7 +53697,7 @@
       </c>
       <c r="R546" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S546" s="13" t="inlineStr">
@@ -54182,7 +54182,7 @@
       </c>
       <c r="R551" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S551" s="13" t="inlineStr">
@@ -54279,7 +54279,7 @@
       </c>
       <c r="R552" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S552" s="13" t="inlineStr">
@@ -54376,7 +54376,7 @@
       </c>
       <c r="R553" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S553" s="13" t="inlineStr">
@@ -58159,7 +58159,7 @@
       </c>
       <c r="R592" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S592" s="13" t="inlineStr">
@@ -60487,7 +60487,7 @@
       </c>
       <c r="R616" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S616" s="13" t="inlineStr">
@@ -61651,7 +61651,7 @@
       </c>
       <c r="R628" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S628" s="13" t="inlineStr">
@@ -62039,7 +62039,7 @@
       </c>
       <c r="R632" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S632" s="13" t="inlineStr">
@@ -62427,7 +62427,7 @@
       </c>
       <c r="R636" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S636" s="13" t="inlineStr">
@@ -62621,7 +62621,7 @@
       </c>
       <c r="R638" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S638" s="13" t="inlineStr">
@@ -63106,7 +63106,7 @@
       </c>
       <c r="R643" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S643" s="13" t="inlineStr">
@@ -65919,7 +65919,7 @@
       </c>
       <c r="R672" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S672" s="13" t="inlineStr">
@@ -66307,7 +66307,7 @@
       </c>
       <c r="R676" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S676" s="13" t="inlineStr">
@@ -72321,7 +72321,7 @@
       </c>
       <c r="R738" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S738" s="15" t="inlineStr">
@@ -73679,7 +73679,7 @@
       </c>
       <c r="R752" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S752" s="15" t="inlineStr">
@@ -73970,7 +73970,7 @@
       </c>
       <c r="R755" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S755" s="15" t="inlineStr">
@@ -74261,7 +74261,7 @@
       </c>
       <c r="R758" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S758" s="15" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S67" s="7" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S98" s="7" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="R182" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S182" s="9" t="inlineStr">
@@ -19553,7 +19553,7 @@
       </c>
       <c r="R194" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S194" s="9" t="inlineStr">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="R200" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S200" s="9" t="inlineStr">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="R220" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S220" s="9" t="inlineStr">
@@ -25179,7 +25179,7 @@
       </c>
       <c r="R252" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S252" s="9" t="inlineStr">
@@ -25373,7 +25373,7 @@
       </c>
       <c r="R254" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S254" s="9" t="inlineStr">
@@ -26052,7 +26052,7 @@
       </c>
       <c r="R261" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S261" s="9" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="R274" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S274" s="9" t="inlineStr">
@@ -51369,7 +51369,7 @@
       </c>
       <c r="R522" s="13" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S522" s="13" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$770</definedName>
@@ -24694,7 +24694,7 @@
       </c>
       <c r="R247" s="9" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S247" s="9" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$769</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$779</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$789</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$789</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$791</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S789"/>
+  <dimension ref="A1:S791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -67966,194 +67966,194 @@
       </c>
     </row>
     <row r="694" ht="46" customHeight="1">
-      <c r="A694" s="15" t="inlineStr">
-        <is>
-          <t>DAT-001</t>
-        </is>
-      </c>
-      <c r="B694" s="15" t="inlineStr">
-        <is>
-          <t>썸</t>
-        </is>
-      </c>
-      <c r="C694" s="15" t="inlineStr">
-        <is>
-          <t>sseom</t>
-        </is>
-      </c>
-      <c r="D694" s="15" t="inlineStr">
-        <is>
-          <t>연애 · 썸 표현</t>
-        </is>
-      </c>
-      <c r="E694" s="15" t="inlineStr">
-        <is>
-          <t>Dating &amp; Romance</t>
-        </is>
-      </c>
-      <c r="F694" s="16" t="inlineStr">
-        <is>
-          <t>The ambiguous stage of mutual interest before officially dating, from English "something."</t>
-        </is>
-      </c>
-      <c r="G694" s="16" t="inlineStr">
-        <is>
-          <t>La etapa ambigua de interés mutuo antes de salir oficialmente, del inglés "something".</t>
-        </is>
-      </c>
-      <c r="H694" s="16" t="inlineStr">
-        <is>
-          <t>正式交往前彼此有好感、關係曖昧不明的階段，源自英文「something」。</t>
-        </is>
-      </c>
-      <c r="I694" s="16" t="inlineStr">
-        <is>
-          <t>正式交往前彼此有好感、关系暧昧不明的阶段，源自英文“something”。</t>
-        </is>
-      </c>
-      <c r="J694" s="16" t="inlineStr">
-        <is>
-          <t>正式に付き合う前の、お互いに気がある曖昧な段階——英語の「something」から。</t>
-        </is>
-      </c>
-      <c r="K694" s="16" t="inlineStr">
-        <is>
-          <t>저 둘이 요즘 썸 타는 것 같아.</t>
-        </is>
-      </c>
-      <c r="L694" s="16" t="inlineStr">
-        <is>
-          <t>I think those two are in the talking stage lately.</t>
-        </is>
-      </c>
-      <c r="M694" s="16" t="inlineStr">
-        <is>
-          <t>Creo que esos dos están en la etapa de "algo más que amigos" últimamente.</t>
-        </is>
-      </c>
-      <c r="N694" s="16" t="inlineStr">
-        <is>
-          <t>那兩個人最近好像在曖昧。</t>
-        </is>
-      </c>
-      <c r="O694" s="16" t="inlineStr">
-        <is>
-          <t>那两个人最近好像在暧昧。</t>
-        </is>
-      </c>
-      <c r="P694" s="16" t="inlineStr">
-        <is>
-          <t>あの二人、最近曖昧な関係みたい。</t>
-        </is>
-      </c>
-      <c r="Q694" s="16" t="inlineStr">
-        <is>
-          <t>Casual relationship talk, dramas</t>
-        </is>
-      </c>
-      <c r="R694" s="15" t="inlineStr">
+      <c r="A694" s="13" t="inlineStr">
+        <is>
+          <t>MEM-253</t>
+        </is>
+      </c>
+      <c r="B694" s="13" t="inlineStr">
+        <is>
+          <t>볼꾸</t>
+        </is>
+      </c>
+      <c r="C694" s="13" t="inlineStr">
+        <is>
+          <t>bol-kku</t>
+        </is>
+      </c>
+      <c r="D694" s="13" t="inlineStr">
+        <is>
+          <t>온라인 밈</t>
+        </is>
+      </c>
+      <c r="E694" s="13" t="inlineStr">
+        <is>
+          <t>Online Memes</t>
+        </is>
+      </c>
+      <c r="F694" s="14" t="inlineStr">
+        <is>
+          <t>Short for 볼펜 꾸미기, "ballpoint-pen decorating": building your own custom pen by picking a pen barrel and adding charms, beads and parts.</t>
+        </is>
+      </c>
+      <c r="G694" s="14" t="inlineStr">
+        <is>
+          <t>Abreviatura de 볼펜 꾸미기, "decorar bolígrafos": armar tu propio bolígrafo eligiendo el cuerpo y añadiendo dijes, cuentas y piezas.</t>
+        </is>
+      </c>
+      <c r="H694" s="14" t="inlineStr">
+        <is>
+          <t>볼펜 꾸미기（裝飾原子筆）的縮寫：自己挑選筆桿，再加上吊飾、珠子和各種配件，做出專屬於自己的原子筆。</t>
+        </is>
+      </c>
+      <c r="I694" s="14" t="inlineStr">
+        <is>
+          <t>볼펜 꾸미기（装饰原子笔）的缩写：自己挑选笔杆，再加上吊饰、珠子和各种配件，做出专属于自己的原子笔。</t>
+        </is>
+      </c>
+      <c r="J694" s="14" t="inlineStr">
+        <is>
+          <t>볼펜 꾸미기（ボールペンデコ）の略。ペン軸を選んでチャームやビーズ、パーツを組み合わせ、自分だけのボールペンを作ること。</t>
+        </is>
+      </c>
+      <c r="K694" s="14" t="inlineStr">
+        <is>
+          <t>주말에 동대문 가서 볼꾸 하고 왔어.</t>
+        </is>
+      </c>
+      <c r="L694" s="14" t="inlineStr">
+        <is>
+          <t>I went to Dongdaemun over the weekend and decorated a pen.</t>
+        </is>
+      </c>
+      <c r="M694" s="14" t="inlineStr">
+        <is>
+          <t>El fin de semana fui a Dongdaemun a decorar un bolígrafo.</t>
+        </is>
+      </c>
+      <c r="N694" s="14" t="inlineStr">
+        <is>
+          <t>週末去東大門做了볼꾸（裝飾原子筆）。</t>
+        </is>
+      </c>
+      <c r="O694" s="14" t="inlineStr">
+        <is>
+          <t>周末去东大门做了볼꾸（装饰原子笔）。</t>
+        </is>
+      </c>
+      <c r="P694" s="14" t="inlineStr">
+        <is>
+          <t>週末に東大門でボールペンデコしてきた。</t>
+        </is>
+      </c>
+      <c r="Q694" s="14" t="inlineStr">
+        <is>
+          <t>Gen Z craft trend, Dongdaemun accessory market, Instagram/TikTok</t>
+        </is>
+      </c>
+      <c r="R694" s="13" t="inlineStr">
         <is>
           <t>Verified (web-checked)</t>
         </is>
       </c>
-      <c r="S694" s="15" t="inlineStr">
+      <c r="S694" s="13" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="695" ht="46" customHeight="1">
-      <c r="A695" s="15" t="inlineStr">
-        <is>
-          <t>DAT-002</t>
-        </is>
-      </c>
-      <c r="B695" s="15" t="inlineStr">
-        <is>
-          <t>썸타다</t>
-        </is>
-      </c>
-      <c r="C695" s="15" t="inlineStr">
-        <is>
-          <t>sseom-ta-da</t>
-        </is>
-      </c>
-      <c r="D695" s="15" t="inlineStr">
-        <is>
-          <t>연애 · 썸 표현</t>
-        </is>
-      </c>
-      <c r="E695" s="15" t="inlineStr">
-        <is>
-          <t>Dating &amp; Romance</t>
-        </is>
-      </c>
-      <c r="F695" s="16" t="inlineStr">
-        <is>
-          <t>To be in that ambiguous, pre-dating phase of mutual interest with someone.</t>
-        </is>
-      </c>
-      <c r="G695" s="16" t="inlineStr">
-        <is>
-          <t>Estar en esa fase ambigua y previa a salir formalmente con alguien.</t>
-        </is>
-      </c>
-      <c r="H695" s="16" t="inlineStr">
-        <is>
-          <t>正式交往前，彼此有好感、關係曖昧不明的階段。</t>
-        </is>
-      </c>
-      <c r="I695" s="16" t="inlineStr">
-        <is>
-          <t>正式交往前，彼此有好感、关系暧昧不明的阶段。</t>
-        </is>
-      </c>
-      <c r="J695" s="16" t="inlineStr">
-        <is>
-          <t>誰かと正式に付き合う前の、お互いに気がある曖昧な段階にいること。</t>
-        </is>
-      </c>
-      <c r="K695" s="16" t="inlineStr">
-        <is>
-          <t>우리 썸탄 지 한 달 됐어.</t>
-        </is>
-      </c>
-      <c r="L695" s="16" t="inlineStr">
-        <is>
-          <t>We've been in the talking stage for a month.</t>
-        </is>
-      </c>
-      <c r="M695" s="16" t="inlineStr">
-        <is>
-          <t>Llevamos un mes en la etapa de "algo más que amigos".</t>
-        </is>
-      </c>
-      <c r="N695" s="16" t="inlineStr">
-        <is>
-          <t>我們曖昧一個月了。</t>
-        </is>
-      </c>
-      <c r="O695" s="16" t="inlineStr">
-        <is>
-          <t>我们暧昧一个月了。</t>
-        </is>
-      </c>
-      <c r="P695" s="16" t="inlineStr">
-        <is>
-          <t>私たち、曖昧な関係になって1ヶ月経った。</t>
-        </is>
-      </c>
-      <c r="Q695" s="16" t="inlineStr">
-        <is>
-          <t>Casual relationship talk</t>
-        </is>
-      </c>
-      <c r="R695" s="15" t="inlineStr">
+      <c r="A695" s="13" t="inlineStr">
+        <is>
+          <t>MEM-254</t>
+        </is>
+      </c>
+      <c r="B695" s="13" t="inlineStr">
+        <is>
+          <t>떡켓팅</t>
+        </is>
+      </c>
+      <c r="C695" s="13" t="inlineStr">
+        <is>
+          <t>tteok-ket-ting</t>
+        </is>
+      </c>
+      <c r="D695" s="13" t="inlineStr">
+        <is>
+          <t>온라인 밈</t>
+        </is>
+      </c>
+      <c r="E695" s="13" t="inlineStr">
+        <is>
+          <t>Online Memes</t>
+        </is>
+      </c>
+      <c r="F695" s="14" t="inlineStr">
+        <is>
+          <t>떡 (rice cake) + 티켓팅 (ticketing): fighting to get a popular rice-cake treat — from a famous tteokbokki spot to a trendy rice-cake dessert — as if you were buying concert tickets.</t>
+        </is>
+      </c>
+      <c r="G695" s="14" t="inlineStr">
+        <is>
+          <t>떡 (pastel de arroz) + 티켓팅 (ticketing): pelear por conseguir un snack de pastel de arroz popular —desde un tteokbokki famoso hasta un postre de moda— como si compraras boletos para un concierto.</t>
+        </is>
+      </c>
+      <c r="H695" s="14" t="inlineStr">
+        <is>
+          <t>떡（年糕）＋티켓팅（搶票）：像搶演唱會門票一樣，拚命搶購熱門的年糕美食，從排隊名店的辣炒年糕到流行的年糕甜點都算。</t>
+        </is>
+      </c>
+      <c r="I695" s="14" t="inlineStr">
+        <is>
+          <t>떡（年糕）＋티켓팅（抢票）：像抢演唱会门票一样，拚命抢购热门的年糕美食，从排队名店的辣炒年糕到流行的年糕甜点都算。</t>
+        </is>
+      </c>
+      <c r="J695" s="14" t="inlineStr">
+        <is>
+          <t>떡（餅）＋티켓팅（チケット争奪戦）：人気の餅グルメ（行列店のトッポッキから流行りの餅スイーツまで）を、コンサートのチケットを取るみたいに必死で手に入れようとすること。</t>
+        </is>
+      </c>
+      <c r="K695" s="14" t="inlineStr">
+        <is>
+          <t>떡켓팅 실패해서 한 시간 넘게 기다렸어.</t>
+        </is>
+      </c>
+      <c r="L695" s="14" t="inlineStr">
+        <is>
+          <t>I lost the rice-cake ticketing and waited over an hour.</t>
+        </is>
+      </c>
+      <c r="M695" s="14" t="inlineStr">
+        <is>
+          <t>Perdí la batalla por el pastel de arroz y esperé más de una hora.</t>
+        </is>
+      </c>
+      <c r="N695" s="14" t="inlineStr">
+        <is>
+          <t>搶年糕失敗，等了一個多小時。</t>
+        </is>
+      </c>
+      <c r="O695" s="14" t="inlineStr">
+        <is>
+          <t>抢年糕失败，等了一个多小时。</t>
+        </is>
+      </c>
+      <c r="P695" s="14" t="inlineStr">
+        <is>
+          <t>떡켓팅に負けて1時間以上待った。</t>
+        </is>
+      </c>
+      <c r="Q695" s="14" t="inlineStr">
+        <is>
+          <t>Food trends, waiting lines, social media posts</t>
+        </is>
+      </c>
+      <c r="R695" s="13" t="inlineStr">
         <is>
           <t>Verified (web-checked)</t>
         </is>
       </c>
-      <c r="S695" s="15" t="inlineStr">
+      <c r="S695" s="13" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
@@ -68162,17 +68162,17 @@
     <row r="696" ht="46" customHeight="1">
       <c r="A696" s="15" t="inlineStr">
         <is>
-          <t>DAT-003</t>
+          <t>DAT-001</t>
         </is>
       </c>
       <c r="B696" s="15" t="inlineStr">
         <is>
-          <t>밀당</t>
+          <t>썸</t>
         </is>
       </c>
       <c r="C696" s="15" t="inlineStr">
         <is>
-          <t>mil-dang</t>
+          <t>sseom</t>
         </is>
       </c>
       <c r="D696" s="15" t="inlineStr">
@@ -68187,62 +68187,62 @@
       </c>
       <c r="F696" s="16" t="inlineStr">
         <is>
-          <t>Short for "pushing and pulling" — playing a little hard to get in a relationship.</t>
+          <t>The ambiguous stage of mutual interest before officially dating, from English "something."</t>
         </is>
       </c>
       <c r="G696" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "empujar y jalar": hacerse un poco el difícil en una relación.</t>
+          <t>La etapa ambigua de interés mutuo antes de salir oficialmente, del inglés "something".</t>
         </is>
       </c>
       <c r="H696" s="16" t="inlineStr">
         <is>
-          <t>「推拉」的簡稱——在感情中欲擒故縱、若即若離。</t>
+          <t>正式交往前彼此有好感、關係曖昧不明的階段，源自英文「something」。</t>
         </is>
       </c>
       <c r="I696" s="16" t="inlineStr">
         <is>
-          <t>“推拉”的简称——在感情中欲擒故纵、若即若离。</t>
+          <t>正式交往前彼此有好感、关系暧昧不明的阶段，源自英文“something”。</t>
         </is>
       </c>
       <c r="J696" s="16" t="inlineStr">
         <is>
-          <t>「押し引き」の略——恋愛でわざと簡単に落ちないようにすること。</t>
+          <t>正式に付き合う前の、お互いに気がある曖昧な段階——英語の「something」から。</t>
         </is>
       </c>
       <c r="K696" s="16" t="inlineStr">
         <is>
-          <t>밀당 좀 그만하고 솔직하게 말해.</t>
+          <t>저 둘이 요즘 썸 타는 것 같아.</t>
         </is>
       </c>
       <c r="L696" s="16" t="inlineStr">
         <is>
-          <t>Stop playing push-and-pull and just be honest.</t>
+          <t>I think those two are in the talking stage lately.</t>
         </is>
       </c>
       <c r="M696" s="16" t="inlineStr">
         <is>
-          <t>Deja de jugar a hacerte el difícil y sé honesto.</t>
+          <t>Creo que esos dos están en la etapa de "algo más que amigos" últimamente.</t>
         </is>
       </c>
       <c r="N696" s="16" t="inlineStr">
         <is>
-          <t>別再欲擒故縱了，老實說吧。</t>
+          <t>那兩個人最近好像在曖昧。</t>
         </is>
       </c>
       <c r="O696" s="16" t="inlineStr">
         <is>
-          <t>别再欲擒故纵了，老实说吧。</t>
+          <t>那两个人最近好像在暧昧。</t>
         </is>
       </c>
       <c r="P696" s="16" t="inlineStr">
         <is>
-          <t>駆け引きはもうやめて、正直に言って。</t>
+          <t>あの二人、最近曖昧な関係みたい。</t>
         </is>
       </c>
       <c r="Q696" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk, dramas</t>
+          <t>Casual relationship talk, dramas</t>
         </is>
       </c>
       <c r="R696" s="15" t="inlineStr">
@@ -68259,17 +68259,17 @@
     <row r="697" ht="46" customHeight="1">
       <c r="A697" s="15" t="inlineStr">
         <is>
-          <t>DAT-004</t>
+          <t>DAT-002</t>
         </is>
       </c>
       <c r="B697" s="15" t="inlineStr">
         <is>
-          <t>어장관리</t>
+          <t>썸타다</t>
         </is>
       </c>
       <c r="C697" s="15" t="inlineStr">
         <is>
-          <t>eo-jang-gwal-li</t>
+          <t>sseom-ta-da</t>
         </is>
       </c>
       <c r="D697" s="15" t="inlineStr">
@@ -68284,62 +68284,62 @@
       </c>
       <c r="F697" s="16" t="inlineStr">
         <is>
-          <t>"Fish-tank management" — keeping multiple romantic prospects on the line at once without committing.</t>
+          <t>To be in that ambiguous, pre-dating phase of mutual interest with someone.</t>
         </is>
       </c>
       <c r="G697" s="16" t="inlineStr">
         <is>
-          <t>"Manejo de pecera": mantener a varios interesados románticos a la espera sin comprometerse con ninguno.</t>
+          <t>Estar en esa fase ambigua y previa a salir formalmente con alguien.</t>
         </is>
       </c>
       <c r="H697" s="16" t="inlineStr">
         <is>
-          <t>「魚缸管理」——同時吊著好幾個對象、不做出承諾，養魚。</t>
+          <t>正式交往前，彼此有好感、關係曖昧不明的階段。</t>
         </is>
       </c>
       <c r="I697" s="16" t="inlineStr">
         <is>
-          <t>“鱼缸管理”——同时吊着好几个对象、不做出承诺，养鱼。</t>
+          <t>正式交往前，彼此有好感、关系暧昧不明的阶段。</t>
         </is>
       </c>
       <c r="J697" s="16" t="inlineStr">
         <is>
-          <t>「養殖場管理」——複数の恋愛候補を、コミットせずに引き止めておくこと。</t>
+          <t>誰かと正式に付き合う前の、お互いに気がある曖昧な段階にいること。</t>
         </is>
       </c>
       <c r="K697" s="16" t="inlineStr">
         <is>
-          <t>걔 완전 어장관리하는 것 같아, 조심해.</t>
+          <t>우리 썸탄 지 한 달 됐어.</t>
         </is>
       </c>
       <c r="L697" s="16" t="inlineStr">
         <is>
-          <t>I think they're totally fish-tanking people, be careful.</t>
+          <t>We've been in the talking stage for a month.</t>
         </is>
       </c>
       <c r="M697" s="16" t="inlineStr">
         <is>
-          <t>Creo que esa persona está jugando con varios a la vez, ten cuidado.</t>
+          <t>Llevamos un mes en la etapa de "algo más que amigos".</t>
         </is>
       </c>
       <c r="N697" s="16" t="inlineStr">
         <is>
-          <t>我覺得他在養魚，小心點。</t>
+          <t>我們曖昧一個月了。</t>
         </is>
       </c>
       <c r="O697" s="16" t="inlineStr">
         <is>
-          <t>我觉得他在养鱼，小心点。</t>
+          <t>我们暧昧一个月了。</t>
         </is>
       </c>
       <c r="P697" s="16" t="inlineStr">
         <is>
-          <t>あの人、完全に複数キープしてる感じ、気をつけて。</t>
+          <t>私たち、曖昧な関係になって1ヶ月経った。</t>
         </is>
       </c>
       <c r="Q697" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk, dramas</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R697" s="15" t="inlineStr">
@@ -68356,17 +68356,17 @@
     <row r="698" ht="46" customHeight="1">
       <c r="A698" s="15" t="inlineStr">
         <is>
-          <t>DAT-005</t>
+          <t>DAT-003</t>
         </is>
       </c>
       <c r="B698" s="15" t="inlineStr">
         <is>
-          <t>삼귀다</t>
+          <t>밀당</t>
         </is>
       </c>
       <c r="C698" s="15" t="inlineStr">
         <is>
-          <t>sam-gwi-da</t>
+          <t>mil-dang</t>
         </is>
       </c>
       <c r="D698" s="15" t="inlineStr">
@@ -68381,62 +68381,62 @@
       </c>
       <c r="F698" s="16" t="inlineStr">
         <is>
-          <t>A playful pun using "3" (삼) as a step before 사귀다 ("to date," which starts with 사=4) — the talking stage.</t>
+          <t>Short for "pushing and pulling" — playing a little hard to get in a relationship.</t>
         </is>
       </c>
       <c r="G698" s="16" t="inlineStr">
         <is>
-          <t>Un juego de palabras usando "3" (삼) como un paso antes de 사귀다 ("salir", que empieza con 사=4): la etapa previa.</t>
+          <t>Abreviatura de "empujar y jalar": hacerse un poco el difícil en una relación.</t>
         </is>
       </c>
       <c r="H698" s="16" t="inlineStr">
         <is>
-          <t>用數字「3」取代「사귀다」（交往，以4開頭）玩的雙關語，指正式交往前的曖昧階段。</t>
+          <t>「推拉」的簡稱——在感情中欲擒故縱、若即若離。</t>
         </is>
       </c>
       <c r="I698" s="16" t="inlineStr">
         <is>
-          <t>用数字“3”取代“사귀다”（交往，以4开头）玩的双关语，指正式交往前的暧昧阶段。</t>
+          <t>“推拉”的简称——在感情中欲擒故纵、若即若离。</t>
         </is>
       </c>
       <c r="J698" s="16" t="inlineStr">
         <is>
-          <t>「3」（삼）を사귀다（付き合う、「4」＝사で始まる）の前段階として使った言葉遊びで、付き合う前の曖昧な段階を表す。</t>
+          <t>「押し引き」の略——恋愛でわざと簡単に落ちないようにすること。</t>
         </is>
       </c>
       <c r="K698" s="16" t="inlineStr">
         <is>
-          <t>우리 지금 삼귀는 사이야.</t>
+          <t>밀당 좀 그만하고 솔직하게 말해.</t>
         </is>
       </c>
       <c r="L698" s="16" t="inlineStr">
         <is>
-          <t>We're in that pre-dating stage right now.</t>
+          <t>Stop playing push-and-pull and just be honest.</t>
         </is>
       </c>
       <c r="M698" s="16" t="inlineStr">
         <is>
-          <t>Ahorita estamos en esa etapa previa a ser novios.</t>
+          <t>Deja de jugar a hacerte el difícil y sé honesto.</t>
         </is>
       </c>
       <c r="N698" s="16" t="inlineStr">
         <is>
-          <t>我們現在算是曖昧中的關係。</t>
+          <t>別再欲擒故縱了，老實說吧。</t>
         </is>
       </c>
       <c r="O698" s="16" t="inlineStr">
         <is>
-          <t>我们现在算是暧昧中的关系。</t>
+          <t>别再欲擒故纵了，老实说吧。</t>
         </is>
       </c>
       <c r="P698" s="16" t="inlineStr">
         <is>
-          <t>私たち、今そういう段階にいるの。</t>
+          <t>駆け引きはもうやめて、正直に言って。</t>
         </is>
       </c>
       <c r="Q698" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>Relationship talk, dramas</t>
         </is>
       </c>
       <c r="R698" s="15" t="inlineStr">
@@ -68453,17 +68453,17 @@
     <row r="699" ht="46" customHeight="1">
       <c r="A699" s="15" t="inlineStr">
         <is>
-          <t>DAT-006</t>
+          <t>DAT-004</t>
         </is>
       </c>
       <c r="B699" s="15" t="inlineStr">
         <is>
-          <t>환승연애</t>
+          <t>어장관리</t>
         </is>
       </c>
       <c r="C699" s="15" t="inlineStr">
         <is>
-          <t>hwan-seung-yeon-ae</t>
+          <t>eo-jang-gwal-li</t>
         </is>
       </c>
       <c r="D699" s="15" t="inlineStr">
@@ -68478,62 +68478,62 @@
       </c>
       <c r="F699" s="16" t="inlineStr">
         <is>
-          <t>"Transfer love" — starting a new relationship right after a breakup, popularized by a reality show of the same name.</t>
+          <t>"Fish-tank management" — keeping multiple romantic prospects on the line at once without committing.</t>
         </is>
       </c>
       <c r="G699" s="16" t="inlineStr">
         <is>
-          <t>"Amor de transbordo": empezar una nueva relación justo después de una ruptura, popularizado por un reality show del mismo nombre.</t>
+          <t>"Manejo de pecera": mantener a varios interesados románticos a la espera sin comprometerse con ninguno.</t>
         </is>
       </c>
       <c r="H699" s="16" t="inlineStr">
         <is>
-          <t>「轉乘戀愛」——分手後立刻投入新戀情，因同名實境節目而爆紅。</t>
+          <t>「魚缸管理」——同時吊著好幾個對象、不做出承諾，養魚。</t>
         </is>
       </c>
       <c r="I699" s="16" t="inlineStr">
         <is>
-          <t>“转乘恋爱”——分手后立刻投入新恋情，因同名实境节目而爆红。</t>
+          <t>“鱼缸管理”——同时吊着好几个对象、不做出承诺，养鱼。</t>
         </is>
       </c>
       <c r="J699" s="16" t="inlineStr">
         <is>
-          <t>「乗り換え恋愛」——別れた直後にすぐ新しい恋愛を始めること、同名のリアリティ番組で話題になった。</t>
+          <t>「養殖場管理」——複数の恋愛候補を、コミットせずに引き止めておくこと。</t>
         </is>
       </c>
       <c r="K699" s="16" t="inlineStr">
         <is>
-          <t>그 커플 완전 환승연애 아니야?</t>
+          <t>걔 완전 어장관리하는 것 같아, 조심해.</t>
         </is>
       </c>
       <c r="L699" s="16" t="inlineStr">
         <is>
-          <t>Isn't that couple a total transfer-love situation?</t>
+          <t>I think they're totally fish-tanking people, be careful.</t>
         </is>
       </c>
       <c r="M699" s="16" t="inlineStr">
         <is>
-          <t>¿Esa pareja no es un caso típico de "amor de transbordo"?</t>
+          <t>Creo que esa persona está jugando con varios a la vez, ten cuidado.</t>
         </is>
       </c>
       <c r="N699" s="16" t="inlineStr">
         <is>
-          <t>那對情侶根本是轉乘戀愛吧？</t>
+          <t>我覺得他在養魚，小心點。</t>
         </is>
       </c>
       <c r="O699" s="16" t="inlineStr">
         <is>
-          <t>那对情侣根本是转乘恋爱吧？</t>
+          <t>我觉得他在养鱼，小心点。</t>
         </is>
       </c>
       <c r="P699" s="16" t="inlineStr">
         <is>
-          <t>あのカップル、完全に乗り換え恋愛じゃない？</t>
+          <t>あの人、完全に複数キープしてる感じ、気をつけて。</t>
         </is>
       </c>
       <c r="Q699" s="16" t="inlineStr">
         <is>
-          <t>Reality show fandom, gossip</t>
+          <t>Relationship talk, dramas</t>
         </is>
       </c>
       <c r="R699" s="15" t="inlineStr">
@@ -68550,17 +68550,17 @@
     <row r="700" ht="46" customHeight="1">
       <c r="A700" s="15" t="inlineStr">
         <is>
-          <t>DAT-007</t>
+          <t>DAT-005</t>
         </is>
       </c>
       <c r="B700" s="15" t="inlineStr">
         <is>
-          <t>잠수이별</t>
+          <t>삼귀다</t>
         </is>
       </c>
       <c r="C700" s="15" t="inlineStr">
         <is>
-          <t>jam-su-i-byeol</t>
+          <t>sam-gwi-da</t>
         </is>
       </c>
       <c r="D700" s="15" t="inlineStr">
@@ -68575,62 +68575,62 @@
       </c>
       <c r="F700" s="16" t="inlineStr">
         <is>
-          <t>"Diving breakup" — ending a relationship by disappearing without explanation, i.e. ghosting.</t>
+          <t>A playful pun using "3" (삼) as a step before 사귀다 ("to date," which starts with 사=4) — the talking stage.</t>
         </is>
       </c>
       <c r="G700" s="16" t="inlineStr">
         <is>
-          <t>"Ruptura de buceo": terminar una relación desapareciendo sin explicación, es decir, ghosting.</t>
+          <t>Un juego de palabras usando "3" (삼) como un paso antes de 사귀다 ("salir", que empieza con 사=4): la etapa previa.</t>
         </is>
       </c>
       <c r="H700" s="16" t="inlineStr">
         <is>
-          <t>「潛水式分手」——不做任何說明就人間蒸發結束關係。</t>
+          <t>用數字「3」取代「사귀다」（交往，以4開頭）玩的雙關語，指正式交往前的曖昧階段。</t>
         </is>
       </c>
       <c r="I700" s="16" t="inlineStr">
         <is>
-          <t>“潜水式分手”——不做任何说明就人间蒸发结束关系。</t>
+          <t>用数字“3”取代“사귀다”（交往，以4开头）玩的双关语，指正式交往前的暧昧阶段。</t>
         </is>
       </c>
       <c r="J700" s="16" t="inlineStr">
         <is>
-          <t>「潜水別れ」——説明もなく姿を消して関係を終わらせること、つまり音信不通。</t>
+          <t>「3」（삼）を사귀다（付き合う、「4」＝사で始まる）の前段階として使った言葉遊びで、付き合う前の曖昧な段階を表す。</t>
         </is>
       </c>
       <c r="K700" s="16" t="inlineStr">
         <is>
-          <t>연락도 없이 잠수이별당했어.</t>
+          <t>우리 지금 삼귀는 사이야.</t>
         </is>
       </c>
       <c r="L700" s="16" t="inlineStr">
         <is>
-          <t>I got ghosted with no explanation at all.</t>
+          <t>We're in that pre-dating stage right now.</t>
         </is>
       </c>
       <c r="M700" s="16" t="inlineStr">
         <is>
-          <t>Me hicieron ghosting sin ninguna explicación.</t>
+          <t>Ahorita estamos en esa etapa previa a ser novios.</t>
         </is>
       </c>
       <c r="N700" s="16" t="inlineStr">
         <is>
-          <t>毫無音訊就被人間蒸發式分手了。</t>
+          <t>我們現在算是曖昧中的關係。</t>
         </is>
       </c>
       <c r="O700" s="16" t="inlineStr">
         <is>
-          <t>毫无音频就被人间蒸发式分手了。</t>
+          <t>我们现在算是暧昧中的关系。</t>
         </is>
       </c>
       <c r="P700" s="16" t="inlineStr">
         <is>
-          <t>連絡もなく自然消滅させられた。</t>
+          <t>私たち、今そういう段階にいるの。</t>
         </is>
       </c>
       <c r="Q700" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R700" s="15" t="inlineStr">
@@ -68647,17 +68647,17 @@
     <row r="701" ht="46" customHeight="1">
       <c r="A701" s="15" t="inlineStr">
         <is>
-          <t>DAT-008</t>
+          <t>DAT-006</t>
         </is>
       </c>
       <c r="B701" s="15" t="inlineStr">
         <is>
-          <t>계약연애</t>
+          <t>환승연애</t>
         </is>
       </c>
       <c r="C701" s="15" t="inlineStr">
         <is>
-          <t>gye-yak-yeon-ae</t>
+          <t>hwan-seung-yeon-ae</t>
         </is>
       </c>
       <c r="D701" s="15" t="inlineStr">
@@ -68672,62 +68672,62 @@
       </c>
       <c r="F701" s="16" t="inlineStr">
         <is>
-          <t>A fake "contract relationship" arranged for practical reasons — a very common K-drama plot device.</t>
+          <t>"Transfer love" — starting a new relationship right after a breakup, popularized by a reality show of the same name.</t>
         </is>
       </c>
       <c r="G701" s="16" t="inlineStr">
         <is>
-          <t>Una falsa "relación por contrato" arreglada por razones prácticas, un recurso argumental muy común en K-dramas.</t>
+          <t>"Amor de transbordo": empezar una nueva relación justo después de una ruptura, popularizado por un reality show del mismo nombre.</t>
         </is>
       </c>
       <c r="H701" s="16" t="inlineStr">
         <is>
-          <t>因現實考量而假裝交往的「契約戀愛」，是韓劇非常常見的劇情設定。</t>
+          <t>「轉乘戀愛」——分手後立刻投入新戀情，因同名實境節目而爆紅。</t>
         </is>
       </c>
       <c r="I701" s="16" t="inlineStr">
         <is>
-          <t>因现实考量而假装交往的“契约恋爱”，是韩剧非常常见的剧情设置。</t>
+          <t>“转乘恋爱”——分手后立刻投入新恋情，因同名实境节目而爆红。</t>
         </is>
       </c>
       <c r="J701" s="16" t="inlineStr">
         <is>
-          <t>現実的な理由で仕組まれた偽の「契約恋愛」——韓国ドラマで非常によくある設定。</t>
+          <t>「乗り換え恋愛」——別れた直後にすぐ新しい恋愛を始めること、同名のリアリティ番組で話題になった。</t>
         </is>
       </c>
       <c r="K701" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 계약연애물이야.</t>
+          <t>그 커플 완전 환승연애 아니야?</t>
         </is>
       </c>
       <c r="L701" s="16" t="inlineStr">
         <is>
-          <t>This drama is a contract-relationship story.</t>
+          <t>Isn't that couple a total transfer-love situation?</t>
         </is>
       </c>
       <c r="M701" s="16" t="inlineStr">
         <is>
-          <t>Este drama es de esos con relación por contrato.</t>
+          <t>¿Esa pareja no es un caso típico de "amor de transbordo"?</t>
         </is>
       </c>
       <c r="N701" s="16" t="inlineStr">
         <is>
-          <t>這部劇是契約戀愛劇情。</t>
+          <t>那對情侶根本是轉乘戀愛吧？</t>
         </is>
       </c>
       <c r="O701" s="16" t="inlineStr">
         <is>
-          <t>这部剧是契约恋爱剧情。</t>
+          <t>那对情侣根本是转乘恋爱吧？</t>
         </is>
       </c>
       <c r="P701" s="16" t="inlineStr">
         <is>
-          <t>このドラマ、契約恋愛ものだよ。</t>
+          <t>あのカップル、完全に乗り換え恋愛じゃない？</t>
         </is>
       </c>
       <c r="Q701" s="16" t="inlineStr">
         <is>
-          <t>K-drama genre talk</t>
+          <t>Reality show fandom, gossip</t>
         </is>
       </c>
       <c r="R701" s="15" t="inlineStr">
@@ -68744,17 +68744,17 @@
     <row r="702" ht="46" customHeight="1">
       <c r="A702" s="15" t="inlineStr">
         <is>
-          <t>DAT-009</t>
+          <t>DAT-007</t>
         </is>
       </c>
       <c r="B702" s="15" t="inlineStr">
         <is>
-          <t>재벌</t>
+          <t>잠수이별</t>
         </is>
       </c>
       <c r="C702" s="15" t="inlineStr">
         <is>
-          <t>jae-beol</t>
+          <t>jam-su-i-byeol</t>
         </is>
       </c>
       <c r="D702" s="15" t="inlineStr">
@@ -68769,62 +68769,62 @@
       </c>
       <c r="F702" s="16" t="inlineStr">
         <is>
-          <t>A chaebol — a large, family-controlled business conglomerate, often a K-drama love interest's background.</t>
+          <t>"Diving breakup" — ending a relationship by disappearing without explanation, i.e. ghosting.</t>
         </is>
       </c>
       <c r="G702" s="16" t="inlineStr">
         <is>
-          <t>Un chaebol: un gran conglomerado empresarial controlado por una familia, a menudo el trasfondo de un interés romántico en K-dramas.</t>
+          <t>"Ruptura de buceo": terminar una relación desapareciendo sin explicación, es decir, ghosting.</t>
         </is>
       </c>
       <c r="H702" s="16" t="inlineStr">
         <is>
-          <t>財閥——大型家族控制的企業集團，常是韓劇男女主角的家世背景設定。</t>
+          <t>「潛水式分手」——不做任何說明就人間蒸發結束關係。</t>
         </is>
       </c>
       <c r="I702" s="16" t="inlineStr">
         <is>
-          <t>财阀——大型家族控制的企业集团，常是韩剧男女主角的家世背景设置。</t>
+          <t>“潜水式分手”——不做任何说明就人间蒸发结束关系。</t>
         </is>
       </c>
       <c r="J702" s="16" t="inlineStr">
         <is>
-          <t>家族経営の大規模企業グループ——韓国ドラマの恋愛相手の設定によく使われる。</t>
+          <t>「潜水別れ」——説明もなく姿を消して関係を終わらせること、つまり音信不通。</t>
         </is>
       </c>
       <c r="K702" s="16" t="inlineStr">
         <is>
-          <t>이번 드라마 남주는 재벌 3세래.</t>
+          <t>연락도 없이 잠수이별당했어.</t>
         </is>
       </c>
       <c r="L702" s="16" t="inlineStr">
         <is>
-          <t>I heard this drama's male lead is a third-generation chaebol heir.</t>
+          <t>I got ghosted with no explanation at all.</t>
         </is>
       </c>
       <c r="M702" s="16" t="inlineStr">
         <is>
-          <t>Escuché que el protagonista de este drama es heredero de tercera generación de un chaebol.</t>
+          <t>Me hicieron ghosting sin ninguna explicación.</t>
         </is>
       </c>
       <c r="N702" s="16" t="inlineStr">
         <is>
-          <t>聽說這次男主角是財閥三代。</t>
+          <t>毫無音訊就被人間蒸發式分手了。</t>
         </is>
       </c>
       <c r="O702" s="16" t="inlineStr">
         <is>
-          <t>听说这次男主角是财阀三代。</t>
+          <t>毫无音频就被人间蒸发式分手了。</t>
         </is>
       </c>
       <c r="P702" s="16" t="inlineStr">
         <is>
-          <t>今回のドラマの男主人公は財閥三世らしい。</t>
+          <t>連絡もなく自然消滅させられた。</t>
         </is>
       </c>
       <c r="Q702" s="16" t="inlineStr">
         <is>
-          <t>K-drama plot talk</t>
+          <t>Relationship talk</t>
         </is>
       </c>
       <c r="R702" s="15" t="inlineStr">
@@ -68841,17 +68841,17 @@
     <row r="703" ht="46" customHeight="1">
       <c r="A703" s="15" t="inlineStr">
         <is>
-          <t>DAT-010</t>
+          <t>DAT-008</t>
         </is>
       </c>
       <c r="B703" s="15" t="inlineStr">
         <is>
-          <t>막장</t>
+          <t>계약연애</t>
         </is>
       </c>
       <c r="C703" s="15" t="inlineStr">
         <is>
-          <t>mak-jang</t>
+          <t>gye-yak-yeon-ae</t>
         </is>
       </c>
       <c r="D703" s="15" t="inlineStr">
@@ -68866,57 +68866,57 @@
       </c>
       <c r="F703" s="16" t="inlineStr">
         <is>
-          <t>"End of the mine shaft" — describes an extreme, over-the-top dramatic plot twist.</t>
+          <t>A fake "contract relationship" arranged for practical reasons — a very common K-drama plot device.</t>
         </is>
       </c>
       <c r="G703" s="16" t="inlineStr">
         <is>
-          <t>"Final del pozo de la mina": describe un giro argumental extremo y exagerado.</t>
+          <t>Una falsa "relación por contrato" arreglada por razones prácticas, un recurso argumental muy común en K-dramas.</t>
         </is>
       </c>
       <c r="H703" s="16" t="inlineStr">
         <is>
-          <t>字面意思是「礦坑盡頭」——形容誇張、狗血到極點的劇情轉折。</t>
+          <t>因現實考量而假裝交往的「契約戀愛」，是韓劇非常常見的劇情設定。</t>
         </is>
       </c>
       <c r="I703" s="16" t="inlineStr">
         <is>
-          <t>字面意思是“矿坑尽头”——形容夸张、狗血到极点的剧情转折。</t>
+          <t>因现实考量而假装交往的“契约恋爱”，是韩剧非常常见的剧情设置。</t>
         </is>
       </c>
       <c r="J703" s="16" t="inlineStr">
         <is>
-          <t>「坑道の奥」——極端で、行き過ぎたドラマチックな展開を表す。</t>
+          <t>現実的な理由で仕組まれた偽の「契約恋愛」——韓国ドラマで非常によくある設定。</t>
         </is>
       </c>
       <c r="K703" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 완전 막장 전개야.</t>
+          <t>이 드라마 계약연애물이야.</t>
         </is>
       </c>
       <c r="L703" s="16" t="inlineStr">
         <is>
-          <t>This drama's plot has gone completely over the top.</t>
+          <t>This drama is a contract-relationship story.</t>
         </is>
       </c>
       <c r="M703" s="16" t="inlineStr">
         <is>
-          <t>La trama de este drama se volvió totalmente exagerada.</t>
+          <t>Este drama es de esos con relación por contrato.</t>
         </is>
       </c>
       <c r="N703" s="16" t="inlineStr">
         <is>
-          <t>這部劇劇情完全狗血。</t>
+          <t>這部劇是契約戀愛劇情。</t>
         </is>
       </c>
       <c r="O703" s="16" t="inlineStr">
         <is>
-          <t>这部剧剧情完全狗血。</t>
+          <t>这部剧是契约恋爱剧情。</t>
         </is>
       </c>
       <c r="P703" s="16" t="inlineStr">
         <is>
-          <t>このドラマ、完全にどろどろ展開になってる。</t>
+          <t>このドラマ、契約恋愛ものだよ。</t>
         </is>
       </c>
       <c r="Q703" s="16" t="inlineStr">
@@ -68938,17 +68938,17 @@
     <row r="704" ht="46" customHeight="1">
       <c r="A704" s="15" t="inlineStr">
         <is>
-          <t>DAT-011</t>
+          <t>DAT-009</t>
         </is>
       </c>
       <c r="B704" s="15" t="inlineStr">
         <is>
-          <t>누나</t>
+          <t>재벌</t>
         </is>
       </c>
       <c r="C704" s="15" t="inlineStr">
         <is>
-          <t>nu-na</t>
+          <t>jae-beol</t>
         </is>
       </c>
       <c r="D704" s="15" t="inlineStr">
@@ -68963,62 +68963,62 @@
       </c>
       <c r="F704" s="16" t="inlineStr">
         <is>
-          <t>What a man calls an older woman — also names the popular "noona romance" drama trope.</t>
+          <t>A chaebol — a large, family-controlled business conglomerate, often a K-drama love interest's background.</t>
         </is>
       </c>
       <c r="G704" s="16" t="inlineStr">
         <is>
-          <t>Cómo un hombre llama a una mujer mayor; también nombra el popular recurso de "romance con noona" en los dramas.</t>
+          <t>Un chaebol: un gran conglomerado empresarial controlado por una familia, a menudo el trasfondo de un interés romántico en K-dramas.</t>
         </is>
       </c>
       <c r="H704" s="16" t="inlineStr">
         <is>
-          <t>男性稱呼年長女性的用語，也用來指稱流行的「姊弟戀」劇情套路。</t>
+          <t>財閥——大型家族控制的企業集團，常是韓劇男女主角的家世背景設定。</t>
         </is>
       </c>
       <c r="I704" s="16" t="inlineStr">
         <is>
-          <t>男性称呼年长女性的用语，也用来指称流行的“姊弟恋”剧情套路。</t>
+          <t>财阀——大型家族控制的企业集团，常是韩剧男女主角的家世背景设置。</t>
         </is>
       </c>
       <c r="J704" s="16" t="inlineStr">
         <is>
-          <t>男性が年上の女性を呼ぶ言葉——人気の「姉さん年上ロマンス」というドラマのトロープの名前でもある。</t>
+          <t>家族経営の大規模企業グループ——韓国ドラマの恋愛相手の設定によく使われる。</t>
         </is>
       </c>
       <c r="K704" s="16" t="inlineStr">
         <is>
-          <t>이 드라마는 누나 로맨스야.</t>
+          <t>이번 드라마 남주는 재벌 3세래.</t>
         </is>
       </c>
       <c r="L704" s="16" t="inlineStr">
         <is>
-          <t>This drama is a noona romance.</t>
+          <t>I heard this drama's male lead is a third-generation chaebol heir.</t>
         </is>
       </c>
       <c r="M704" s="16" t="inlineStr">
         <is>
-          <t>Este drama es un romance con una "noona" (mujer mayor).</t>
+          <t>Escuché que el protagonista de este drama es heredero de tercera generación de un chaebol.</t>
         </is>
       </c>
       <c r="N704" s="16" t="inlineStr">
         <is>
-          <t>這部劇是姊弟戀劇情。</t>
+          <t>聽說這次男主角是財閥三代。</t>
         </is>
       </c>
       <c r="O704" s="16" t="inlineStr">
         <is>
-          <t>这部剧是姊弟恋剧情。</t>
+          <t>听说这次男主角是财阀三代。</t>
         </is>
       </c>
       <c r="P704" s="16" t="inlineStr">
         <is>
-          <t>このドラマは年上女性ロマンスだよ。</t>
+          <t>今回のドラマの男主人公は財閥三世らしい。</t>
         </is>
       </c>
       <c r="Q704" s="16" t="inlineStr">
         <is>
-          <t>K-drama genre talk</t>
+          <t>K-drama plot talk</t>
         </is>
       </c>
       <c r="R704" s="15" t="inlineStr">
@@ -69035,17 +69035,17 @@
     <row r="705" ht="46" customHeight="1">
       <c r="A705" s="15" t="inlineStr">
         <is>
-          <t>DAT-012</t>
+          <t>DAT-010</t>
         </is>
       </c>
       <c r="B705" s="15" t="inlineStr">
         <is>
-          <t>츤데레</t>
+          <t>막장</t>
         </is>
       </c>
       <c r="C705" s="15" t="inlineStr">
         <is>
-          <t>cheun-de-re</t>
+          <t>mak-jang</t>
         </is>
       </c>
       <c r="D705" s="15" t="inlineStr">
@@ -69060,62 +69060,62 @@
       </c>
       <c r="F705" s="16" t="inlineStr">
         <is>
-          <t>A cold-and-prickly-on-the-outside, warm-on-the-inside personality type (originally Japanese, widely used in Korean too).</t>
+          <t>"End of the mine shaft" — describes an extreme, over-the-top dramatic plot twist.</t>
         </is>
       </c>
       <c r="G705" s="16" t="inlineStr">
         <is>
-          <t>Un tipo de personalidad fría por fuera pero cálida por dentro (de origen japonés, muy usado también en coreano).</t>
+          <t>"Final del pozo de la mina": describe un giro argumental extremo y exagerado.</t>
         </is>
       </c>
       <c r="H705" s="16" t="inlineStr">
         <is>
-          <t>外表冷淡尖銳、內心溫暖的性格類型，傲嬌，原為日文用語，在韓國也廣泛使用。</t>
+          <t>字面意思是「礦坑盡頭」——形容誇張、狗血到極點的劇情轉折。</t>
         </is>
       </c>
       <c r="I705" s="16" t="inlineStr">
         <is>
-          <t>外表冷淡尖锐、内心温暖的性格类型，傲娇，原为日文用语，在韩国也广泛使用。</t>
+          <t>字面意思是“矿坑尽头”——形容夸张、狗血到极点的剧情转折。</t>
         </is>
       </c>
       <c r="J705" s="16" t="inlineStr">
         <is>
-          <t>外見は冷たくてトゲトゲしいけど、内面は温かい性格タイプ（元々日本語で、韓国でも広く使われている）。</t>
+          <t>「坑道の奥」——極端で、行き過ぎたドラマチックな展開を表す。</t>
         </is>
       </c>
       <c r="K705" s="16" t="inlineStr">
         <is>
-          <t>저 캐릭터 완전 츤데레야.</t>
+          <t>이 드라마 완전 막장 전개야.</t>
         </is>
       </c>
       <c r="L705" s="16" t="inlineStr">
         <is>
-          <t>That character is a total tsundere.</t>
+          <t>This drama's plot has gone completely over the top.</t>
         </is>
       </c>
       <c r="M705" s="16" t="inlineStr">
         <is>
-          <t>Ese personaje es un tsundere total.</t>
+          <t>La trama de este drama se volvió totalmente exagerada.</t>
         </is>
       </c>
       <c r="N705" s="16" t="inlineStr">
         <is>
-          <t>那個角色完全是傲嬌。</t>
+          <t>這部劇劇情完全狗血。</t>
         </is>
       </c>
       <c r="O705" s="16" t="inlineStr">
         <is>
-          <t>那个角色完全是傲娇。</t>
+          <t>这部剧剧情完全狗血。</t>
         </is>
       </c>
       <c r="P705" s="16" t="inlineStr">
         <is>
-          <t>あのキャラ、完全にツンデレだよね。</t>
+          <t>このドラマ、完全にどろどろ展開になってる。</t>
         </is>
       </c>
       <c r="Q705" s="16" t="inlineStr">
         <is>
-          <t>Drama/anime fan talk</t>
+          <t>K-drama genre talk</t>
         </is>
       </c>
       <c r="R705" s="15" t="inlineStr">
@@ -69132,17 +69132,17 @@
     <row r="706" ht="46" customHeight="1">
       <c r="A706" s="15" t="inlineStr">
         <is>
-          <t>DAT-013</t>
+          <t>DAT-011</t>
         </is>
       </c>
       <c r="B706" s="15" t="inlineStr">
         <is>
-          <t>재회</t>
+          <t>누나</t>
         </is>
       </c>
       <c r="C706" s="15" t="inlineStr">
         <is>
-          <t>jae-hoe</t>
+          <t>nu-na</t>
         </is>
       </c>
       <c r="D706" s="15" t="inlineStr">
@@ -69157,62 +69157,62 @@
       </c>
       <c r="F706" s="16" t="inlineStr">
         <is>
-          <t>Reuniting with an ex-partner.</t>
+          <t>What a man calls an older woman — also names the popular "noona romance" drama trope.</t>
         </is>
       </c>
       <c r="G706" s="16" t="inlineStr">
         <is>
-          <t>Reencontrarse con una expareja.</t>
+          <t>Cómo un hombre llama a una mujer mayor; también nombra el popular recurso de "romance con noona" en los dramas.</t>
         </is>
       </c>
       <c r="H706" s="16" t="inlineStr">
         <is>
-          <t>與前任重新復合。</t>
+          <t>男性稱呼年長女性的用語，也用來指稱流行的「姊弟戀」劇情套路。</t>
         </is>
       </c>
       <c r="I706" s="16" t="inlineStr">
         <is>
-          <t>与前任重新复合。</t>
+          <t>男性称呼年长女性的用语，也用来指称流行的“姊弟恋”剧情套路。</t>
         </is>
       </c>
       <c r="J706" s="16" t="inlineStr">
         <is>
-          <t>元恋人とよりを戻すこと。</t>
+          <t>男性が年上の女性を呼ぶ言葉——人気の「姉さん年上ロマンス」というドラマのトロープの名前でもある。</t>
         </is>
       </c>
       <c r="K706" s="16" t="inlineStr">
         <is>
-          <t>그 커플 결국 재회했대.</t>
+          <t>이 드라마는 누나 로맨스야.</t>
         </is>
       </c>
       <c r="L706" s="16" t="inlineStr">
         <is>
-          <t>I heard that couple got back together in the end.</t>
+          <t>This drama is a noona romance.</t>
         </is>
       </c>
       <c r="M706" s="16" t="inlineStr">
         <is>
-          <t>Escuché que esa pareja al final volvió.</t>
+          <t>Este drama es un romance con una "noona" (mujer mayor).</t>
         </is>
       </c>
       <c r="N706" s="16" t="inlineStr">
         <is>
-          <t>聽說那對情侶最後復合了。</t>
+          <t>這部劇是姊弟戀劇情。</t>
         </is>
       </c>
       <c r="O706" s="16" t="inlineStr">
         <is>
-          <t>听说那对情侣最后复合了。</t>
+          <t>这部剧是姊弟恋剧情。</t>
         </is>
       </c>
       <c r="P706" s="16" t="inlineStr">
         <is>
-          <t>あのカップル、結局復縁したらしい。</t>
+          <t>このドラマは年上女性ロマンスだよ。</t>
         </is>
       </c>
       <c r="Q706" s="16" t="inlineStr">
         <is>
-          <t>K-drama plot talk, gossip</t>
+          <t>K-drama genre talk</t>
         </is>
       </c>
       <c r="R706" s="15" t="inlineStr">
@@ -69229,17 +69229,17 @@
     <row r="707" ht="46" customHeight="1">
       <c r="A707" s="15" t="inlineStr">
         <is>
-          <t>DAT-014</t>
+          <t>DAT-012</t>
         </is>
       </c>
       <c r="B707" s="15" t="inlineStr">
         <is>
-          <t>짝사랑</t>
+          <t>츤데레</t>
         </is>
       </c>
       <c r="C707" s="15" t="inlineStr">
         <is>
-          <t>jjak-sa-rang</t>
+          <t>cheun-de-re</t>
         </is>
       </c>
       <c r="D707" s="15" t="inlineStr">
@@ -69254,62 +69254,62 @@
       </c>
       <c r="F707" s="16" t="inlineStr">
         <is>
-          <t>Unrequited, one-sided love.</t>
+          <t>A cold-and-prickly-on-the-outside, warm-on-the-inside personality type (originally Japanese, widely used in Korean too).</t>
         </is>
       </c>
       <c r="G707" s="16" t="inlineStr">
         <is>
-          <t>Amor no correspondido, unilateral.</t>
+          <t>Un tipo de personalidad fría por fuera pero cálida por dentro (de origen japonés, muy usado también en coreano).</t>
         </is>
       </c>
       <c r="H707" s="16" t="inlineStr">
         <is>
-          <t>得不到回應的單方面愛戀。</t>
+          <t>外表冷淡尖銳、內心溫暖的性格類型，傲嬌，原為日文用語，在韓國也廣泛使用。</t>
         </is>
       </c>
       <c r="I707" s="16" t="inlineStr">
         <is>
-          <t>得不到回应的单方面爱恋。</t>
+          <t>外表冷淡尖锐、内心温暖的性格类型，傲娇，原为日文用语，在韩国也广泛使用。</t>
         </is>
       </c>
       <c r="J707" s="16" t="inlineStr">
         <is>
-          <t>報われない、一方的な恋。</t>
+          <t>外見は冷たくてトゲトゲしいけど、内面は温かい性格タイプ（元々日本語で、韓国でも広く使われている）。</t>
         </is>
       </c>
       <c r="K707" s="16" t="inlineStr">
         <is>
-          <t>고등학생 때 짝사랑했던 애 기억나.</t>
+          <t>저 캐릭터 완전 츤데레야.</t>
         </is>
       </c>
       <c r="L707" s="16" t="inlineStr">
         <is>
-          <t>I remember the person I had a one-sided crush on in high school.</t>
+          <t>That character is a total tsundere.</t>
         </is>
       </c>
       <c r="M707" s="16" t="inlineStr">
         <is>
-          <t>Recuerdo a la persona de la que estuve enamorado sin ser correspondido en la prepa.</t>
+          <t>Ese personaje es un tsundere total.</t>
         </is>
       </c>
       <c r="N707" s="16" t="inlineStr">
         <is>
-          <t>我還記得高中時單戀過的那個人。</t>
+          <t>那個角色完全是傲嬌。</t>
         </is>
       </c>
       <c r="O707" s="16" t="inlineStr">
         <is>
-          <t>我还记得高中时单恋过的那个人。</t>
+          <t>那个角色完全是傲娇。</t>
         </is>
       </c>
       <c r="P707" s="16" t="inlineStr">
         <is>
-          <t>高校生の時に片思いしてた人のこと覚えてる。</t>
+          <t>あのキャラ、完全にツンデレだよね。</t>
         </is>
       </c>
       <c r="Q707" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>Drama/anime fan talk</t>
         </is>
       </c>
       <c r="R707" s="15" t="inlineStr">
@@ -69326,17 +69326,17 @@
     <row r="708" ht="46" customHeight="1">
       <c r="A708" s="15" t="inlineStr">
         <is>
-          <t>DAT-015</t>
+          <t>DAT-013</t>
         </is>
       </c>
       <c r="B708" s="15" t="inlineStr">
         <is>
-          <t>애정촌</t>
+          <t>재회</t>
         </is>
       </c>
       <c r="C708" s="15" t="inlineStr">
         <is>
-          <t>ae-jeong-chon</t>
+          <t>jae-hoe</t>
         </is>
       </c>
       <c r="D708" s="15" t="inlineStr">
@@ -69351,62 +69351,62 @@
       </c>
       <c r="F708" s="16" t="inlineStr">
         <is>
-          <t>"Love village" — the classic setting/format used in Korean dating reality shows.</t>
+          <t>Reuniting with an ex-partner.</t>
         </is>
       </c>
       <c r="G708" s="16" t="inlineStr">
         <is>
-          <t>"Pueblo del amor": el escenario o formato clásico usado en los reality shows de citas coreanos.</t>
+          <t>Reencontrarse con una expareja.</t>
         </is>
       </c>
       <c r="H708" s="16" t="inlineStr">
         <is>
-          <t>「愛情村」——韓國戀愛實境節目經典的場景設定與節目形式。</t>
+          <t>與前任重新復合。</t>
         </is>
       </c>
       <c r="I708" s="16" t="inlineStr">
         <is>
-          <t>“爱情村”——韩国恋爱实境节目经典的场景设置与节目形式。</t>
+          <t>与前任重新复合。</t>
         </is>
       </c>
       <c r="J708" s="16" t="inlineStr">
         <is>
-          <t>「愛の村」——韓国の恋愛リアリティ番組の定番の舞台設定・フォーマット。</t>
+          <t>元恋人とよりを戻すこと。</t>
         </is>
       </c>
       <c r="K708" s="16" t="inlineStr">
         <is>
-          <t>애정촌 나온 커플 아직도 만나?</t>
+          <t>그 커플 결국 재회했대.</t>
         </is>
       </c>
       <c r="L708" s="16" t="inlineStr">
         <is>
-          <t>Is that couple from the love-village show still together?</t>
+          <t>I heard that couple got back together in the end.</t>
         </is>
       </c>
       <c r="M708" s="16" t="inlineStr">
         <is>
-          <t>¿Esa pareja del show de citas todavía sigue junta?</t>
+          <t>Escuché que esa pareja al final volvió.</t>
         </is>
       </c>
       <c r="N708" s="16" t="inlineStr">
         <is>
-          <t>那對從愛情村出來的情侶還在一起嗎？</t>
+          <t>聽說那對情侶最後復合了。</t>
         </is>
       </c>
       <c r="O708" s="16" t="inlineStr">
         <is>
-          <t>那对从爱情村出来的情侣还在一起吗？</t>
+          <t>听说那对情侣最后复合了。</t>
         </is>
       </c>
       <c r="P708" s="16" t="inlineStr">
         <is>
-          <t>あの恋の村から出てきたカップル、まだ付き合ってる？</t>
+          <t>あのカップル、結局復縁したらしい。</t>
         </is>
       </c>
       <c r="Q708" s="16" t="inlineStr">
         <is>
-          <t>Dating reality shows</t>
+          <t>K-drama plot talk, gossip</t>
         </is>
       </c>
       <c r="R708" s="15" t="inlineStr">
@@ -69423,17 +69423,17 @@
     <row r="709" ht="46" customHeight="1">
       <c r="A709" s="15" t="inlineStr">
         <is>
-          <t>DAT-016</t>
+          <t>DAT-014</t>
         </is>
       </c>
       <c r="B709" s="15" t="inlineStr">
         <is>
-          <t>심쿵</t>
+          <t>짝사랑</t>
         </is>
       </c>
       <c r="C709" s="15" t="inlineStr">
         <is>
-          <t>sim-kung</t>
+          <t>jjak-sa-rang</t>
         </is>
       </c>
       <c r="D709" s="15" t="inlineStr">
@@ -69448,62 +69448,62 @@
       </c>
       <c r="F709" s="16" t="inlineStr">
         <is>
-          <t>"Heart-thump" — a swoon-worthy, heart-fluttering moment.</t>
+          <t>Unrequited, one-sided love.</t>
         </is>
       </c>
       <c r="G709" s="16" t="inlineStr">
         <is>
-          <t>"Latido de corazón": un momento que hace suspirar y acelera el corazón.</t>
+          <t>Amor no correspondido, unilateral.</t>
         </is>
       </c>
       <c r="H709" s="16" t="inlineStr">
         <is>
-          <t>「心臟砰咚」——令人心動、心跳加速的瞬間。</t>
+          <t>得不到回應的單方面愛戀。</t>
         </is>
       </c>
       <c r="I709" s="16" t="inlineStr">
         <is>
-          <t>“心脏砰咚”——令人心动、心跳加速的瞬间。</t>
+          <t>得不到回应的单方面爱恋。</t>
         </is>
       </c>
       <c r="J709" s="16" t="inlineStr">
         <is>
-          <t>「心臓ドキン」——胸きゅんする瞬間。</t>
+          <t>報われない、一方的な恋。</t>
         </is>
       </c>
       <c r="K709" s="16" t="inlineStr">
         <is>
-          <t>그 장면 완전 심쿵이었어.</t>
+          <t>고등학생 때 짝사랑했던 애 기억나.</t>
         </is>
       </c>
       <c r="L709" s="16" t="inlineStr">
         <is>
-          <t>That scene was such a heart-flutter moment.</t>
+          <t>I remember the person I had a one-sided crush on in high school.</t>
         </is>
       </c>
       <c r="M709" s="16" t="inlineStr">
         <is>
-          <t>Esa escena fue un momento que hizo latir el corazón muy fuerte.</t>
+          <t>Recuerdo a la persona de la que estuve enamorado sin ser correspondido en la prepa.</t>
         </is>
       </c>
       <c r="N709" s="16" t="inlineStr">
         <is>
-          <t>那個畫面完全讓人心動。</t>
+          <t>我還記得高中時單戀過的那個人。</t>
         </is>
       </c>
       <c r="O709" s="16" t="inlineStr">
         <is>
-          <t>那个画面完全让人心动。</t>
+          <t>我还记得高中时单恋过的那个人。</t>
         </is>
       </c>
       <c r="P709" s="16" t="inlineStr">
         <is>
-          <t>あのシーン、完全にキュンとした。</t>
+          <t>高校生の時に片思いしてた人のこと覚えてる。</t>
         </is>
       </c>
       <c r="Q709" s="16" t="inlineStr">
         <is>
-          <t>K-drama reactions</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R709" s="15" t="inlineStr">
@@ -69520,17 +69520,17 @@
     <row r="710" ht="46" customHeight="1">
       <c r="A710" s="15" t="inlineStr">
         <is>
-          <t>DAT-017</t>
+          <t>DAT-015</t>
         </is>
       </c>
       <c r="B710" s="15" t="inlineStr">
         <is>
-          <t>첫사랑</t>
+          <t>애정촌</t>
         </is>
       </c>
       <c r="C710" s="15" t="inlineStr">
         <is>
-          <t>cheot-sa-rang</t>
+          <t>ae-jeong-chon</t>
         </is>
       </c>
       <c r="D710" s="15" t="inlineStr">
@@ -69545,62 +69545,62 @@
       </c>
       <c r="F710" s="16" t="inlineStr">
         <is>
-          <t>One's very first love.</t>
+          <t>"Love village" — the classic setting/format used in Korean dating reality shows.</t>
         </is>
       </c>
       <c r="G710" s="16" t="inlineStr">
         <is>
-          <t>El primer amor de una persona.</t>
+          <t>"Pueblo del amor": el escenario o formato clásico usado en los reality shows de citas coreanos.</t>
         </is>
       </c>
       <c r="H710" s="16" t="inlineStr">
         <is>
-          <t>一個人生命中最初的戀愛對象，初戀。</t>
+          <t>「愛情村」——韓國戀愛實境節目經典的場景設定與節目形式。</t>
         </is>
       </c>
       <c r="I710" s="16" t="inlineStr">
         <is>
-          <t>一个人生命中最初的恋爱对象，初恋。</t>
+          <t>“爱情村”——韩国恋爱实境节目经典的场景设置与节目形式。</t>
         </is>
       </c>
       <c r="J710" s="16" t="inlineStr">
         <is>
-          <t>人生で最初の恋。</t>
+          <t>「愛の村」——韓国の恋愛リアリティ番組の定番の舞台設定・フォーマット。</t>
         </is>
       </c>
       <c r="K710" s="16" t="inlineStr">
         <is>
-          <t>그 드라마 보니까 첫사랑 생각나더라.</t>
+          <t>애정촌 나온 커플 아직도 만나?</t>
         </is>
       </c>
       <c r="L710" s="16" t="inlineStr">
         <is>
-          <t>Watching that drama made me think of my first love.</t>
+          <t>Is that couple from the love-village show still together?</t>
         </is>
       </c>
       <c r="M710" s="16" t="inlineStr">
         <is>
-          <t>Ver ese drama me hizo pensar en mi primer amor.</t>
+          <t>¿Esa pareja del show de citas todavía sigue junta?</t>
         </is>
       </c>
       <c r="N710" s="16" t="inlineStr">
         <is>
-          <t>看那部劇讓我想起初戀。</t>
+          <t>那對從愛情村出來的情侶還在一起嗎？</t>
         </is>
       </c>
       <c r="O710" s="16" t="inlineStr">
         <is>
-          <t>看那部剧让我想起初恋。</t>
+          <t>那对从爱情村出来的情侣还在一起吗？</t>
         </is>
       </c>
       <c r="P710" s="16" t="inlineStr">
         <is>
-          <t>あのドラマ見てたら初恋を思い出した。</t>
+          <t>あの恋の村から出てきたカップル、まだ付き合ってる？</t>
         </is>
       </c>
       <c r="Q710" s="16" t="inlineStr">
         <is>
-          <t>Casual nostalgia talk</t>
+          <t>Dating reality shows</t>
         </is>
       </c>
       <c r="R710" s="15" t="inlineStr">
@@ -69617,17 +69617,17 @@
     <row r="711" ht="46" customHeight="1">
       <c r="A711" s="15" t="inlineStr">
         <is>
-          <t>DAT-018</t>
+          <t>DAT-016</t>
         </is>
       </c>
       <c r="B711" s="15" t="inlineStr">
         <is>
-          <t>국민첫사랑</t>
+          <t>심쿵</t>
         </is>
       </c>
       <c r="C711" s="15" t="inlineStr">
         <is>
-          <t>guk-min-cheot-sa-rang</t>
+          <t>sim-kung</t>
         </is>
       </c>
       <c r="D711" s="15" t="inlineStr">
@@ -69642,62 +69642,62 @@
       </c>
       <c r="F711" s="16" t="inlineStr">
         <is>
-          <t>"Nation's first love" — an actress or idol seen as an idealized, universally beloved first-love figure.</t>
+          <t>"Heart-thump" — a swoon-worthy, heart-fluttering moment.</t>
         </is>
       </c>
       <c r="G711" s="16" t="inlineStr">
         <is>
-          <t>"Primer amor de la nación": una actriz o ídolo vista como una figura idealizada de primer amor querida por todos.</t>
+          <t>"Latido de corazón": un momento que hace suspirar y acelera el corazón.</t>
         </is>
       </c>
       <c r="H711" s="16" t="inlineStr">
         <is>
-          <t>「國民初戀」——被視為理想化、全民共同初戀形象的女演員或偶像。</t>
+          <t>「心臟砰咚」——令人心動、心跳加速的瞬間。</t>
         </is>
       </c>
       <c r="I711" s="16" t="inlineStr">
         <is>
-          <t>“国民初恋”——被视为理想化、全民共同初恋形象的女演员或偶像。</t>
+          <t>“心脏砰咚”——令人心动、心跳加速的瞬间。</t>
         </is>
       </c>
       <c r="J711" s="16" t="inlineStr">
         <is>
-          <t>「国民の初恋」——理想化された、国民全員に愛される初恋の象徴とされる女優やアイドル。</t>
+          <t>「心臓ドキン」——胸きゅんする瞬間。</t>
         </is>
       </c>
       <c r="K711" s="16" t="inlineStr">
         <is>
-          <t>그 배우는 국민첫사랑으로 불려.</t>
+          <t>그 장면 완전 심쿵이었어.</t>
         </is>
       </c>
       <c r="L711" s="16" t="inlineStr">
         <is>
-          <t>That actress is called the nation's first love.</t>
+          <t>That scene was such a heart-flutter moment.</t>
         </is>
       </c>
       <c r="M711" s="16" t="inlineStr">
         <is>
-          <t>A esa actriz la llaman el primer amor de la nación.</t>
+          <t>Esa escena fue un momento que hizo latir el corazón muy fuerte.</t>
         </is>
       </c>
       <c r="N711" s="16" t="inlineStr">
         <is>
-          <t>那位演員被稱為國民初戀。</t>
+          <t>那個畫面完全讓人心動。</t>
         </is>
       </c>
       <c r="O711" s="16" t="inlineStr">
         <is>
-          <t>那位演员被称为国民初恋。</t>
+          <t>那个画面完全让人心动。</t>
         </is>
       </c>
       <c r="P711" s="16" t="inlineStr">
         <is>
-          <t>あの女優は国民的初恋と呼ばれてる。</t>
+          <t>あのシーン、完全にキュンとした。</t>
         </is>
       </c>
       <c r="Q711" s="16" t="inlineStr">
         <is>
-          <t>Media coverage, fan talk</t>
+          <t>K-drama reactions</t>
         </is>
       </c>
       <c r="R711" s="15" t="inlineStr">
@@ -69714,17 +69714,17 @@
     <row r="712" ht="46" customHeight="1">
       <c r="A712" s="15" t="inlineStr">
         <is>
-          <t>DAT-019</t>
+          <t>DAT-017</t>
         </is>
       </c>
       <c r="B712" s="15" t="inlineStr">
         <is>
-          <t>훈남</t>
+          <t>첫사랑</t>
         </is>
       </c>
       <c r="C712" s="15" t="inlineStr">
         <is>
-          <t>hun-nam</t>
+          <t>cheot-sa-rang</t>
         </is>
       </c>
       <c r="D712" s="15" t="inlineStr">
@@ -69739,62 +69739,62 @@
       </c>
       <c r="F712" s="16" t="inlineStr">
         <is>
-          <t>A warm, wholesome, good-looking man — approachable rather than intimidating.</t>
+          <t>One's very first love.</t>
         </is>
       </c>
       <c r="G712" s="16" t="inlineStr">
         <is>
-          <t>Un hombre cálido, agradable y atractivo — cercano en lugar de intimidante.</t>
+          <t>El primer amor de una persona.</t>
         </is>
       </c>
       <c r="H712" s="16" t="inlineStr">
         <is>
-          <t>溫暖、樸實、外表出眾的男性，給人親切而非有距離感的印象，暖男。</t>
+          <t>一個人生命中最初的戀愛對象，初戀。</t>
         </is>
       </c>
       <c r="I712" s="16" t="inlineStr">
         <is>
-          <t>温暖、朴实、外表出众的男性，给人亲切而非有距离感的印象，暖男。</t>
+          <t>一个人生命中最初的恋爱对象，初恋。</t>
         </is>
       </c>
       <c r="J712" s="16" t="inlineStr">
         <is>
-          <t>温かく、素朴で、見た目の良い男性——威圧感がなく親しみやすい。</t>
+          <t>人生で最初の恋。</t>
         </is>
       </c>
       <c r="K712" s="16" t="inlineStr">
         <is>
-          <t>저 남주 완전 훈남 스타일이야.</t>
+          <t>그 드라마 보니까 첫사랑 생각나더라.</t>
         </is>
       </c>
       <c r="L712" s="16" t="inlineStr">
         <is>
-          <t>That male lead is totally the wholesome good-looking type.</t>
+          <t>Watching that drama made me think of my first love.</t>
         </is>
       </c>
       <c r="M712" s="16" t="inlineStr">
         <is>
-          <t>Ese protagonista es totalmente del tipo agradable y atractivo.</t>
+          <t>Ver ese drama me hizo pensar en mi primer amor.</t>
         </is>
       </c>
       <c r="N712" s="16" t="inlineStr">
         <is>
-          <t>那個男主角完全是暖男型。</t>
+          <t>看那部劇讓我想起初戀。</t>
         </is>
       </c>
       <c r="O712" s="16" t="inlineStr">
         <is>
-          <t>那个男主角完全是暖男型。</t>
+          <t>看那部剧让我想起初恋。</t>
         </is>
       </c>
       <c r="P712" s="16" t="inlineStr">
         <is>
-          <t>あの男主人公、完全に好青年タイプだよね。</t>
+          <t>あのドラマ見てたら初恋を思い出した。</t>
         </is>
       </c>
       <c r="Q712" s="16" t="inlineStr">
         <is>
-          <t>K-drama casting talk</t>
+          <t>Casual nostalgia talk</t>
         </is>
       </c>
       <c r="R712" s="15" t="inlineStr">
@@ -69811,17 +69811,17 @@
     <row r="713" ht="46" customHeight="1">
       <c r="A713" s="15" t="inlineStr">
         <is>
-          <t>DAT-020</t>
+          <t>DAT-018</t>
         </is>
       </c>
       <c r="B713" s="15" t="inlineStr">
         <is>
-          <t>훈녀</t>
+          <t>국민첫사랑</t>
         </is>
       </c>
       <c r="C713" s="15" t="inlineStr">
         <is>
-          <t>hun-nyeo</t>
+          <t>guk-min-cheot-sa-rang</t>
         </is>
       </c>
       <c r="D713" s="15" t="inlineStr">
@@ -69836,62 +69836,62 @@
       </c>
       <c r="F713" s="16" t="inlineStr">
         <is>
-          <t>The female equivalent of 훈남 — warm, approachable, and good-looking.</t>
+          <t>"Nation's first love" — an actress or idol seen as an idealized, universally beloved first-love figure.</t>
         </is>
       </c>
       <c r="G713" s="16" t="inlineStr">
         <is>
-          <t>El equivalente femenino de 훈남: cálida, cercana y atractiva.</t>
+          <t>"Primer amor de la nación": una actriz o ídolo vista como una figura idealizada de primer amor querida por todos.</t>
         </is>
       </c>
       <c r="H713" s="16" t="inlineStr">
         <is>
-          <t>훈남的女性版本——溫暖、親切又好看的女性。</t>
+          <t>「國民初戀」——被視為理想化、全民共同初戀形象的女演員或偶像。</t>
         </is>
       </c>
       <c r="I713" s="16" t="inlineStr">
         <is>
-          <t>훈남的女性版本——温暖、亲切又好看的女性。</t>
+          <t>“国民初恋”——被视为理想化、全民共同初恋形象的女演员或偶像。</t>
         </is>
       </c>
       <c r="J713" s="16" t="inlineStr">
         <is>
-          <t>훈남の女性版——温かく、親しみやすくて、見た目の良い女性。</t>
+          <t>「国民の初恋」——理想化された、国民全員に愛される初恋の象徴とされる女優やアイドル。</t>
         </is>
       </c>
       <c r="K713" s="16" t="inlineStr">
         <is>
-          <t>그 여배우는 훈녀 이미지로 유명해.</t>
+          <t>그 배우는 국민첫사랑으로 불려.</t>
         </is>
       </c>
       <c r="L713" s="16" t="inlineStr">
         <is>
-          <t>That actress is known for her wholesome good-looking image.</t>
+          <t>That actress is called the nation's first love.</t>
         </is>
       </c>
       <c r="M713" s="16" t="inlineStr">
         <is>
-          <t>Esa actriz es conocida por su imagen cálida y atractiva.</t>
+          <t>A esa actriz la llaman el primer amor de la nación.</t>
         </is>
       </c>
       <c r="N713" s="16" t="inlineStr">
         <is>
-          <t>那位女演員以暖女形象聞名。</t>
+          <t>那位演員被稱為國民初戀。</t>
         </is>
       </c>
       <c r="O713" s="16" t="inlineStr">
         <is>
-          <t>那位女演员以暖女形象闻名。</t>
+          <t>那位演员被称为国民初恋。</t>
         </is>
       </c>
       <c r="P713" s="16" t="inlineStr">
         <is>
-          <t>あの女優、好感度高い美人イメージで有名。</t>
+          <t>あの女優は国民的初恋と呼ばれてる。</t>
         </is>
       </c>
       <c r="Q713" s="16" t="inlineStr">
         <is>
-          <t>K-drama casting talk</t>
+          <t>Media coverage, fan talk</t>
         </is>
       </c>
       <c r="R713" s="15" t="inlineStr">
@@ -69908,17 +69908,17 @@
     <row r="714" ht="46" customHeight="1">
       <c r="A714" s="15" t="inlineStr">
         <is>
-          <t>DAT-021</t>
+          <t>DAT-019</t>
         </is>
       </c>
       <c r="B714" s="15" t="inlineStr">
         <is>
-          <t>나쁜남자</t>
+          <t>훈남</t>
         </is>
       </c>
       <c r="C714" s="15" t="inlineStr">
         <is>
-          <t>na-ppeun-nam-ja</t>
+          <t>hun-nam</t>
         </is>
       </c>
       <c r="D714" s="15" t="inlineStr">
@@ -69933,62 +69933,62 @@
       </c>
       <c r="F714" s="16" t="inlineStr">
         <is>
-          <t>The "bad boy" trope — a cold, dangerous-seeming male lead who softens for the heroine.</t>
+          <t>A warm, wholesome, good-looking man — approachable rather than intimidating.</t>
         </is>
       </c>
       <c r="G714" s="16" t="inlineStr">
         <is>
-          <t>El arquetipo del "chico malo": un protagonista frío y de apariencia peligrosa que se enternece por la protagonista.</t>
+          <t>Un hombre cálido, agradable y atractivo — cercano en lugar de intimidante.</t>
         </is>
       </c>
       <c r="H714" s="16" t="inlineStr">
         <is>
-          <t>「壞男人」套路——外表冷酷、帶點危險氣息，卻在女主角面前逐漸軟化的男主角類型。</t>
+          <t>溫暖、樸實、外表出眾的男性，給人親切而非有距離感的印象，暖男。</t>
         </is>
       </c>
       <c r="I714" s="16" t="inlineStr">
         <is>
-          <t>“坏男人”套路——外表冷酷、带点危险气息，却在女主角面前逐渐软化的男主角类型。</t>
+          <t>温暖、朴实、外表出众的男性，给人亲切而非有距离感的印象，暖男。</t>
         </is>
       </c>
       <c r="J714" s="16" t="inlineStr">
         <is>
-          <t>「悪い男」トロープ——冷たくて危険に見えるが、ヒロインの前で心を開いていく男性主人公。</t>
+          <t>温かく、素朴で、見た目の良い男性——威圧感がなく親しみやすい。</t>
         </is>
       </c>
       <c r="K714" s="16" t="inlineStr">
         <is>
-          <t>나쁜남자 클리셰인데도 계속 보게 돼.</t>
+          <t>저 남주 완전 훈남 스타일이야.</t>
         </is>
       </c>
       <c r="L714" s="16" t="inlineStr">
         <is>
-          <t>Even though it's the bad-boy cliché, I keep watching anyway.</t>
+          <t>That male lead is totally the wholesome good-looking type.</t>
         </is>
       </c>
       <c r="M714" s="16" t="inlineStr">
         <is>
-          <t>Aunque es el cliché del chico malo, sigo viéndolo de todas formas.</t>
+          <t>Ese protagonista es totalmente del tipo agradable y atractivo.</t>
         </is>
       </c>
       <c r="N714" s="16" t="inlineStr">
         <is>
-          <t>雖然是壞男人的老梗，還是會一直看下去。</t>
+          <t>那個男主角完全是暖男型。</t>
         </is>
       </c>
       <c r="O714" s="16" t="inlineStr">
         <is>
-          <t>虽然是坏男人的老梗，还是会一直看下去。</t>
+          <t>那个男主角完全是暖男型。</t>
         </is>
       </c>
       <c r="P714" s="16" t="inlineStr">
         <is>
-          <t>ワルの魅力系クリシェなのに、つい見ちゃう。</t>
+          <t>あの男主人公、完全に好青年タイプだよね。</t>
         </is>
       </c>
       <c r="Q714" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>K-drama casting talk</t>
         </is>
       </c>
       <c r="R714" s="15" t="inlineStr">
@@ -70005,17 +70005,17 @@
     <row r="715" ht="46" customHeight="1">
       <c r="A715" s="15" t="inlineStr">
         <is>
-          <t>DAT-022</t>
+          <t>DAT-020</t>
         </is>
       </c>
       <c r="B715" s="15" t="inlineStr">
         <is>
-          <t>소개팅</t>
+          <t>훈녀</t>
         </is>
       </c>
       <c r="C715" s="15" t="inlineStr">
         <is>
-          <t>so-gae-ting</t>
+          <t>hun-nyeo</t>
         </is>
       </c>
       <c r="D715" s="15" t="inlineStr">
@@ -70030,62 +70030,62 @@
       </c>
       <c r="F715" s="16" t="inlineStr">
         <is>
-          <t>A blind date, typically set up by a mutual friend.</t>
+          <t>The female equivalent of 훈남 — warm, approachable, and good-looking.</t>
         </is>
       </c>
       <c r="G715" s="16" t="inlineStr">
         <is>
-          <t>Una cita a ciegas, generalmente organizada por un amigo en común.</t>
+          <t>El equivalente femenino de 훈남: cálida, cercana y atractiva.</t>
         </is>
       </c>
       <c r="H715" s="16" t="inlineStr">
         <is>
-          <t>通常由共同朋友安排的相親約會。</t>
+          <t>훈남的女性版本——溫暖、親切又好看的女性。</t>
         </is>
       </c>
       <c r="I715" s="16" t="inlineStr">
         <is>
-          <t>通常由共同朋友安排的相亲约会。</t>
+          <t>훈남的女性版本——温暖、亲切又好看的女性。</t>
         </is>
       </c>
       <c r="J715" s="16" t="inlineStr">
         <is>
-          <t>友人が仲介する、一対一の紹介デート。</t>
+          <t>훈남の女性版——温かく、親しみやすくて、見た目の良い女性。</t>
         </is>
       </c>
       <c r="K715" s="16" t="inlineStr">
         <is>
-          <t>친구가 소개팅 시켜준대.</t>
+          <t>그 여배우는 훈녀 이미지로 유명해.</t>
         </is>
       </c>
       <c r="L715" s="16" t="inlineStr">
         <is>
-          <t>My friend is setting me up on a blind date.</t>
+          <t>That actress is known for her wholesome good-looking image.</t>
         </is>
       </c>
       <c r="M715" s="16" t="inlineStr">
         <is>
-          <t>Mi amiga me va a organizar una cita a ciegas.</t>
+          <t>Esa actriz es conocida por su imagen cálida y atractiva.</t>
         </is>
       </c>
       <c r="N715" s="16" t="inlineStr">
         <is>
-          <t>朋友要幫我安排相親。</t>
+          <t>那位女演員以暖女形象聞名。</t>
         </is>
       </c>
       <c r="O715" s="16" t="inlineStr">
         <is>
-          <t>朋友要帮我安排相亲。</t>
+          <t>那位女演员以暖女形象闻名。</t>
         </is>
       </c>
       <c r="P715" s="16" t="inlineStr">
         <is>
-          <t>友達が紹介デートセッティングしてくれるって。</t>
+          <t>あの女優、好感度高い美人イメージで有名。</t>
         </is>
       </c>
       <c r="Q715" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>K-drama casting talk</t>
         </is>
       </c>
       <c r="R715" s="15" t="inlineStr">
@@ -70102,17 +70102,17 @@
     <row r="716" ht="46" customHeight="1">
       <c r="A716" s="15" t="inlineStr">
         <is>
-          <t>DAT-023</t>
+          <t>DAT-021</t>
         </is>
       </c>
       <c r="B716" s="15" t="inlineStr">
         <is>
-          <t>모솔</t>
+          <t>나쁜남자</t>
         </is>
       </c>
       <c r="C716" s="15" t="inlineStr">
         <is>
-          <t>mo-sol</t>
+          <t>na-ppeun-nam-ja</t>
         </is>
       </c>
       <c r="D716" s="15" t="inlineStr">
@@ -70127,62 +70127,62 @@
       </c>
       <c r="F716" s="16" t="inlineStr">
         <is>
-          <t>Short for "solo since birth" — someone who has never dated anyone.</t>
+          <t>The "bad boy" trope — a cold, dangerous-seeming male lead who softens for the heroine.</t>
         </is>
       </c>
       <c r="G716" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "soltero de nacimiento": alguien que nunca ha salido con nadie.</t>
+          <t>El arquetipo del "chico malo": un protagonista frío y de apariencia peligrosa que se enternece por la protagonista.</t>
         </is>
       </c>
       <c r="H716" s="16" t="inlineStr">
         <is>
-          <t>「從娘胎開始就單身」的簡稱——從來沒有交往過的人，母胎單身。</t>
+          <t>「壞男人」套路——外表冷酷、帶點危險氣息，卻在女主角面前逐漸軟化的男主角類型。</t>
         </is>
       </c>
       <c r="I716" s="16" t="inlineStr">
         <is>
-          <t>“从娘胎开始就单身”的简称——从来没有交往过的人，母胎单身。</t>
+          <t>“坏男人”套路——外表冷酷、带点危险气息，却在女主角面前逐渐软化的男主角类型。</t>
         </is>
       </c>
       <c r="J716" s="16" t="inlineStr">
         <is>
-          <t>「生まれてからずっとソロ」の略——今まで誰とも付き合ったことがない人。</t>
+          <t>「悪い男」トロープ——冷たくて危険に見えるが、ヒロインの前で心を開いていく男性主人公。</t>
         </is>
       </c>
       <c r="K716" s="16" t="inlineStr">
         <is>
-          <t>나 아직도 모솔이야.</t>
+          <t>나쁜남자 클리셰인데도 계속 보게 돼.</t>
         </is>
       </c>
       <c r="L716" s="16" t="inlineStr">
         <is>
-          <t>I'm still someone who's never dated.</t>
+          <t>Even though it's the bad-boy cliché, I keep watching anyway.</t>
         </is>
       </c>
       <c r="M716" s="16" t="inlineStr">
         <is>
-          <t>Todavía soy alguien que nunca ha salido con nadie.</t>
+          <t>Aunque es el cliché del chico malo, sigo viéndolo de todas formas.</t>
         </is>
       </c>
       <c r="N716" s="16" t="inlineStr">
         <is>
-          <t>我還是母胎單身。</t>
+          <t>雖然是壞男人的老梗，還是會一直看下去。</t>
         </is>
       </c>
       <c r="O716" s="16" t="inlineStr">
         <is>
-          <t>我还是母胎单身。</t>
+          <t>虽然是坏男人的老梗，还是会一直看下去。</t>
         </is>
       </c>
       <c r="P716" s="16" t="inlineStr">
         <is>
-          <t>私はまだ恋愛経験ゼロだよ。</t>
+          <t>ワルの魅力系クリシェなのに、つい見ちゃう。</t>
         </is>
       </c>
       <c r="Q716" s="16" t="inlineStr">
         <is>
-          <t>Casual self-description</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R716" s="15" t="inlineStr">
@@ -70199,17 +70199,17 @@
     <row r="717" ht="46" customHeight="1">
       <c r="A717" s="15" t="inlineStr">
         <is>
-          <t>DAT-024</t>
+          <t>DAT-022</t>
         </is>
       </c>
       <c r="B717" s="15" t="inlineStr">
         <is>
-          <t>자만추</t>
+          <t>소개팅</t>
         </is>
       </c>
       <c r="C717" s="15" t="inlineStr">
         <is>
-          <t>ja-man-chu</t>
+          <t>so-gae-ting</t>
         </is>
       </c>
       <c r="D717" s="15" t="inlineStr">
@@ -70224,57 +70224,57 @@
       </c>
       <c r="F717" s="16" t="inlineStr">
         <is>
-          <t>Short for "seeking a natural meeting" — wanting to meet a partner organically rather than through a setup.</t>
+          <t>A blind date, typically set up by a mutual friend.</t>
         </is>
       </c>
       <c r="G717" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "buscar un encuentro natural": querer conocer a una pareja de forma orgánica en lugar de por una cita arreglada.</t>
+          <t>Una cita a ciegas, generalmente organizada por un amigo en común.</t>
         </is>
       </c>
       <c r="H717" s="16" t="inlineStr">
         <is>
-          <t>「追求自然相遇」的簡稱——希望自然而然認識對象，而非透過相親介紹。</t>
+          <t>通常由共同朋友安排的相親約會。</t>
         </is>
       </c>
       <c r="I717" s="16" t="inlineStr">
         <is>
-          <t>“追求自然相遇”的简称——希望自然而然认识对象，而非通过相亲介绍。</t>
+          <t>通常由共同朋友安排的相亲约会。</t>
         </is>
       </c>
       <c r="J717" s="16" t="inlineStr">
         <is>
-          <t>「自然な出会いを求める」の略——紹介ではなく、自然に相手と出会いたいという願望。</t>
+          <t>友人が仲介する、一対一の紹介デート。</t>
         </is>
       </c>
       <c r="K717" s="16" t="inlineStr">
         <is>
-          <t>나는 자만추 스타일이라 소개팅은 안 해.</t>
+          <t>친구가 소개팅 시켜준대.</t>
         </is>
       </c>
       <c r="L717" s="16" t="inlineStr">
         <is>
-          <t>I'm the natural-encounter type, so I don't do blind dates.</t>
+          <t>My friend is setting me up on a blind date.</t>
         </is>
       </c>
       <c r="M717" s="16" t="inlineStr">
         <is>
-          <t>Soy del tipo que prefiere encuentros naturales, así que no hago citas a ciegas.</t>
+          <t>Mi amiga me va a organizar una cita a ciegas.</t>
         </is>
       </c>
       <c r="N717" s="16" t="inlineStr">
         <is>
-          <t>我是喜歡自然認識的類型，不太相親。</t>
+          <t>朋友要幫我安排相親。</t>
         </is>
       </c>
       <c r="O717" s="16" t="inlineStr">
         <is>
-          <t>我是喜欢自然认识的类型，不太相亲。</t>
+          <t>朋友要帮我安排相亲。</t>
         </is>
       </c>
       <c r="P717" s="16" t="inlineStr">
         <is>
-          <t>私は自然な出会い派だから、合コンはしない。</t>
+          <t>友達が紹介デートセッティングしてくれるって。</t>
         </is>
       </c>
       <c r="Q717" s="16" t="inlineStr">
@@ -70296,17 +70296,17 @@
     <row r="718" ht="46" customHeight="1">
       <c r="A718" s="15" t="inlineStr">
         <is>
-          <t>DAT-025</t>
+          <t>DAT-023</t>
         </is>
       </c>
       <c r="B718" s="15" t="inlineStr">
         <is>
-          <t>여사친</t>
+          <t>모솔</t>
         </is>
       </c>
       <c r="C718" s="15" t="inlineStr">
         <is>
-          <t>yeo-sa-chin</t>
+          <t>mo-sol</t>
         </is>
       </c>
       <c r="D718" s="15" t="inlineStr">
@@ -70321,62 +70321,62 @@
       </c>
       <c r="F718" s="16" t="inlineStr">
         <is>
-          <t>Short for "female friend" — used to clarify a woman is just a friend, not a romantic interest.</t>
+          <t>Short for "solo since birth" — someone who has never dated anyone.</t>
         </is>
       </c>
       <c r="G718" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "amiga mujer": se usa para aclarar que una mujer es solo una amiga, no un interés romántico.</t>
+          <t>Abreviatura de "soltero de nacimiento": alguien que nunca ha salido con nadie.</t>
         </is>
       </c>
       <c r="H718" s="16" t="inlineStr">
         <is>
-          <t>「女性朋友」的簡稱——用來澄清某位女性只是朋友、並非戀愛對象。</t>
+          <t>「從娘胎開始就單身」的簡稱——從來沒有交往過的人，母胎單身。</t>
         </is>
       </c>
       <c r="I718" s="16" t="inlineStr">
         <is>
-          <t>“女性朋友”的简称——用来澄清某位女性只是朋友、并非恋爱对象。</t>
+          <t>“从娘胎开始就单身”的简称——从来没有交往过的人，母胎单身。</t>
         </is>
       </c>
       <c r="J718" s="16" t="inlineStr">
         <is>
-          <t>「女性の友達」の略——恋愛対象ではなく、ただの友達であることを明確にする時に使う。</t>
+          <t>「生まれてからずっとソロ」の略——今まで誰とも付き合ったことがない人。</t>
         </is>
       </c>
       <c r="K718" s="16" t="inlineStr">
         <is>
-          <t>그냥 여사친이야, 오해하지 마.</t>
+          <t>나 아직도 모솔이야.</t>
         </is>
       </c>
       <c r="L718" s="16" t="inlineStr">
         <is>
-          <t>She's just a female friend, don't get the wrong idea.</t>
+          <t>I'm still someone who's never dated.</t>
         </is>
       </c>
       <c r="M718" s="16" t="inlineStr">
         <is>
-          <t>Es solo mi amiga, no te confundas.</t>
+          <t>Todavía soy alguien que nunca ha salido con nadie.</t>
         </is>
       </c>
       <c r="N718" s="16" t="inlineStr">
         <is>
-          <t>只是女性朋友而已，別誤會。</t>
+          <t>我還是母胎單身。</t>
         </is>
       </c>
       <c r="O718" s="16" t="inlineStr">
         <is>
-          <t>只是女性朋友而已，别误会。</t>
+          <t>我还是母胎单身。</t>
         </is>
       </c>
       <c r="P718" s="16" t="inlineStr">
         <is>
-          <t>ただの女友達だよ、誤解しないで。</t>
+          <t>私はまだ恋愛経験ゼロだよ。</t>
         </is>
       </c>
       <c r="Q718" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship clarifications</t>
+          <t>Casual self-description</t>
         </is>
       </c>
       <c r="R718" s="15" t="inlineStr">
@@ -70393,17 +70393,17 @@
     <row r="719" ht="46" customHeight="1">
       <c r="A719" s="15" t="inlineStr">
         <is>
-          <t>DAT-026</t>
+          <t>DAT-024</t>
         </is>
       </c>
       <c r="B719" s="15" t="inlineStr">
         <is>
-          <t>남사친</t>
+          <t>자만추</t>
         </is>
       </c>
       <c r="C719" s="15" t="inlineStr">
         <is>
-          <t>nam-sa-chin</t>
+          <t>ja-man-chu</t>
         </is>
       </c>
       <c r="D719" s="15" t="inlineStr">
@@ -70418,62 +70418,62 @@
       </c>
       <c r="F719" s="16" t="inlineStr">
         <is>
-          <t>Short for "male friend" — used to clarify a man is just a friend, not a romantic interest.</t>
+          <t>Short for "seeking a natural meeting" — wanting to meet a partner organically rather than through a setup.</t>
         </is>
       </c>
       <c r="G719" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "amigo hombre": se usa para aclarar que un hombre es solo un amigo, no un interés romántico.</t>
+          <t>Abreviatura de "buscar un encuentro natural": querer conocer a una pareja de forma orgánica en lugar de por una cita arreglada.</t>
         </is>
       </c>
       <c r="H719" s="16" t="inlineStr">
         <is>
-          <t>「男性朋友」的簡稱——用來澄清某位男性只是朋友、並非戀愛對象。</t>
+          <t>「追求自然相遇」的簡稱——希望自然而然認識對象，而非透過相親介紹。</t>
         </is>
       </c>
       <c r="I719" s="16" t="inlineStr">
         <is>
-          <t>“男性朋友”的简称——用来澄清某位男性只是朋友、并非恋爱对象。</t>
+          <t>“追求自然相遇”的简称——希望自然而然认识对象，而非通过相亲介绍。</t>
         </is>
       </c>
       <c r="J719" s="16" t="inlineStr">
         <is>
-          <t>「男性の友達」の略——恋愛対象ではなく、ただの友達であることを明確にする時に使う。</t>
+          <t>「自然な出会いを求める」の略——紹介ではなく、自然に相手と出会いたいという願望。</t>
         </is>
       </c>
       <c r="K719" s="16" t="inlineStr">
         <is>
-          <t>남사친이랑 영화 보러 갔어.</t>
+          <t>나는 자만추 스타일이라 소개팅은 안 해.</t>
         </is>
       </c>
       <c r="L719" s="16" t="inlineStr">
         <is>
-          <t>I went to see a movie with my guy friend.</t>
+          <t>I'm the natural-encounter type, so I don't do blind dates.</t>
         </is>
       </c>
       <c r="M719" s="16" t="inlineStr">
         <is>
-          <t>Fui al cine con mi amigo (no es nada romántico).</t>
+          <t>Soy del tipo que prefiere encuentros naturales, así que no hago citas a ciegas.</t>
         </is>
       </c>
       <c r="N719" s="16" t="inlineStr">
         <is>
-          <t>跟男性朋友去看電影了。</t>
+          <t>我是喜歡自然認識的類型，不太相親。</t>
         </is>
       </c>
       <c r="O719" s="16" t="inlineStr">
         <is>
-          <t>跟男性朋友去看电影了。</t>
+          <t>我是喜欢自然认识的类型，不太相亲。</t>
         </is>
       </c>
       <c r="P719" s="16" t="inlineStr">
         <is>
-          <t>男友達と映画見に行った。</t>
+          <t>私は自然な出会い派だから、合コンはしない。</t>
         </is>
       </c>
       <c r="Q719" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship clarifications</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R719" s="15" t="inlineStr">
@@ -70490,17 +70490,17 @@
     <row r="720" ht="46" customHeight="1">
       <c r="A720" s="15" t="inlineStr">
         <is>
-          <t>DAT-027</t>
+          <t>DAT-025</t>
         </is>
       </c>
       <c r="B720" s="15" t="inlineStr">
         <is>
-          <t>애칭</t>
+          <t>여사친</t>
         </is>
       </c>
       <c r="C720" s="15" t="inlineStr">
         <is>
-          <t>ae-ching</t>
+          <t>yeo-sa-chin</t>
         </is>
       </c>
       <c r="D720" s="15" t="inlineStr">
@@ -70515,62 +70515,62 @@
       </c>
       <c r="F720" s="16" t="inlineStr">
         <is>
-          <t>A cute nickname used between romantic partners.</t>
+          <t>Short for "female friend" — used to clarify a woman is just a friend, not a romantic interest.</t>
         </is>
       </c>
       <c r="G720" s="16" t="inlineStr">
         <is>
-          <t>Un apodo tierno usado entre parejas románticas.</t>
+          <t>Abreviatura de "amiga mujer": se usa para aclarar que una mujer es solo una amiga, no un interés romántico.</t>
         </is>
       </c>
       <c r="H720" s="16" t="inlineStr">
         <is>
-          <t>情侶之間使用的可愛暱稱。</t>
+          <t>「女性朋友」的簡稱——用來澄清某位女性只是朋友、並非戀愛對象。</t>
         </is>
       </c>
       <c r="I720" s="16" t="inlineStr">
         <is>
-          <t>情侣之间使用的可爱暱称。</t>
+          <t>“女性朋友”的简称——用来澄清某位女性只是朋友、并非恋爱对象。</t>
         </is>
       </c>
       <c r="J720" s="16" t="inlineStr">
         <is>
-          <t>恋人同士で使う可愛いニックネーム。</t>
+          <t>「女性の友達」の略——恋愛対象ではなく、ただの友達であることを明確にする時に使う。</t>
         </is>
       </c>
       <c r="K720" s="16" t="inlineStr">
         <is>
-          <t>둘이 애칭까지 있는 거 보니 진짜 사귀나 봐.</t>
+          <t>그냥 여사친이야, 오해하지 마.</t>
         </is>
       </c>
       <c r="L720" s="16" t="inlineStr">
         <is>
-          <t>Seeing they even have pet names for each other, they must really be dating.</t>
+          <t>She's just a female friend, don't get the wrong idea.</t>
         </is>
       </c>
       <c r="M720" s="16" t="inlineStr">
         <is>
-          <t>Al ver que tienen apodos cariñosos entre ellos, seguro que sí están saliendo.</t>
+          <t>Es solo mi amiga, no te confundas.</t>
         </is>
       </c>
       <c r="N720" s="16" t="inlineStr">
         <is>
-          <t>看到兩個人連暱稱都有了，看來真的在交往。</t>
+          <t>只是女性朋友而已，別誤會。</t>
         </is>
       </c>
       <c r="O720" s="16" t="inlineStr">
         <is>
-          <t>看到两个人连暱称都有了，看来真的在交往。</t>
+          <t>只是女性朋友而已，别误会。</t>
         </is>
       </c>
       <c r="P720" s="16" t="inlineStr">
         <is>
-          <t>二人とも愛称まであるなんて、本当に付き合ってるみたいだね。</t>
+          <t>ただの女友達だよ、誤解しないで。</t>
         </is>
       </c>
       <c r="Q720" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, dramas</t>
+          <t>Casual relationship clarifications</t>
         </is>
       </c>
       <c r="R720" s="15" t="inlineStr">
@@ -70587,17 +70587,17 @@
     <row r="721" ht="46" customHeight="1">
       <c r="A721" s="15" t="inlineStr">
         <is>
-          <t>DAT-028</t>
+          <t>DAT-026</t>
         </is>
       </c>
       <c r="B721" s="15" t="inlineStr">
         <is>
-          <t>럽스타그램</t>
+          <t>남사친</t>
         </is>
       </c>
       <c r="C721" s="15" t="inlineStr">
         <is>
-          <t>leob-seu-ta-geu-raem</t>
+          <t>nam-sa-chin</t>
         </is>
       </c>
       <c r="D721" s="15" t="inlineStr">
@@ -70612,62 +70612,62 @@
       </c>
       <c r="F721" s="16" t="inlineStr">
         <is>
-          <t>"Love + Instagram" — social media posts where a couple shows off their relationship.</t>
+          <t>Short for "male friend" — used to clarify a man is just a friend, not a romantic interest.</t>
         </is>
       </c>
       <c r="G721" s="16" t="inlineStr">
         <is>
-          <t>"Amor + Instagram": publicaciones en redes sociales donde una pareja muestra su relación.</t>
+          <t>Abreviatura de "amigo hombre": se usa para aclarar que un hombre es solo un amigo, no un interés romántico.</t>
         </is>
       </c>
       <c r="H721" s="16" t="inlineStr">
         <is>
-          <t>「愛情＋Instagram」——情侶在社群媒體上曬恩愛的貼文。</t>
+          <t>「男性朋友」的簡稱——用來澄清某位男性只是朋友、並非戀愛對象。</t>
         </is>
       </c>
       <c r="I721" s="16" t="inlineStr">
         <is>
-          <t>“爱情＋Instagram”——情侣在社群媒体上晒恩爱的贴文。</t>
+          <t>“男性朋友”的简称——用来澄清某位男性只是朋友、并非恋爱对象。</t>
         </is>
       </c>
       <c r="J721" s="16" t="inlineStr">
         <is>
-          <t>「愛＋Instagram」——カップルが交際をアピールするSNS投稿。</t>
+          <t>「男性の友達」の略——恋愛対象ではなく、ただの友達であることを明確にする時に使う。</t>
         </is>
       </c>
       <c r="K721" s="16" t="inlineStr">
         <is>
-          <t>럽스타그램 보니까 진짜 좋아 보인다.</t>
+          <t>남사친이랑 영화 보러 갔어.</t>
         </is>
       </c>
       <c r="L721" s="16" t="inlineStr">
         <is>
-          <t>Seeing their couple posts, they really look happy together.</t>
+          <t>I went to see a movie with my guy friend.</t>
         </is>
       </c>
       <c r="M721" s="16" t="inlineStr">
         <is>
-          <t>Al ver sus publicaciones de pareja, de verdad se ven felices juntos.</t>
+          <t>Fui al cine con mi amigo (no es nada romántico).</t>
         </is>
       </c>
       <c r="N721" s="16" t="inlineStr">
         <is>
-          <t>看他們曬恩愛，感覺真的很幸福。</t>
+          <t>跟男性朋友去看電影了。</t>
         </is>
       </c>
       <c r="O721" s="16" t="inlineStr">
         <is>
-          <t>看他们晒恩爱，感觉真的很幸福。</t>
+          <t>跟男性朋友去看电影了。</t>
         </is>
       </c>
       <c r="P721" s="16" t="inlineStr">
         <is>
-          <t>ラブグラム見てたら、本当に幸せそうだった。</t>
+          <t>男友達と映画見に行った。</t>
         </is>
       </c>
       <c r="Q721" s="16" t="inlineStr">
         <is>
-          <t>Instagram couple culture</t>
+          <t>Casual relationship clarifications</t>
         </is>
       </c>
       <c r="R721" s="15" t="inlineStr">
@@ -70684,17 +70684,17 @@
     <row r="722" ht="46" customHeight="1">
       <c r="A722" s="15" t="inlineStr">
         <is>
-          <t>DAT-029</t>
+          <t>DAT-027</t>
         </is>
       </c>
       <c r="B722" s="15" t="inlineStr">
         <is>
-          <t>캔디</t>
+          <t>애칭</t>
         </is>
       </c>
       <c r="C722" s="15" t="inlineStr">
         <is>
-          <t>kaen-di</t>
+          <t>ae-ching</t>
         </is>
       </c>
       <c r="D722" s="15" t="inlineStr">
@@ -70709,62 +70709,62 @@
       </c>
       <c r="F722" s="16" t="inlineStr">
         <is>
-          <t>A plucky, resilient, kind female lead trope who stays positive despite hardship, named after the classic character Candy Candy.</t>
+          <t>A cute nickname used between romantic partners.</t>
         </is>
       </c>
       <c r="G722" s="16" t="inlineStr">
         <is>
-          <t>Un arquetipo de protagonista femenina animosa, resiliente y bondadosa que se mantiene positiva a pesar de las dificultades, en honor al clásico personaje Candy Candy.</t>
+          <t>Un apodo tierno usado entre parejas románticas.</t>
         </is>
       </c>
       <c r="H722" s="16" t="inlineStr">
         <is>
-          <t>堅強樂觀、即使歷經困境仍保持正向的女主角類型，源自經典角色《小甜甜》。</t>
+          <t>情侶之間使用的可愛暱稱。</t>
         </is>
       </c>
       <c r="I722" s="16" t="inlineStr">
         <is>
-          <t>坚强乐观、即使历经困境仍保持正向的女主角类型，源自经典角色《小甜甜》。</t>
+          <t>情侣之间使用的可爱暱称。</t>
         </is>
       </c>
       <c r="J722" s="16" t="inlineStr">
         <is>
-          <t>逆境にもめげず前向きな、芯の強いヒロインのトロープ——古典キャラクター「キャンディキャンディ」に由来。</t>
+          <t>恋人同士で使う可愛いニックネーム。</t>
         </is>
       </c>
       <c r="K722" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 여주 완전 캔디형이야.</t>
+          <t>둘이 애칭까지 있는 거 보니 진짜 사귀나 봐.</t>
         </is>
       </c>
       <c r="L722" s="16" t="inlineStr">
         <is>
-          <t>This drama's female lead is a total Candy-type heroine.</t>
+          <t>Seeing they even have pet names for each other, they must really be dating.</t>
         </is>
       </c>
       <c r="M722" s="16" t="inlineStr">
         <is>
-          <t>La protagonista de este drama es totalmente del tipo Candy.</t>
+          <t>Al ver que tienen apodos cariñosos entre ellos, seguro que sí están saliendo.</t>
         </is>
       </c>
       <c r="N722" s="16" t="inlineStr">
         <is>
-          <t>這部劇女主角完全是小甜甜類型。</t>
+          <t>看到兩個人連暱稱都有了，看來真的在交往。</t>
         </is>
       </c>
       <c r="O722" s="16" t="inlineStr">
         <is>
-          <t>这部剧女主角完全是小甜甜类型。</t>
+          <t>看到两个人连暱称都有了，看来真的在交往。</t>
         </is>
       </c>
       <c r="P722" s="16" t="inlineStr">
         <is>
-          <t>このドラマのヒロイン、完全にキャンディ型だよね。</t>
+          <t>二人とも愛称まであるなんて、本当に付き合ってるみたいだね。</t>
         </is>
       </c>
       <c r="Q722" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>Couple culture, dramas</t>
         </is>
       </c>
       <c r="R722" s="15" t="inlineStr">
@@ -70781,17 +70781,17 @@
     <row r="723" ht="46" customHeight="1">
       <c r="A723" s="15" t="inlineStr">
         <is>
-          <t>DAT-030</t>
+          <t>DAT-028</t>
         </is>
       </c>
       <c r="B723" s="15" t="inlineStr">
         <is>
-          <t>출생의 비밀</t>
+          <t>럽스타그램</t>
         </is>
       </c>
       <c r="C723" s="15" t="inlineStr">
         <is>
-          <t>chul-saeng-ui bi-mil</t>
+          <t>leob-seu-ta-geu-raem</t>
         </is>
       </c>
       <c r="D723" s="15" t="inlineStr">
@@ -70806,62 +70806,62 @@
       </c>
       <c r="F723" s="16" t="inlineStr">
         <is>
-          <t>A classic K-drama plot device where a character's true parentage or origin is secretly hidden and later revealed.</t>
+          <t>"Love + Instagram" — social media posts where a couple shows off their relationship.</t>
         </is>
       </c>
       <c r="G723" s="16" t="inlineStr">
         <is>
-          <t>Un clásico recurso argumental de los K-dramas donde el verdadero origen o parentesco de un personaje se oculta en secreto y se revela después.</t>
+          <t>"Amor + Instagram": publicaciones en redes sociales donde una pareja muestra su relación.</t>
         </is>
       </c>
       <c r="H723" s="16" t="inlineStr">
         <is>
-          <t>韓劇經典劇情套路——角色真實身世或血緣被隱藏、後來才揭曉的設定，出生之謎。</t>
+          <t>「愛情＋Instagram」——情侶在社群媒體上曬恩愛的貼文。</t>
         </is>
       </c>
       <c r="I723" s="16" t="inlineStr">
         <is>
-          <t>韩剧经典剧情套路——角色真实身世或血缘被隐藏、后来才揭晓的设置，出生之谜。</t>
+          <t>“爱情＋Instagram”——情侣在社群媒体上晒恩爱的贴文。</t>
         </is>
       </c>
       <c r="J723" s="16" t="inlineStr">
         <is>
-          <t>韓国ドラマの定番展開で、キャラクターの本当の親や出自が隠されていて、後で明かされるというもの。</t>
+          <t>「愛＋Instagram」——カップルが交際をアピールするSNS投稿。</t>
         </is>
       </c>
       <c r="K723" s="16" t="inlineStr">
         <is>
-          <t>이 드라마도 결국 출생의 비밀이 나왔어.</t>
+          <t>럽스타그램 보니까 진짜 좋아 보인다.</t>
         </is>
       </c>
       <c r="L723" s="16" t="inlineStr">
         <is>
-          <t>This drama ended up having a secret-birth twist too.</t>
+          <t>Seeing their couple posts, they really look happy together.</t>
         </is>
       </c>
       <c r="M723" s="16" t="inlineStr">
         <is>
-          <t>Este drama también terminó teniendo el giro del secreto de nacimiento.</t>
+          <t>Al ver sus publicaciones de pareja, de verdad se ven felices juntos.</t>
         </is>
       </c>
       <c r="N723" s="16" t="inlineStr">
         <is>
-          <t>這部劇最後也出現了出生之謎的劇情。</t>
+          <t>看他們曬恩愛，感覺真的很幸福。</t>
         </is>
       </c>
       <c r="O723" s="16" t="inlineStr">
         <is>
-          <t>这部剧最后也出现了出生之谜的剧情。</t>
+          <t>看他们晒恩爱，感觉真的很幸福。</t>
         </is>
       </c>
       <c r="P723" s="16" t="inlineStr">
         <is>
-          <t>このドラマも結局出生の秘密が出てきた。</t>
+          <t>ラブグラム見てたら、本当に幸せそうだった。</t>
         </is>
       </c>
       <c r="Q723" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>Instagram couple culture</t>
         </is>
       </c>
       <c r="R723" s="15" t="inlineStr">
@@ -70878,17 +70878,17 @@
     <row r="724" ht="46" customHeight="1">
       <c r="A724" s="15" t="inlineStr">
         <is>
-          <t>DAT-031</t>
+          <t>DAT-029</t>
         </is>
       </c>
       <c r="B724" s="15" t="inlineStr">
         <is>
-          <t>고부갈등</t>
+          <t>캔디</t>
         </is>
       </c>
       <c r="C724" s="15" t="inlineStr">
         <is>
-          <t>go-bu-gal-deung</t>
+          <t>kaen-di</t>
         </is>
       </c>
       <c r="D724" s="15" t="inlineStr">
@@ -70903,57 +70903,57 @@
       </c>
       <c r="F724" s="16" t="inlineStr">
         <is>
-          <t>Tension and conflict between a wife and her mother-in-law, a very common drama theme.</t>
+          <t>A plucky, resilient, kind female lead trope who stays positive despite hardship, named after the classic character Candy Candy.</t>
         </is>
       </c>
       <c r="G724" s="16" t="inlineStr">
         <is>
-          <t>Tensión y conflicto entre una esposa y su suegra, un tema muy común en los dramas.</t>
+          <t>Un arquetipo de protagonista femenina animosa, resiliente y bondadosa que se mantiene positiva a pesar de las dificultades, en honor al clásico personaje Candy Candy.</t>
         </is>
       </c>
       <c r="H724" s="16" t="inlineStr">
         <is>
-          <t>妻子與婆婆之間的緊張與衝突，是韓劇非常常見的題材，婆媳問題。</t>
+          <t>堅強樂觀、即使歷經困境仍保持正向的女主角類型，源自經典角色《小甜甜》。</t>
         </is>
       </c>
       <c r="I724" s="16" t="inlineStr">
         <is>
-          <t>妻子与婆婆之间的紧张与冲突，是韩剧非常常见的题材，婆媳问题。</t>
+          <t>坚强乐观、即使历经困境仍保持正向的女主角类型，源自经典角色《小甜甜》。</t>
         </is>
       </c>
       <c r="J724" s="16" t="inlineStr">
         <is>
-          <t>妻と姑の間の緊張と対立——ドラマの非常によくあるテーマ。</t>
+          <t>逆境にもめげず前向きな、芯の強いヒロインのトロープ——古典キャラクター「キャンディキャンディ」に由来。</t>
         </is>
       </c>
       <c r="K724" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 고부갈등이 너무 스트레스야.</t>
+          <t>이 드라마 여주 완전 캔디형이야.</t>
         </is>
       </c>
       <c r="L724" s="16" t="inlineStr">
         <is>
-          <t>This drama's mother-in-law conflict is so stressful to watch.</t>
+          <t>This drama's female lead is a total Candy-type heroine.</t>
         </is>
       </c>
       <c r="M724" s="16" t="inlineStr">
         <is>
-          <t>El conflicto con la suegra en este drama da mucho estrés de ver.</t>
+          <t>La protagonista de este drama es totalmente del tipo Candy.</t>
         </is>
       </c>
       <c r="N724" s="16" t="inlineStr">
         <is>
-          <t>這部劇的婆媳問題看得好有壓力。</t>
+          <t>這部劇女主角完全是小甜甜類型。</t>
         </is>
       </c>
       <c r="O724" s="16" t="inlineStr">
         <is>
-          <t>这部剧的婆媳问题看得好有压力。</t>
+          <t>这部剧女主角完全是小甜甜类型。</t>
         </is>
       </c>
       <c r="P724" s="16" t="inlineStr">
         <is>
-          <t>このドラマの嫁姑問題、見てて本当にストレス溜まる。</t>
+          <t>このドラマのヒロイン、完全にキャンディ型だよね。</t>
         </is>
       </c>
       <c r="Q724" s="16" t="inlineStr">
@@ -70975,17 +70975,17 @@
     <row r="725" ht="46" customHeight="1">
       <c r="A725" s="15" t="inlineStr">
         <is>
-          <t>DAT-032</t>
+          <t>DAT-030</t>
         </is>
       </c>
       <c r="B725" s="15" t="inlineStr">
         <is>
-          <t>삼각관계</t>
+          <t>출생의 비밀</t>
         </is>
       </c>
       <c r="C725" s="15" t="inlineStr">
         <is>
-          <t>sam-gak-gwan-gye</t>
+          <t>chul-saeng-ui bi-mil</t>
         </is>
       </c>
       <c r="D725" s="15" t="inlineStr">
@@ -71000,57 +71000,57 @@
       </c>
       <c r="F725" s="16" t="inlineStr">
         <is>
-          <t>A romantic storyline involving three people with overlapping feelings for each other.</t>
+          <t>A classic K-drama plot device where a character's true parentage or origin is secretly hidden and later revealed.</t>
         </is>
       </c>
       <c r="G725" s="16" t="inlineStr">
         <is>
-          <t>Una trama romántica que involucra a tres personas con sentimientos cruzados entre ellas.</t>
+          <t>Un clásico recurso argumental de los K-dramas donde el verdadero origen o parentesco de un personaje se oculta en secreto y se revela después.</t>
         </is>
       </c>
       <c r="H725" s="16" t="inlineStr">
         <is>
-          <t>三個人之間互有情愫、糾葛交織的戀愛劇情，三角關係。</t>
+          <t>韓劇經典劇情套路——角色真實身世或血緣被隱藏、後來才揭曉的設定，出生之謎。</t>
         </is>
       </c>
       <c r="I725" s="16" t="inlineStr">
         <is>
-          <t>三个人之间互有情愫、纠葛交织的恋爱剧情，三角关系。</t>
+          <t>韩剧经典剧情套路——角色真实身世或血缘被隐藏、后来才揭晓的设置，出生之谜。</t>
         </is>
       </c>
       <c r="J725" s="16" t="inlineStr">
         <is>
-          <t>三人が互いに感情を抱き合う恋愛ストーリーライン。</t>
+          <t>韓国ドラマの定番展開で、キャラクターの本当の親や出自が隠されていて、後で明かされるというもの。</t>
         </is>
       </c>
       <c r="K725" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 삼각관계 너무 답답해.</t>
+          <t>이 드라마도 결국 출생의 비밀이 나왔어.</t>
         </is>
       </c>
       <c r="L725" s="16" t="inlineStr">
         <is>
-          <t>This drama's love triangle is so frustrating.</t>
+          <t>This drama ended up having a secret-birth twist too.</t>
         </is>
       </c>
       <c r="M725" s="16" t="inlineStr">
         <is>
-          <t>El triángulo amoroso de este drama es muy frustrante.</t>
+          <t>Este drama también terminó teniendo el giro del secreto de nacimiento.</t>
         </is>
       </c>
       <c r="N725" s="16" t="inlineStr">
         <is>
-          <t>這部劇的三角關係讓人好鬱悶。</t>
+          <t>這部劇最後也出現了出生之謎的劇情。</t>
         </is>
       </c>
       <c r="O725" s="16" t="inlineStr">
         <is>
-          <t>这部剧的三角关系让人好郁闷。</t>
+          <t>这部剧最后也出现了出生之谜的剧情。</t>
         </is>
       </c>
       <c r="P725" s="16" t="inlineStr">
         <is>
-          <t>このドラマの三角関係、本当にもどかしい。</t>
+          <t>このドラマも結局出生の秘密が出てきた。</t>
         </is>
       </c>
       <c r="Q725" s="16" t="inlineStr">
@@ -71072,17 +71072,17 @@
     <row r="726" ht="46" customHeight="1">
       <c r="A726" s="15" t="inlineStr">
         <is>
-          <t>DAT-033</t>
+          <t>DAT-031</t>
         </is>
       </c>
       <c r="B726" s="15" t="inlineStr">
         <is>
-          <t>시한부</t>
+          <t>고부갈등</t>
         </is>
       </c>
       <c r="C726" s="15" t="inlineStr">
         <is>
-          <t>si-han-bu</t>
+          <t>go-bu-gal-deung</t>
         </is>
       </c>
       <c r="D726" s="15" t="inlineStr">
@@ -71097,57 +71097,57 @@
       </c>
       <c r="F726" s="16" t="inlineStr">
         <is>
-          <t>A drama plot device where a character has a terminal illness, often driving the emotional storyline.</t>
+          <t>Tension and conflict between a wife and her mother-in-law, a very common drama theme.</t>
         </is>
       </c>
       <c r="G726" s="16" t="inlineStr">
         <is>
-          <t>Un recurso argumental donde un personaje tiene una enfermedad terminal, a menudo impulsando la trama emocional.</t>
+          <t>Tensión y conflicto entre una esposa y su suegra, un tema muy común en los dramas.</t>
         </is>
       </c>
       <c r="H726" s="16" t="inlineStr">
         <is>
-          <t>角色罹患絕症的劇情設定，常用來推動情感張力，絕症設定。</t>
+          <t>妻子與婆婆之間的緊張與衝突，是韓劇非常常見的題材，婆媳問題。</t>
         </is>
       </c>
       <c r="I726" s="16" t="inlineStr">
         <is>
-          <t>角色罹患绝症的剧情设置，常用来推动情感张力，绝症设置。</t>
+          <t>妻子与婆婆之间的紧张与冲突，是韩剧非常常见的题材，婆媳问题。</t>
         </is>
       </c>
       <c r="J726" s="16" t="inlineStr">
         <is>
-          <t>キャラクターが不治の病を患うドラマの設定で、感情的なストーリーラインを引っ張ることが多い。</t>
+          <t>妻と姑の間の緊張と対立——ドラマの非常によくあるテーマ。</t>
         </is>
       </c>
       <c r="K726" s="16" t="inlineStr">
         <is>
-          <t>시한부 설정인 거 알고 나서 더 슬프게 봤어.</t>
+          <t>이 드라마 고부갈등이 너무 스트레스야.</t>
         </is>
       </c>
       <c r="L726" s="16" t="inlineStr">
         <is>
-          <t>Once I found out about the terminal illness twist, I watched it even more sadly.</t>
+          <t>This drama's mother-in-law conflict is so stressful to watch.</t>
         </is>
       </c>
       <c r="M726" s="16" t="inlineStr">
         <is>
-          <t>Después de saber del giro de la enfermedad terminal, lo vi con más tristeza.</t>
+          <t>El conflicto con la suegra en este drama da mucho estrés de ver.</t>
         </is>
       </c>
       <c r="N726" s="16" t="inlineStr">
         <is>
-          <t>知道是絕症設定之後看得更難過了。</t>
+          <t>這部劇的婆媳問題看得好有壓力。</t>
         </is>
       </c>
       <c r="O726" s="16" t="inlineStr">
         <is>
-          <t>知道是绝症设置之后看得更难过了。</t>
+          <t>这部剧的婆媳问题看得好有压力。</t>
         </is>
       </c>
       <c r="P726" s="16" t="inlineStr">
         <is>
-          <t>余命宣告の設定だと知ってから、もっと悲しく見てしまった。</t>
+          <t>このドラマの嫁姑問題、見てて本当にストレス溜まる。</t>
         </is>
       </c>
       <c r="Q726" s="16" t="inlineStr">
@@ -71169,17 +71169,17 @@
     <row r="727" ht="46" customHeight="1">
       <c r="A727" s="15" t="inlineStr">
         <is>
-          <t>DAT-034</t>
+          <t>DAT-032</t>
         </is>
       </c>
       <c r="B727" s="15" t="inlineStr">
         <is>
-          <t>정략결혼</t>
+          <t>삼각관계</t>
         </is>
       </c>
       <c r="C727" s="15" t="inlineStr">
         <is>
-          <t>jeong-ryak-gyeol-hon</t>
+          <t>sam-gak-gwan-gye</t>
         </is>
       </c>
       <c r="D727" s="15" t="inlineStr">
@@ -71194,57 +71194,57 @@
       </c>
       <c r="F727" s="16" t="inlineStr">
         <is>
-          <t>A marriage arranged for business, family, or political reasons rather than love — a common drama setup.</t>
+          <t>A romantic storyline involving three people with overlapping feelings for each other.</t>
         </is>
       </c>
       <c r="G727" s="16" t="inlineStr">
         <is>
-          <t>Un matrimonio arreglado por razones de negocios, familia o política en lugar de amor; un montaje común en los dramas.</t>
+          <t>Una trama romántica que involucra a tres personas con sentimientos cruzados entre ellas.</t>
         </is>
       </c>
       <c r="H727" s="16" t="inlineStr">
         <is>
-          <t>因商業、家族或政治因素而非愛情所安排的婚姻，是韓劇常見的設定，利益聯姻。</t>
+          <t>三個人之間互有情愫、糾葛交織的戀愛劇情，三角關係。</t>
         </is>
       </c>
       <c r="I727" s="16" t="inlineStr">
         <is>
-          <t>因商业、家族或政治因素而非爱情所安排的婚姻，是韩剧常见的设置，利益联姻。</t>
+          <t>三个人之间互有情愫、纠葛交织的恋爱剧情，三角关系。</t>
         </is>
       </c>
       <c r="J727" s="16" t="inlineStr">
         <is>
-          <t>恋愛ではなく、ビジネスや家族、政治的な理由で決められた結婚——ドラマによくある設定。</t>
+          <t>三人が互いに感情を抱き合う恋愛ストーリーライン。</t>
         </is>
       </c>
       <c r="K727" s="16" t="inlineStr">
         <is>
-          <t>정략결혼으로 시작했는데 진짜 사랑에 빠졌어.</t>
+          <t>이 드라마 삼각관계 너무 답답해.</t>
         </is>
       </c>
       <c r="L727" s="16" t="inlineStr">
         <is>
-          <t>It started as an arranged marriage, but they really fell in love.</t>
+          <t>This drama's love triangle is so frustrating.</t>
         </is>
       </c>
       <c r="M727" s="16" t="inlineStr">
         <is>
-          <t>Empezó como un matrimonio arreglado, pero de verdad se enamoraron.</t>
+          <t>El triángulo amoroso de este drama es muy frustrante.</t>
         </is>
       </c>
       <c r="N727" s="16" t="inlineStr">
         <is>
-          <t>雖然是利益聯姻開始的，但真的墜入愛河了。</t>
+          <t>這部劇的三角關係讓人好鬱悶。</t>
         </is>
       </c>
       <c r="O727" s="16" t="inlineStr">
         <is>
-          <t>虽然是利益联姻开始的，但真的坠入爱河了。</t>
+          <t>这部剧的三角关系让人好郁闷。</t>
         </is>
       </c>
       <c r="P727" s="16" t="inlineStr">
         <is>
-          <t>政略結婚で始まったのに、本当に恋に落ちた。</t>
+          <t>このドラマの三角関係、本当にもどかしい。</t>
         </is>
       </c>
       <c r="Q727" s="16" t="inlineStr">
@@ -71266,17 +71266,17 @@
     <row r="728" ht="46" customHeight="1">
       <c r="A728" s="15" t="inlineStr">
         <is>
-          <t>DAT-035</t>
+          <t>DAT-033</t>
         </is>
       </c>
       <c r="B728" s="15" t="inlineStr">
         <is>
-          <t>신데렐라</t>
+          <t>시한부</t>
         </is>
       </c>
       <c r="C728" s="15" t="inlineStr">
         <is>
-          <t>sin-de-rel-la</t>
+          <t>si-han-bu</t>
         </is>
       </c>
       <c r="D728" s="15" t="inlineStr">
@@ -71291,57 +71291,57 @@
       </c>
       <c r="F728" s="16" t="inlineStr">
         <is>
-          <t>A story trope where an ordinary or poor character rises into a wealthy or elite world, often through romance.</t>
+          <t>A drama plot device where a character has a terminal illness, often driving the emotional storyline.</t>
         </is>
       </c>
       <c r="G728" s="16" t="inlineStr">
         <is>
-          <t>Un arquetipo narrativo donde un personaje común o pobre asciende a un mundo rico o de élite, a menudo a través del romance.</t>
+          <t>Un recurso argumental donde un personaje tiene una enfermedad terminal, a menudo impulsando la trama emocional.</t>
         </is>
       </c>
       <c r="H728" s="16" t="inlineStr">
         <is>
-          <t>平凡或貧窮的角色透過戀愛躍升進入富裕上流世界的劇情套路，灰姑娘故事。</t>
+          <t>角色罹患絕症的劇情設定，常用來推動情感張力，絕症設定。</t>
         </is>
       </c>
       <c r="I728" s="16" t="inlineStr">
         <is>
-          <t>平凡或贫穷的角色通过恋爱跃升进入富裕上流世界的剧情套路，灰姑娘故事。</t>
+          <t>角色罹患绝症的剧情设置，常用来推动情感张力，绝症设置。</t>
         </is>
       </c>
       <c r="J728" s="16" t="inlineStr">
         <is>
-          <t>平凡または貧しいキャラクターが、恋愛を通じて裕福またはエリートの世界に上り詰めるストーリートロープ。</t>
+          <t>キャラクターが不治の病を患うドラマの設定で、感情的なストーリーラインを引っ張ることが多い。</t>
         </is>
       </c>
       <c r="K728" s="16" t="inlineStr">
         <is>
-          <t>완전 신데렐라 스토리다.</t>
+          <t>시한부 설정인 거 알고 나서 더 슬프게 봤어.</t>
         </is>
       </c>
       <c r="L728" s="16" t="inlineStr">
         <is>
-          <t>It's a total Cinderella story.</t>
+          <t>Once I found out about the terminal illness twist, I watched it even more sadly.</t>
         </is>
       </c>
       <c r="M728" s="16" t="inlineStr">
         <is>
-          <t>Es una historia de Cenicienta total.</t>
+          <t>Después de saber del giro de la enfermedad terminal, lo vi con más tristeza.</t>
         </is>
       </c>
       <c r="N728" s="16" t="inlineStr">
         <is>
-          <t>完全是灰姑娘的故事。</t>
+          <t>知道是絕症設定之後看得更難過了。</t>
         </is>
       </c>
       <c r="O728" s="16" t="inlineStr">
         <is>
-          <t>完全是灰姑娘的故事。</t>
+          <t>知道是绝症设置之后看得更难过了。</t>
         </is>
       </c>
       <c r="P728" s="16" t="inlineStr">
         <is>
-          <t>完全にシンデレラストーリーだね。</t>
+          <t>余命宣告の設定だと知ってから、もっと悲しく見てしまった。</t>
         </is>
       </c>
       <c r="Q728" s="16" t="inlineStr">
@@ -71363,17 +71363,17 @@
     <row r="729" ht="46" customHeight="1">
       <c r="A729" s="15" t="inlineStr">
         <is>
-          <t>DAT-036</t>
+          <t>DAT-034</t>
         </is>
       </c>
       <c r="B729" s="15" t="inlineStr">
         <is>
-          <t>소울메이트</t>
+          <t>정략결혼</t>
         </is>
       </c>
       <c r="C729" s="15" t="inlineStr">
         <is>
-          <t>so-ul-me-i-teu</t>
+          <t>jeong-ryak-gyeol-hon</t>
         </is>
       </c>
       <c r="D729" s="15" t="inlineStr">
@@ -71388,62 +71388,62 @@
       </c>
       <c r="F729" s="16" t="inlineStr">
         <is>
-          <t>A person who feels like a perfect emotional match, a soulmate.</t>
+          <t>A marriage arranged for business, family, or political reasons rather than love — a common drama setup.</t>
         </is>
       </c>
       <c r="G729" s="16" t="inlineStr">
         <is>
-          <t>Una persona que se siente como una pareja emocional perfecta, un alma gemela.</t>
+          <t>Un matrimonio arreglado por razones de negocios, familia o política en lugar de amor; un montaje común en los dramas.</t>
         </is>
       </c>
       <c r="H729" s="16" t="inlineStr">
         <is>
-          <t>感覺與自己完美契合的靈魂伴侶。</t>
+          <t>因商業、家族或政治因素而非愛情所安排的婚姻，是韓劇常見的設定，利益聯姻。</t>
         </is>
       </c>
       <c r="I729" s="16" t="inlineStr">
         <is>
-          <t>感觉与自己完美契合的灵魂伴侣。</t>
+          <t>因商业、家族或政治因素而非爱情所安排的婚姻，是韩剧常见的设置，利益联姻。</t>
         </is>
       </c>
       <c r="J729" s="16" t="inlineStr">
         <is>
-          <t>完璧な心の相性を感じさせる人——魂の伴侶。</t>
+          <t>恋愛ではなく、ビジネスや家族、政治的な理由で決められた結婚——ドラマによくある設定。</t>
         </is>
       </c>
       <c r="K729" s="16" t="inlineStr">
         <is>
-          <t>둘이 완전 소울메이트 같아.</t>
+          <t>정략결혼으로 시작했는데 진짜 사랑에 빠졌어.</t>
         </is>
       </c>
       <c r="L729" s="16" t="inlineStr">
         <is>
-          <t>Those two seem like total soulmates.</t>
+          <t>It started as an arranged marriage, but they really fell in love.</t>
         </is>
       </c>
       <c r="M729" s="16" t="inlineStr">
         <is>
-          <t>Esos dos parecen almas gemelas totales.</t>
+          <t>Empezó como un matrimonio arreglado, pero de verdad se enamoraron.</t>
         </is>
       </c>
       <c r="N729" s="16" t="inlineStr">
         <is>
-          <t>那兩個人真的像靈魂伴侶。</t>
+          <t>雖然是利益聯姻開始的，但真的墜入愛河了。</t>
         </is>
       </c>
       <c r="O729" s="16" t="inlineStr">
         <is>
-          <t>那两个人真的像灵魂伴侣。</t>
+          <t>虽然是利益联姻开始的，但真的坠入爱河了。</t>
         </is>
       </c>
       <c r="P729" s="16" t="inlineStr">
         <is>
-          <t>あの二人、完全にソウルメイトみたい。</t>
+          <t>政略結婚で始まったのに、本当に恋に落ちた。</t>
         </is>
       </c>
       <c r="Q729" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R729" s="15" t="inlineStr">
@@ -71460,17 +71460,17 @@
     <row r="730" ht="46" customHeight="1">
       <c r="A730" s="15" t="inlineStr">
         <is>
-          <t>DAT-037</t>
+          <t>DAT-035</t>
         </is>
       </c>
       <c r="B730" s="15" t="inlineStr">
         <is>
-          <t>이상형</t>
+          <t>신데렐라</t>
         </is>
       </c>
       <c r="C730" s="15" t="inlineStr">
         <is>
-          <t>i-sang-hyeong</t>
+          <t>sin-de-rel-la</t>
         </is>
       </c>
       <c r="D730" s="15" t="inlineStr">
@@ -71485,62 +71485,62 @@
       </c>
       <c r="F730" s="16" t="inlineStr">
         <is>
-          <t>A person's ideal type or preferred qualities in a romantic partner.</t>
+          <t>A story trope where an ordinary or poor character rises into a wealthy or elite world, often through romance.</t>
         </is>
       </c>
       <c r="G730" s="16" t="inlineStr">
         <is>
-          <t>El tipo ideal o las cualidades preferidas de una persona en una pareja romántica.</t>
+          <t>Un arquetipo narrativo donde un personaje común o pobre asciende a un mundo rico o de élite, a menudo a través del romance.</t>
         </is>
       </c>
       <c r="H730" s="16" t="inlineStr">
         <is>
-          <t>一個人心目中理想的戀愛對象條件或類型，理想型。</t>
+          <t>平凡或貧窮的角色透過戀愛躍升進入富裕上流世界的劇情套路，灰姑娘故事。</t>
         </is>
       </c>
       <c r="I730" s="16" t="inlineStr">
         <is>
-          <t>一个人心目中理想的恋爱对象条件或类型，理想型。</t>
+          <t>平凡或贫穷的角色通过恋爱跃升进入富裕上流世界的剧情套路，灰姑娘故事。</t>
         </is>
       </c>
       <c r="J730" s="16" t="inlineStr">
         <is>
-          <t>恋愛相手に求める理想のタイプや条件。</t>
+          <t>平凡または貧しいキャラクターが、恋愛を通じて裕福またはエリートの世界に上り詰めるストーリートロープ。</t>
         </is>
       </c>
       <c r="K730" s="16" t="inlineStr">
         <is>
-          <t>내 이상형은 웃음이 많은 사람이야.</t>
+          <t>완전 신데렐라 스토리다.</t>
         </is>
       </c>
       <c r="L730" s="16" t="inlineStr">
         <is>
-          <t>My ideal type is someone who laughs a lot.</t>
+          <t>It's a total Cinderella story.</t>
         </is>
       </c>
       <c r="M730" s="16" t="inlineStr">
         <is>
-          <t>Mi tipo ideal es alguien que se ríe mucho.</t>
+          <t>Es una historia de Cenicienta total.</t>
         </is>
       </c>
       <c r="N730" s="16" t="inlineStr">
         <is>
-          <t>我的理想型是很愛笑的人。</t>
+          <t>完全是灰姑娘的故事。</t>
         </is>
       </c>
       <c r="O730" s="16" t="inlineStr">
         <is>
-          <t>我的理想型是很爱笑的人。</t>
+          <t>完全是灰姑娘的故事。</t>
         </is>
       </c>
       <c r="P730" s="16" t="inlineStr">
         <is>
-          <t>私の理想のタイプは、よく笑う人。</t>
+          <t>完全にシンデレラストーリーだね。</t>
         </is>
       </c>
       <c r="Q730" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R730" s="15" t="inlineStr">
@@ -71557,17 +71557,17 @@
     <row r="731" ht="46" customHeight="1">
       <c r="A731" s="15" t="inlineStr">
         <is>
-          <t>DAT-038</t>
+          <t>DAT-036</t>
         </is>
       </c>
       <c r="B731" s="15" t="inlineStr">
         <is>
-          <t>이상형월드컵</t>
+          <t>소울메이트</t>
         </is>
       </c>
       <c r="C731" s="15" t="inlineStr">
         <is>
-          <t>i-sang-hyeong-wol-deu-keop</t>
+          <t>so-ul-me-i-teu</t>
         </is>
       </c>
       <c r="D731" s="15" t="inlineStr">
@@ -71582,62 +71582,62 @@
       </c>
       <c r="F731" s="16" t="inlineStr">
         <is>
-          <t>"Ideal type World Cup" — a bracket-style elimination game where you repeatedly pick a favorite between two options.</t>
+          <t>A person who feels like a perfect emotional match, a soulmate.</t>
         </is>
       </c>
       <c r="G731" s="16" t="inlineStr">
         <is>
-          <t>"Mundial de tipo ideal": un juego de eliminación en formato de llaves donde eliges repetidamente a tu favorito entre dos opciones.</t>
+          <t>Una persona que se siente como una pareja emocional perfecta, un alma gemela.</t>
         </is>
       </c>
       <c r="H731" s="16" t="inlineStr">
         <is>
-          <t>「理想型世界盃」——透過兩兩淘汰的方式反覆選出最愛的錦標賽形式小遊戲。</t>
+          <t>感覺與自己完美契合的靈魂伴侶。</t>
         </is>
       </c>
       <c r="I731" s="16" t="inlineStr">
         <is>
-          <t>“理想型世界杯”——通过两两淘汰的方式反复选出最爱的锦标赛形式小游戏。</t>
+          <t>感觉与自己完美契合的灵魂伴侣。</t>
         </is>
       </c>
       <c r="J731" s="16" t="inlineStr">
         <is>
-          <t>「理想のタイプワールドカップ」——二択を繰り返してお気に入りを選ぶ、トーナメント形式のゲーム。</t>
+          <t>完璧な心の相性を感じさせる人——魂の伴侶。</t>
         </is>
       </c>
       <c r="K731" s="16" t="inlineStr">
         <is>
-          <t>최애 이상형월드컵 했는데 결승까지 갔어.</t>
+          <t>둘이 완전 소울메이트 같아.</t>
         </is>
       </c>
       <c r="L731" s="16" t="inlineStr">
         <is>
-          <t>I did the ideal-type bracket for my bias and they made it to the finals.</t>
+          <t>Those two seem like total soulmates.</t>
         </is>
       </c>
       <c r="M731" s="16" t="inlineStr">
         <is>
-          <t>Hice el torneo de tipo ideal de mi bias y llegó hasta la final.</t>
+          <t>Esos dos parecen almas gemelas totales.</t>
         </is>
       </c>
       <c r="N731" s="16" t="inlineStr">
         <is>
-          <t>玩了本命的理想型世界盃，結果進到決賽了。</t>
+          <t>那兩個人真的像靈魂伴侶。</t>
         </is>
       </c>
       <c r="O731" s="16" t="inlineStr">
         <is>
-          <t>玩了本命的理想型世界杯，结果进到决赛了。</t>
+          <t>那两个人真的像灵魂伴侣。</t>
         </is>
       </c>
       <c r="P731" s="16" t="inlineStr">
         <is>
-          <t>推しの理想のタイプワールドカップやったら、決勝まで行った。</t>
+          <t>あの二人、完全にソウルメイトみたい。</t>
         </is>
       </c>
       <c r="Q731" s="16" t="inlineStr">
         <is>
-          <t>Online games, fan content</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R731" s="15" t="inlineStr">
@@ -71654,17 +71654,17 @@
     <row r="732" ht="46" customHeight="1">
       <c r="A732" s="15" t="inlineStr">
         <is>
-          <t>DAT-039</t>
+          <t>DAT-037</t>
         </is>
       </c>
       <c r="B732" s="15" t="inlineStr">
         <is>
-          <t>열애설</t>
+          <t>이상형</t>
         </is>
       </c>
       <c r="C732" s="15" t="inlineStr">
         <is>
-          <t>yeol-ae-seol</t>
+          <t>i-sang-hyeong</t>
         </is>
       </c>
       <c r="D732" s="15" t="inlineStr">
@@ -71679,62 +71679,62 @@
       </c>
       <c r="F732" s="16" t="inlineStr">
         <is>
-          <t>"Hot romance rumor" — a rumor or report that a celebrity is secretly dating someone.</t>
+          <t>A person's ideal type or preferred qualities in a romantic partner.</t>
         </is>
       </c>
       <c r="G732" s="16" t="inlineStr">
         <is>
-          <t>"Rumor de romance ardiente": un rumor o reporte de que una celebridad está saliendo en secreto con alguien.</t>
+          <t>El tipo ideal o las cualidades preferidas de una persona en una pareja romántica.</t>
         </is>
       </c>
       <c r="H732" s="16" t="inlineStr">
         <is>
-          <t>「熱戀傳聞」——傳出藝人正在秘密交往的緋聞或報導。</t>
+          <t>一個人心目中理想的戀愛對象條件或類型，理想型。</t>
         </is>
       </c>
       <c r="I732" s="16" t="inlineStr">
         <is>
-          <t>“热恋传闻”——传出艺人正在秘密交往的绯闻或报导。</t>
+          <t>一个人心目中理想的恋爱对象条件或类型，理想型。</t>
         </is>
       </c>
       <c r="J732" s="16" t="inlineStr">
         <is>
-          <t>「熱い恋の噂」——芸能人が密かに誰かと付き合っているという噂や報道。</t>
+          <t>恋愛相手に求める理想のタイプや条件。</t>
         </is>
       </c>
       <c r="K732" s="16" t="inlineStr">
         <is>
-          <t>열애설 터졌다는 기사 봤어?</t>
+          <t>내 이상형은 웃음이 많은 사람이야.</t>
         </is>
       </c>
       <c r="L732" s="16" t="inlineStr">
         <is>
-          <t>Did you see the article about the dating rumor breaking?</t>
+          <t>My ideal type is someone who laughs a lot.</t>
         </is>
       </c>
       <c r="M732" s="16" t="inlineStr">
         <is>
-          <t>¿Viste el artículo sobre el rumor de romance que salió?</t>
+          <t>Mi tipo ideal es alguien que se ríe mucho.</t>
         </is>
       </c>
       <c r="N732" s="16" t="inlineStr">
         <is>
-          <t>你看到那則戀愛緋聞爆出的新聞了嗎？</t>
+          <t>我的理想型是很愛笑的人。</t>
         </is>
       </c>
       <c r="O732" s="16" t="inlineStr">
         <is>
-          <t>你看到那则恋爱绯闻爆出的新闻了吗？</t>
+          <t>我的理想型是很爱笑的人。</t>
         </is>
       </c>
       <c r="P732" s="16" t="inlineStr">
         <is>
-          <t>熱愛報道出たってニュース見た？</t>
+          <t>私の理想のタイプは、よく笑う人。</t>
         </is>
       </c>
       <c r="Q732" s="16" t="inlineStr">
         <is>
-          <t>Entertainment news</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R732" s="15" t="inlineStr">
@@ -71751,17 +71751,17 @@
     <row r="733" ht="46" customHeight="1">
       <c r="A733" s="15" t="inlineStr">
         <is>
-          <t>DAT-040</t>
+          <t>DAT-038</t>
         </is>
       </c>
       <c r="B733" s="15" t="inlineStr">
         <is>
-          <t>럽라인</t>
+          <t>이상형월드컵</t>
         </is>
       </c>
       <c r="C733" s="15" t="inlineStr">
         <is>
-          <t>leob-la-in</t>
+          <t>i-sang-hyeong-wol-deu-keop</t>
         </is>
       </c>
       <c r="D733" s="15" t="inlineStr">
@@ -71776,62 +71776,62 @@
       </c>
       <c r="F733" s="16" t="inlineStr">
         <is>
-          <t>"Love line" — the romantic pairing or storyline within a show.</t>
+          <t>"Ideal type World Cup" — a bracket-style elimination game where you repeatedly pick a favorite between two options.</t>
         </is>
       </c>
       <c r="G733" s="16" t="inlineStr">
         <is>
-          <t>"Línea de amor": la pareja romántica o trama dentro de un programa.</t>
+          <t>"Mundial de tipo ideal": un juego de eliminación en formato de llaves donde eliges repetidamente a tu favorito entre dos opciones.</t>
         </is>
       </c>
       <c r="H733" s="16" t="inlineStr">
         <is>
-          <t>「愛情線」——一部作品中的戀愛配對或感情發展劇情線。</t>
+          <t>「理想型世界盃」——透過兩兩淘汰的方式反覆選出最愛的錦標賽形式小遊戲。</t>
         </is>
       </c>
       <c r="I733" s="16" t="inlineStr">
         <is>
-          <t>“爱情线”——一部作品中的恋爱配对或感情发展剧情线。</t>
+          <t>“理想型世界杯”——通过两两淘汰的方式反复选出最爱的锦标赛形式小游戏。</t>
         </is>
       </c>
       <c r="J733" s="16" t="inlineStr">
         <is>
-          <t>「恋愛ライン」——番組内の恋愛カップリングやストーリーライン。</t>
+          <t>「理想のタイプワールドカップ」——二択を繰り返してお気に入りを選ぶ、トーナメント形式のゲーム。</t>
         </is>
       </c>
       <c r="K733" s="16" t="inlineStr">
         <is>
-          <t>이번 시즌 럽라인이 제일 기대돼.</t>
+          <t>최애 이상형월드컵 했는데 결승까지 갔어.</t>
         </is>
       </c>
       <c r="L733" s="16" t="inlineStr">
         <is>
-          <t>This season's romance storyline is what I'm most excited for.</t>
+          <t>I did the ideal-type bracket for my bias and they made it to the finals.</t>
         </is>
       </c>
       <c r="M733" s="16" t="inlineStr">
         <is>
-          <t>La línea romántica de esta temporada es lo que más me emociona.</t>
+          <t>Hice el torneo de tipo ideal de mi bias y llegó hasta la final.</t>
         </is>
       </c>
       <c r="N733" s="16" t="inlineStr">
         <is>
-          <t>這季最期待的就是感情線發展。</t>
+          <t>玩了本命的理想型世界盃，結果進到決賽了。</t>
         </is>
       </c>
       <c r="O733" s="16" t="inlineStr">
         <is>
-          <t>这季最期待的就是感情线发展。</t>
+          <t>玩了本命的理想型世界杯，结果进到决赛了。</t>
         </is>
       </c>
       <c r="P733" s="16" t="inlineStr">
         <is>
-          <t>今シーズンのラブラインが一番楽しみ。</t>
+          <t>推しの理想のタイプワールドカップやったら、決勝まで行った。</t>
         </is>
       </c>
       <c r="Q733" s="16" t="inlineStr">
         <is>
-          <t>Drama discussion threads</t>
+          <t>Online games, fan content</t>
         </is>
       </c>
       <c r="R733" s="15" t="inlineStr">
@@ -71848,17 +71848,17 @@
     <row r="734" ht="46" customHeight="1">
       <c r="A734" s="15" t="inlineStr">
         <is>
-          <t>DAT-041</t>
+          <t>DAT-039</t>
         </is>
       </c>
       <c r="B734" s="15" t="inlineStr">
         <is>
-          <t>커플링</t>
+          <t>열애설</t>
         </is>
       </c>
       <c r="C734" s="15" t="inlineStr">
         <is>
-          <t>keo-peul-ling</t>
+          <t>yeol-ae-seol</t>
         </is>
       </c>
       <c r="D734" s="15" t="inlineStr">
@@ -71873,62 +71873,62 @@
       </c>
       <c r="F734" s="16" t="inlineStr">
         <is>
-          <t>"Coupling" — fans pairing up two characters or idols as a romantic match, whether canon or imagined.</t>
+          <t>"Hot romance rumor" — a rumor or report that a celebrity is secretly dating someone.</t>
         </is>
       </c>
       <c r="G734" s="16" t="inlineStr">
         <is>
-          <t>"Emparejamiento": los fans emparejando a dos personajes o ídolos como pareja romántica, sea canónica o imaginada.</t>
+          <t>"Rumor de romance ardiente": un rumor o reporte de que una celebridad está saliendo en secreto con alguien.</t>
         </is>
       </c>
       <c r="H734" s="16" t="inlineStr">
         <is>
-          <t>粉絲將兩個角色或偶像配成一對的戀愛想像，無論是官方認證還是純粉絲腦補。</t>
+          <t>「熱戀傳聞」——傳出藝人正在秘密交往的緋聞或報導。</t>
         </is>
       </c>
       <c r="I734" s="16" t="inlineStr">
         <is>
-          <t>粉丝将两个角色或偶像配成一对的恋爱想像，无论是官方认证还是纯粉丝脑补。</t>
+          <t>“热恋传闻”——传出艺人正在秘密交往的绯闻或报导。</t>
         </is>
       </c>
       <c r="J734" s="16" t="inlineStr">
         <is>
-          <t>ファンが二人のキャラクターやアイドルを恋愛の組み合わせとして見ること、公式でも妄想でも。</t>
+          <t>「熱い恋の噂」——芸能人が密かに誰かと付き合っているという噂や報道。</t>
         </is>
       </c>
       <c r="K734" s="16" t="inlineStr">
         <is>
-          <t>이 둘 커플링 진짜 인기 많아.</t>
+          <t>열애설 터졌다는 기사 봤어?</t>
         </is>
       </c>
       <c r="L734" s="16" t="inlineStr">
         <is>
-          <t>This pairing is really popular among fans.</t>
+          <t>Did you see the article about the dating rumor breaking?</t>
         </is>
       </c>
       <c r="M734" s="16" t="inlineStr">
         <is>
-          <t>Esta pareja (shippeada) es muy popular entre los fans.</t>
+          <t>¿Viste el artículo sobre el rumor de romance que salió?</t>
         </is>
       </c>
       <c r="N734" s="16" t="inlineStr">
         <is>
-          <t>這對CP真的超受歡迎。</t>
+          <t>你看到那則戀愛緋聞爆出的新聞了嗎？</t>
         </is>
       </c>
       <c r="O734" s="16" t="inlineStr">
         <is>
-          <t>这对CP真的超受欢迎。</t>
+          <t>你看到那则恋爱绯闻爆出的新闻了吗？</t>
         </is>
       </c>
       <c r="P734" s="16" t="inlineStr">
         <is>
-          <t>このカップリング、本当に人気ある。</t>
+          <t>熱愛報道出たってニュース見た？</t>
         </is>
       </c>
       <c r="Q734" s="16" t="inlineStr">
         <is>
-          <t>Fan fiction, shipping culture</t>
+          <t>Entertainment news</t>
         </is>
       </c>
       <c r="R734" s="15" t="inlineStr">
@@ -71945,17 +71945,17 @@
     <row r="735" ht="46" customHeight="1">
       <c r="A735" s="15" t="inlineStr">
         <is>
-          <t>DAT-042</t>
+          <t>DAT-040</t>
         </is>
       </c>
       <c r="B735" s="15" t="inlineStr">
         <is>
-          <t>짝남</t>
+          <t>럽라인</t>
         </is>
       </c>
       <c r="C735" s="15" t="inlineStr">
         <is>
-          <t>jjak-nam</t>
+          <t>leob-la-in</t>
         </is>
       </c>
       <c r="D735" s="15" t="inlineStr">
@@ -71970,62 +71970,62 @@
       </c>
       <c r="F735" s="16" t="inlineStr">
         <is>
-          <t>Short for 짝사랑하는 남자 ("the guy I have a one-sided crush on") — your crush.</t>
+          <t>"Love line" — the romantic pairing or storyline within a show.</t>
         </is>
       </c>
       <c r="G735" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 짝사랑하는 남자 ("el chico del que estoy enamorada en secreto"): tu crush.</t>
+          <t>"Línea de amor": la pareja romántica o trama dentro de un programa.</t>
         </is>
       </c>
       <c r="H735" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 남자（暗戀的男生）的縮寫——你暗戀的對象。</t>
+          <t>「愛情線」——一部作品中的戀愛配對或感情發展劇情線。</t>
         </is>
       </c>
       <c r="I735" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 남자（暗恋的男生）的缩写——你暗恋的对象。</t>
+          <t>“爱情线”——一部作品中的恋爱配对或感情发展剧情线。</t>
         </is>
       </c>
       <c r="J735" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 남자（片思いしている男性）の略——片思いの相手。</t>
+          <t>「恋愛ライン」——番組内の恋愛カップリングやストーリーライン。</t>
         </is>
       </c>
       <c r="K735" s="16" t="inlineStr">
         <is>
-          <t>짝남 앞에서 완전 얼음 됐어.</t>
+          <t>이번 시즌 럽라인이 제일 기대돼.</t>
         </is>
       </c>
       <c r="L735" s="16" t="inlineStr">
         <is>
-          <t>I totally froze up in front of my crush.</t>
+          <t>This season's romance storyline is what I'm most excited for.</t>
         </is>
       </c>
       <c r="M735" s="16" t="inlineStr">
         <is>
-          <t>Me quedé completamente congelada frente a mi crush.</t>
+          <t>La línea romántica de esta temporada es lo que más me emociona.</t>
         </is>
       </c>
       <c r="N735" s="16" t="inlineStr">
         <is>
-          <t>在喜歡的男生面前完全僵住了。</t>
+          <t>這季最期待的就是感情線發展。</t>
         </is>
       </c>
       <c r="O735" s="16" t="inlineStr">
         <is>
-          <t>在喜欢的男生面前完全僵住了。</t>
+          <t>这季最期待的就是感情线发展。</t>
         </is>
       </c>
       <c r="P735" s="16" t="inlineStr">
         <is>
-          <t>好きな人の前で完全に固まっちゃった。</t>
+          <t>今シーズンのラブラインが一番楽しみ。</t>
         </is>
       </c>
       <c r="Q735" s="16" t="inlineStr">
         <is>
-          <t>Casual crush talk</t>
+          <t>Drama discussion threads</t>
         </is>
       </c>
       <c r="R735" s="15" t="inlineStr">
@@ -72042,17 +72042,17 @@
     <row r="736" ht="46" customHeight="1">
       <c r="A736" s="15" t="inlineStr">
         <is>
-          <t>DAT-043</t>
+          <t>DAT-041</t>
         </is>
       </c>
       <c r="B736" s="15" t="inlineStr">
         <is>
-          <t>짝녀</t>
+          <t>커플링</t>
         </is>
       </c>
       <c r="C736" s="15" t="inlineStr">
         <is>
-          <t>jjak-nyeo</t>
+          <t>keo-peul-ling</t>
         </is>
       </c>
       <c r="D736" s="15" t="inlineStr">
@@ -72067,62 +72067,62 @@
       </c>
       <c r="F736" s="16" t="inlineStr">
         <is>
-          <t>Short for 짝사랑하는 여자 ("the girl I have a one-sided crush on") — your crush.</t>
+          <t>"Coupling" — fans pairing up two characters or idols as a romantic match, whether canon or imagined.</t>
         </is>
       </c>
       <c r="G736" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 짝사랑하는 여자 ("la chica de la que estoy enamorado en secreto"): tu crush.</t>
+          <t>"Emparejamiento": los fans emparejando a dos personajes o ídolos como pareja romántica, sea canónica o imaginada.</t>
         </is>
       </c>
       <c r="H736" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 여자（暗戀的女生）的縮寫——你暗戀的對象。</t>
+          <t>粉絲將兩個角色或偶像配成一對的戀愛想像，無論是官方認證還是純粉絲腦補。</t>
         </is>
       </c>
       <c r="I736" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 여자（暗恋的女生）的缩写——你暗恋的对象。</t>
+          <t>粉丝将两个角色或偶像配成一对的恋爱想像，无论是官方认证还是纯粉丝脑补。</t>
         </is>
       </c>
       <c r="J736" s="16" t="inlineStr">
         <is>
-          <t>짝사랑하는 여자（片思いしている女性）の略——片思いの相手。</t>
+          <t>ファンが二人のキャラクターやアイドルを恋愛の組み合わせとして見ること、公式でも妄想でも。</t>
         </is>
       </c>
       <c r="K736" s="16" t="inlineStr">
         <is>
-          <t>짝녀한테 어떻게 말 걸지 고민이야.</t>
+          <t>이 둘 커플링 진짜 인기 많아.</t>
         </is>
       </c>
       <c r="L736" s="16" t="inlineStr">
         <is>
-          <t>I'm stressing over how to talk to my crush.</t>
+          <t>This pairing is really popular among fans.</t>
         </is>
       </c>
       <c r="M736" s="16" t="inlineStr">
         <is>
-          <t>Estoy preocupado por cómo hablarle a mi crush.</t>
+          <t>Esta pareja (shippeada) es muy popular entre los fans.</t>
         </is>
       </c>
       <c r="N736" s="16" t="inlineStr">
         <is>
-          <t>煩惱要怎麼跟喜歡的女生搭話。</t>
+          <t>這對CP真的超受歡迎。</t>
         </is>
       </c>
       <c r="O736" s="16" t="inlineStr">
         <is>
-          <t>烦恼要怎么跟喜欢的女生搭话。</t>
+          <t>这对CP真的超受欢迎。</t>
         </is>
       </c>
       <c r="P736" s="16" t="inlineStr">
         <is>
-          <t>好きな人にどう話しかけるか悩んでる。</t>
+          <t>このカップリング、本当に人気ある。</t>
         </is>
       </c>
       <c r="Q736" s="16" t="inlineStr">
         <is>
-          <t>Casual crush talk</t>
+          <t>Fan fiction, shipping culture</t>
         </is>
       </c>
       <c r="R736" s="15" t="inlineStr">
@@ -72139,17 +72139,17 @@
     <row r="737" ht="46" customHeight="1">
       <c r="A737" s="15" t="inlineStr">
         <is>
-          <t>DAT-044</t>
+          <t>DAT-042</t>
         </is>
       </c>
       <c r="B737" s="15" t="inlineStr">
         <is>
-          <t>대시</t>
+          <t>짝남</t>
         </is>
       </c>
       <c r="C737" s="15" t="inlineStr">
         <is>
-          <t>dae-si</t>
+          <t>jjak-nam</t>
         </is>
       </c>
       <c r="D737" s="15" t="inlineStr">
@@ -72164,67 +72164,67 @@
       </c>
       <c r="F737" s="16" t="inlineStr">
         <is>
-          <t>"Dash" — making a romantic move on someone, like asking them out.</t>
+          <t>Short for 짝사랑하는 남자 ("the guy I have a one-sided crush on") — your crush.</t>
         </is>
       </c>
       <c r="G737" s="16" t="inlineStr">
         <is>
-          <t>"Dash": hacer un movimiento romántico hacia alguien, como invitarlo a salir.</t>
+          <t>Abreviatura de 짝사랑하는 남자 ("el chico del que estoy enamorada en secreto"): tu crush.</t>
         </is>
       </c>
       <c r="H737" s="16" t="inlineStr">
         <is>
-          <t>主動採取行動追求某人，例如開口邀約，主動出擊。</t>
+          <t>짝사랑하는 남자（暗戀的男生）的縮寫——你暗戀的對象。</t>
         </is>
       </c>
       <c r="I737" s="16" t="inlineStr">
         <is>
-          <t>主动采取行动追求某人，例如开口邀约，主动出击。</t>
+          <t>짝사랑하는 남자（暗恋的男生）的缩写——你暗恋的对象。</t>
         </is>
       </c>
       <c r="J737" s="16" t="inlineStr">
         <is>
-          <t>「ダッシュ」——デートに誘うなど、恋愛的なアクションを起こすこと。</t>
+          <t>짝사랑하는 남자（片思いしている男性）の略——片思いの相手。</t>
         </is>
       </c>
       <c r="K737" s="16" t="inlineStr">
         <is>
-          <t>드디어 대시했어!</t>
+          <t>짝남 앞에서 완전 얼음 됐어.</t>
         </is>
       </c>
       <c r="L737" s="16" t="inlineStr">
         <is>
-          <t>I finally made a move!</t>
+          <t>I totally froze up in front of my crush.</t>
         </is>
       </c>
       <c r="M737" s="16" t="inlineStr">
         <is>
-          <t>¡Por fin di el paso!</t>
+          <t>Me quedé completamente congelada frente a mi crush.</t>
         </is>
       </c>
       <c r="N737" s="16" t="inlineStr">
         <is>
-          <t>終於主動出擊了！</t>
+          <t>在喜歡的男生面前完全僵住了。</t>
         </is>
       </c>
       <c r="O737" s="16" t="inlineStr">
         <is>
-          <t>终于主动出击了！</t>
+          <t>在喜欢的男生面前完全僵住了。</t>
         </is>
       </c>
       <c r="P737" s="16" t="inlineStr">
         <is>
-          <t>ついにアタックした！</t>
+          <t>好きな人の前で完全に固まっちゃった。</t>
         </is>
       </c>
       <c r="Q737" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Casual crush talk</t>
         </is>
       </c>
       <c r="R737" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S737" s="15" t="inlineStr">
@@ -72236,17 +72236,17 @@
     <row r="738" ht="46" customHeight="1">
       <c r="A738" s="15" t="inlineStr">
         <is>
-          <t>DAT-045</t>
+          <t>DAT-043</t>
         </is>
       </c>
       <c r="B738" s="15" t="inlineStr">
         <is>
-          <t>애프터</t>
+          <t>짝녀</t>
         </is>
       </c>
       <c r="C738" s="15" t="inlineStr">
         <is>
-          <t>ae-peu-teo</t>
+          <t>jjak-nyeo</t>
         </is>
       </c>
       <c r="D738" s="15" t="inlineStr">
@@ -72261,62 +72261,62 @@
       </c>
       <c r="F738" s="16" t="inlineStr">
         <is>
-          <t>"After" — a follow-up date arranged after an initial blind date.</t>
+          <t>Short for 짝사랑하는 여자 ("the girl I have a one-sided crush on") — your crush.</t>
         </is>
       </c>
       <c r="G738" s="16" t="inlineStr">
         <is>
-          <t>"After": una cita de seguimiento organizada después de una cita a ciegas inicial.</t>
+          <t>Abreviatura de 짝사랑하는 여자 ("la chica de la que estoy enamorado en secreto"): tu crush.</t>
         </is>
       </c>
       <c r="H738" s="16" t="inlineStr">
         <is>
-          <t>相親後安排的後續約會。</t>
+          <t>짝사랑하는 여자（暗戀的女生）的縮寫——你暗戀的對象。</t>
         </is>
       </c>
       <c r="I738" s="16" t="inlineStr">
         <is>
-          <t>相亲后安排的后续约会。</t>
+          <t>짝사랑하는 여자（暗恋的女生）的缩写——你暗恋的对象。</t>
         </is>
       </c>
       <c r="J738" s="16" t="inlineStr">
         <is>
-          <t>最初の合コンの後に設定される、フォローアップのデート——「アフター」。</t>
+          <t>짝사랑하는 여자（片思いしている女性）の略——片思いの相手。</t>
         </is>
       </c>
       <c r="K738" s="16" t="inlineStr">
         <is>
-          <t>소개팅 애프터 신청 받았어.</t>
+          <t>짝녀한테 어떻게 말 걸지 고민이야.</t>
         </is>
       </c>
       <c r="L738" s="16" t="inlineStr">
         <is>
-          <t>I got asked for a follow-up date after the blind date.</t>
+          <t>I'm stressing over how to talk to my crush.</t>
         </is>
       </c>
       <c r="M738" s="16" t="inlineStr">
         <is>
-          <t>Me pidieron una segunda cita después de la cita a ciegas.</t>
+          <t>Estoy preocupado por cómo hablarle a mi crush.</t>
         </is>
       </c>
       <c r="N738" s="16" t="inlineStr">
         <is>
-          <t>相親後收到了續攤約會的邀約。</t>
+          <t>煩惱要怎麼跟喜歡的女生搭話。</t>
         </is>
       </c>
       <c r="O738" s="16" t="inlineStr">
         <is>
-          <t>相亲后收到了续摊约会的邀约。</t>
+          <t>烦恼要怎么跟喜欢的女生搭话。</t>
         </is>
       </c>
       <c r="P738" s="16" t="inlineStr">
         <is>
-          <t>合コンのアフターに誘われた。</t>
+          <t>好きな人にどう話しかけるか悩んでる。</t>
         </is>
       </c>
       <c r="Q738" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Casual crush talk</t>
         </is>
       </c>
       <c r="R738" s="15" t="inlineStr">
@@ -72333,17 +72333,17 @@
     <row r="739" ht="46" customHeight="1">
       <c r="A739" s="15" t="inlineStr">
         <is>
-          <t>DAT-046</t>
+          <t>DAT-044</t>
         </is>
       </c>
       <c r="B739" s="15" t="inlineStr">
         <is>
-          <t>그린라이트</t>
+          <t>대시</t>
         </is>
       </c>
       <c r="C739" s="15" t="inlineStr">
         <is>
-          <t>geu-rin-la-i-teu</t>
+          <t>dae-si</t>
         </is>
       </c>
       <c r="D739" s="15" t="inlineStr">
@@ -72358,57 +72358,57 @@
       </c>
       <c r="F739" s="16" t="inlineStr">
         <is>
-          <t>"Green light" — a signal that someone is romantically interested and open to being pursued.</t>
+          <t>"Dash" — making a romantic move on someone, like asking them out.</t>
         </is>
       </c>
       <c r="G739" s="16" t="inlineStr">
         <is>
-          <t>"Luz verde": una señal de que alguien está interesado románticamente y abierto a ser conquistado.</t>
+          <t>"Dash": hacer un movimiento romántico hacia alguien, como invitarlo a salir.</t>
         </is>
       </c>
       <c r="H739" s="16" t="inlineStr">
         <is>
-          <t>「綠燈」——表示對方對你有意思、可以繼續追求的訊號。</t>
+          <t>主動採取行動追求某人，例如開口邀約，主動出擊。</t>
         </is>
       </c>
       <c r="I739" s="16" t="inlineStr">
         <is>
-          <t>“绿灯”——表示对方对你有意思、可以继续追求的信号。</t>
+          <t>主动采取行动追求某人，例如开口邀约，主动出击。</t>
         </is>
       </c>
       <c r="J739" s="16" t="inlineStr">
         <is>
-          <t>「青信号」——相手が恋愛的に興味を持っていて、アプローチを受け入れる準備があるというサイン。</t>
+          <t>「ダッシュ」——デートに誘うなど、恋愛的なアクションを起こすこと。</t>
         </is>
       </c>
       <c r="K739" s="16" t="inlineStr">
         <is>
-          <t>그거 완전 그린라이트 아니야?</t>
+          <t>드디어 대시했어!</t>
         </is>
       </c>
       <c r="L739" s="16" t="inlineStr">
         <is>
-          <t>Isn't that a total green light?</t>
+          <t>I finally made a move!</t>
         </is>
       </c>
       <c r="M739" s="16" t="inlineStr">
         <is>
-          <t>¿Eso no es una luz verde total?</t>
+          <t>¡Por fin di el paso!</t>
         </is>
       </c>
       <c r="N739" s="16" t="inlineStr">
         <is>
-          <t>那不完全是綠燈訊號嗎？</t>
+          <t>終於主動出擊了！</t>
         </is>
       </c>
       <c r="O739" s="16" t="inlineStr">
         <is>
-          <t>那不完全是绿灯信号吗？</t>
+          <t>终于主动出击了！</t>
         </is>
       </c>
       <c r="P739" s="16" t="inlineStr">
         <is>
-          <t>それって完全にグリーンライトじゃない？</t>
+          <t>ついにアタックした！</t>
         </is>
       </c>
       <c r="Q739" s="16" t="inlineStr">
@@ -72418,7 +72418,7 @@
       </c>
       <c r="R739" s="15" t="inlineStr">
         <is>
-          <t>Verified (web-checked)</t>
+          <t>Draft — please double-check</t>
         </is>
       </c>
       <c r="S739" s="15" t="inlineStr">
@@ -72430,17 +72430,17 @@
     <row r="740" ht="46" customHeight="1">
       <c r="A740" s="15" t="inlineStr">
         <is>
-          <t>DAT-047</t>
+          <t>DAT-045</t>
         </is>
       </c>
       <c r="B740" s="15" t="inlineStr">
         <is>
-          <t>훈훈하다</t>
+          <t>애프터</t>
         </is>
       </c>
       <c r="C740" s="15" t="inlineStr">
         <is>
-          <t>hun-hun-ha-da</t>
+          <t>ae-peu-teo</t>
         </is>
       </c>
       <c r="D740" s="15" t="inlineStr">
@@ -72455,62 +72455,62 @@
       </c>
       <c r="F740" s="16" t="inlineStr">
         <is>
-          <t>Describes a warm, wholesome, feel-good atmosphere or moment — or a warmly attractive appearance.</t>
+          <t>"After" — a follow-up date arranged after an initial blind date.</t>
         </is>
       </c>
       <c r="G740" s="16" t="inlineStr">
         <is>
-          <t>Describe un ambiente o momento cálido, agradable y de buen sentir — o una apariencia cálidamente atractiva.</t>
+          <t>"After": una cita de seguimiento organizada después de una cita a ciegas inicial.</t>
         </is>
       </c>
       <c r="H740" s="16" t="inlineStr">
         <is>
-          <t>形容溫暖、樸實、讓人感覺舒服的氛圍或瞬間，也可形容外表溫暖有魅力。</t>
+          <t>相親後安排的後續約會。</t>
         </is>
       </c>
       <c r="I740" s="16" t="inlineStr">
         <is>
-          <t>形容温暖、朴实、让人感觉舒服的氛围或瞬间，也可形容外表温暖有魅力。</t>
+          <t>相亲后安排的后续约会。</t>
         </is>
       </c>
       <c r="J740" s="16" t="inlineStr">
         <is>
-          <t>温かく、素朴で、心地よい雰囲気や瞬間——または温かみのある魅力的な外見を表す。</t>
+          <t>最初の合コンの後に設定される、フォローアップのデート——「アフター」。</t>
         </is>
       </c>
       <c r="K740" s="16" t="inlineStr">
         <is>
-          <t>이 훈훈한 미담 봐봐.</t>
+          <t>소개팅 애프터 신청 받았어.</t>
         </is>
       </c>
       <c r="L740" s="16" t="inlineStr">
         <is>
-          <t>Check out this warm, feel-good story.</t>
+          <t>I got asked for a follow-up date after the blind date.</t>
         </is>
       </c>
       <c r="M740" s="16" t="inlineStr">
         <is>
-          <t>Mira esta historia tan cálida y conmovedora.</t>
+          <t>Me pidieron una segunda cita después de la cita a ciegas.</t>
         </is>
       </c>
       <c r="N740" s="16" t="inlineStr">
         <is>
-          <t>看看這則暖心的故事。</t>
+          <t>相親後收到了續攤約會的邀約。</t>
         </is>
       </c>
       <c r="O740" s="16" t="inlineStr">
         <is>
-          <t>看看这则暖心的故事。</t>
+          <t>相亲后收到了续摊约会的邀约。</t>
         </is>
       </c>
       <c r="P740" s="16" t="inlineStr">
         <is>
-          <t>このほのぼのする美談見て。</t>
+          <t>合コンのアフターに誘われた。</t>
         </is>
       </c>
       <c r="Q740" s="16" t="inlineStr">
         <is>
-          <t>Feel-good news, casual compliments</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R740" s="15" t="inlineStr">
@@ -72527,17 +72527,17 @@
     <row r="741" ht="46" customHeight="1">
       <c r="A741" s="15" t="inlineStr">
         <is>
-          <t>DAT-048</t>
+          <t>DAT-046</t>
         </is>
       </c>
       <c r="B741" s="15" t="inlineStr">
         <is>
-          <t>이별</t>
+          <t>그린라이트</t>
         </is>
       </c>
       <c r="C741" s="15" t="inlineStr">
         <is>
-          <t>i-byeol</t>
+          <t>geu-rin-la-i-teu</t>
         </is>
       </c>
       <c r="D741" s="15" t="inlineStr">
@@ -72552,62 +72552,62 @@
       </c>
       <c r="F741" s="16" t="inlineStr">
         <is>
-          <t>The ending of a romantic relationship.</t>
+          <t>"Green light" — a signal that someone is romantically interested and open to being pursued.</t>
         </is>
       </c>
       <c r="G741" s="16" t="inlineStr">
         <is>
-          <t>El fin de una relación romántica.</t>
+          <t>"Luz verde": una señal de que alguien está interesado románticamente y abierto a ser conquistado.</t>
         </is>
       </c>
       <c r="H741" s="16" t="inlineStr">
         <is>
-          <t>一段戀愛關係的結束，分手。</t>
+          <t>「綠燈」——表示對方對你有意思、可以繼續追求的訊號。</t>
         </is>
       </c>
       <c r="I741" s="16" t="inlineStr">
         <is>
-          <t>一段恋爱关系的结束，分手。</t>
+          <t>“绿灯”——表示对方对你有意思、可以继续追求的信号。</t>
         </is>
       </c>
       <c r="J741" s="16" t="inlineStr">
         <is>
-          <t>恋愛関係の終わり。</t>
+          <t>「青信号」——相手が恋愛的に興味を持っていて、アプローチを受け入れる準備があるというサイン。</t>
         </is>
       </c>
       <c r="K741" s="16" t="inlineStr">
         <is>
-          <t>이별 후에 한동안 힘들었어.</t>
+          <t>그거 완전 그린라이트 아니야?</t>
         </is>
       </c>
       <c r="L741" s="16" t="inlineStr">
         <is>
-          <t>I had a hard time for a while after the breakup.</t>
+          <t>Isn't that a total green light?</t>
         </is>
       </c>
       <c r="M741" s="16" t="inlineStr">
         <is>
-          <t>La pasé mal por un tiempo después de la ruptura.</t>
+          <t>¿Eso no es una luz verde total?</t>
         </is>
       </c>
       <c r="N741" s="16" t="inlineStr">
         <is>
-          <t>分手後有一陣子過得很辛苦。</t>
+          <t>那不完全是綠燈訊號嗎？</t>
         </is>
       </c>
       <c r="O741" s="16" t="inlineStr">
         <is>
-          <t>分手后有一阵子过得很辛苦。</t>
+          <t>那不完全是绿灯信号吗？</t>
         </is>
       </c>
       <c r="P741" s="16" t="inlineStr">
         <is>
-          <t>別れた後、しばらく辛かった。</t>
+          <t>それって完全にグリーンライトじゃない？</t>
         </is>
       </c>
       <c r="Q741" s="16" t="inlineStr">
         <is>
-          <t>K-drama plot talk, casual speech</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R741" s="15" t="inlineStr">
@@ -72624,17 +72624,17 @@
     <row r="742" ht="46" customHeight="1">
       <c r="A742" s="15" t="inlineStr">
         <is>
-          <t>DAT-049</t>
+          <t>DAT-047</t>
         </is>
       </c>
       <c r="B742" s="15" t="inlineStr">
         <is>
-          <t>곰신</t>
+          <t>훈훈하다</t>
         </is>
       </c>
       <c r="C742" s="15" t="inlineStr">
         <is>
-          <t>gom-sin</t>
+          <t>hun-hun-ha-da</t>
         </is>
       </c>
       <c r="D742" s="15" t="inlineStr">
@@ -72649,62 +72649,62 @@
       </c>
       <c r="F742" s="16" t="inlineStr">
         <is>
-          <t>Short for 고무신 (traditional rubber shoes) — a girlfriend patiently waiting for her boyfriend to finish mandatory military service.</t>
+          <t>Describes a warm, wholesome, feel-good atmosphere or moment — or a warmly attractive appearance.</t>
         </is>
       </c>
       <c r="G742" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 고무신 (zapatos tradicionales de goma): una novia que espera pacientemente a que su novio termine el servicio militar obligatorio.</t>
+          <t>Describe un ambiente o momento cálido, agradable y de buen sentir — o una apariencia cálidamente atractiva.</t>
         </is>
       </c>
       <c r="H742" s="16" t="inlineStr">
         <is>
-          <t>고무신（傳統膠鞋）的縮寫——耐心等待男友服完兵役的女友。</t>
+          <t>形容溫暖、樸實、讓人感覺舒服的氛圍或瞬間，也可形容外表溫暖有魅力。</t>
         </is>
       </c>
       <c r="I742" s="16" t="inlineStr">
         <is>
-          <t>고무신（传统胶鞋）的缩写——耐心等待男友服完兵役的女友。</t>
+          <t>形容温暖、朴实、让人感觉舒服的氛围或瞬间，也可形容外表温暖有魅力。</t>
         </is>
       </c>
       <c r="J742" s="16" t="inlineStr">
         <is>
-          <t>고무신（伝統的なゴム靴）の略——兵役を終えるのを待つ彼女のこと。</t>
+          <t>温かく、素朴で、心地よい雰囲気や瞬間——または温かみのある魅力的な外見を表す。</t>
         </is>
       </c>
       <c r="K742" s="16" t="inlineStr">
         <is>
-          <t>곰신 생활 이제 6개월 남았어.</t>
+          <t>이 훈훈한 미담 봐봐.</t>
         </is>
       </c>
       <c r="L742" s="16" t="inlineStr">
         <is>
-          <t>I only have six months left of being a waiting girlfriend.</t>
+          <t>Check out this warm, feel-good story.</t>
         </is>
       </c>
       <c r="M742" s="16" t="inlineStr">
         <is>
-          <t>Solo me quedan seis meses esperando a que termine el servicio militar.</t>
+          <t>Mira esta historia tan cálida y conmovedora.</t>
         </is>
       </c>
       <c r="N742" s="16" t="inlineStr">
         <is>
-          <t>等男友退伍的日子只剩六個月了。</t>
+          <t>看看這則暖心的故事。</t>
         </is>
       </c>
       <c r="O742" s="16" t="inlineStr">
         <is>
-          <t>等男友退伍的日子只剩六个月了。</t>
+          <t>看看这则暖心的故事。</t>
         </is>
       </c>
       <c r="P742" s="16" t="inlineStr">
         <is>
-          <t>彼の除隊を待つ生活も、あと6ヶ月。</t>
+          <t>このほのぼのする美談見て。</t>
         </is>
       </c>
       <c r="Q742" s="16" t="inlineStr">
         <is>
-          <t>Military service relationship talk</t>
+          <t>Feel-good news, casual compliments</t>
         </is>
       </c>
       <c r="R742" s="15" t="inlineStr">
@@ -72721,17 +72721,17 @@
     <row r="743" ht="46" customHeight="1">
       <c r="A743" s="15" t="inlineStr">
         <is>
-          <t>DAT-050</t>
+          <t>DAT-048</t>
         </is>
       </c>
       <c r="B743" s="15" t="inlineStr">
         <is>
-          <t>장거리연애</t>
+          <t>이별</t>
         </is>
       </c>
       <c r="C743" s="15" t="inlineStr">
         <is>
-          <t>jang-geo-ri-yeon-ae</t>
+          <t>i-byeol</t>
         </is>
       </c>
       <c r="D743" s="15" t="inlineStr">
@@ -72746,62 +72746,62 @@
       </c>
       <c r="F743" s="16" t="inlineStr">
         <is>
-          <t>A romantic relationship where the couple lives far apart from each other.</t>
+          <t>The ending of a romantic relationship.</t>
         </is>
       </c>
       <c r="G743" s="16" t="inlineStr">
         <is>
-          <t>Una relación romántica donde la pareja vive lejos el uno del otro.</t>
+          <t>El fin de una relación romántica.</t>
         </is>
       </c>
       <c r="H743" s="16" t="inlineStr">
         <is>
-          <t>情侶分隔兩地、住得很遠的戀愛關係，遠距離戀愛。</t>
+          <t>一段戀愛關係的結束，分手。</t>
         </is>
       </c>
       <c r="I743" s="16" t="inlineStr">
         <is>
-          <t>情侣分隔两地、住得很远的恋爱关系，远距离恋爱。</t>
+          <t>一段恋爱关系的结束，分手。</t>
         </is>
       </c>
       <c r="J743" s="16" t="inlineStr">
         <is>
-          <t>カップルが離れて暮らす恋愛関係。</t>
+          <t>恋愛関係の終わり。</t>
         </is>
       </c>
       <c r="K743" s="16" t="inlineStr">
         <is>
-          <t>장거리연애 힘들지만 잘 버티고 있어.</t>
+          <t>이별 후에 한동안 힘들었어.</t>
         </is>
       </c>
       <c r="L743" s="16" t="inlineStr">
         <is>
-          <t>Long-distance is hard, but we're holding up well.</t>
+          <t>I had a hard time for a while after the breakup.</t>
         </is>
       </c>
       <c r="M743" s="16" t="inlineStr">
         <is>
-          <t>La distancia es difícil, pero lo estamos llevando bien.</t>
+          <t>La pasé mal por un tiempo después de la ruptura.</t>
         </is>
       </c>
       <c r="N743" s="16" t="inlineStr">
         <is>
-          <t>遠距離戀愛雖然辛苦，但撐得很好。</t>
+          <t>分手後有一陣子過得很辛苦。</t>
         </is>
       </c>
       <c r="O743" s="16" t="inlineStr">
         <is>
-          <t>远距离恋爱虽然辛苦，但撑得很好。</t>
+          <t>分手后有一阵子过得很辛苦。</t>
         </is>
       </c>
       <c r="P743" s="16" t="inlineStr">
         <is>
-          <t>遠距離恋愛は大変だけど、うまくやってる。</t>
+          <t>別れた後、しばらく辛かった。</t>
         </is>
       </c>
       <c r="Q743" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk</t>
+          <t>K-drama plot talk, casual speech</t>
         </is>
       </c>
       <c r="R743" s="15" t="inlineStr">
@@ -72818,17 +72818,17 @@
     <row r="744" ht="46" customHeight="1">
       <c r="A744" s="15" t="inlineStr">
         <is>
-          <t>DAT-051</t>
+          <t>DAT-049</t>
         </is>
       </c>
       <c r="B744" s="15" t="inlineStr">
         <is>
-          <t>권태기</t>
+          <t>곰신</t>
         </is>
       </c>
       <c r="C744" s="15" t="inlineStr">
         <is>
-          <t>gwon-tae-gi</t>
+          <t>gom-sin</t>
         </is>
       </c>
       <c r="D744" s="15" t="inlineStr">
@@ -72843,62 +72843,62 @@
       </c>
       <c r="F744" s="16" t="inlineStr">
         <is>
-          <t>A phase in a relationship marked by boredom or waning excitement.</t>
+          <t>Short for 고무신 (traditional rubber shoes) — a girlfriend patiently waiting for her boyfriend to finish mandatory military service.</t>
         </is>
       </c>
       <c r="G744" s="16" t="inlineStr">
         <is>
-          <t>Una fase en una relación marcada por el aburrimiento o la disminución del entusiasmo.</t>
+          <t>Abreviatura de 고무신 (zapatos tradicionales de goma): una novia que espera pacientemente a que su novio termine el servicio militar obligatorio.</t>
         </is>
       </c>
       <c r="H744" s="16" t="inlineStr">
         <is>
-          <t>感情中出現無聊感或熱情消退的階段，倦怠期。</t>
+          <t>고무신（傳統膠鞋）的縮寫——耐心等待男友服完兵役的女友。</t>
         </is>
       </c>
       <c r="I744" s="16" t="inlineStr">
         <is>
-          <t>感情中出现无聊感或热情消退的阶段，倦怠期。</t>
+          <t>고무신（传统胶鞋）的缩写——耐心等待男友服完兵役的女友。</t>
         </is>
       </c>
       <c r="J744" s="16" t="inlineStr">
         <is>
-          <t>退屈さや情熱の低下が見られる、関係の一時期。</t>
+          <t>고무신（伝統的なゴム靴）の略——兵役を終えるのを待つ彼女のこと。</t>
         </is>
       </c>
       <c r="K744" s="16" t="inlineStr">
         <is>
-          <t>우리 요즘 권태기인 것 같아.</t>
+          <t>곰신 생활 이제 6개월 남았어.</t>
         </is>
       </c>
       <c r="L744" s="16" t="inlineStr">
         <is>
-          <t>I think we're going through a relationship rut lately.</t>
+          <t>I only have six months left of being a waiting girlfriend.</t>
         </is>
       </c>
       <c r="M744" s="16" t="inlineStr">
         <is>
-          <t>Creo que estamos pasando por una etapa de aburrimiento últimamente.</t>
+          <t>Solo me quedan seis meses esperando a que termine el servicio militar.</t>
         </is>
       </c>
       <c r="N744" s="16" t="inlineStr">
         <is>
-          <t>我們最近好像進入倦怠期了。</t>
+          <t>等男友退伍的日子只剩六個月了。</t>
         </is>
       </c>
       <c r="O744" s="16" t="inlineStr">
         <is>
-          <t>我们最近好像进入倦怠期了。</t>
+          <t>等男友退伍的日子只剩六个月了。</t>
         </is>
       </c>
       <c r="P744" s="16" t="inlineStr">
         <is>
-          <t>最近倦怠期っぽい気がする。</t>
+          <t>彼の除隊を待つ生活も、あと6ヶ月。</t>
         </is>
       </c>
       <c r="Q744" s="16" t="inlineStr">
         <is>
-          <t>Relationship talk, dramas</t>
+          <t>Military service relationship talk</t>
         </is>
       </c>
       <c r="R744" s="15" t="inlineStr">
@@ -72915,17 +72915,17 @@
     <row r="745" ht="46" customHeight="1">
       <c r="A745" s="15" t="inlineStr">
         <is>
-          <t>DAT-052</t>
+          <t>DAT-050</t>
         </is>
       </c>
       <c r="B745" s="15" t="inlineStr">
         <is>
-          <t>연상연하</t>
+          <t>장거리연애</t>
         </is>
       </c>
       <c r="C745" s="15" t="inlineStr">
         <is>
-          <t>yeon-sang-yeon-ha</t>
+          <t>jang-geo-ri-yeon-ae</t>
         </is>
       </c>
       <c r="D745" s="15" t="inlineStr">
@@ -72940,62 +72940,62 @@
       </c>
       <c r="F745" s="16" t="inlineStr">
         <is>
-          <t>A relationship where one partner is noticeably older (연상) and the other younger (연하) — a common K-drama dynamic.</t>
+          <t>A romantic relationship where the couple lives far apart from each other.</t>
         </is>
       </c>
       <c r="G745" s="16" t="inlineStr">
         <is>
-          <t>Una relación donde una pareja es notablemente mayor (연상) y la otra más joven (연하), una dinámica común en los K-dramas.</t>
+          <t>Una relación romántica donde la pareja vive lejos el uno del otro.</t>
         </is>
       </c>
       <c r="H745" s="16" t="inlineStr">
         <is>
-          <t>一方明顯年長（연상）、另一方較年輕（연하）的戀愛關係——韓劇常見的組合。</t>
+          <t>情侶分隔兩地、住得很遠的戀愛關係，遠距離戀愛。</t>
         </is>
       </c>
       <c r="I745" s="16" t="inlineStr">
         <is>
-          <t>一方明显年长（연상）、另一方较年轻（연하）的恋爱关系——韩剧常见的组合。</t>
+          <t>情侣分隔两地、住得很远的恋爱关系，远距离恋爱。</t>
         </is>
       </c>
       <c r="J745" s="16" t="inlineStr">
         <is>
-          <t>一方が明らかに年上（연상）、もう一方が年下（연하）の恋愛関係——韓国ドラマによくある組み合わせ。</t>
+          <t>カップルが離れて暮らす恋愛関係。</t>
         </is>
       </c>
       <c r="K745" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 연상연하 커플이야.</t>
+          <t>장거리연애 힘들지만 잘 버티고 있어.</t>
         </is>
       </c>
       <c r="L745" s="16" t="inlineStr">
         <is>
-          <t>This drama has an age-gap couple.</t>
+          <t>Long-distance is hard, but we're holding up well.</t>
         </is>
       </c>
       <c r="M745" s="16" t="inlineStr">
         <is>
-          <t>Este drama tiene una pareja con diferencia de edad.</t>
+          <t>La distancia es difícil, pero lo estamos llevando bien.</t>
         </is>
       </c>
       <c r="N745" s="16" t="inlineStr">
         <is>
-          <t>這部劇是姊弟戀組合。</t>
+          <t>遠距離戀愛雖然辛苦，但撐得很好。</t>
         </is>
       </c>
       <c r="O745" s="16" t="inlineStr">
         <is>
-          <t>这部剧是姊弟恋组合。</t>
+          <t>远距离恋爱虽然辛苦，但撑得很好。</t>
         </is>
       </c>
       <c r="P745" s="16" t="inlineStr">
         <is>
-          <t>このドラマ、年上年下カップルだよ。</t>
+          <t>遠距離恋愛は大変だけど、うまくやってる。</t>
         </is>
       </c>
       <c r="Q745" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>Relationship talk</t>
         </is>
       </c>
       <c r="R745" s="15" t="inlineStr">
@@ -73012,17 +73012,17 @@
     <row r="746" ht="46" customHeight="1">
       <c r="A746" s="15" t="inlineStr">
         <is>
-          <t>DAT-053</t>
+          <t>DAT-051</t>
         </is>
       </c>
       <c r="B746" s="15" t="inlineStr">
         <is>
-          <t>로맨스판타지</t>
+          <t>권태기</t>
         </is>
       </c>
       <c r="C746" s="15" t="inlineStr">
         <is>
-          <t>ro-maen-seu-pan-ta-ji</t>
+          <t>gwon-tae-gi</t>
         </is>
       </c>
       <c r="D746" s="15" t="inlineStr">
@@ -73037,62 +73037,62 @@
       </c>
       <c r="F746" s="16" t="inlineStr">
         <is>
-          <t>"Romantasy" — a hugely popular web novel and webtoon genre blending romance with a fantasy setting, often featuring reincarnation.</t>
+          <t>A phase in a relationship marked by boredom or waning excitement.</t>
         </is>
       </c>
       <c r="G746" s="16" t="inlineStr">
         <is>
-          <t>"Romantasía": un género de novelas web y webtoons muy popular que combina romance con un escenario de fantasía, a menudo con reencarnación.</t>
+          <t>Una fase en una relación marcada por el aburrimiento o la disminución del entusiasmo.</t>
         </is>
       </c>
       <c r="H746" s="16" t="inlineStr">
         <is>
-          <t>「浪漫奇幻」——結合戀愛與奇幻背景設定、常帶有轉生元素的超人氣網路小說與網漫類型。</t>
+          <t>感情中出現無聊感或熱情消退的階段，倦怠期。</t>
         </is>
       </c>
       <c r="I746" s="16" t="inlineStr">
         <is>
-          <t>“浪漫奇幻”——结合恋爱与奇幻背景设置、常带有转生元素的超人气网络小说与网漫类型。</t>
+          <t>感情中出现无聊感或热情消退的阶段，倦怠期。</t>
         </is>
       </c>
       <c r="J746" s="16" t="inlineStr">
         <is>
-          <t>「ロマンタジー」——恋愛とファンタジー設定を組み合わせた、ウェブ小説とウェブトゥーンで大人気のジャンルで、転生要素を含むことが多い。</t>
+          <t>退屈さや情熱の低下が見られる、関係の一時期。</t>
         </is>
       </c>
       <c r="K746" s="16" t="inlineStr">
         <is>
-          <t>요즘 로맨스판타지 웹툰에 완전 빠졌어.</t>
+          <t>우리 요즘 권태기인 것 같아.</t>
         </is>
       </c>
       <c r="L746" s="16" t="inlineStr">
         <is>
-          <t>I've totally fallen into romance-fantasy webtoons lately.</t>
+          <t>I think we're going through a relationship rut lately.</t>
         </is>
       </c>
       <c r="M746" s="16" t="inlineStr">
         <is>
-          <t>Últimamente estoy súper metida en los webtoons de romance y fantasía.</t>
+          <t>Creo que estamos pasando por una etapa de aburrimiento últimamente.</t>
         </is>
       </c>
       <c r="N746" s="16" t="inlineStr">
         <is>
-          <t>最近完全沉迷浪漫奇幻網漫。</t>
+          <t>我們最近好像進入倦怠期了。</t>
         </is>
       </c>
       <c r="O746" s="16" t="inlineStr">
         <is>
-          <t>最近完全沉迷浪漫奇幻网漫。</t>
+          <t>我们最近好像进入倦怠期了。</t>
         </is>
       </c>
       <c r="P746" s="16" t="inlineStr">
         <is>
-          <t>最近ロマンスファンタジーのウェブトゥーンにハマってる。</t>
+          <t>最近倦怠期っぽい気がする。</t>
         </is>
       </c>
       <c r="Q746" s="16" t="inlineStr">
         <is>
-          <t>Webtoon/web novel genre talk</t>
+          <t>Relationship talk, dramas</t>
         </is>
       </c>
       <c r="R746" s="15" t="inlineStr">
@@ -73109,17 +73109,17 @@
     <row r="747" ht="46" customHeight="1">
       <c r="A747" s="15" t="inlineStr">
         <is>
-          <t>DAT-054</t>
+          <t>DAT-052</t>
         </is>
       </c>
       <c r="B747" s="15" t="inlineStr">
         <is>
-          <t>상사병</t>
+          <t>연상연하</t>
         </is>
       </c>
       <c r="C747" s="15" t="inlineStr">
         <is>
-          <t>sang-sa-byeong</t>
+          <t>yeon-sang-yeon-ha</t>
         </is>
       </c>
       <c r="D747" s="15" t="inlineStr">
@@ -73134,62 +73134,62 @@
       </c>
       <c r="F747" s="16" t="inlineStr">
         <is>
-          <t>"Longing illness" — being so consumed by romantic longing for someone that it feels like a sickness.</t>
+          <t>A relationship where one partner is noticeably older (연상) and the other younger (연하) — a common K-drama dynamic.</t>
         </is>
       </c>
       <c r="G747" s="16" t="inlineStr">
         <is>
-          <t>"Enfermedad de anhelo": estar tan consumido por el anhelo romántico por alguien que se siente como una enfermedad.</t>
+          <t>Una relación donde una pareja es notablemente mayor (연상) y la otra más joven (연하), una dinámica común en los K-dramas.</t>
         </is>
       </c>
       <c r="H747" s="16" t="inlineStr">
         <is>
-          <t>「思念之病」——被對某人的思念淹沒到彷彿生病一般，相思病。</t>
+          <t>一方明顯年長（연상）、另一方較年輕（연하）的戀愛關係——韓劇常見的組合。</t>
         </is>
       </c>
       <c r="I747" s="16" t="inlineStr">
         <is>
-          <t>“思念之病”——被对某人的思念淹没到仿佛生病一般，相思病。</t>
+          <t>一方明显年长（연상）、另一方较年轻（연하）的恋爱关系——韩剧常见的组合。</t>
         </is>
       </c>
       <c r="J747" s="16" t="inlineStr">
         <is>
-          <t>「恋しさの病」——誰かへの恋しさに完全にとらわれて、まるで病気のように感じること。</t>
+          <t>一方が明らかに年上（연상）、もう一方が年下（연하）の恋愛関係——韓国ドラマによくある組み合わせ。</t>
         </is>
       </c>
       <c r="K747" s="16" t="inlineStr">
         <is>
-          <t>완전 상사병 걸린 것 같아.</t>
+          <t>이 드라마 연상연하 커플이야.</t>
         </is>
       </c>
       <c r="L747" s="16" t="inlineStr">
         <is>
-          <t>I think I've totally caught lovesickness.</t>
+          <t>This drama has an age-gap couple.</t>
         </is>
       </c>
       <c r="M747" s="16" t="inlineStr">
         <is>
-          <t>Creo que me dio mal de amores por completo.</t>
+          <t>Este drama tiene una pareja con diferencia de edad.</t>
         </is>
       </c>
       <c r="N747" s="16" t="inlineStr">
         <is>
-          <t>我好像得了相思病。</t>
+          <t>這部劇是姊弟戀組合。</t>
         </is>
       </c>
       <c r="O747" s="16" t="inlineStr">
         <is>
-          <t>我好像得了相思病。</t>
+          <t>这部剧是姊弟恋组合。</t>
         </is>
       </c>
       <c r="P747" s="16" t="inlineStr">
         <is>
-          <t>完全に恋煩いにかかったみたい。</t>
+          <t>このドラマ、年上年下カップルだよ。</t>
         </is>
       </c>
       <c r="Q747" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk, casual speech</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R747" s="15" t="inlineStr">
@@ -73206,17 +73206,17 @@
     <row r="748" ht="46" customHeight="1">
       <c r="A748" s="15" t="inlineStr">
         <is>
-          <t>DAT-055</t>
+          <t>DAT-053</t>
         </is>
       </c>
       <c r="B748" s="15" t="inlineStr">
         <is>
-          <t>첫눈에반하다</t>
+          <t>로맨스판타지</t>
         </is>
       </c>
       <c r="C748" s="15" t="inlineStr">
         <is>
-          <t>cheot-nun-e-ban-ha-da</t>
+          <t>ro-maen-seu-pan-ta-ji</t>
         </is>
       </c>
       <c r="D748" s="15" t="inlineStr">
@@ -73231,62 +73231,62 @@
       </c>
       <c r="F748" s="16" t="inlineStr">
         <is>
-          <t>Falling in love with someone the very first moment you see them.</t>
+          <t>"Romantasy" — a hugely popular web novel and webtoon genre blending romance with a fantasy setting, often featuring reincarnation.</t>
         </is>
       </c>
       <c r="G748" s="16" t="inlineStr">
         <is>
-          <t>Enamorarse de alguien desde el primer momento en que lo ves.</t>
+          <t>"Romantasía": un género de novelas web y webtoons muy popular que combina romance con un escenario de fantasía, a menudo con reencarnación.</t>
         </is>
       </c>
       <c r="H748" s="16" t="inlineStr">
         <is>
-          <t>第一眼看到某人就墜入愛河，一見鍾情。</t>
+          <t>「浪漫奇幻」——結合戀愛與奇幻背景設定、常帶有轉生元素的超人氣網路小說與網漫類型。</t>
         </is>
       </c>
       <c r="I748" s="16" t="inlineStr">
         <is>
-          <t>第一眼看到某人就坠入爱河，一见钟情。</t>
+          <t>“浪漫奇幻”——结合恋爱与奇幻背景设置、常带有转生元素的超人气网络小说与网漫类型。</t>
         </is>
       </c>
       <c r="J748" s="16" t="inlineStr">
         <is>
-          <t>相手を初めて見た瞬間に恋に落ちること。</t>
+          <t>「ロマンタジー」——恋愛とファンタジー設定を組み合わせた、ウェブ小説とウェブトゥーンで大人気のジャンルで、転生要素を含むことが多い。</t>
         </is>
       </c>
       <c r="K748" s="16" t="inlineStr">
         <is>
-          <t>첫눈에반했다는 게 무슨 느낌인지 이제 알겠어.</t>
+          <t>요즘 로맨스판타지 웹툰에 완전 빠졌어.</t>
         </is>
       </c>
       <c r="L748" s="16" t="inlineStr">
         <is>
-          <t>I finally understand what love at first sight feels like.</t>
+          <t>I've totally fallen into romance-fantasy webtoons lately.</t>
         </is>
       </c>
       <c r="M748" s="16" t="inlineStr">
         <is>
-          <t>Por fin entiendo qué se siente el amor a primera vista.</t>
+          <t>Últimamente estoy súper metida en los webtoons de romance y fantasía.</t>
         </is>
       </c>
       <c r="N748" s="16" t="inlineStr">
         <is>
-          <t>現在終於懂一見鍾情是什麼感覺了。</t>
+          <t>最近完全沉迷浪漫奇幻網漫。</t>
         </is>
       </c>
       <c r="O748" s="16" t="inlineStr">
         <is>
-          <t>现在终于懂一见钟情是什么感觉了。</t>
+          <t>最近完全沉迷浪漫奇幻网漫。</t>
         </is>
       </c>
       <c r="P748" s="16" t="inlineStr">
         <is>
-          <t>一目惚れってどんな感じかやっとわかった。</t>
+          <t>最近ロマンスファンタジーのウェブトゥーンにハマってる。</t>
         </is>
       </c>
       <c r="Q748" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>Webtoon/web novel genre talk</t>
         </is>
       </c>
       <c r="R748" s="15" t="inlineStr">
@@ -73303,17 +73303,17 @@
     <row r="749" ht="46" customHeight="1">
       <c r="A749" s="15" t="inlineStr">
         <is>
-          <t>DAT-056</t>
+          <t>DAT-054</t>
         </is>
       </c>
       <c r="B749" s="15" t="inlineStr">
         <is>
-          <t>고백</t>
+          <t>상사병</t>
         </is>
       </c>
       <c r="C749" s="15" t="inlineStr">
         <is>
-          <t>go-baek</t>
+          <t>sang-sa-byeong</t>
         </is>
       </c>
       <c r="D749" s="15" t="inlineStr">
@@ -73328,62 +73328,62 @@
       </c>
       <c r="F749" s="16" t="inlineStr">
         <is>
-          <t>Confessing romantic feelings to someone.</t>
+          <t>"Longing illness" — being so consumed by romantic longing for someone that it feels like a sickness.</t>
         </is>
       </c>
       <c r="G749" s="16" t="inlineStr">
         <is>
-          <t>Confesar sentimientos románticos a alguien.</t>
+          <t>"Enfermedad de anhelo": estar tan consumido por el anhelo romántico por alguien que se siente como una enfermedad.</t>
         </is>
       </c>
       <c r="H749" s="16" t="inlineStr">
         <is>
-          <t>向某人表白自己的戀愛心意，告白。</t>
+          <t>「思念之病」——被對某人的思念淹沒到彷彿生病一般，相思病。</t>
         </is>
       </c>
       <c r="I749" s="16" t="inlineStr">
         <is>
-          <t>向某人表白自己的恋爱心意，告白。</t>
+          <t>“思念之病”——被对某人的思念淹没到仿佛生病一般，相思病。</t>
         </is>
       </c>
       <c r="J749" s="16" t="inlineStr">
         <is>
-          <t>相手に恋愛感情を打ち明けること。</t>
+          <t>「恋しさの病」——誰かへの恋しさに完全にとらわれて、まるで病気のように感じること。</t>
         </is>
       </c>
       <c r="K749" s="16" t="inlineStr">
         <is>
-          <t>드디어 고백했어!</t>
+          <t>완전 상사병 걸린 것 같아.</t>
         </is>
       </c>
       <c r="L749" s="16" t="inlineStr">
         <is>
-          <t>I finally confessed my feelings!</t>
+          <t>I think I've totally caught lovesickness.</t>
         </is>
       </c>
       <c r="M749" s="16" t="inlineStr">
         <is>
-          <t>¡Por fin confesé mis sentimientos!</t>
+          <t>Creo que me dio mal de amores por completo.</t>
         </is>
       </c>
       <c r="N749" s="16" t="inlineStr">
         <is>
-          <t>終於告白了！</t>
+          <t>我好像得了相思病。</t>
         </is>
       </c>
       <c r="O749" s="16" t="inlineStr">
         <is>
-          <t>终于告白了！</t>
+          <t>我好像得了相思病。</t>
         </is>
       </c>
       <c r="P749" s="16" t="inlineStr">
         <is>
-          <t>ついに告白した！</t>
+          <t>完全に恋煩いにかかったみたい。</t>
         </is>
       </c>
       <c r="Q749" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk, casual dating talk</t>
+          <t>K-drama trope talk, casual speech</t>
         </is>
       </c>
       <c r="R749" s="15" t="inlineStr">
@@ -73400,17 +73400,17 @@
     <row r="750" ht="46" customHeight="1">
       <c r="A750" s="15" t="inlineStr">
         <is>
-          <t>DAT-057</t>
+          <t>DAT-055</t>
         </is>
       </c>
       <c r="B750" s="15" t="inlineStr">
         <is>
-          <t>데이트코스</t>
+          <t>첫눈에반하다</t>
         </is>
       </c>
       <c r="C750" s="15" t="inlineStr">
         <is>
-          <t>de-i-teu-ko-seu</t>
+          <t>cheot-nun-e-ban-ha-da</t>
         </is>
       </c>
       <c r="D750" s="15" t="inlineStr">
@@ -73425,62 +73425,62 @@
       </c>
       <c r="F750" s="16" t="inlineStr">
         <is>
-          <t>"Date course" — a planned sequence of activities and locations for a date.</t>
+          <t>Falling in love with someone the very first moment you see them.</t>
         </is>
       </c>
       <c r="G750" s="16" t="inlineStr">
         <is>
-          <t>"Curso de cita": una secuencia planeada de actividades y lugares para una cita.</t>
+          <t>Enamorarse de alguien desde el primer momento en que lo ves.</t>
         </is>
       </c>
       <c r="H750" s="16" t="inlineStr">
         <is>
-          <t>事先規劃好的約會活動與地點行程，約會行程。</t>
+          <t>第一眼看到某人就墜入愛河，一見鍾情。</t>
         </is>
       </c>
       <c r="I750" s="16" t="inlineStr">
         <is>
-          <t>事先规划好的约会活动与地点行程，约会行程。</t>
+          <t>第一眼看到某人就坠入爱河，一见钟情。</t>
         </is>
       </c>
       <c r="J750" s="16" t="inlineStr">
         <is>
-          <t>「デートコース」——事前に計画されたデートの活動や場所の順序。</t>
+          <t>相手を初めて見た瞬間に恋に落ちること。</t>
         </is>
       </c>
       <c r="K750" s="16" t="inlineStr">
         <is>
-          <t>데이트코스 다 짜놨어.</t>
+          <t>첫눈에반했다는 게 무슨 느낌인지 이제 알겠어.</t>
         </is>
       </c>
       <c r="L750" s="16" t="inlineStr">
         <is>
-          <t>I already planned out the whole date itinerary.</t>
+          <t>I finally understand what love at first sight feels like.</t>
         </is>
       </c>
       <c r="M750" s="16" t="inlineStr">
         <is>
-          <t>Ya planeé todo el itinerario de la cita.</t>
+          <t>Por fin entiendo qué se siente el amor a primera vista.</t>
         </is>
       </c>
       <c r="N750" s="16" t="inlineStr">
         <is>
-          <t>已經規劃好整個約會行程了。</t>
+          <t>現在終於懂一見鍾情是什麼感覺了。</t>
         </is>
       </c>
       <c r="O750" s="16" t="inlineStr">
         <is>
-          <t>已经规划好整个约会行程了。</t>
+          <t>现在终于懂一见钟情是什么感觉了。</t>
         </is>
       </c>
       <c r="P750" s="16" t="inlineStr">
         <is>
-          <t>デートコース、全部計画済み。</t>
+          <t>一目惚れってどんな感じかやっとわかった。</t>
         </is>
       </c>
       <c r="Q750" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R750" s="15" t="inlineStr">
@@ -73497,17 +73497,17 @@
     <row r="751" ht="46" customHeight="1">
       <c r="A751" s="15" t="inlineStr">
         <is>
-          <t>DAT-058</t>
+          <t>DAT-056</t>
         </is>
       </c>
       <c r="B751" s="15" t="inlineStr">
         <is>
-          <t>백일</t>
+          <t>고백</t>
         </is>
       </c>
       <c r="C751" s="15" t="inlineStr">
         <is>
-          <t>baek-il</t>
+          <t>go-baek</t>
         </is>
       </c>
       <c r="D751" s="15" t="inlineStr">
@@ -73522,62 +73522,62 @@
       </c>
       <c r="F751" s="16" t="inlineStr">
         <is>
-          <t>The 100-day relationship milestone, commonly celebrated by Korean couples.</t>
+          <t>Confessing romantic feelings to someone.</t>
         </is>
       </c>
       <c r="G751" s="16" t="inlineStr">
         <is>
-          <t>El hito de los 100 días de relación, comúnmente celebrado por las parejas coreanas.</t>
+          <t>Confesar sentimientos románticos a alguien.</t>
         </is>
       </c>
       <c r="H751" s="16" t="inlineStr">
         <is>
-          <t>韓國情侶常慶祝的交往一百天紀念日。</t>
+          <t>向某人表白自己的戀愛心意，告白。</t>
         </is>
       </c>
       <c r="I751" s="16" t="inlineStr">
         <is>
-          <t>韩国情侣常庆祝的交往一百天纪念日。</t>
+          <t>向某人表白自己的恋爱心意，告白。</t>
         </is>
       </c>
       <c r="J751" s="16" t="inlineStr">
         <is>
-          <t>韓国のカップルがよく祝う、交際100日の記念日。</t>
+          <t>相手に恋愛感情を打ち明けること。</t>
         </is>
       </c>
       <c r="K751" s="16" t="inlineStr">
         <is>
-          <t>이번 주 백일이라 선물 준비했어.</t>
+          <t>드디어 고백했어!</t>
         </is>
       </c>
       <c r="L751" s="16" t="inlineStr">
         <is>
-          <t>This week is our 100-day anniversary, so I prepared a gift.</t>
+          <t>I finally confessed my feelings!</t>
         </is>
       </c>
       <c r="M751" s="16" t="inlineStr">
         <is>
-          <t>Esta semana cumplimos 100 días, así que preparé un regalo.</t>
+          <t>¡Por fin confesé mis sentimientos!</t>
         </is>
       </c>
       <c r="N751" s="16" t="inlineStr">
         <is>
-          <t>這禮拜是百日紀念，準備了禮物。</t>
+          <t>終於告白了！</t>
         </is>
       </c>
       <c r="O751" s="16" t="inlineStr">
         <is>
-          <t>这礼拜是百日纪念，准备了礼物。</t>
+          <t>终于告白了！</t>
         </is>
       </c>
       <c r="P751" s="16" t="inlineStr">
         <is>
-          <t>今週100日記念日だから、プレゼント準備した。</t>
+          <t>ついに告白した！</t>
         </is>
       </c>
       <c r="Q751" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, casual dating talk</t>
+          <t>K-drama trope talk, casual dating talk</t>
         </is>
       </c>
       <c r="R751" s="15" t="inlineStr">
@@ -73594,17 +73594,17 @@
     <row r="752" ht="46" customHeight="1">
       <c r="A752" s="15" t="inlineStr">
         <is>
-          <t>DAT-059</t>
+          <t>DAT-057</t>
         </is>
       </c>
       <c r="B752" s="15" t="inlineStr">
         <is>
-          <t>연애세포</t>
+          <t>데이트코스</t>
         </is>
       </c>
       <c r="C752" s="15" t="inlineStr">
         <is>
-          <t>yeon-ae-se-po</t>
+          <t>de-i-teu-ko-seu</t>
         </is>
       </c>
       <c r="D752" s="15" t="inlineStr">
@@ -73619,57 +73619,57 @@
       </c>
       <c r="F752" s="16" t="inlineStr">
         <is>
-          <t>"Romance cells" — one's inner drive or interest in dating and romance.</t>
+          <t>"Date course" — a planned sequence of activities and locations for a date.</t>
         </is>
       </c>
       <c r="G752" s="16" t="inlineStr">
         <is>
-          <t>"Células de romance": el impulso o interés interno de alguien por las citas y el romance.</t>
+          <t>"Curso de cita": una secuencia planeada de actividades y lugares para una cita.</t>
         </is>
       </c>
       <c r="H752" s="16" t="inlineStr">
         <is>
-          <t>「戀愛細胞」——一個人對談戀愛、交往的內在動力或興趣。</t>
+          <t>事先規劃好的約會活動與地點行程，約會行程。</t>
         </is>
       </c>
       <c r="I752" s="16" t="inlineStr">
         <is>
-          <t>“恋爱细胞”——一个人对谈恋爱、交往的内在动力或兴趣。</t>
+          <t>事先规划好的约会活动与地点行程，约会行程。</t>
         </is>
       </c>
       <c r="J752" s="16" t="inlineStr">
         <is>
-          <t>「恋愛の細胞」——恋愛やデートへの内なる意欲や興味。</t>
+          <t>「デートコース」——事前に計画されたデートの活動や場所の順序。</t>
         </is>
       </c>
       <c r="K752" s="16" t="inlineStr">
         <is>
-          <t>연애세포가 다 죽은 것 같아.</t>
+          <t>데이트코스 다 짜놨어.</t>
         </is>
       </c>
       <c r="L752" s="16" t="inlineStr">
         <is>
-          <t>I feel like my romance drive has completely died.</t>
+          <t>I already planned out the whole date itinerary.</t>
         </is>
       </c>
       <c r="M752" s="16" t="inlineStr">
         <is>
-          <t>Siento que mi interés por el romance murió por completo.</t>
+          <t>Ya planeé todo el itinerario de la cita.</t>
         </is>
       </c>
       <c r="N752" s="16" t="inlineStr">
         <is>
-          <t>感覺我的戀愛細胞都死光了。</t>
+          <t>已經規劃好整個約會行程了。</t>
         </is>
       </c>
       <c r="O752" s="16" t="inlineStr">
         <is>
-          <t>感觉我的恋爱细胞都死光了。</t>
+          <t>已经规划好整个约会行程了。</t>
         </is>
       </c>
       <c r="P752" s="16" t="inlineStr">
         <is>
-          <t>恋愛細胞が全部死んだ気がする。</t>
+          <t>デートコース、全部計画済み。</t>
         </is>
       </c>
       <c r="Q752" s="16" t="inlineStr">
@@ -73691,17 +73691,17 @@
     <row r="753" ht="46" customHeight="1">
       <c r="A753" s="15" t="inlineStr">
         <is>
-          <t>DAT-060</t>
+          <t>DAT-058</t>
         </is>
       </c>
       <c r="B753" s="15" t="inlineStr">
         <is>
-          <t>순정만화</t>
+          <t>백일</t>
         </is>
       </c>
       <c r="C753" s="15" t="inlineStr">
         <is>
-          <t>sun-jeong-man-hwa</t>
+          <t>baek-il</t>
         </is>
       </c>
       <c r="D753" s="15" t="inlineStr">
@@ -73716,67 +73716,67 @@
       </c>
       <c r="F753" s="16" t="inlineStr">
         <is>
-          <t>"Pure-love comic" — a genre label for sweet, innocent romance stories, often used to describe an idealized real-life romance.</t>
+          <t>The 100-day relationship milestone, commonly celebrated by Korean couples.</t>
         </is>
       </c>
       <c r="G753" s="16" t="inlineStr">
         <is>
-          <t>"Cómic de amor puro": una etiqueta de género para historias de romance dulces e inocentes, usada a menudo para describir un romance real idealizado.</t>
+          <t>El hito de los 100 días de relación, comúnmente celebrado por las parejas coreanas.</t>
         </is>
       </c>
       <c r="H753" s="16" t="inlineStr">
         <is>
-          <t>「純愛漫畫」——形容甜美、純真的戀愛故事類型，也用來形容如漫畫般理想化的真實戀情。</t>
+          <t>韓國情侶常慶祝的交往一百天紀念日。</t>
         </is>
       </c>
       <c r="I753" s="16" t="inlineStr">
         <is>
-          <t>“纯爱漫画”——形容甜美、纯真的恋爱故事类型，也用来形容如漫画般理想化的真实恋情。</t>
+          <t>韩国情侣常庆祝的交往一百天纪念日。</t>
         </is>
       </c>
       <c r="J753" s="16" t="inlineStr">
         <is>
-          <t>「純粋な愛の漫画」——甘く純粋な恋愛物語のジャンルラベルで、理想化された現実の恋愛を表現するのにも使われる。</t>
+          <t>韓国のカップルがよく祝う、交際100日の記念日。</t>
         </is>
       </c>
       <c r="K753" s="16" t="inlineStr">
         <is>
-          <t>저 커플 완전 순정만화 그 자체야.</t>
+          <t>이번 주 백일이라 선물 준비했어.</t>
         </is>
       </c>
       <c r="L753" s="16" t="inlineStr">
         <is>
-          <t>That couple is literally a pure-love comic come to life.</t>
+          <t>This week is our 100-day anniversary, so I prepared a gift.</t>
         </is>
       </c>
       <c r="M753" s="16" t="inlineStr">
         <is>
-          <t>Esa pareja es literalmente un cómic de amor puro hecho realidad.</t>
+          <t>Esta semana cumplimos 100 días, así que preparé un regalo.</t>
         </is>
       </c>
       <c r="N753" s="16" t="inlineStr">
         <is>
-          <t>那對情侶完全就是純愛漫畫本人。</t>
+          <t>這禮拜是百日紀念，準備了禮物。</t>
         </is>
       </c>
       <c r="O753" s="16" t="inlineStr">
         <is>
-          <t>那对情侣完全就是纯爱漫画本人。</t>
+          <t>这礼拜是百日纪念，准备了礼物。</t>
         </is>
       </c>
       <c r="P753" s="16" t="inlineStr">
         <is>
-          <t>あのカップル、完全に純愛漫画そのものだよ。</t>
+          <t>今週100日記念日だから、プレゼント準備した。</t>
         </is>
       </c>
       <c r="Q753" s="16" t="inlineStr">
         <is>
-          <t>K-drama/romance trope talk</t>
+          <t>Couple culture, casual dating talk</t>
         </is>
       </c>
       <c r="R753" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S753" s="15" t="inlineStr">
@@ -73788,17 +73788,17 @@
     <row r="754" ht="46" customHeight="1">
       <c r="A754" s="15" t="inlineStr">
         <is>
-          <t>DAT-061</t>
+          <t>DAT-059</t>
         </is>
       </c>
       <c r="B754" s="15" t="inlineStr">
         <is>
-          <t>심장저격</t>
+          <t>연애세포</t>
         </is>
       </c>
       <c r="C754" s="15" t="inlineStr">
         <is>
-          <t>sim-jang-jeo-gyeok</t>
+          <t>yeon-ae-se-po</t>
         </is>
       </c>
       <c r="D754" s="15" t="inlineStr">
@@ -73813,67 +73813,67 @@
       </c>
       <c r="F754" s="16" t="inlineStr">
         <is>
-          <t>"Heart sniper" — something that strikes directly at your heart, usually describing a romantic or swoon-worthy moment.</t>
+          <t>"Romance cells" — one's inner drive or interest in dating and romance.</t>
         </is>
       </c>
       <c r="G754" s="16" t="inlineStr">
         <is>
-          <t>"Francotirador del corazón": algo que golpea directamente tu corazón, generalmente describiendo un momento romántico o que hace suspirar.</t>
+          <t>"Células de romance": el impulso o interés interno de alguien por las citas y el romance.</t>
         </is>
       </c>
       <c r="H754" s="16" t="inlineStr">
         <is>
-          <t>「心臟狙擊」——直接命中內心、通常用來形容浪漫或令人心動的瞬間。</t>
+          <t>「戀愛細胞」——一個人對談戀愛、交往的內在動力或興趣。</t>
         </is>
       </c>
       <c r="I754" s="16" t="inlineStr">
         <is>
-          <t>“心脏狙击”——直接命中内心、通常用来形容浪漫或令人心动的瞬间。</t>
+          <t>“恋爱细胞”——一个人对谈恋爱、交往的内在动力或兴趣。</t>
         </is>
       </c>
       <c r="J754" s="16" t="inlineStr">
         <is>
-          <t>「心臓狙撃」——ロマンチックで胸きゅんする瞬間を表す時によく使われる、直接心臓を突き刺すようなもの。</t>
+          <t>「恋愛の細胞」——恋愛やデートへの内なる意欲や興味。</t>
         </is>
       </c>
       <c r="K754" s="16" t="inlineStr">
         <is>
-          <t>그 대사 완전 심장저격이었어.</t>
+          <t>연애세포가 다 죽은 것 같아.</t>
         </is>
       </c>
       <c r="L754" s="16" t="inlineStr">
         <is>
-          <t>That line was a total heart sniper.</t>
+          <t>I feel like my romance drive has completely died.</t>
         </is>
       </c>
       <c r="M754" s="16" t="inlineStr">
         <is>
-          <t>Esa frase fue un disparo directo al corazón.</t>
+          <t>Siento que mi interés por el romance murió por completo.</t>
         </is>
       </c>
       <c r="N754" s="16" t="inlineStr">
         <is>
-          <t>那句台詞完全是心臟狙擊。</t>
+          <t>感覺我的戀愛細胞都死光了。</t>
         </is>
       </c>
       <c r="O754" s="16" t="inlineStr">
         <is>
-          <t>那句台词完全是心脏狙击。</t>
+          <t>感觉我的恋爱细胞都死光了。</t>
         </is>
       </c>
       <c r="P754" s="16" t="inlineStr">
         <is>
-          <t>あのセリフ、完全に心臓狙撃だった。</t>
+          <t>恋愛細胞が全部死んだ気がする。</t>
         </is>
       </c>
       <c r="Q754" s="16" t="inlineStr">
         <is>
-          <t>K-drama reactions</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R754" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S754" s="15" t="inlineStr">
@@ -73885,17 +73885,17 @@
     <row r="755" ht="46" customHeight="1">
       <c r="A755" s="15" t="inlineStr">
         <is>
-          <t>DAT-062</t>
+          <t>DAT-060</t>
         </is>
       </c>
       <c r="B755" s="15" t="inlineStr">
         <is>
-          <t>애교</t>
+          <t>순정만화</t>
         </is>
       </c>
       <c r="C755" s="15" t="inlineStr">
         <is>
-          <t>ae-gyo</t>
+          <t>sun-jeong-man-hwa</t>
         </is>
       </c>
       <c r="D755" s="15" t="inlineStr">
@@ -73910,67 +73910,67 @@
       </c>
       <c r="F755" s="16" t="inlineStr">
         <is>
-          <t>Deliberately cute, affectionate speech or behavior — a cutesy voice, pouty expressions, or playful gestures used to charm someone.</t>
+          <t>"Pure-love comic" — a genre label for sweet, innocent romance stories, often used to describe an idealized real-life romance.</t>
         </is>
       </c>
       <c r="G755" s="16" t="inlineStr">
         <is>
-          <t>Habla o comportamiento tierno y afectuoso deliberado: una voz melosa, expresiones de puchero o gestos juguetones usados para encantar a alguien.</t>
+          <t>"Cómic de amor puro": una etiqueta de género para historias de romance dulces e inocentes, usada a menudo para describir un romance real idealizado.</t>
         </is>
       </c>
       <c r="H755" s="16" t="inlineStr">
         <is>
-          <t>刻意展現可愛、撒嬌的言行——嗲聲嗲氣、嘟嘴或俏皮動作，用來討人喜歡，撒嬌。</t>
+          <t>「純愛漫畫」——形容甜美、純真的戀愛故事類型，也用來形容如漫畫般理想化的真實戀情。</t>
         </is>
       </c>
       <c r="I755" s="16" t="inlineStr">
         <is>
-          <t>刻意展现可爱、撒娇的言行——嗲声嗲气、嘟嘴或俏皮动作，用来讨人喜欢，撒娇。</t>
+          <t>“纯爱漫画”——形容甜美、纯真的恋爱故事类型，也用来形容如漫画般理想化的真实恋情。</t>
         </is>
       </c>
       <c r="J755" s="16" t="inlineStr">
         <is>
-          <t>わざと可愛く、愛情を込めた話し方や振る舞い——甘えた声、拗ねた表情、遊び心のあるジェスチャーで相手を魅了すること。</t>
+          <t>「純粋な愛の漫画」——甘く純粋な恋愛物語のジャンルラベルで、理想化された現実の恋愛を表現するのにも使われる。</t>
         </is>
       </c>
       <c r="K755" s="16" t="inlineStr">
         <is>
-          <t>애교 좀 부려봐!</t>
+          <t>저 커플 완전 순정만화 그 자체야.</t>
         </is>
       </c>
       <c r="L755" s="16" t="inlineStr">
         <is>
-          <t>Do some aegyo for me!</t>
+          <t>That couple is literally a pure-love comic come to life.</t>
         </is>
       </c>
       <c r="M755" s="16" t="inlineStr">
         <is>
-          <t>¡Hazme un poco de aegyo!</t>
+          <t>Esa pareja es literalmente un cómic de amor puro hecho realidad.</t>
         </is>
       </c>
       <c r="N755" s="16" t="inlineStr">
         <is>
-          <t>撒嬌一下嘛！</t>
+          <t>那對情侶完全就是純愛漫畫本人。</t>
         </is>
       </c>
       <c r="O755" s="16" t="inlineStr">
         <is>
-          <t>撒娇一下嘛！</t>
+          <t>那对情侣完全就是纯爱漫画本人。</t>
         </is>
       </c>
       <c r="P755" s="16" t="inlineStr">
         <is>
-          <t>愛嬌見せてよ！</t>
+          <t>あのカップル、完全に純愛漫画そのものだよ。</t>
         </is>
       </c>
       <c r="Q755" s="16" t="inlineStr">
         <is>
-          <t>Variety shows, couple culture</t>
+          <t>K-drama/romance trope talk</t>
         </is>
       </c>
       <c r="R755" s="15" t="inlineStr">
         <is>
-          <t>Verified (web-checked)</t>
+          <t>Draft — please double-check</t>
         </is>
       </c>
       <c r="S755" s="15" t="inlineStr">
@@ -73982,17 +73982,17 @@
     <row r="756" ht="46" customHeight="1">
       <c r="A756" s="15" t="inlineStr">
         <is>
-          <t>DAT-063</t>
+          <t>DAT-061</t>
         </is>
       </c>
       <c r="B756" s="15" t="inlineStr">
         <is>
-          <t>사랑꾼</t>
+          <t>심장저격</t>
         </is>
       </c>
       <c r="C756" s="15" t="inlineStr">
         <is>
-          <t>sa-rang-kkun</t>
+          <t>sim-jang-jeo-gyeok</t>
         </is>
       </c>
       <c r="D756" s="15" t="inlineStr">
@@ -74007,67 +74007,67 @@
       </c>
       <c r="F756" s="16" t="inlineStr">
         <is>
-          <t>"Love expert" — someone devotedly romantic who dotes openly on their partner.</t>
+          <t>"Heart sniper" — something that strikes directly at your heart, usually describing a romantic or swoon-worthy moment.</t>
         </is>
       </c>
       <c r="G756" s="16" t="inlineStr">
         <is>
-          <t>"Experto en amor": alguien devotamente romántico que consiente abiertamente a su pareja.</t>
+          <t>"Francotirador del corazón": algo que golpea directamente tu corazón, generalmente describiendo un momento romántico o que hace suspirar.</t>
         </is>
       </c>
       <c r="H756" s="16" t="inlineStr">
         <is>
-          <t>「愛情達人」——全心全意投入戀愛、公開寵愛另一半的人。</t>
+          <t>「心臟狙擊」——直接命中內心、通常用來形容浪漫或令人心動的瞬間。</t>
         </is>
       </c>
       <c r="I756" s="16" t="inlineStr">
         <is>
-          <t>“爱情达人”——全心全意投入恋爱、公开宠爱另一半的人。</t>
+          <t>“心脏狙击”——直接命中内心、通常用来形容浪漫或令人心动的瞬间。</t>
         </is>
       </c>
       <c r="J756" s="16" t="inlineStr">
         <is>
-          <t>「愛の達人」——恋人に対して献身的で、公然と甘やかす人。</t>
+          <t>「心臓狙撃」——ロマンチックで胸きゅんする瞬間を表す時によく使われる、直接心臓を突き刺すようなもの。</t>
         </is>
       </c>
       <c r="K756" s="16" t="inlineStr">
         <is>
-          <t>저 사람 완전 사랑꾼이야.</t>
+          <t>그 대사 완전 심장저격이었어.</t>
         </is>
       </c>
       <c r="L756" s="16" t="inlineStr">
         <is>
-          <t>That person is a total devoted romantic.</t>
+          <t>That line was a total heart sniper.</t>
         </is>
       </c>
       <c r="M756" s="16" t="inlineStr">
         <is>
-          <t>Esa persona es completamente entregada en el amor.</t>
+          <t>Esa frase fue un disparo directo al corazón.</t>
         </is>
       </c>
       <c r="N756" s="16" t="inlineStr">
         <is>
-          <t>那個人完全是寵愛型戀人。</t>
+          <t>那句台詞完全是心臟狙擊。</t>
         </is>
       </c>
       <c r="O756" s="16" t="inlineStr">
         <is>
-          <t>那个人完全是宠爱型恋人。</t>
+          <t>那句台词完全是心脏狙击。</t>
         </is>
       </c>
       <c r="P756" s="16" t="inlineStr">
         <is>
-          <t>あの人は本当に愛情深いタイプだよ。</t>
+          <t>あのセリフ、完全に心臓狙撃だった。</t>
         </is>
       </c>
       <c r="Q756" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, variety shows</t>
+          <t>K-drama reactions</t>
         </is>
       </c>
       <c r="R756" s="15" t="inlineStr">
         <is>
-          <t>Verified (web-checked)</t>
+          <t>Draft — please double-check</t>
         </is>
       </c>
       <c r="S756" s="15" t="inlineStr">
@@ -74079,17 +74079,17 @@
     <row r="757" ht="46" customHeight="1">
       <c r="A757" s="15" t="inlineStr">
         <is>
-          <t>DAT-064</t>
+          <t>DAT-062</t>
         </is>
       </c>
       <c r="B757" s="15" t="inlineStr">
         <is>
-          <t>잉꼬부부</t>
+          <t>애교</t>
         </is>
       </c>
       <c r="C757" s="15" t="inlineStr">
         <is>
-          <t>ing-kko-bu-bu</t>
+          <t>ae-gyo</t>
         </is>
       </c>
       <c r="D757" s="15" t="inlineStr">
@@ -74104,62 +74104,62 @@
       </c>
       <c r="F757" s="16" t="inlineStr">
         <is>
-          <t>"Lovebird couple" — a married couple who are openly and consistently affectionate with each other.</t>
+          <t>Deliberately cute, affectionate speech or behavior — a cutesy voice, pouty expressions, or playful gestures used to charm someone.</t>
         </is>
       </c>
       <c r="G757" s="16" t="inlineStr">
         <is>
-          <t>"Pareja de pájaros del amor": una pareja casada que es abierta y constantemente cariñosa entre sí.</t>
+          <t>Habla o comportamiento tierno y afectuoso deliberado: una voz melosa, expresiones de puchero o gestos juguetones usados para encantar a alguien.</t>
         </is>
       </c>
       <c r="H757" s="16" t="inlineStr">
         <is>
-          <t>「鴛鴦夫妻」——公開且持續展現親密恩愛的夫妻，恩愛夫妻。</t>
+          <t>刻意展現可愛、撒嬌的言行——嗲聲嗲氣、嘟嘴或俏皮動作，用來討人喜歡，撒嬌。</t>
         </is>
       </c>
       <c r="I757" s="16" t="inlineStr">
         <is>
-          <t>“鸳鸯夫妻”——公开且持续展现亲密恩爱的夫妻，恩爱夫妻。</t>
+          <t>刻意展现可爱、撒娇的言行——嗲声嗲气、嘟嘴或俏皮动作，用来讨人喜欢，撒娇。</t>
         </is>
       </c>
       <c r="J757" s="16" t="inlineStr">
         <is>
-          <t>「インコ夫婦」——常に公然と愛情表現をし合う夫婦。</t>
+          <t>わざと可愛く、愛情を込めた話し方や振る舞い——甘えた声、拗ねた表情、遊び心のあるジェスチャーで相手を魅了すること。</t>
         </is>
       </c>
       <c r="K757" s="16" t="inlineStr">
         <is>
-          <t>저 부부 완전 잉꼬부부야.</t>
+          <t>애교 좀 부려봐!</t>
         </is>
       </c>
       <c r="L757" s="16" t="inlineStr">
         <is>
-          <t>That couple is total lovebirds.</t>
+          <t>Do some aegyo for me!</t>
         </is>
       </c>
       <c r="M757" s="16" t="inlineStr">
         <is>
-          <t>Esa pareja es como tortolitos, siempre cariñosos.</t>
+          <t>¡Hazme un poco de aegyo!</t>
         </is>
       </c>
       <c r="N757" s="16" t="inlineStr">
         <is>
-          <t>那對夫妻完全是恩愛夫妻。</t>
+          <t>撒嬌一下嘛！</t>
         </is>
       </c>
       <c r="O757" s="16" t="inlineStr">
         <is>
-          <t>那对夫妻完全是恩爱夫妻。</t>
+          <t>撒娇一下嘛！</t>
         </is>
       </c>
       <c r="P757" s="16" t="inlineStr">
         <is>
-          <t>あの夫婦、完全におしどり夫婦だよね。</t>
+          <t>愛嬌見せてよ！</t>
         </is>
       </c>
       <c r="Q757" s="16" t="inlineStr">
         <is>
-          <t>Celebrity couple talk</t>
+          <t>Variety shows, couple culture</t>
         </is>
       </c>
       <c r="R757" s="15" t="inlineStr">
@@ -74176,17 +74176,17 @@
     <row r="758" ht="46" customHeight="1">
       <c r="A758" s="15" t="inlineStr">
         <is>
-          <t>DAT-065</t>
+          <t>DAT-063</t>
         </is>
       </c>
       <c r="B758" s="15" t="inlineStr">
         <is>
-          <t>남친룩</t>
+          <t>사랑꾼</t>
         </is>
       </c>
       <c r="C758" s="15" t="inlineStr">
         <is>
-          <t>nam-chin-ruk</t>
+          <t>sa-rang-kkun</t>
         </is>
       </c>
       <c r="D758" s="15" t="inlineStr">
@@ -74201,62 +74201,62 @@
       </c>
       <c r="F758" s="16" t="inlineStr">
         <is>
-          <t>"Boyfriend look" — a guy's outfit or vibe that makes him look like the ideal boyfriend on a date; fans also use it for idol photos that feel like a date.</t>
+          <t>"Love expert" — someone devotedly romantic who dotes openly on their partner.</t>
         </is>
       </c>
       <c r="G758" s="16" t="inlineStr">
         <is>
-          <t>"Look de novio": el outfit o la vibra de un chico que lo hace ver como el novio ideal en una cita; los fans también lo usan para fotos de idols que parecen de una cita.</t>
+          <t>"Experto en amor": alguien devotamente romántico que consiente abiertamente a su pareja.</t>
         </is>
       </c>
       <c r="H758" s="16" t="inlineStr">
         <is>
-          <t>「男友風」——男生看起來像約會中理想男友的穿搭或氛圍；粉絲也用來形容像約會照的偶像照片。</t>
+          <t>「愛情達人」——全心全意投入戀愛、公開寵愛另一半的人。</t>
         </is>
       </c>
       <c r="I758" s="16" t="inlineStr">
         <is>
-          <t>“男友风”——男生看起来像约会中理想男友的穿搭或氛围；粉丝也用来形容像约会照的偶像照片。</t>
+          <t>“爱情达人”——全心全意投入恋爱、公开宠爱另一半的人。</t>
         </is>
       </c>
       <c r="J758" s="16" t="inlineStr">
         <is>
-          <t>「彼氏ルック」——デート中の理想の彼氏みたいに見える男性の服装や雰囲気。デートっぽいアイドルの写真にも使う。</t>
+          <t>「愛の達人」——恋人に対して献身的で、公然と甘やかす人。</t>
         </is>
       </c>
       <c r="K758" s="16" t="inlineStr">
         <is>
-          <t>이 사진 완전 남친룩이다.</t>
+          <t>저 사람 완전 사랑꾼이야.</t>
         </is>
       </c>
       <c r="L758" s="16" t="inlineStr">
         <is>
-          <t>This photo is total boyfriend look.</t>
+          <t>That person is a total devoted romantic.</t>
         </is>
       </c>
       <c r="M758" s="16" t="inlineStr">
         <is>
-          <t>Esta foto es puro look de novio.</t>
+          <t>Esa persona es completamente entregada en el amor.</t>
         </is>
       </c>
       <c r="N758" s="16" t="inlineStr">
         <is>
-          <t>這張照片完全是男友風。</t>
+          <t>那個人完全是寵愛型戀人。</t>
         </is>
       </c>
       <c r="O758" s="16" t="inlineStr">
         <is>
-          <t>这张照片完全是男友风。</t>
+          <t>那个人完全是宠爱型恋人。</t>
         </is>
       </c>
       <c r="P758" s="16" t="inlineStr">
         <is>
-          <t>この写真、完全に彼氏ルックだ。</t>
+          <t>あの人は本当に愛情深いタイプだよ。</t>
         </is>
       </c>
       <c r="Q758" s="16" t="inlineStr">
         <is>
-          <t>Fashion talk</t>
+          <t>Couple culture, variety shows</t>
         </is>
       </c>
       <c r="R758" s="15" t="inlineStr">
@@ -74273,17 +74273,17 @@
     <row r="759" ht="46" customHeight="1">
       <c r="A759" s="15" t="inlineStr">
         <is>
-          <t>DAT-066</t>
+          <t>DAT-064</t>
         </is>
       </c>
       <c r="B759" s="15" t="inlineStr">
         <is>
-          <t>결혼각</t>
+          <t>잉꼬부부</t>
         </is>
       </c>
       <c r="C759" s="15" t="inlineStr">
         <is>
-          <t>gyeol-hon-gak</t>
+          <t>ing-kko-bu-bu</t>
         </is>
       </c>
       <c r="D759" s="15" t="inlineStr">
@@ -74298,67 +74298,67 @@
       </c>
       <c r="F759" s="16" t="inlineStr">
         <is>
-          <t>"Marriage angle" — signs or vibes suggesting a couple might be headed toward marriage.</t>
+          <t>"Lovebird couple" — a married couple who are openly and consistently affectionate with each other.</t>
         </is>
       </c>
       <c r="G759" s="16" t="inlineStr">
         <is>
-          <t>"Ángulo de matrimonio": señales o vibra que sugieren que una pareja podría estar encaminada al matrimonio.</t>
+          <t>"Pareja de pájaros del amor": una pareja casada que es abierta y constantemente cariñosa entre sí.</t>
         </is>
       </c>
       <c r="H759" s="16" t="inlineStr">
         <is>
-          <t>「結婚角度」——顯示一對情侶可能正朝向結婚發展的跡象或氛圍。</t>
+          <t>「鴛鴦夫妻」——公開且持續展現親密恩愛的夫妻，恩愛夫妻。</t>
         </is>
       </c>
       <c r="I759" s="16" t="inlineStr">
         <is>
-          <t>“结婚角度”——显示一对情侣可能正朝向结婚发展的迹象或氛围。</t>
+          <t>“鸳鸯夫妻”——公开且持续展现亲密恩爱的夫妻，恩爱夫妻。</t>
         </is>
       </c>
       <c r="J759" s="16" t="inlineStr">
         <is>
-          <t>「結婚角度」——カップルが結婚に向かっているように見える兆候や雰囲気。</t>
+          <t>「インコ夫婦」——常に公然と愛情表現をし合う夫婦。</t>
         </is>
       </c>
       <c r="K759" s="16" t="inlineStr">
         <is>
-          <t>둘이 완전 결혼각이야.</t>
+          <t>저 부부 완전 잉꼬부부야.</t>
         </is>
       </c>
       <c r="L759" s="16" t="inlineStr">
         <is>
-          <t>Those two have total marriage vibes.</t>
+          <t>That couple is total lovebirds.</t>
         </is>
       </c>
       <c r="M759" s="16" t="inlineStr">
         <is>
-          <t>Esos dos tienen toda la pinta de ir hacia el matrimonio.</t>
+          <t>Esa pareja es como tortolitos, siempre cariñosos.</t>
         </is>
       </c>
       <c r="N759" s="16" t="inlineStr">
         <is>
-          <t>兩人完全有結婚跡象。</t>
+          <t>那對夫妻完全是恩愛夫妻。</t>
         </is>
       </c>
       <c r="O759" s="16" t="inlineStr">
         <is>
-          <t>两人完全有结婚迹象。</t>
+          <t>那对夫妻完全是恩爱夫妻。</t>
         </is>
       </c>
       <c r="P759" s="16" t="inlineStr">
         <is>
-          <t>二人とも完全に結婚の気配だよね。</t>
+          <t>あの夫婦、完全におしどり夫婦だよね。</t>
         </is>
       </c>
       <c r="Q759" s="16" t="inlineStr">
         <is>
-          <t>Celebrity couple speculation</t>
+          <t>Celebrity couple talk</t>
         </is>
       </c>
       <c r="R759" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S759" s="15" t="inlineStr">
@@ -74370,17 +74370,17 @@
     <row r="760" ht="46" customHeight="1">
       <c r="A760" s="15" t="inlineStr">
         <is>
-          <t>DAT-067</t>
+          <t>DAT-065</t>
         </is>
       </c>
       <c r="B760" s="15" t="inlineStr">
         <is>
-          <t>열애중</t>
+          <t>남친룩</t>
         </is>
       </c>
       <c r="C760" s="15" t="inlineStr">
         <is>
-          <t>yeol-ae-jung</t>
+          <t>nam-chin-ruk</t>
         </is>
       </c>
       <c r="D760" s="15" t="inlineStr">
@@ -74395,62 +74395,62 @@
       </c>
       <c r="F760" s="16" t="inlineStr">
         <is>
-          <t>"Currently in a hot romance" — actively dating someone, often used in celebrity news.</t>
+          <t>"Boyfriend look" — a guy's outfit or vibe that makes him look like the ideal boyfriend on a date; fans also use it for idol photos that feel like a date.</t>
         </is>
       </c>
       <c r="G760" s="16" t="inlineStr">
         <is>
-          <t>"Actualmente en un romance ardiente": saliendo activamente con alguien, a menudo usado en noticias de celebridades.</t>
+          <t>"Look de novio": el outfit o la vibra de un chico que lo hace ver como el novio ideal en una cita; los fans también lo usan para fotos de idols que parecen de una cita.</t>
         </is>
       </c>
       <c r="H760" s="16" t="inlineStr">
         <is>
-          <t>「熱戀中」——正在積極交往中，常用於藝人新聞報導。</t>
+          <t>「男友風」——男生看起來像約會中理想男友的穿搭或氛圍；粉絲也用來形容像約會照的偶像照片。</t>
         </is>
       </c>
       <c r="I760" s="16" t="inlineStr">
         <is>
-          <t>“热恋中”——正在积极交往中，常用于艺人新闻报导。</t>
+          <t>“男友风”——男生看起来像约会中理想男友的穿搭或氛围；粉丝也用来形容像约会照的偶像照片。</t>
         </is>
       </c>
       <c r="J760" s="16" t="inlineStr">
         <is>
-          <t>「熱い恋の最中」——現在誰かと積極的に交際していること、芸能ニュースでよく使われる。</t>
+          <t>「彼氏ルック」——デート中の理想の彼氏みたいに見える男性の服装や雰囲気。デートっぽいアイドルの写真にも使う。</t>
         </is>
       </c>
       <c r="K760" s="16" t="inlineStr">
         <is>
-          <t>두 사람 열애중이라는 기사 떴어.</t>
+          <t>이 사진 완전 남친룩이다.</t>
         </is>
       </c>
       <c r="L760" s="16" t="inlineStr">
         <is>
-          <t>An article came out saying the two of them are dating.</t>
+          <t>This photo is total boyfriend look.</t>
         </is>
       </c>
       <c r="M760" s="16" t="inlineStr">
         <is>
-          <t>Salió un artículo diciendo que esos dos están saliendo.</t>
+          <t>Esta foto es puro look de novio.</t>
         </is>
       </c>
       <c r="N760" s="16" t="inlineStr">
         <is>
-          <t>有報導說兩人正在熱戀中。</t>
+          <t>這張照片完全是男友風。</t>
         </is>
       </c>
       <c r="O760" s="16" t="inlineStr">
         <is>
-          <t>有报导说两人正在热恋中。</t>
+          <t>这张照片完全是男友风。</t>
         </is>
       </c>
       <c r="P760" s="16" t="inlineStr">
         <is>
-          <t>二人とも熱愛中だっていう記事出た。</t>
+          <t>この写真、完全に彼氏ルックだ。</t>
         </is>
       </c>
       <c r="Q760" s="16" t="inlineStr">
         <is>
-          <t>Entertainment news</t>
+          <t>Fashion talk</t>
         </is>
       </c>
       <c r="R760" s="15" t="inlineStr">
@@ -74467,17 +74467,17 @@
     <row r="761" ht="46" customHeight="1">
       <c r="A761" s="15" t="inlineStr">
         <is>
-          <t>DAT-068</t>
+          <t>DAT-066</t>
         </is>
       </c>
       <c r="B761" s="15" t="inlineStr">
         <is>
-          <t>솔로탈출</t>
+          <t>결혼각</t>
         </is>
       </c>
       <c r="C761" s="15" t="inlineStr">
         <is>
-          <t>sol-lo-tal-chul</t>
+          <t>gyeol-hon-gak</t>
         </is>
       </c>
       <c r="D761" s="15" t="inlineStr">
@@ -74492,67 +74492,67 @@
       </c>
       <c r="F761" s="16" t="inlineStr">
         <is>
-          <t>"Escaping single life" — finally entering a relationship after being single for a while.</t>
+          <t>"Marriage angle" — signs or vibes suggesting a couple might be headed toward marriage.</t>
         </is>
       </c>
       <c r="G761" s="16" t="inlineStr">
         <is>
-          <t>"Escapar de la soltería": finalmente entrar en una relación después de haber estado soltero por un tiempo.</t>
+          <t>"Ángulo de matrimonio": señales o vibra que sugieren que una pareja podría estar encaminada al matrimonio.</t>
         </is>
       </c>
       <c r="H761" s="16" t="inlineStr">
         <is>
-          <t>「逃離單身」——經過一段單身期後終於進入一段感情，脫單。</t>
+          <t>「結婚角度」——顯示一對情侶可能正朝向結婚發展的跡象或氛圍。</t>
         </is>
       </c>
       <c r="I761" s="16" t="inlineStr">
         <is>
-          <t>“逃离单身”——经过一段单身期后终于进入一段感情，脱单。</t>
+          <t>“结婚角度”——显示一对情侣可能正朝向结婚发展的迹象或氛围。</t>
         </is>
       </c>
       <c r="J761" s="16" t="inlineStr">
         <is>
-          <t>「シングル生活からの脱出」——しばらく独身だった後、ついに恋愛関係に入ること。</t>
+          <t>「結婚角度」——カップルが結婚に向かっているように見える兆候や雰囲気。</t>
         </is>
       </c>
       <c r="K761" s="16" t="inlineStr">
         <is>
-          <t>드디어 솔로탈출 했어!</t>
+          <t>둘이 완전 결혼각이야.</t>
         </is>
       </c>
       <c r="L761" s="16" t="inlineStr">
         <is>
-          <t>I finally escaped single life!</t>
+          <t>Those two have total marriage vibes.</t>
         </is>
       </c>
       <c r="M761" s="16" t="inlineStr">
         <is>
-          <t>¡Por fin dejé de estar soltera!</t>
+          <t>Esos dos tienen toda la pinta de ir hacia el matrimonio.</t>
         </is>
       </c>
       <c r="N761" s="16" t="inlineStr">
         <is>
-          <t>終於脫單了！</t>
+          <t>兩人完全有結婚跡象。</t>
         </is>
       </c>
       <c r="O761" s="16" t="inlineStr">
         <is>
-          <t>终于脱单了！</t>
+          <t>两人完全有结婚迹象。</t>
         </is>
       </c>
       <c r="P761" s="16" t="inlineStr">
         <is>
-          <t>ついに脱ソロした！</t>
+          <t>二人とも完全に結婚の気配だよね。</t>
         </is>
       </c>
       <c r="Q761" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Celebrity couple speculation</t>
         </is>
       </c>
       <c r="R761" s="15" t="inlineStr">
         <is>
-          <t>Verified (web-checked)</t>
+          <t>Draft — please double-check</t>
         </is>
       </c>
       <c r="S761" s="15" t="inlineStr">
@@ -74564,17 +74564,17 @@
     <row r="762" ht="46" customHeight="1">
       <c r="A762" s="15" t="inlineStr">
         <is>
-          <t>DAT-069</t>
+          <t>DAT-067</t>
         </is>
       </c>
       <c r="B762" s="15" t="inlineStr">
         <is>
-          <t>연애고수</t>
+          <t>열애중</t>
         </is>
       </c>
       <c r="C762" s="15" t="inlineStr">
         <is>
-          <t>yeon-ae-go-su</t>
+          <t>yeol-ae-jung</t>
         </is>
       </c>
       <c r="D762" s="15" t="inlineStr">
@@ -74589,62 +74589,62 @@
       </c>
       <c r="F762" s="16" t="inlineStr">
         <is>
-          <t>Someone skilled and experienced at romance and relationships.</t>
+          <t>"Currently in a hot romance" — actively dating someone, often used in celebrity news.</t>
         </is>
       </c>
       <c r="G762" s="16" t="inlineStr">
         <is>
-          <t>Alguien hábil y experimentado en el romance y las relaciones.</t>
+          <t>"Actualmente en un romance ardiente": saliendo activamente con alguien, a menudo usado en noticias de celebridades.</t>
         </is>
       </c>
       <c r="H762" s="16" t="inlineStr">
         <is>
-          <t>在感情與戀愛方面經驗豐富、技巧熟練的人，戀愛高手。</t>
+          <t>「熱戀中」——正在積極交往中，常用於藝人新聞報導。</t>
         </is>
       </c>
       <c r="I762" s="16" t="inlineStr">
         <is>
-          <t>在感情与恋爱方面经验丰富、技巧熟练的人，恋爱高手。</t>
+          <t>“热恋中”——正在积极交往中，常用于艺人新闻报导。</t>
         </is>
       </c>
       <c r="J762" s="16" t="inlineStr">
         <is>
-          <t>恋愛や交際に長けていて、経験豊富な人。</t>
+          <t>「熱い恋の最中」——現在誰かと積極的に交際していること、芸能ニュースでよく使われる。</t>
         </is>
       </c>
       <c r="K762" s="16" t="inlineStr">
         <is>
-          <t>쟤는 진짜 연애고수야.</t>
+          <t>두 사람 열애중이라는 기사 떴어.</t>
         </is>
       </c>
       <c r="L762" s="16" t="inlineStr">
         <is>
-          <t>That person is a real dating master.</t>
+          <t>An article came out saying the two of them are dating.</t>
         </is>
       </c>
       <c r="M762" s="16" t="inlineStr">
         <is>
-          <t>Esa persona es una verdadera maestra del amor.</t>
+          <t>Salió un artículo diciendo que esos dos están saliendo.</t>
         </is>
       </c>
       <c r="N762" s="16" t="inlineStr">
         <is>
-          <t>那個人真的是戀愛高手。</t>
+          <t>有報導說兩人正在熱戀中。</t>
         </is>
       </c>
       <c r="O762" s="16" t="inlineStr">
         <is>
-          <t>那个人真的是恋爱高手。</t>
+          <t>有报导说两人正在热恋中。</t>
         </is>
       </c>
       <c r="P762" s="16" t="inlineStr">
         <is>
-          <t>あの人は本当に恋愛マスターだよ。</t>
+          <t>二人とも熱愛中だっていう記事出た。</t>
         </is>
       </c>
       <c r="Q762" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>Entertainment news</t>
         </is>
       </c>
       <c r="R762" s="15" t="inlineStr">
@@ -74661,17 +74661,17 @@
     <row r="763" ht="46" customHeight="1">
       <c r="A763" s="15" t="inlineStr">
         <is>
-          <t>DAT-070</t>
+          <t>DAT-068</t>
         </is>
       </c>
       <c r="B763" s="15" t="inlineStr">
         <is>
-          <t>애정표현</t>
+          <t>솔로탈출</t>
         </is>
       </c>
       <c r="C763" s="15" t="inlineStr">
         <is>
-          <t>ae-jeong-pyo-hyeon</t>
+          <t>sol-lo-tal-chul</t>
         </is>
       </c>
       <c r="D763" s="15" t="inlineStr">
@@ -74686,62 +74686,62 @@
       </c>
       <c r="F763" s="16" t="inlineStr">
         <is>
-          <t>Openly expressing affection toward a partner, whether verbally or physically.</t>
+          <t>"Escaping single life" — finally entering a relationship after being single for a while.</t>
         </is>
       </c>
       <c r="G763" s="16" t="inlineStr">
         <is>
-          <t>Expresar abiertamente afecto hacia una pareja, ya sea verbal o físicamente.</t>
+          <t>"Escapar de la soltería": finalmente entrar en una relación después de haber estado soltero por un tiempo.</t>
         </is>
       </c>
       <c r="H763" s="16" t="inlineStr">
         <is>
-          <t>無論是言語或肢體上，公開向伴侶表達愛意。</t>
+          <t>「逃離單身」——經過一段單身期後終於進入一段感情，脫單。</t>
         </is>
       </c>
       <c r="I763" s="16" t="inlineStr">
         <is>
-          <t>无论是言语或肢体上，公开向伴侣表达爱意。</t>
+          <t>“逃离单身”——经过一段单身期后终于进入一段感情，脱单。</t>
         </is>
       </c>
       <c r="J763" s="16" t="inlineStr">
         <is>
-          <t>言葉でも身体的にでも、パートナーに対して公然と愛情を表すこと。</t>
+          <t>「シングル生活からの脱出」——しばらく独身だった後、ついに恋愛関係に入ること。</t>
         </is>
       </c>
       <c r="K763" s="16" t="inlineStr">
         <is>
-          <t>둘이 애정표현이 진짜 많아.</t>
+          <t>드디어 솔로탈출 했어!</t>
         </is>
       </c>
       <c r="L763" s="16" t="inlineStr">
         <is>
-          <t>Those two show a lot of affection toward each other.</t>
+          <t>I finally escaped single life!</t>
         </is>
       </c>
       <c r="M763" s="16" t="inlineStr">
         <is>
-          <t>Esos dos se muestran mucho cariño mutuamente.</t>
+          <t>¡Por fin dejé de estar soltera!</t>
         </is>
       </c>
       <c r="N763" s="16" t="inlineStr">
         <is>
-          <t>兩個人真的很常表達愛意。</t>
+          <t>終於脫單了！</t>
         </is>
       </c>
       <c r="O763" s="16" t="inlineStr">
         <is>
-          <t>两个人真的很常表达爱意。</t>
+          <t>终于脱单了！</t>
         </is>
       </c>
       <c r="P763" s="16" t="inlineStr">
         <is>
-          <t>二人とも愛情表現が本当に多いよね。</t>
+          <t>ついに脱ソロした！</t>
         </is>
       </c>
       <c r="Q763" s="16" t="inlineStr">
         <is>
-          <t>Couple culture, dramas</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R763" s="15" t="inlineStr">
@@ -74758,17 +74758,17 @@
     <row r="764" ht="46" customHeight="1">
       <c r="A764" s="15" t="inlineStr">
         <is>
-          <t>DAT-071</t>
+          <t>DAT-069</t>
         </is>
       </c>
       <c r="B764" s="15" t="inlineStr">
         <is>
-          <t>짝꿍</t>
+          <t>연애고수</t>
         </is>
       </c>
       <c r="C764" s="15" t="inlineStr">
         <is>
-          <t>jjak-kkung</t>
+          <t>yeon-ae-go-su</t>
         </is>
       </c>
       <c r="D764" s="15" t="inlineStr">
@@ -74783,62 +74783,62 @@
       </c>
       <c r="F764" s="16" t="inlineStr">
         <is>
-          <t>A cute, informal term for a significant other or a close paired friend.</t>
+          <t>Someone skilled and experienced at romance and relationships.</t>
         </is>
       </c>
       <c r="G764" s="16" t="inlineStr">
         <is>
-          <t>Un término tierno e informal para una pareja sentimental o un amigo cercano emparejado.</t>
+          <t>Alguien hábil y experimentado en el romance y las relaciones.</t>
         </is>
       </c>
       <c r="H764" s="16" t="inlineStr">
         <is>
-          <t>對另一半或親密好友的可愛、非正式稱呼。</t>
+          <t>在感情與戀愛方面經驗豐富、技巧熟練的人，戀愛高手。</t>
         </is>
       </c>
       <c r="I764" s="16" t="inlineStr">
         <is>
-          <t>对另一半或亲密好友的可爱、非正式称呼。</t>
+          <t>在感情与恋爱方面经验丰富、技巧熟练的人，恋爱高手。</t>
         </is>
       </c>
       <c r="J764" s="16" t="inlineStr">
         <is>
-          <t>恋人や親しい相手を指す、可愛くてカジュアルな呼び方。</t>
+          <t>恋愛や交際に長けていて、経験豊富な人。</t>
         </is>
       </c>
       <c r="K764" s="16" t="inlineStr">
         <is>
-          <t>내 짝꿍이랑 데이트하고 왔어.</t>
+          <t>쟤는 진짜 연애고수야.</t>
         </is>
       </c>
       <c r="L764" s="16" t="inlineStr">
         <is>
-          <t>I just came back from a date with my sweetheart.</t>
+          <t>That person is a real dating master.</t>
         </is>
       </c>
       <c r="M764" s="16" t="inlineStr">
         <is>
-          <t>Acabo de volver de una cita con mi pareja.</t>
+          <t>Esa persona es una verdadera maestra del amor.</t>
         </is>
       </c>
       <c r="N764" s="16" t="inlineStr">
         <is>
-          <t>剛跟我的另一半約會回來。</t>
+          <t>那個人真的是戀愛高手。</t>
         </is>
       </c>
       <c r="O764" s="16" t="inlineStr">
         <is>
-          <t>刚跟我的另一半约会回来。</t>
+          <t>那个人真的是恋爱高手。</t>
         </is>
       </c>
       <c r="P764" s="16" t="inlineStr">
         <is>
-          <t>相棒とデートしてきた。</t>
+          <t>あの人は本当に恋愛マスターだよ。</t>
         </is>
       </c>
       <c r="Q764" s="16" t="inlineStr">
         <is>
-          <t>Casual couple talk</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R764" s="15" t="inlineStr">
@@ -74855,17 +74855,17 @@
     <row r="765" ht="46" customHeight="1">
       <c r="A765" s="15" t="inlineStr">
         <is>
-          <t>DAT-072</t>
+          <t>DAT-070</t>
         </is>
       </c>
       <c r="B765" s="15" t="inlineStr">
         <is>
-          <t>알콩달콩</t>
+          <t>애정표현</t>
         </is>
       </c>
       <c r="C765" s="15" t="inlineStr">
         <is>
-          <t>al-kong-dal-kong</t>
+          <t>ae-jeong-pyo-hyeon</t>
         </is>
       </c>
       <c r="D765" s="15" t="inlineStr">
@@ -74880,57 +74880,57 @@
       </c>
       <c r="F765" s="16" t="inlineStr">
         <is>
-          <t>A cute expression describing a couple being sweetly, playfully affectionate together.</t>
+          <t>Openly expressing affection toward a partner, whether verbally or physically.</t>
         </is>
       </c>
       <c r="G765" s="16" t="inlineStr">
         <is>
-          <t>Una expresión tierna que describe a una pareja siendo dulce y juguetonamente cariñosa entre sí.</t>
+          <t>Expresar abiertamente afecto hacia una pareja, ya sea verbal o físicamente.</t>
         </is>
       </c>
       <c r="H765" s="16" t="inlineStr">
         <is>
-          <t>形容一對情侶甜蜜、俏皮地相處，甜甜蜜蜜。</t>
+          <t>無論是言語或肢體上，公開向伴侶表達愛意。</t>
         </is>
       </c>
       <c r="I765" s="16" t="inlineStr">
         <is>
-          <t>形容一对情侣甜蜜、俏皮地相处，甜甜蜜蜜。</t>
+          <t>无论是言语或肢体上，公开向伴侣表达爱意。</t>
         </is>
       </c>
       <c r="J765" s="16" t="inlineStr">
         <is>
-          <t>カップルが甘く、遊び心を持って愛情深く過ごしている様子を表す可愛い表現。</t>
+          <t>言葉でも身体的にでも、パートナーに対して公然と愛情を表すこと。</t>
         </is>
       </c>
       <c r="K765" s="16" t="inlineStr">
         <is>
-          <t>둘이 알콩달콩 잘 지내고 있어.</t>
+          <t>둘이 애정표현이 진짜 많아.</t>
         </is>
       </c>
       <c r="L765" s="16" t="inlineStr">
         <is>
-          <t>The two of them are doing well, all sweet and lovey-dovey.</t>
+          <t>Those two show a lot of affection toward each other.</t>
         </is>
       </c>
       <c r="M765" s="16" t="inlineStr">
         <is>
-          <t>Esos dos la están pasando bien, muy dulces y cariñosos.</t>
+          <t>Esos dos se muestran mucho cariño mutuamente.</t>
         </is>
       </c>
       <c r="N765" s="16" t="inlineStr">
         <is>
-          <t>兩個人甜甜蜜蜜地過得很好。</t>
+          <t>兩個人真的很常表達愛意。</t>
         </is>
       </c>
       <c r="O765" s="16" t="inlineStr">
         <is>
-          <t>两个人甜甜蜜蜜地过得很好。</t>
+          <t>两个人真的很常表达爱意。</t>
         </is>
       </c>
       <c r="P765" s="16" t="inlineStr">
         <is>
-          <t>二人ともラブラブでうまくやってる。</t>
+          <t>二人とも愛情表現が本当に多いよね。</t>
         </is>
       </c>
       <c r="Q765" s="16" t="inlineStr">
@@ -74952,17 +74952,17 @@
     <row r="766" ht="46" customHeight="1">
       <c r="A766" s="15" t="inlineStr">
         <is>
-          <t>DAT-073</t>
+          <t>DAT-071</t>
         </is>
       </c>
       <c r="B766" s="15" t="inlineStr">
         <is>
-          <t>핑크빛</t>
+          <t>짝꿍</t>
         </is>
       </c>
       <c r="C766" s="15" t="inlineStr">
         <is>
-          <t>ping-keu-bit</t>
+          <t>jjak-kkung</t>
         </is>
       </c>
       <c r="D766" s="15" t="inlineStr">
@@ -74977,62 +74977,62 @@
       </c>
       <c r="F766" s="16" t="inlineStr">
         <is>
-          <t>"Pink-tinted" — describes a romantic, love-filled mood or atmosphere.</t>
+          <t>A cute, informal term for a significant other or a close paired friend.</t>
         </is>
       </c>
       <c r="G766" s="16" t="inlineStr">
         <is>
-          <t>"Teñido de rosa": describe un ambiente o estado de ánimo romántico y lleno de amor.</t>
+          <t>Un término tierno e informal para una pareja sentimental o un amigo cercano emparejado.</t>
         </is>
       </c>
       <c r="H766" s="16" t="inlineStr">
         <is>
-          <t>「粉紅色調」——形容浪漫、充滿愛意的氛圍或心情。</t>
+          <t>對另一半或親密好友的可愛、非正式稱呼。</t>
         </is>
       </c>
       <c r="I766" s="16" t="inlineStr">
         <is>
-          <t>“粉红色调”——形容浪漫、充满爱意的氛围或心情。</t>
+          <t>对另一半或亲密好友的可爱、非正式称呼。</t>
         </is>
       </c>
       <c r="J766" s="16" t="inlineStr">
         <is>
-          <t>「ピンク色」——ロマンチックで愛情に満ちた雰囲気や気分を表す。</t>
+          <t>恋人や親しい相手を指す、可愛くてカジュアルな呼び方。</t>
         </is>
       </c>
       <c r="K766" s="16" t="inlineStr">
         <is>
-          <t>둘 사이에 핑크빛 기류가 흘러.</t>
+          <t>내 짝꿍이랑 데이트하고 왔어.</t>
         </is>
       </c>
       <c r="L766" s="16" t="inlineStr">
         <is>
-          <t>There's a rosy romantic vibe flowing between the two of them.</t>
+          <t>I just came back from a date with my sweetheart.</t>
         </is>
       </c>
       <c r="M766" s="16" t="inlineStr">
         <is>
-          <t>Hay un aire romántico y rosado fluyendo entre esos dos.</t>
+          <t>Acabo de volver de una cita con mi pareja.</t>
         </is>
       </c>
       <c r="N766" s="16" t="inlineStr">
         <is>
-          <t>兩人之間流動著粉紅氛圍。</t>
+          <t>剛跟我的另一半約會回來。</t>
         </is>
       </c>
       <c r="O766" s="16" t="inlineStr">
         <is>
-          <t>两人之间流动着粉红氛围。</t>
+          <t>刚跟我的另一半约会回来。</t>
         </is>
       </c>
       <c r="P766" s="16" t="inlineStr">
         <is>
-          <t>二人の間にバラ色の空気が流れてる。</t>
+          <t>相棒とデートしてきた。</t>
         </is>
       </c>
       <c r="Q766" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk, gossip</t>
+          <t>Casual couple talk</t>
         </is>
       </c>
       <c r="R766" s="15" t="inlineStr">
@@ -75049,17 +75049,17 @@
     <row r="767" ht="46" customHeight="1">
       <c r="A767" s="15" t="inlineStr">
         <is>
-          <t>DAT-074</t>
+          <t>DAT-072</t>
         </is>
       </c>
       <c r="B767" s="15" t="inlineStr">
         <is>
-          <t>이별후유증</t>
+          <t>알콩달콩</t>
         </is>
       </c>
       <c r="C767" s="15" t="inlineStr">
         <is>
-          <t>i-byeol-hu-yu-jeung</t>
+          <t>al-kong-dal-kong</t>
         </is>
       </c>
       <c r="D767" s="15" t="inlineStr">
@@ -75074,62 +75074,62 @@
       </c>
       <c r="F767" s="16" t="inlineStr">
         <is>
-          <t>The emotional aftereffects that linger after a relationship ends.</t>
+          <t>A cute expression describing a couple being sweetly, playfully affectionate together.</t>
         </is>
       </c>
       <c r="G767" s="16" t="inlineStr">
         <is>
-          <t>Los efectos emocionales posteriores que persisten después de que termina una relación.</t>
+          <t>Una expresión tierna que describe a una pareja siendo dulce y juguetonamente cariñosa entre sí.</t>
         </is>
       </c>
       <c r="H767" s="16" t="inlineStr">
         <is>
-          <t>一段感情結束後持續存在的情緒後遺症，分手後遺症。</t>
+          <t>形容一對情侶甜蜜、俏皮地相處，甜甜蜜蜜。</t>
         </is>
       </c>
       <c r="I767" s="16" t="inlineStr">
         <is>
-          <t>一段感情结束后持续存在的情绪后遗症，分手后遗症。</t>
+          <t>形容一对情侣甜蜜、俏皮地相处，甜甜蜜蜜。</t>
         </is>
       </c>
       <c r="J767" s="16" t="inlineStr">
         <is>
-          <t>恋愛関係が終わった後も続く、感情的な後遺症。</t>
+          <t>カップルが甘く、遊び心を持って愛情深く過ごしている様子を表す可愛い表現。</t>
         </is>
       </c>
       <c r="K767" s="16" t="inlineStr">
         <is>
-          <t>이별후유증이 생각보다 오래 갔어.</t>
+          <t>둘이 알콩달콩 잘 지내고 있어.</t>
         </is>
       </c>
       <c r="L767" s="16" t="inlineStr">
         <is>
-          <t>The breakup aftermath lasted longer than I expected.</t>
+          <t>The two of them are doing well, all sweet and lovey-dovey.</t>
         </is>
       </c>
       <c r="M767" s="16" t="inlineStr">
         <is>
-          <t>Las secuelas de la ruptura duraron más de lo que esperaba.</t>
+          <t>Esos dos la están pasando bien, muy dulces y cariñosos.</t>
         </is>
       </c>
       <c r="N767" s="16" t="inlineStr">
         <is>
-          <t>分手後遺症比想像中持續更久。</t>
+          <t>兩個人甜甜蜜蜜地過得很好。</t>
         </is>
       </c>
       <c r="O767" s="16" t="inlineStr">
         <is>
-          <t>分手后遗症比想像中持续更久。</t>
+          <t>两个人甜甜蜜蜜地过得很好。</t>
         </is>
       </c>
       <c r="P767" s="16" t="inlineStr">
         <is>
-          <t>失恋の後遺症が思ったより長引いた。</t>
+          <t>二人ともラブラブでうまくやってる。</t>
         </is>
       </c>
       <c r="Q767" s="16" t="inlineStr">
         <is>
-          <t>Casual relationship talk</t>
+          <t>Couple culture, dramas</t>
         </is>
       </c>
       <c r="R767" s="15" t="inlineStr">
@@ -75146,17 +75146,17 @@
     <row r="768" ht="46" customHeight="1">
       <c r="A768" s="15" t="inlineStr">
         <is>
-          <t>DAT-075</t>
+          <t>DAT-073</t>
         </is>
       </c>
       <c r="B768" s="15" t="inlineStr">
         <is>
-          <t>연애전선</t>
+          <t>핑크빛</t>
         </is>
       </c>
       <c r="C768" s="15" t="inlineStr">
         <is>
-          <t>yeon-ae-jeon-seon</t>
+          <t>ping-keu-bit</t>
         </is>
       </c>
       <c r="D768" s="15" t="inlineStr">
@@ -75171,67 +75171,67 @@
       </c>
       <c r="F768" s="16" t="inlineStr">
         <is>
-          <t>"Romance front line" — a weather-front-style metaphor for the current state of someone's love life.</t>
+          <t>"Pink-tinted" — describes a romantic, love-filled mood or atmosphere.</t>
         </is>
       </c>
       <c r="G768" s="16" t="inlineStr">
         <is>
-          <t>"Frente romántico": una metáfora al estilo de un frente meteorológico para el estado actual de la vida amorosa de alguien.</t>
+          <t>"Teñido de rosa": describe un ambiente o estado de ánimo romántico y lleno de amor.</t>
         </is>
       </c>
       <c r="H768" s="16" t="inlineStr">
         <is>
-          <t>「戀愛前線」——借用天氣鋒面概念，比喻某人目前的感情狀態。</t>
+          <t>「粉紅色調」——形容浪漫、充滿愛意的氛圍或心情。</t>
         </is>
       </c>
       <c r="I768" s="16" t="inlineStr">
         <is>
-          <t>“恋爱前线”——借用天气锋面概念，比喻某人目前的感情状态。</t>
+          <t>“粉红色调”——形容浪漫、充满爱意的氛围或心情。</t>
         </is>
       </c>
       <c r="J768" s="16" t="inlineStr">
         <is>
-          <t>「恋愛の前線」——天気の前線に例えて、誰かの恋愛状況の現状を表す言葉。</t>
+          <t>「ピンク色」——ロマンチックで愛情に満ちた雰囲気や気分を表す。</t>
         </is>
       </c>
       <c r="K768" s="16" t="inlineStr">
         <is>
-          <t>요즘 연애전선 어때?</t>
+          <t>둘 사이에 핑크빛 기류가 흘러.</t>
         </is>
       </c>
       <c r="L768" s="16" t="inlineStr">
         <is>
-          <t>How's your love life going these days?</t>
+          <t>There's a rosy romantic vibe flowing between the two of them.</t>
         </is>
       </c>
       <c r="M768" s="16" t="inlineStr">
         <is>
-          <t>¿Cómo va tu vida amorosa últimamente?</t>
+          <t>Hay un aire romántico y rosado fluyendo entre esos dos.</t>
         </is>
       </c>
       <c r="N768" s="16" t="inlineStr">
         <is>
-          <t>最近戀愛前線如何？</t>
+          <t>兩人之間流動著粉紅氛圍。</t>
         </is>
       </c>
       <c r="O768" s="16" t="inlineStr">
         <is>
-          <t>最近恋爱前线如何？</t>
+          <t>两人之间流动着粉红氛围。</t>
         </is>
       </c>
       <c r="P768" s="16" t="inlineStr">
         <is>
-          <t>最近恋愛前線どう？</t>
+          <t>二人の間にバラ色の空気が流れてる。</t>
         </is>
       </c>
       <c r="Q768" s="16" t="inlineStr">
         <is>
-          <t>Casual dating talk</t>
+          <t>K-drama trope talk, gossip</t>
         </is>
       </c>
       <c r="R768" s="15" t="inlineStr">
         <is>
-          <t>Draft — please double-check</t>
+          <t>Verified (web-checked)</t>
         </is>
       </c>
       <c r="S768" s="15" t="inlineStr">
@@ -75243,17 +75243,17 @@
     <row r="769" ht="46" customHeight="1">
       <c r="A769" s="15" t="inlineStr">
         <is>
-          <t>DAT-076</t>
+          <t>DAT-074</t>
         </is>
       </c>
       <c r="B769" s="15" t="inlineStr">
         <is>
-          <t>커플브이로그</t>
+          <t>이별후유증</t>
         </is>
       </c>
       <c r="C769" s="15" t="inlineStr">
         <is>
-          <t>keo-peul-beu-i-ro-geu</t>
+          <t>i-byeol-hu-yu-jeung</t>
         </is>
       </c>
       <c r="D769" s="15" t="inlineStr">
@@ -75268,62 +75268,62 @@
       </c>
       <c r="F769" s="16" t="inlineStr">
         <is>
-          <t>Video content a couple makes together documenting their relationship and daily life.</t>
+          <t>The emotional aftereffects that linger after a relationship ends.</t>
         </is>
       </c>
       <c r="G769" s="16" t="inlineStr">
         <is>
-          <t>Contenido de video que una pareja hace junta documentando su relación y vida diaria.</t>
+          <t>Los efectos emocionales posteriores que persisten después de que termina una relación.</t>
         </is>
       </c>
       <c r="H769" s="16" t="inlineStr">
         <is>
-          <t>情侶一起拍攝、記錄兩人關係與日常生活的影片內容。</t>
+          <t>一段感情結束後持續存在的情緒後遺症，分手後遺症。</t>
         </is>
       </c>
       <c r="I769" s="16" t="inlineStr">
         <is>
-          <t>情侣一起拍摄、记录两人关系与日常生活的视频内容。</t>
+          <t>一段感情结束后持续存在的情绪后遗症，分手后遗症。</t>
         </is>
       </c>
       <c r="J769" s="16" t="inlineStr">
         <is>
-          <t>カップルが一緒に作る、二人の関係や日常生活を記録した動画コンテンツ。</t>
+          <t>恋愛関係が終わった後も続く、感情的な後遺症。</t>
         </is>
       </c>
       <c r="K769" s="16" t="inlineStr">
         <is>
-          <t>이 커플브이로그 보면 나도 연애하고 싶어져.</t>
+          <t>이별후유증이 생각보다 오래 갔어.</t>
         </is>
       </c>
       <c r="L769" s="16" t="inlineStr">
         <is>
-          <t>Watching this couple vlog makes me want to date too.</t>
+          <t>The breakup aftermath lasted longer than I expected.</t>
         </is>
       </c>
       <c r="M769" s="16" t="inlineStr">
         <is>
-          <t>Ver este vlog de pareja me dan ganas de tener novio también.</t>
+          <t>Las secuelas de la ruptura duraron más de lo que esperaba.</t>
         </is>
       </c>
       <c r="N769" s="16" t="inlineStr">
         <is>
-          <t>看這個情侶Vlog會讓人也想談戀愛。</t>
+          <t>分手後遺症比想像中持續更久。</t>
         </is>
       </c>
       <c r="O769" s="16" t="inlineStr">
         <is>
-          <t>看这个情侣Vlog会让人也想谈恋爱。</t>
+          <t>分手后遗症比想像中持续更久。</t>
         </is>
       </c>
       <c r="P769" s="16" t="inlineStr">
         <is>
-          <t>このカップルVlog見てると、私も恋したくなる。</t>
+          <t>失恋の後遺症が思ったより長引いた。</t>
         </is>
       </c>
       <c r="Q769" s="16" t="inlineStr">
         <is>
-          <t>YouTube couple content</t>
+          <t>Casual relationship talk</t>
         </is>
       </c>
       <c r="R769" s="15" t="inlineStr">
@@ -75340,17 +75340,17 @@
     <row r="770" ht="46" customHeight="1">
       <c r="A770" s="15" t="inlineStr">
         <is>
-          <t>DAT-077</t>
+          <t>DAT-075</t>
         </is>
       </c>
       <c r="B770" s="15" t="inlineStr">
         <is>
-          <t>심쿵포인트</t>
+          <t>연애전선</t>
         </is>
       </c>
       <c r="C770" s="15" t="inlineStr">
         <is>
-          <t>sim-kung-po-in-teu</t>
+          <t>yeon-ae-jeon-seon</t>
         </is>
       </c>
       <c r="D770" s="15" t="inlineStr">
@@ -75365,67 +75365,67 @@
       </c>
       <c r="F770" s="16" t="inlineStr">
         <is>
-          <t>The specific moment or detail that makes you fall for someone or feel butterflies.</t>
+          <t>"Romance front line" — a weather-front-style metaphor for the current state of someone's love life.</t>
         </is>
       </c>
       <c r="G770" s="16" t="inlineStr">
         <is>
-          <t>El momento o detalle específico que te hace enamorarte de alguien o sentir mariposas.</t>
+          <t>"Frente romántico": una metáfora al estilo de un frente meteorológico para el estado actual de la vida amorosa de alguien.</t>
         </is>
       </c>
       <c r="H770" s="16" t="inlineStr">
         <is>
-          <t>讓你對某人心動、產生小鹿亂撞感覺的特定瞬間或細節，心動點。</t>
+          <t>「戀愛前線」——借用天氣鋒面概念，比喻某人目前的感情狀態。</t>
         </is>
       </c>
       <c r="I770" s="16" t="inlineStr">
         <is>
-          <t>让你对某人心动、产生小鹿乱撞感觉的特定瞬间或细节，心动点。</t>
+          <t>“恋爱前线”——借用天气锋面概念，比喻某人目前的感情状态。</t>
         </is>
       </c>
       <c r="J770" s="16" t="inlineStr">
         <is>
-          <t>誰かに惹かれたり、胸がときめいたりする特定の瞬間や細部。</t>
+          <t>「恋愛の前線」——天気の前線に例えて、誰かの恋愛状況の現状を表す言葉。</t>
         </is>
       </c>
       <c r="K770" s="16" t="inlineStr">
         <is>
-          <t>그 미소가 내 심쿵포인트였어.</t>
+          <t>요즘 연애전선 어때?</t>
         </is>
       </c>
       <c r="L770" s="16" t="inlineStr">
         <is>
-          <t>That smile was my heart-flutter moment.</t>
+          <t>How's your love life going these days?</t>
         </is>
       </c>
       <c r="M770" s="16" t="inlineStr">
         <is>
-          <t>Esa sonrisa fue mi punto de flechazo.</t>
+          <t>¿Cómo va tu vida amorosa últimamente?</t>
         </is>
       </c>
       <c r="N770" s="16" t="inlineStr">
         <is>
-          <t>那個微笑就是我的心動點。</t>
+          <t>最近戀愛前線如何？</t>
         </is>
       </c>
       <c r="O770" s="16" t="inlineStr">
         <is>
-          <t>那个微笑就是我的心动点。</t>
+          <t>最近恋爱前线如何？</t>
         </is>
       </c>
       <c r="P770" s="16" t="inlineStr">
         <is>
-          <t>あの笑顔が私のキュンポイントだった。</t>
+          <t>最近恋愛前線どう？</t>
         </is>
       </c>
       <c r="Q770" s="16" t="inlineStr">
         <is>
-          <t>Casual dating/crush talk</t>
+          <t>Casual dating talk</t>
         </is>
       </c>
       <c r="R770" s="15" t="inlineStr">
         <is>
-          <t>Verified (web-checked)</t>
+          <t>Draft — please double-check</t>
         </is>
       </c>
       <c r="S770" s="15" t="inlineStr">
@@ -75437,17 +75437,17 @@
     <row r="771" ht="46" customHeight="1">
       <c r="A771" s="15" t="inlineStr">
         <is>
-          <t>DAT-078</t>
+          <t>DAT-076</t>
         </is>
       </c>
       <c r="B771" s="15" t="inlineStr">
         <is>
-          <t>천일</t>
+          <t>커플브이로그</t>
         </is>
       </c>
       <c r="C771" s="15" t="inlineStr">
         <is>
-          <t>cheon-il</t>
+          <t>keo-peul-beu-i-ro-geu</t>
         </is>
       </c>
       <c r="D771" s="15" t="inlineStr">
@@ -75462,62 +75462,62 @@
       </c>
       <c r="F771" s="16" t="inlineStr">
         <is>
-          <t>The 1,000-day relationship milestone, a bigger version of the 100-day celebration.</t>
+          <t>Video content a couple makes together documenting their relationship and daily life.</t>
         </is>
       </c>
       <c r="G771" s="16" t="inlineStr">
         <is>
-          <t>El hito de los 1,000 días de relación, una versión más grande de la celebración de los 100 días.</t>
+          <t>Contenido de video que una pareja hace junta documentando su relación y vida diaria.</t>
         </is>
       </c>
       <c r="H771" s="16" t="inlineStr">
         <is>
-          <t>交往滿一千天的紀念日，是百日紀念的加強版。</t>
+          <t>情侶一起拍攝、記錄兩人關係與日常生活的影片內容。</t>
         </is>
       </c>
       <c r="I771" s="16" t="inlineStr">
         <is>
-          <t>交往满一千天的纪念日，是百日纪念的加强版。</t>
+          <t>情侣一起拍摄、记录两人关系与日常生活的视频内容。</t>
         </is>
       </c>
       <c r="J771" s="16" t="inlineStr">
         <is>
-          <t>100日記念日をさらに大きくした、交際1000日の記念日。</t>
+          <t>カップルが一緒に作る、二人の関係や日常生活を記録した動画コンテンツ。</t>
         </is>
       </c>
       <c r="K771" s="16" t="inlineStr">
         <is>
-          <t>다음 달이 우리 천일이야.</t>
+          <t>이 커플브이로그 보면 나도 연애하고 싶어져.</t>
         </is>
       </c>
       <c r="L771" s="16" t="inlineStr">
         <is>
-          <t>Next month is our 1,000-day anniversary.</t>
+          <t>Watching this couple vlog makes me want to date too.</t>
         </is>
       </c>
       <c r="M771" s="16" t="inlineStr">
         <is>
-          <t>El próximo mes cumplimos 1,000 días.</t>
+          <t>Ver este vlog de pareja me dan ganas de tener novio también.</t>
         </is>
       </c>
       <c r="N771" s="16" t="inlineStr">
         <is>
-          <t>下個月是我們的千日紀念。</t>
+          <t>看這個情侶Vlog會讓人也想談戀愛。</t>
         </is>
       </c>
       <c r="O771" s="16" t="inlineStr">
         <is>
-          <t>下个月是我们的千日纪念。</t>
+          <t>看这个情侣Vlog会让人也想谈恋爱。</t>
         </is>
       </c>
       <c r="P771" s="16" t="inlineStr">
         <is>
-          <t>来月が私たちの1000日記念日。</t>
+          <t>このカップルVlog見てると、私も恋したくなる。</t>
         </is>
       </c>
       <c r="Q771" s="16" t="inlineStr">
         <is>
-          <t>Couple culture</t>
+          <t>YouTube couple content</t>
         </is>
       </c>
       <c r="R771" s="15" t="inlineStr">
@@ -75534,17 +75534,17 @@
     <row r="772" ht="46" customHeight="1">
       <c r="A772" s="15" t="inlineStr">
         <is>
-          <t>DAT-079</t>
+          <t>DAT-077</t>
         </is>
       </c>
       <c r="B772" s="15" t="inlineStr">
         <is>
-          <t>열애인정</t>
+          <t>심쿵포인트</t>
         </is>
       </c>
       <c r="C772" s="15" t="inlineStr">
         <is>
-          <t>yeol-ae-in-jeong</t>
+          <t>sim-kung-po-in-teu</t>
         </is>
       </c>
       <c r="D772" s="15" t="inlineStr">
@@ -75559,62 +75559,62 @@
       </c>
       <c r="F772" s="16" t="inlineStr">
         <is>
-          <t>When a celebrity couple officially confirms they're dating, often via their agency.</t>
+          <t>The specific moment or detail that makes you fall for someone or feel butterflies.</t>
         </is>
       </c>
       <c r="G772" s="16" t="inlineStr">
         <is>
-          <t>Cuando una pareja de celebridades confirma oficialmente que está saliendo, a menudo a través de su agencia.</t>
+          <t>El momento o detalle específico que te hace enamorarte de alguien o sentir mariposas.</t>
         </is>
       </c>
       <c r="H772" s="16" t="inlineStr">
         <is>
-          <t>名人情侶（常透過經紀公司）正式承認交往關係，承認戀情。</t>
+          <t>讓你對某人心動、產生小鹿亂撞感覺的特定瞬間或細節，心動點。</t>
         </is>
       </c>
       <c r="I772" s="16" t="inlineStr">
         <is>
-          <t>名人情侣（常通过经纪公司）正式承认交往关系，承认恋情。</t>
+          <t>让你对某人心动、产生小鹿乱撞感觉的特定瞬间或细节，心动点。</t>
         </is>
       </c>
       <c r="J772" s="16" t="inlineStr">
         <is>
-          <t>芸能人カップルが、事務所を通じてなど正式に交際を認めること。</t>
+          <t>誰かに惹かれたり、胸がときめいたりする特定の瞬間や細部。</t>
         </is>
       </c>
       <c r="K772" s="16" t="inlineStr">
         <is>
-          <t>결국 열애인정 했대!</t>
+          <t>그 미소가 내 심쿵포인트였어.</t>
         </is>
       </c>
       <c r="L772" s="16" t="inlineStr">
         <is>
-          <t>They finally confirmed the relationship!</t>
+          <t>That smile was my heart-flutter moment.</t>
         </is>
       </c>
       <c r="M772" s="16" t="inlineStr">
         <is>
-          <t>¡Al final confirmaron la relación!</t>
+          <t>Esa sonrisa fue mi punto de flechazo.</t>
         </is>
       </c>
       <c r="N772" s="16" t="inlineStr">
         <is>
-          <t>最後承認戀情了！</t>
+          <t>那個微笑就是我的心動點。</t>
         </is>
       </c>
       <c r="O772" s="16" t="inlineStr">
         <is>
-          <t>最后承认恋情了！</t>
+          <t>那个微笑就是我的心动点。</t>
         </is>
       </c>
       <c r="P772" s="16" t="inlineStr">
         <is>
-          <t>ついに交際を認めたって！</t>
+          <t>あの笑顔が私のキュンポイントだった。</t>
         </is>
       </c>
       <c r="Q772" s="16" t="inlineStr">
         <is>
-          <t>Entertainment news</t>
+          <t>Casual dating/crush talk</t>
         </is>
       </c>
       <c r="R772" s="15" t="inlineStr">
@@ -75631,17 +75631,17 @@
     <row r="773" ht="46" customHeight="1">
       <c r="A773" s="15" t="inlineStr">
         <is>
-          <t>DAT-080</t>
+          <t>DAT-078</t>
         </is>
       </c>
       <c r="B773" s="15" t="inlineStr">
         <is>
-          <t>사내연애</t>
+          <t>천일</t>
         </is>
       </c>
       <c r="C773" s="15" t="inlineStr">
         <is>
-          <t>sa-nae-yeon-ae</t>
+          <t>cheon-il</t>
         </is>
       </c>
       <c r="D773" s="15" t="inlineStr">
@@ -75656,62 +75656,62 @@
       </c>
       <c r="F773" s="16" t="inlineStr">
         <is>
-          <t>Dating a coworker at the same company — a common drama trope.</t>
+          <t>The 1,000-day relationship milestone, a bigger version of the 100-day celebration.</t>
         </is>
       </c>
       <c r="G773" s="16" t="inlineStr">
         <is>
-          <t>Salir con un compañero de trabajo de la misma empresa; un cliché común en los dramas.</t>
+          <t>El hito de los 1,000 días de relación, una versión más grande de la celebración de los 100 días.</t>
         </is>
       </c>
       <c r="H773" s="16" t="inlineStr">
         <is>
-          <t>與同公司同事交往，是韓劇常見的劇情套路，辦公室戀情。</t>
+          <t>交往滿一千天的紀念日，是百日紀念的加強版。</t>
         </is>
       </c>
       <c r="I773" s="16" t="inlineStr">
         <is>
-          <t>与同公司同事交往，是韩剧常见的剧情套路，办公室恋情。</t>
+          <t>交往满一千天的纪念日，是百日纪念的加强版。</t>
         </is>
       </c>
       <c r="J773" s="16" t="inlineStr">
         <is>
-          <t>同じ会社の同僚と付き合うこと——ドラマによくあるトロープ。</t>
+          <t>100日記念日をさらに大きくした、交際1000日の記念日。</t>
         </is>
       </c>
       <c r="K773" s="16" t="inlineStr">
         <is>
-          <t>이 드라마 사내연애 전개가 진짜 설레.</t>
+          <t>다음 달이 우리 천일이야.</t>
         </is>
       </c>
       <c r="L773" s="16" t="inlineStr">
         <is>
-          <t>This drama's workplace romance storyline is so exciting.</t>
+          <t>Next month is our 1,000-day anniversary.</t>
         </is>
       </c>
       <c r="M773" s="16" t="inlineStr">
         <is>
-          <t>La trama de romance de oficina de este drama es muy emocionante.</t>
+          <t>El próximo mes cumplimos 1,000 días.</t>
         </is>
       </c>
       <c r="N773" s="16" t="inlineStr">
         <is>
-          <t>這部劇的辦公室戀情發展真的很讓人心動。</t>
+          <t>下個月是我們的千日紀念。</t>
         </is>
       </c>
       <c r="O773" s="16" t="inlineStr">
         <is>
-          <t>这部剧的办公室恋情发展真的很让人心动。</t>
+          <t>下个月是我们的千日纪念。</t>
         </is>
       </c>
       <c r="P773" s="16" t="inlineStr">
         <is>
-          <t>このドラマの社内恋愛展開、本当にドキドキする。</t>
+          <t>来月が私たちの1000日記念日。</t>
         </is>
       </c>
       <c r="Q773" s="16" t="inlineStr">
         <is>
-          <t>K-drama trope talk</t>
+          <t>Couple culture</t>
         </is>
       </c>
       <c r="R773" s="15" t="inlineStr">
@@ -75728,17 +75728,17 @@
     <row r="774" ht="46" customHeight="1">
       <c r="A774" s="15" t="inlineStr">
         <is>
-          <t>DAT-081</t>
+          <t>DAT-079</t>
         </is>
       </c>
       <c r="B774" s="15" t="inlineStr">
         <is>
-          <t>패완얼</t>
+          <t>열애인정</t>
         </is>
       </c>
       <c r="C774" s="15" t="inlineStr">
         <is>
-          <t>pae-wan-eol</t>
+          <t>yeol-ae-in-jeong</t>
         </is>
       </c>
       <c r="D774" s="15" t="inlineStr">
@@ -75753,62 +75753,62 @@
       </c>
       <c r="F774" s="16" t="inlineStr">
         <is>
-          <t>Short for "fashion is completed by the face" — a saying that a good-looking face elevates any outfit, no matter how simple.</t>
+          <t>When a celebrity couple officially confirms they're dating, often via their agency.</t>
         </is>
       </c>
       <c r="G774" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de "la moda se completa con la cara": un dicho que dice que una cara atractiva mejora cualquier atuendo, sin importar lo simple que sea.</t>
+          <t>Cuando una pareja de celebridades confirma oficialmente que está saliendo, a menudo a través de su agencia.</t>
         </is>
       </c>
       <c r="H774" s="16" t="inlineStr">
         <is>
-          <t>「時尚的完成是臉」的簡稱——意指帥氣或漂亮的長相能撐起任何穿搭。</t>
+          <t>名人情侶（常透過經紀公司）正式承認交往關係，承認戀情。</t>
         </is>
       </c>
       <c r="I774" s="16" t="inlineStr">
         <is>
-          <t>“时尚的完成是脸”的简称——意指帅气或漂亮的长相能撑起任何穿搭。</t>
+          <t>名人情侣（常通过经纪公司）正式承认交往关系，承认恋情。</t>
         </is>
       </c>
       <c r="J774" s="16" t="inlineStr">
         <is>
-          <t>「ファッションの完成は顔」の略——どんなにシンプルな服でも、整った顔立ちが引き立てるという言葉。</t>
+          <t>芸能人カップルが、事務所を通じてなど正式に交際を認めること。</t>
         </is>
       </c>
       <c r="K774" s="16" t="inlineStr">
         <is>
-          <t>역시 패완얼이야, 뭘 입어도 잘 어울려.</t>
+          <t>결국 열애인정 했대!</t>
         </is>
       </c>
       <c r="L774" s="16" t="inlineStr">
         <is>
-          <t>It's true, fashion's finished by the face — they look good in anything.</t>
+          <t>They finally confirmed the relationship!</t>
         </is>
       </c>
       <c r="M774" s="16" t="inlineStr">
         <is>
-          <t>Es cierto, la cara lo completa todo — se le ve bien cualquier cosa.</t>
+          <t>¡Al final confirmaron la relación!</t>
         </is>
       </c>
       <c r="N774" s="16" t="inlineStr">
         <is>
-          <t>果然臉才是關鍵，穿什麼都好看。</t>
+          <t>最後承認戀情了！</t>
         </is>
       </c>
       <c r="O774" s="16" t="inlineStr">
         <is>
-          <t>果然脸才是关键，穿什么都好看。</t>
+          <t>最后承认恋情了！</t>
         </is>
       </c>
       <c r="P774" s="16" t="inlineStr">
         <is>
-          <t>やっぱり顔が全て、何着ても似合う。</t>
+          <t>ついに交際を認めたって！</t>
         </is>
       </c>
       <c r="Q774" s="16" t="inlineStr">
         <is>
-          <t>Fashion/beauty banter</t>
+          <t>Entertainment news</t>
         </is>
       </c>
       <c r="R774" s="15" t="inlineStr">
@@ -75825,17 +75825,17 @@
     <row r="775" ht="46" customHeight="1">
       <c r="A775" s="15" t="inlineStr">
         <is>
-          <t>DAT-082</t>
+          <t>DAT-080</t>
         </is>
       </c>
       <c r="B775" s="15" t="inlineStr">
         <is>
-          <t>금사빠</t>
+          <t>사내연애</t>
         </is>
       </c>
       <c r="C775" s="15" t="inlineStr">
         <is>
-          <t>geum-sa-ppa</t>
+          <t>sa-nae-yeon-ae</t>
         </is>
       </c>
       <c r="D775" s="15" t="inlineStr">
@@ -75850,62 +75850,62 @@
       </c>
       <c r="F775" s="16" t="inlineStr">
         <is>
-          <t>Short for 금방 사랑에 빠지는 사람 — someone who falls in love super easily.</t>
+          <t>Dating a coworker at the same company — a common drama trope.</t>
         </is>
       </c>
       <c r="G775" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 금방 사랑에 빠지는 사람: alguien que se enamora con mucha facilidad.</t>
+          <t>Salir con un compañero de trabajo de la misma empresa; un cliché común en los dramas.</t>
         </is>
       </c>
       <c r="H775" s="16" t="inlineStr">
         <is>
-          <t>금방 사랑에 빠지는 사람（很快就墜入愛河的人）的縮寫：超容易動心的人。</t>
+          <t>與同公司同事交往，是韓劇常見的劇情套路，辦公室戀情。</t>
         </is>
       </c>
       <c r="I775" s="16" t="inlineStr">
         <is>
-          <t>금방 사랑에 빠지는 사람（很快就坠入爱河的人）的缩写：超容易动心的人。</t>
+          <t>与同公司同事交往，是韩剧常见的剧情套路，办公室恋情。</t>
         </is>
       </c>
       <c r="J775" s="16" t="inlineStr">
         <is>
-          <t>금방 사랑에 빠지는 사람（すぐ恋に落ちる人）の略。惚れっぽい人。</t>
+          <t>同じ会社の同僚と付き合うこと——ドラマによくあるトロープ。</t>
         </is>
       </c>
       <c r="K775" s="16" t="inlineStr">
         <is>
-          <t>나 금사빠라 웃어 주기만 해도 반해.</t>
+          <t>이 드라마 사내연애 전개가 진짜 설레.</t>
         </is>
       </c>
       <c r="L775" s="16" t="inlineStr">
         <is>
-          <t>I fall in love fast — one smile and I'm gone.</t>
+          <t>This drama's workplace romance storyline is so exciting.</t>
         </is>
       </c>
       <c r="M775" s="16" t="inlineStr">
         <is>
-          <t>Me enamoro rápido, con una sonrisa ya caigo.</t>
+          <t>La trama de romance de oficina de este drama es muy emocionante.</t>
         </is>
       </c>
       <c r="N775" s="16" t="inlineStr">
         <is>
-          <t>我很容易動心，對我笑一下就淪陷了。</t>
+          <t>這部劇的辦公室戀情發展真的很讓人心動。</t>
         </is>
       </c>
       <c r="O775" s="16" t="inlineStr">
         <is>
-          <t>我很容易动心，对我笑一下就沦陷了。</t>
+          <t>这部剧的办公室恋情发展真的很让人心动。</t>
         </is>
       </c>
       <c r="P775" s="16" t="inlineStr">
         <is>
-          <t>惚れっぽいから、笑ってくれただけで好きになる。</t>
+          <t>このドラマの社内恋愛展開、本当にドキドキする。</t>
         </is>
       </c>
       <c r="Q775" s="16" t="inlineStr">
         <is>
-          <t>Dating talk, fandom</t>
+          <t>K-drama trope talk</t>
         </is>
       </c>
       <c r="R775" s="15" t="inlineStr">
@@ -75922,17 +75922,17 @@
     <row r="776" ht="46" customHeight="1">
       <c r="A776" s="15" t="inlineStr">
         <is>
-          <t>DAT-083</t>
+          <t>DAT-081</t>
         </is>
       </c>
       <c r="B776" s="15" t="inlineStr">
         <is>
-          <t>플러팅</t>
+          <t>패완얼</t>
         </is>
       </c>
       <c r="C776" s="15" t="inlineStr">
         <is>
-          <t>peul-reo-ting</t>
+          <t>pae-wan-eol</t>
         </is>
       </c>
       <c r="D776" s="15" t="inlineStr">
@@ -75947,62 +75947,62 @@
       </c>
       <c r="F776" s="16" t="inlineStr">
         <is>
-          <t>Flirting — little words or actions that signal romantic interest, from English "flirting."</t>
+          <t>Short for "fashion is completed by the face" — a saying that a good-looking face elevates any outfit, no matter how simple.</t>
         </is>
       </c>
       <c r="G776" s="16" t="inlineStr">
         <is>
-          <t>Coquetear: pequeñas palabras o gestos que muestran interés romántico, del inglés "flirting".</t>
+          <t>Abreviatura de "la moda se completa con la cara": un dicho que dice que una cara atractiva mejora cualquier atuendo, sin importar lo simple que sea.</t>
         </is>
       </c>
       <c r="H776" s="16" t="inlineStr">
         <is>
-          <t>調情、放電——用小小的話語或舉動釋放好感，來自英文「flirting」。</t>
+          <t>「時尚的完成是臉」的簡稱——意指帥氣或漂亮的長相能撐起任何穿搭。</t>
         </is>
       </c>
       <c r="I776" s="16" t="inlineStr">
         <is>
-          <t>调情、放电——用小小的话语或举动释放好感，来自英文“flirting”。</t>
+          <t>“时尚的完成是脸”的简称——意指帅气或漂亮的长相能撑起任何穿搭。</t>
         </is>
       </c>
       <c r="J776" s="16" t="inlineStr">
         <is>
-          <t>さりげない言動で好意を伝えること。英語の「flirting」から。脈ありアピール。</t>
+          <t>「ファッションの完成は顔」の略——どんなにシンプルな服でも、整った顔立ちが引き立てるという言葉。</t>
         </is>
       </c>
       <c r="K776" s="16" t="inlineStr">
         <is>
-          <t>방금 그거 플러팅이야? 나한테 왜 이래.</t>
+          <t>역시 패완얼이야, 뭘 입어도 잘 어울려.</t>
         </is>
       </c>
       <c r="L776" s="16" t="inlineStr">
         <is>
-          <t>Wait, was that flirting just now? Why are you doing this to me?</t>
+          <t>It's true, fashion's finished by the face — they look good in anything.</t>
         </is>
       </c>
       <c r="M776" s="16" t="inlineStr">
         <is>
-          <t>Espera, ¿eso fue coqueteo? ¿Por qué me haces esto?</t>
+          <t>Es cierto, la cara lo completa todo — se le ve bien cualquier cosa.</t>
         </is>
       </c>
       <c r="N776" s="16" t="inlineStr">
         <is>
-          <t>剛剛那是在撩我嗎？你幹嘛這樣。</t>
+          <t>果然臉才是關鍵，穿什麼都好看。</t>
         </is>
       </c>
       <c r="O776" s="16" t="inlineStr">
         <is>
-          <t>刚刚那是在撩我吗？你干嘛这样。</t>
+          <t>果然脸才是关键，穿什么都好看。</t>
         </is>
       </c>
       <c r="P776" s="16" t="inlineStr">
         <is>
-          <t>今のってアプローチ？なんでそういうことするの。</t>
+          <t>やっぱり顔が全て、何着ても似合う。</t>
         </is>
       </c>
       <c r="Q776" s="16" t="inlineStr">
         <is>
-          <t>Dating talk, dating shows, social media</t>
+          <t>Fashion/beauty banter</t>
         </is>
       </c>
       <c r="R776" s="15" t="inlineStr">
@@ -76019,17 +76019,17 @@
     <row r="777" ht="46" customHeight="1">
       <c r="A777" s="15" t="inlineStr">
         <is>
-          <t>DAT-084</t>
+          <t>DAT-082</t>
         </is>
       </c>
       <c r="B777" s="15" t="inlineStr">
         <is>
-          <t>읽씹</t>
+          <t>금사빠</t>
         </is>
       </c>
       <c r="C777" s="15" t="inlineStr">
         <is>
-          <t>ilk-ssip</t>
+          <t>geum-sa-ppa</t>
         </is>
       </c>
       <c r="D777" s="15" t="inlineStr">
@@ -76044,62 +76044,62 @@
       </c>
       <c r="F777" s="16" t="inlineStr">
         <is>
-          <t>Reading a message and not replying — short for 읽고 씹다 ("read and ignore").</t>
+          <t>Short for 금방 사랑에 빠지는 사람 — someone who falls in love super easily.</t>
         </is>
       </c>
       <c r="G777" s="16" t="inlineStr">
         <is>
-          <t>Leer un mensaje y no responder; abreviatura de 읽고 씹다 ("leer e ignorar"). Dejar en visto.</t>
+          <t>Abreviatura de 금방 사랑에 빠지는 사람: alguien que se enamora con mucha facilidad.</t>
         </is>
       </c>
       <c r="H777" s="16" t="inlineStr">
         <is>
-          <t>已讀不回——讀了訊息卻不回，是「읽고 씹다（讀了就無視）」的縮寫。</t>
+          <t>금방 사랑에 빠지는 사람（很快就墜入愛河的人）的縮寫：超容易動心的人。</t>
         </is>
       </c>
       <c r="I777" s="16" t="inlineStr">
         <is>
-          <t>已读不回——读了消息却不回，是“읽고 씹다（读了就无视）”的缩写。</t>
+          <t>금방 사랑에 빠지는 사람（很快就坠入爱河的人）的缩写：超容易动心的人。</t>
         </is>
       </c>
       <c r="J777" s="16" t="inlineStr">
         <is>
-          <t>既読スルー。「읽고 씹다（読んで無視する）」の略。</t>
+          <t>금방 사랑에 빠지는 사람（すぐ恋に落ちる人）の略。惚れっぽい人。</t>
         </is>
       </c>
       <c r="K777" s="16" t="inlineStr">
         <is>
-          <t>어제 보낸 카톡 아직도 읽씹이야.</t>
+          <t>나 금사빠라 웃어 주기만 해도 반해.</t>
         </is>
       </c>
       <c r="L777" s="16" t="inlineStr">
         <is>
-          <t>The message I sent yesterday is still left on read.</t>
+          <t>I fall in love fast — one smile and I'm gone.</t>
         </is>
       </c>
       <c r="M777" s="16" t="inlineStr">
         <is>
-          <t>El mensaje que mandé ayer sigue en visto.</t>
+          <t>Me enamoro rápido, con una sonrisa ya caigo.</t>
         </is>
       </c>
       <c r="N777" s="16" t="inlineStr">
         <is>
-          <t>我昨天傳的訊息到現在還是已讀不回。</t>
+          <t>我很容易動心，對我笑一下就淪陷了。</t>
         </is>
       </c>
       <c r="O777" s="16" t="inlineStr">
         <is>
-          <t>我昨天传的消息到现在还是已读不回。</t>
+          <t>我很容易动心，对我笑一下就沦陷了。</t>
         </is>
       </c>
       <c r="P777" s="16" t="inlineStr">
         <is>
-          <t>昨日送ったメッセージ、まだ既読スルーされてる。</t>
+          <t>惚れっぽいから、笑ってくれただけで好きになる。</t>
         </is>
       </c>
       <c r="Q777" s="16" t="inlineStr">
         <is>
-          <t>Messaging, dating, friendships</t>
+          <t>Dating talk, fandom</t>
         </is>
       </c>
       <c r="R777" s="15" t="inlineStr">
@@ -76116,17 +76116,17 @@
     <row r="778" ht="46" customHeight="1">
       <c r="A778" s="15" t="inlineStr">
         <is>
-          <t>DAT-085</t>
+          <t>DAT-083</t>
         </is>
       </c>
       <c r="B778" s="15" t="inlineStr">
         <is>
-          <t>안읽씹</t>
+          <t>플러팅</t>
         </is>
       </c>
       <c r="C778" s="15" t="inlineStr">
         <is>
-          <t>an-ilk-ssip</t>
+          <t>peul-reo-ting</t>
         </is>
       </c>
       <c r="D778" s="15" t="inlineStr">
@@ -76141,62 +76141,62 @@
       </c>
       <c r="F778" s="16" t="inlineStr">
         <is>
-          <t>Not even opening a message and not replying — short for 안 읽고 씹다 ("ignore without reading").</t>
+          <t>Flirting — little words or actions that signal romantic interest, from English "flirting."</t>
         </is>
       </c>
       <c r="G778" s="16" t="inlineStr">
         <is>
-          <t>Ni siquiera abrir el mensaje y no responder; abreviatura de 안 읽고 씹다 ("ignorar sin leer").</t>
+          <t>Coquetear: pequeñas palabras o gestos que muestran interés romántico, del inglés "flirting".</t>
         </is>
       </c>
       <c r="H778" s="16" t="inlineStr">
         <is>
-          <t>未讀不回——連訊息都不點開也不回，是「안 읽고 씹다（不讀就無視）」的縮寫。</t>
+          <t>調情、放電——用小小的話語或舉動釋放好感，來自英文「flirting」。</t>
         </is>
       </c>
       <c r="I778" s="16" t="inlineStr">
         <is>
-          <t>未读不回——连消息都不点开也不回，是“안 읽고 씹다（不读就无视）”的缩写。</t>
+          <t>调情、放电——用小小的话语或举动释放好感，来自英文“flirting”。</t>
         </is>
       </c>
       <c r="J778" s="16" t="inlineStr">
         <is>
-          <t>未読スルー。メッセージを開きもせず返さないこと。「안 읽고 씹다」の略。</t>
+          <t>さりげない言動で好意を伝えること。英語の「flirting」から。脈ありアピール。</t>
         </is>
       </c>
       <c r="K778" s="16" t="inlineStr">
         <is>
-          <t>읽씹보다 안읽씹이 더 신경 쓰여.</t>
+          <t>방금 그거 플러팅이야? 나한테 왜 이래.</t>
         </is>
       </c>
       <c r="L778" s="16" t="inlineStr">
         <is>
-          <t>Being left on unread bothers me more than being left on read.</t>
+          <t>Wait, was that flirting just now? Why are you doing this to me?</t>
         </is>
       </c>
       <c r="M778" s="16" t="inlineStr">
         <is>
-          <t>Me molesta más que ni lo abra a que me deje en visto.</t>
+          <t>Espera, ¿eso fue coqueteo? ¿Por qué me haces esto?</t>
         </is>
       </c>
       <c r="N778" s="16" t="inlineStr">
         <is>
-          <t>比起已讀不回，未讀不回更讓我在意。</t>
+          <t>剛剛那是在撩我嗎？你幹嘛這樣。</t>
         </is>
       </c>
       <c r="O778" s="16" t="inlineStr">
         <is>
-          <t>比起已读不回，未读不回更让我在意。</t>
+          <t>刚刚那是在撩我吗？你干嘛这样。</t>
         </is>
       </c>
       <c r="P778" s="16" t="inlineStr">
         <is>
-          <t>既読スルーより未読スルーのほうが気になる。</t>
+          <t>今のってアプローチ？なんでそういうことするの。</t>
         </is>
       </c>
       <c r="Q778" s="16" t="inlineStr">
         <is>
-          <t>Messaging, dating, friendships</t>
+          <t>Dating talk, dating shows, social media</t>
         </is>
       </c>
       <c r="R778" s="15" t="inlineStr">
@@ -76213,17 +76213,17 @@
     <row r="779" ht="46" customHeight="1">
       <c r="A779" s="15" t="inlineStr">
         <is>
-          <t>DAT-086</t>
+          <t>DAT-084</t>
         </is>
       </c>
       <c r="B779" s="15" t="inlineStr">
         <is>
-          <t>선톡</t>
+          <t>읽씹</t>
         </is>
       </c>
       <c r="C779" s="15" t="inlineStr">
         <is>
-          <t>seon-tok</t>
+          <t>ilk-ssip</t>
         </is>
       </c>
       <c r="D779" s="15" t="inlineStr">
@@ -76238,62 +76238,62 @@
       </c>
       <c r="F779" s="16" t="inlineStr">
         <is>
-          <t>Sending the first message — 선 (first) + 톡 (KakaoTalk message). Often a sign of interest.</t>
+          <t>Reading a message and not replying — short for 읽고 씹다 ("read and ignore").</t>
         </is>
       </c>
       <c r="G779" s="16" t="inlineStr">
         <is>
-          <t>Mandar el primer mensaje: 선 (primero) + 톡 (mensaje de KakaoTalk). Suele ser señal de interés.</t>
+          <t>Leer un mensaje y no responder; abreviatura de 읽고 씹다 ("leer e ignorar"). Dejar en visto.</t>
         </is>
       </c>
       <c r="H779" s="16" t="inlineStr">
         <is>
-          <t>主動先傳訊息——선（先）＋톡（KakaoTalk訊息），常被當成有好感的訊號。</t>
+          <t>已讀不回——讀了訊息卻不回，是「읽고 씹다（讀了就無視）」的縮寫。</t>
         </is>
       </c>
       <c r="I779" s="16" t="inlineStr">
         <is>
-          <t>主动先传消息——선（先）＋톡（KakaoTalk消息），常被当成有好感的信号。</t>
+          <t>已读不回——读了消息却不回，是“읽고 씹다（读了就无视）”的缩写。</t>
         </is>
       </c>
       <c r="J779" s="16" t="inlineStr">
         <is>
-          <t>自分から先にメッセージを送ること。선（先）＋톡（カカオトーク）。好意のサインとされがち。</t>
+          <t>既読スルー。「읽고 씹다（読んで無視する）」の略。</t>
         </is>
       </c>
       <c r="K779" s="16" t="inlineStr">
         <is>
-          <t>오늘은 내가 선톡 해볼까?</t>
+          <t>어제 보낸 카톡 아직도 읽씹이야.</t>
         </is>
       </c>
       <c r="L779" s="16" t="inlineStr">
         <is>
-          <t>Should I be the one to text first today?</t>
+          <t>The message I sent yesterday is still left on read.</t>
         </is>
       </c>
       <c r="M779" s="16" t="inlineStr">
         <is>
-          <t>¿Y si hoy le escribo yo primero?</t>
+          <t>El mensaje que mandé ayer sigue en visto.</t>
         </is>
       </c>
       <c r="N779" s="16" t="inlineStr">
         <is>
-          <t>今天要不要換我先傳訊息？</t>
+          <t>我昨天傳的訊息到現在還是已讀不回。</t>
         </is>
       </c>
       <c r="O779" s="16" t="inlineStr">
         <is>
-          <t>今天要不要换我先传消息？</t>
+          <t>我昨天传的消息到现在还是已读不回。</t>
         </is>
       </c>
       <c r="P779" s="16" t="inlineStr">
         <is>
-          <t>今日は私から先にLINEしてみようかな？</t>
+          <t>昨日送ったメッセージ、まだ既読スルーされてる。</t>
         </is>
       </c>
       <c r="Q779" s="16" t="inlineStr">
         <is>
-          <t>Dating, crushes, messaging</t>
+          <t>Messaging, dating, friendships</t>
         </is>
       </c>
       <c r="R779" s="15" t="inlineStr">
@@ -76310,17 +76310,17 @@
     <row r="780" ht="46" customHeight="1">
       <c r="A780" s="15" t="inlineStr">
         <is>
-          <t>DAT-087</t>
+          <t>DAT-085</t>
         </is>
       </c>
       <c r="B780" s="15" t="inlineStr">
         <is>
-          <t>깻잎논쟁</t>
+          <t>안읽씹</t>
         </is>
       </c>
       <c r="C780" s="15" t="inlineStr">
         <is>
-          <t>kkaen-nip-non-jaeng</t>
+          <t>an-ilk-ssip</t>
         </is>
       </c>
       <c r="D780" s="15" t="inlineStr">
@@ -76335,62 +76335,62 @@
       </c>
       <c r="F780" s="16" t="inlineStr">
         <is>
-          <t>The famous debate over whether it's okay for your partner to help a friend of the other gender peel apart a stuck pickled perilla leaf.</t>
+          <t>Not even opening a message and not replying — short for 안 읽고 씹다 ("ignore without reading").</t>
         </is>
       </c>
       <c r="G780" s="16" t="inlineStr">
         <is>
-          <t>El famoso debate sobre si está bien que tu pareja ayude a una amiga o un amigo del otro género a separar una hoja de perilla en conserva pegada.</t>
+          <t>Ni siquiera abrir el mensaje y no responder; abreviatura de 안 읽고 씹다 ("ignorar sin leer").</t>
         </is>
       </c>
       <c r="H780" s="16" t="inlineStr">
         <is>
-          <t>有名的「芝麻葉之爭」：另一半幫異性朋友夾開黏在一起的醃芝麻葉，到底可不可以？</t>
+          <t>未讀不回——連訊息都不點開也不回，是「안 읽고 씹다（不讀就無視）」的縮寫。</t>
         </is>
       </c>
       <c r="I780" s="16" t="inlineStr">
         <is>
-          <t>有名的“芝麻叶之争”：另一半帮异性朋友夹开黏在一起的腌芝麻叶，到底可不可以？</t>
+          <t>未读不回——连消息都不点开也不回，是“안 읽고 씹다（不读就无视）”的缩写。</t>
         </is>
       </c>
       <c r="J780" s="16" t="inlineStr">
         <is>
-          <t>恋人が異性の友達のために、くっついたエゴマの葉の醤油漬けを箸ではがしてあげるのはアリかナシか、という有名な論争。</t>
+          <t>未読スルー。メッセージを開きもせず返さないこと。「안 읽고 씹다」の略。</t>
         </is>
       </c>
       <c r="K780" s="16" t="inlineStr">
         <is>
-          <t>깻잎논쟁 너는 괜찮아, 안 괜찮아?</t>
+          <t>읽씹보다 안읽씹이 더 신경 쓰여.</t>
         </is>
       </c>
       <c r="L780" s="16" t="inlineStr">
         <is>
-          <t>The perilla leaf debate — are you okay with it or not?</t>
+          <t>Being left on unread bothers me more than being left on read.</t>
         </is>
       </c>
       <c r="M780" s="16" t="inlineStr">
         <is>
-          <t>El debate de la hoja de perilla: ¿te parece bien o no?</t>
+          <t>Me molesta más que ni lo abra a que me deje en visto.</t>
         </is>
       </c>
       <c r="N780" s="16" t="inlineStr">
         <is>
-          <t>芝麻葉之爭，你OK還是不OK？</t>
+          <t>比起已讀不回，未讀不回更讓我在意。</t>
         </is>
       </c>
       <c r="O780" s="16" t="inlineStr">
         <is>
-          <t>芝麻叶之争，你OK还是不OK？</t>
+          <t>比起已读不回，未读不回更让我在意。</t>
         </is>
       </c>
       <c r="P780" s="16" t="inlineStr">
         <is>
-          <t>エゴマの葉論争、あなたはアリ派？ナシ派？</t>
+          <t>既読スルーより未読スルーのほうが気になる。</t>
         </is>
       </c>
       <c r="Q780" s="16" t="inlineStr">
         <is>
-          <t>Dating talk, variety shows, icebreakers</t>
+          <t>Messaging, dating, friendships</t>
         </is>
       </c>
       <c r="R780" s="15" t="inlineStr">
@@ -76407,17 +76407,17 @@
     <row r="781" ht="46" customHeight="1">
       <c r="A781" s="15" t="inlineStr">
         <is>
-          <t>DAT-088</t>
+          <t>DAT-086</t>
         </is>
       </c>
       <c r="B781" s="15" t="inlineStr">
         <is>
-          <t>테토남</t>
+          <t>선톡</t>
         </is>
       </c>
       <c r="C781" s="15" t="inlineStr">
         <is>
-          <t>te-to-nam</t>
+          <t>seon-tok</t>
         </is>
       </c>
       <c r="D781" s="15" t="inlineStr">
@@ -76432,62 +76432,62 @@
       </c>
       <c r="F781" s="16" t="inlineStr">
         <is>
-          <t>A guy with a bold, driven, take-charge vibe — from 테스토스테론 (testosterone) + 남 (man). Women can be 테토녀.</t>
+          <t>Sending the first message — 선 (first) + 톡 (KakaoTalk message). Often a sign of interest.</t>
         </is>
       </c>
       <c r="G781" s="16" t="inlineStr">
         <is>
-          <t>Un chico con vibra decidida, enérgica y de líder; de 테스토스테론 (testosterona) + 남 (hombre). Ellas pueden ser 테토녀.</t>
+          <t>Mandar el primer mensaje: 선 (primero) + 톡 (mensaje de KakaoTalk). Suele ser señal de interés.</t>
         </is>
       </c>
       <c r="H781" s="16" t="inlineStr">
         <is>
-          <t>Teto男——個性直接、有衝勁、愛主導的男生，來自「테스토스테론（睪固酮）＋남（男）」。女生則叫테토녀。</t>
+          <t>主動先傳訊息——선（先）＋톡（KakaoTalk訊息），常被當成有好感的訊號。</t>
         </is>
       </c>
       <c r="I781" s="16" t="inlineStr">
         <is>
-          <t>Teto男——个性直接、有冲劲、爱主导的男生，来自“테스토스테론（睾固酮）＋남（男）”。女生则叫테토녀。</t>
+          <t>主动先传消息——선（先）＋톡（KakaoTalk消息），常被当成有好感的信号。</t>
         </is>
       </c>
       <c r="J781" s="16" t="inlineStr">
         <is>
-          <t>テト男。押しが強くて行動派、リードするタイプの男性。「테스토스테론（テストステロン）＋남（男）」から。女性なら테토녀。</t>
+          <t>自分から先にメッセージを送ること。선（先）＋톡（カカオトーク）。好意のサインとされがち。</t>
         </is>
       </c>
       <c r="K781" s="16" t="inlineStr">
         <is>
-          <t>걔는 완전 테토남 스타일이야. 뭐든 바로 직진해.</t>
+          <t>오늘은 내가 선톡 해볼까?</t>
         </is>
       </c>
       <c r="L781" s="16" t="inlineStr">
         <is>
-          <t>He's totally a teto guy. He goes straight for whatever he wants.</t>
+          <t>Should I be the one to text first today?</t>
         </is>
       </c>
       <c r="M781" s="16" t="inlineStr">
         <is>
-          <t>Es un teto total: va directo por lo que quiere.</t>
+          <t>¿Y si hoy le escribo yo primero?</t>
         </is>
       </c>
       <c r="N781" s="16" t="inlineStr">
         <is>
-          <t>他完全是Teto男類型，想要什麼就直接衝。</t>
+          <t>今天要不要換我先傳訊息？</t>
         </is>
       </c>
       <c r="O781" s="16" t="inlineStr">
         <is>
-          <t>他完全是Teto男类型，想要什么就直接冲。</t>
+          <t>今天要不要换我先传消息？</t>
         </is>
       </c>
       <c r="P781" s="16" t="inlineStr">
         <is>
-          <t>あの人は完全にテト男タイプ。何でもすぐ直進するの。</t>
+          <t>今日は私から先にLINEしてみようかな？</t>
         </is>
       </c>
       <c r="Q781" s="16" t="inlineStr">
         <is>
-          <t>Dating talk, personality-type memes, social media</t>
+          <t>Dating, crushes, messaging</t>
         </is>
       </c>
       <c r="R781" s="15" t="inlineStr">
@@ -76504,17 +76504,17 @@
     <row r="782" ht="46" customHeight="1">
       <c r="A782" s="15" t="inlineStr">
         <is>
-          <t>DAT-089</t>
+          <t>DAT-087</t>
         </is>
       </c>
       <c r="B782" s="15" t="inlineStr">
         <is>
-          <t>에겐남</t>
+          <t>깻잎논쟁</t>
         </is>
       </c>
       <c r="C782" s="15" t="inlineStr">
         <is>
-          <t>e-gen-nam</t>
+          <t>kkaen-nip-non-jaeng</t>
         </is>
       </c>
       <c r="D782" s="15" t="inlineStr">
@@ -76529,62 +76529,62 @@
       </c>
       <c r="F782" s="16" t="inlineStr">
         <is>
-          <t>A soft, emotionally attentive guy who values empathy — from 에스트로겐 (estrogen) + 남 (man). Women can be 에겐녀.</t>
+          <t>The famous debate over whether it's okay for your partner to help a friend of the other gender peel apart a stuck pickled perilla leaf.</t>
         </is>
       </c>
       <c r="G782" s="16" t="inlineStr">
         <is>
-          <t>Un chico suave y atento a las emociones que valora la empatía; de 에스트로겐 (estrógeno) + 남 (hombre). Ellas pueden ser 에겐녀.</t>
+          <t>El famoso debate sobre si está bien que tu pareja ayude a una amiga o un amigo del otro género a separar una hoja de perilla en conserva pegada.</t>
         </is>
       </c>
       <c r="H782" s="16" t="inlineStr">
         <is>
-          <t>Egen男——溫柔、細膩、重視共感的男生，來自「에스트로겐（雌激素）＋남（男）」。女生則叫에겐녀。</t>
+          <t>有名的「芝麻葉之爭」：另一半幫異性朋友夾開黏在一起的醃芝麻葉，到底可不可以？</t>
         </is>
       </c>
       <c r="I782" s="16" t="inlineStr">
         <is>
-          <t>Egen男——温柔、细腻、重视共感的男生，来自“에스트로겐（雌激素）＋남（男）”。女生则叫에겐녀。</t>
+          <t>有名的“芝麻叶之争”：另一半帮异性朋友夹开黏在一起的腌芝麻叶，到底可不可以？</t>
         </is>
       </c>
       <c r="J782" s="16" t="inlineStr">
         <is>
-          <t>エゲン男。優しくて感情に寄り添う、共感タイプの男性。「에스트로겐（エストロゲン）＋남（男）」から。女性なら에겐녀。</t>
+          <t>恋人が異性の友達のために、くっついたエゴマの葉の醤油漬けを箸ではがしてあげるのはアリかナシか、という有名な論争。</t>
         </is>
       </c>
       <c r="K782" s="16" t="inlineStr">
         <is>
-          <t>내 이상형은 섬세한 에겐남이야.</t>
+          <t>깻잎논쟁 너는 괜찮아, 안 괜찮아?</t>
         </is>
       </c>
       <c r="L782" s="16" t="inlineStr">
         <is>
-          <t>My ideal type is a thoughtful egen guy.</t>
+          <t>The perilla leaf debate — are you okay with it or not?</t>
         </is>
       </c>
       <c r="M782" s="16" t="inlineStr">
         <is>
-          <t>Mi tipo ideal es un chico egen detallista.</t>
+          <t>El debate de la hoja de perilla: ¿te parece bien o no?</t>
         </is>
       </c>
       <c r="N782" s="16" t="inlineStr">
         <is>
-          <t>我的理想型是細心的Egen男。</t>
+          <t>芝麻葉之爭，你OK還是不OK？</t>
         </is>
       </c>
       <c r="O782" s="16" t="inlineStr">
         <is>
-          <t>我的理想型是细心的Egen男。</t>
+          <t>芝麻叶之争，你OK还是不OK？</t>
         </is>
       </c>
       <c r="P782" s="16" t="inlineStr">
         <is>
-          <t>私の理想のタイプは繊細なエゲン男。</t>
+          <t>エゴマの葉論争、あなたはアリ派？ナシ派？</t>
         </is>
       </c>
       <c r="Q782" s="16" t="inlineStr">
         <is>
-          <t>Dating talk, personality-type memes, social media</t>
+          <t>Dating talk, variety shows, icebreakers</t>
         </is>
       </c>
       <c r="R782" s="15" t="inlineStr">
@@ -76601,17 +76601,17 @@
     <row r="783" ht="46" customHeight="1">
       <c r="A783" s="15" t="inlineStr">
         <is>
-          <t>DAT-090</t>
+          <t>DAT-088</t>
         </is>
       </c>
       <c r="B783" s="15" t="inlineStr">
         <is>
-          <t>썸남</t>
+          <t>테토남</t>
         </is>
       </c>
       <c r="C783" s="15" t="inlineStr">
         <is>
-          <t>sseom-nam</t>
+          <t>te-to-nam</t>
         </is>
       </c>
       <c r="D783" s="15" t="inlineStr">
@@ -76626,62 +76626,62 @@
       </c>
       <c r="F783" s="16" t="inlineStr">
         <is>
-          <t>The guy you're in a 썸 (talking stage) with; the girl version is 썸녀.</t>
+          <t>A guy with a bold, driven, take-charge vibe — from 테스토스테론 (testosterone) + 남 (man). Women can be 테토녀.</t>
         </is>
       </c>
       <c r="G783" s="16" t="inlineStr">
         <is>
-          <t>El chico con el que estás en 썸 (etapa de conocerse); la versión femenina es 썸녀.</t>
+          <t>Un chico con vibra decidida, enérgica y de líder; de 테스토스테론 (testosterona) + 남 (hombre). Ellas pueden ser 테토녀.</t>
         </is>
       </c>
       <c r="H783" s="16" t="inlineStr">
         <is>
-          <t>正在跟你搞썸（曖昧）的男生；女生版本是썸녀。</t>
+          <t>Teto男——個性直接、有衝勁、愛主導的男生，來自「테스토스테론（睪固酮）＋남（男）」。女生則叫테토녀。</t>
         </is>
       </c>
       <c r="I783" s="16" t="inlineStr">
         <is>
-          <t>正在跟你搞썸（暧昧）的男生；女生版本是썸녀。</t>
+          <t>Teto男——个性直接、有冲劲、爱主导的男生，来自“테스토스테론（睾固酮）＋남（男）”。女生则叫테토녀。</t>
         </is>
       </c>
       <c r="J783" s="16" t="inlineStr">
         <is>
-          <t>썸（付き合う前のいい感じ）の相手の男性。女性版は썸녀。</t>
+          <t>テト男。押しが強くて行動派、リードするタイプの男性。「테스토스테론（テストステロン）＋남（男）」から。女性なら테토녀。</t>
         </is>
       </c>
       <c r="K783" s="16" t="inlineStr">
         <is>
-          <t>썸남한테 선톡 올까?</t>
+          <t>걔는 완전 테토남 스타일이야. 뭐든 바로 직진해.</t>
         </is>
       </c>
       <c r="L783" s="16" t="inlineStr">
         <is>
-          <t>Will my talking-stage guy text me first?</t>
+          <t>He's totally a teto guy. He goes straight for whatever he wants.</t>
         </is>
       </c>
       <c r="M783" s="16" t="inlineStr">
         <is>
-          <t>¿Me escribirá primero el chico con el que estoy en algo?</t>
+          <t>Es un teto total: va directo por lo que quiere.</t>
         </is>
       </c>
       <c r="N783" s="16" t="inlineStr">
         <is>
-          <t>曖昧對象會先傳訊息給我嗎？</t>
+          <t>他完全是Teto男類型，想要什麼就直接衝。</t>
         </is>
       </c>
       <c r="O783" s="16" t="inlineStr">
         <is>
-          <t>暧昧对象会先传消息给我吗？</t>
+          <t>他完全是Teto男类型，想要什么就直接冲。</t>
         </is>
       </c>
       <c r="P783" s="16" t="inlineStr">
         <is>
-          <t>썸남から先にLINE来るかな？</t>
+          <t>あの人は完全にテト男タイプ。何でもすぐ直進するの。</t>
         </is>
       </c>
       <c r="Q783" s="16" t="inlineStr">
         <is>
-          <t>Chats with friends, dating talk, dramas</t>
+          <t>Dating talk, personality-type memes, social media</t>
         </is>
       </c>
       <c r="R783" s="15" t="inlineStr">
@@ -76698,17 +76698,17 @@
     <row r="784" ht="46" customHeight="1">
       <c r="A784" s="15" t="inlineStr">
         <is>
-          <t>DAT-091</t>
+          <t>DAT-089</t>
         </is>
       </c>
       <c r="B784" s="15" t="inlineStr">
         <is>
-          <t>데이트통장</t>
+          <t>에겐남</t>
         </is>
       </c>
       <c r="C784" s="15" t="inlineStr">
         <is>
-          <t>de-i-teu-tong-jang</t>
+          <t>e-gen-nam</t>
         </is>
       </c>
       <c r="D784" s="15" t="inlineStr">
@@ -76723,62 +76723,62 @@
       </c>
       <c r="F784" s="16" t="inlineStr">
         <is>
-          <t>A shared bank account a couple both pay into to cover date costs.</t>
+          <t>A soft, emotionally attentive guy who values empathy — from 에스트로겐 (estrogen) + 남 (man). Women can be 에겐녀.</t>
         </is>
       </c>
       <c r="G784" s="16" t="inlineStr">
         <is>
-          <t>Una cuenta bancaria compartida en la que la pareja deposita dinero para pagar sus citas.</t>
+          <t>Un chico suave y atento a las emociones que valora la empatía; de 에스트로겐 (estrógeno) + 남 (hombre). Ellas pueden ser 에겐녀.</t>
         </is>
       </c>
       <c r="H784" s="16" t="inlineStr">
         <is>
-          <t>情侶一起存錢、專門用來支付約會開銷的共同帳戶。</t>
+          <t>Egen男——溫柔、細膩、重視共感的男生，來自「에스트로겐（雌激素）＋남（男）」。女生則叫에겐녀。</t>
         </is>
       </c>
       <c r="I784" s="16" t="inlineStr">
         <is>
-          <t>情侣一起存钱、专门用来支付约会开销的共同帐户。</t>
+          <t>Egen男——温柔、细腻、重视共感的男生，来自“에스트로겐（雌激素）＋남（男）”。女生则叫에겐녀。</t>
         </is>
       </c>
       <c r="J784" s="16" t="inlineStr">
         <is>
-          <t>カップルが二人でお金を入れて、デート代を払うための共同口座。</t>
+          <t>エゲン男。優しくて感情に寄り添う、共感タイプの男性。「에스트로겐（エストロゲン）＋남（男）」から。女性なら에겐녀。</t>
         </is>
       </c>
       <c r="K784" s="16" t="inlineStr">
         <is>
-          <t>우리 이번 달부터 데이트통장 만들었어.</t>
+          <t>내 이상형은 섬세한 에겐남이야.</t>
         </is>
       </c>
       <c r="L784" s="16" t="inlineStr">
         <is>
-          <t>We started a shared date account this month.</t>
+          <t>My ideal type is a thoughtful egen guy.</t>
         </is>
       </c>
       <c r="M784" s="16" t="inlineStr">
         <is>
-          <t>Este mes abrimos una cuenta compartida para las citas.</t>
+          <t>Mi tipo ideal es un chico egen detallista.</t>
         </is>
       </c>
       <c r="N784" s="16" t="inlineStr">
         <is>
-          <t>我們這個月開始用約會共同帳戶了。</t>
+          <t>我的理想型是細心的Egen男。</t>
         </is>
       </c>
       <c r="O784" s="16" t="inlineStr">
         <is>
-          <t>我们这个月开始用约会共同帐户了。</t>
+          <t>我的理想型是细心的Egen男。</t>
         </is>
       </c>
       <c r="P784" s="16" t="inlineStr">
         <is>
-          <t>今月から데이트통장（デート用の共同口座）作ったよ。</t>
+          <t>私の理想のタイプは繊細なエゲン男。</t>
         </is>
       </c>
       <c r="Q784" s="16" t="inlineStr">
         <is>
-          <t>Couples, dating advice, online debates</t>
+          <t>Dating talk, personality-type memes, social media</t>
         </is>
       </c>
       <c r="R784" s="15" t="inlineStr">
@@ -76795,17 +76795,17 @@
     <row r="785" ht="46" customHeight="1">
       <c r="A785" s="15" t="inlineStr">
         <is>
-          <t>DAT-092</t>
+          <t>DAT-090</t>
         </is>
       </c>
       <c r="B785" s="15" t="inlineStr">
         <is>
-          <t>돌싱</t>
+          <t>썸남</t>
         </is>
       </c>
       <c r="C785" s="15" t="inlineStr">
         <is>
-          <t>dol-sing</t>
+          <t>sseom-nam</t>
         </is>
       </c>
       <c r="D785" s="15" t="inlineStr">
@@ -76820,62 +76820,62 @@
       </c>
       <c r="F785" s="16" t="inlineStr">
         <is>
-          <t>Short for 돌아온 싱글 ("returned single") — someone who is single again after a divorce.</t>
+          <t>The guy you're in a 썸 (talking stage) with; the girl version is 썸녀.</t>
         </is>
       </c>
       <c r="G785" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 돌아온 싱글 ("soltero que regresa"): alguien que vuelve a estar soltero tras un divorcio.</t>
+          <t>El chico con el que estás en 썸 (etapa de conocerse); la versión femenina es 썸녀.</t>
         </is>
       </c>
       <c r="H785" s="16" t="inlineStr">
         <is>
-          <t>돌아온 싱글（回歸單身）的縮寫，指離婚後重新單身的人。</t>
+          <t>正在跟你搞썸（曖昧）的男生；女生版本是썸녀。</t>
         </is>
       </c>
       <c r="I785" s="16" t="inlineStr">
         <is>
-          <t>돌아온 싱글（回归单身）的缩写，指离婚后重新单身的人。</t>
+          <t>正在跟你搞썸（暧昧）的男生；女生版本是썸녀。</t>
         </is>
       </c>
       <c r="J785" s="16" t="inlineStr">
         <is>
-          <t>돌아온 싱글（戻ってきたシングル）の略。離婚して再び独身になった人。</t>
+          <t>썸（付き合う前のいい感じ）の相手の男性。女性版は썸녀。</t>
         </is>
       </c>
       <c r="K785" s="16" t="inlineStr">
         <is>
-          <t>요즘 돌싱 연애 프로그램이 인기야.</t>
+          <t>썸남한테 선톡 올까?</t>
         </is>
       </c>
       <c r="L785" s="16" t="inlineStr">
         <is>
-          <t>Dating shows for divorced singles are popular these days.</t>
+          <t>Will my talking-stage guy text me first?</t>
         </is>
       </c>
       <c r="M785" s="16" t="inlineStr">
         <is>
-          <t>Hoy en día están de moda los realities de citas para divorciados.</t>
+          <t>¿Me escribirá primero el chico con el que estoy en algo?</t>
         </is>
       </c>
       <c r="N785" s="16" t="inlineStr">
         <is>
-          <t>最近離婚單身族的戀愛節目很紅。</t>
+          <t>曖昧對象會先傳訊息給我嗎？</t>
         </is>
       </c>
       <c r="O785" s="16" t="inlineStr">
         <is>
-          <t>最近离婚单身族的恋爱节目很红。</t>
+          <t>暧昧对象会先传消息给我吗？</t>
         </is>
       </c>
       <c r="P785" s="16" t="inlineStr">
         <is>
-          <t>最近、돌싱（バツイチ）の恋愛番組が人気だよ。</t>
+          <t>썸남から先にLINE来るかな？</t>
         </is>
       </c>
       <c r="Q785" s="16" t="inlineStr">
         <is>
-          <t>TV, news, dating shows</t>
+          <t>Chats with friends, dating talk, dramas</t>
         </is>
       </c>
       <c r="R785" s="15" t="inlineStr">
@@ -76892,17 +76892,17 @@
     <row r="786" ht="46" customHeight="1">
       <c r="A786" s="15" t="inlineStr">
         <is>
-          <t>DAT-093</t>
+          <t>DAT-091</t>
         </is>
       </c>
       <c r="B786" s="15" t="inlineStr">
         <is>
-          <t>연프</t>
+          <t>데이트통장</t>
         </is>
       </c>
       <c r="C786" s="15" t="inlineStr">
         <is>
-          <t>yeon-peu</t>
+          <t>de-i-teu-tong-jang</t>
         </is>
       </c>
       <c r="D786" s="15" t="inlineStr">
@@ -76917,62 +76917,62 @@
       </c>
       <c r="F786" s="16" t="inlineStr">
         <is>
-          <t>Short for 연애 프로그램 — a dating reality show.</t>
+          <t>A shared bank account a couple both pay into to cover date costs.</t>
         </is>
       </c>
       <c r="G786" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 연애 프로그램: un reality de citas.</t>
+          <t>Una cuenta bancaria compartida en la que la pareja deposita dinero para pagar sus citas.</t>
         </is>
       </c>
       <c r="H786" s="16" t="inlineStr">
         <is>
-          <t>연애 프로그램的縮寫，戀愛實境節目。</t>
+          <t>情侶一起存錢、專門用來支付約會開銷的共同帳戶。</t>
         </is>
       </c>
       <c r="I786" s="16" t="inlineStr">
         <is>
-          <t>연애 프로그램的缩写，恋爱实境节目。</t>
+          <t>情侣一起存钱、专门用来支付约会开销的共同帐户。</t>
         </is>
       </c>
       <c r="J786" s="16" t="inlineStr">
         <is>
-          <t>연애 프로그램の略。恋愛リアリティ番組（恋リア）。</t>
+          <t>カップルが二人でお金を入れて、デート代を払うための共同口座。</t>
         </is>
       </c>
       <c r="K786" s="16" t="inlineStr">
         <is>
-          <t>요즘 무슨 연프 봐?</t>
+          <t>우리 이번 달부터 데이트통장 만들었어.</t>
         </is>
       </c>
       <c r="L786" s="16" t="inlineStr">
         <is>
-          <t>Which dating show are you watching these days?</t>
+          <t>We started a shared date account this month.</t>
         </is>
       </c>
       <c r="M786" s="16" t="inlineStr">
         <is>
-          <t>¿Qué reality de citas estás viendo últimamente?</t>
+          <t>Este mes abrimos una cuenta compartida para las citas.</t>
         </is>
       </c>
       <c r="N786" s="16" t="inlineStr">
         <is>
-          <t>最近在看哪個戀綜？</t>
+          <t>我們這個月開始用約會共同帳戶了。</t>
         </is>
       </c>
       <c r="O786" s="16" t="inlineStr">
         <is>
-          <t>最近在看哪个恋综？</t>
+          <t>我们这个月开始用约会共同帐户了。</t>
         </is>
       </c>
       <c r="P786" s="16" t="inlineStr">
         <is>
-          <t>最近どの恋リア見てる？</t>
+          <t>今月から데이트통장（デート用の共同口座）作ったよ。</t>
         </is>
       </c>
       <c r="Q786" s="16" t="inlineStr">
         <is>
-          <t>TV and streaming talk, SNS</t>
+          <t>Couples, dating advice, online debates</t>
         </is>
       </c>
       <c r="R786" s="15" t="inlineStr">
@@ -76989,17 +76989,17 @@
     <row r="787" ht="46" customHeight="1">
       <c r="A787" s="15" t="inlineStr">
         <is>
-          <t>DAT-094</t>
+          <t>DAT-092</t>
         </is>
       </c>
       <c r="B787" s="15" t="inlineStr">
         <is>
-          <t>인만추</t>
+          <t>돌싱</t>
         </is>
       </c>
       <c r="C787" s="15" t="inlineStr">
         <is>
-          <t>in-man-chu</t>
+          <t>dol-sing</t>
         </is>
       </c>
       <c r="D787" s="15" t="inlineStr">
@@ -77014,62 +77014,62 @@
       </c>
       <c r="F787" s="16" t="inlineStr">
         <is>
-          <t>Short for 인위적인 만남 추구, "pursuing artificial meetings": preferring to meet partners through set-ups like blind dates, apps or matchmaking events instead of waiting to meet someone naturally. The opposite of 자만추.</t>
+          <t>Short for 돌아온 싱글 ("returned single") — someone who is single again after a divorce.</t>
         </is>
       </c>
       <c r="G787" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 인위적인 만남 추구, "buscar encuentros artificiales": preferir conocer pareja por citas a ciegas, apps o eventos de citas en lugar de esperar a conocer a alguien de forma natural. Lo contrario de 자만추.</t>
+          <t>Abreviatura de 돌아온 싱글 ("soltero que regresa"): alguien que vuelve a estar soltero tras un divorcio.</t>
         </is>
       </c>
       <c r="H787" s="16" t="inlineStr">
         <is>
-          <t>인위적인 만남 추구的縮寫，「追求人為的相遇」：比起等待自然認識，更喜歡透過聯誼、交友軟體、相親活動等安排好的機會認識對象。和자만추相反。</t>
+          <t>돌아온 싱글（回歸單身）的縮寫，指離婚後重新單身的人。</t>
         </is>
       </c>
       <c r="I787" s="16" t="inlineStr">
         <is>
-          <t>인위적인 만남 추구的缩写，“追求人为的相遇”：比起等待自然认识，更喜欢通过联谊、交友软件、相亲活动等安排好的机会认识对象。和자만추相反。</t>
+          <t>돌아온 싱글（回归单身）的缩写，指离婚后重新单身的人。</t>
         </is>
       </c>
       <c r="J787" s="16" t="inlineStr">
         <is>
-          <t>인위적인 만남 추구の略で「作られた出会いを求める」。自然な出会いを待つより、合コン・紹介・マッチングアプリなど用意された場で相手を探すこと。자만추の反対。</t>
+          <t>돌아온 싱글（戻ってきたシングル）の略。離婚して再び独身になった人。</t>
         </is>
       </c>
       <c r="K787" s="16" t="inlineStr">
         <is>
-          <t>자만추는 포기했어, 이제 인만추야.</t>
+          <t>요즘 돌싱 연애 프로그램이 인기야.</t>
         </is>
       </c>
       <c r="L787" s="16" t="inlineStr">
         <is>
-          <t>I gave up on meeting someone naturally — I'm all about set-ups now.</t>
+          <t>Dating shows for divorced singles are popular these days.</t>
         </is>
       </c>
       <c r="M787" s="16" t="inlineStr">
         <is>
-          <t>Ya me rendí con conocer a alguien de forma natural; ahora voy a por citas organizadas.</t>
+          <t>Hoy en día están de moda los realities de citas para divorciados.</t>
         </is>
       </c>
       <c r="N787" s="16" t="inlineStr">
         <is>
-          <t>我放棄自然相遇了，現在走인만추路線。</t>
+          <t>最近離婚單身族的戀愛節目很紅。</t>
         </is>
       </c>
       <c r="O787" s="16" t="inlineStr">
         <is>
-          <t>我放弃自然相遇了，现在走인만추路线。</t>
+          <t>最近离婚单身族的恋爱节目很红。</t>
         </is>
       </c>
       <c r="P787" s="16" t="inlineStr">
         <is>
-          <t>自然な出会いはもう諦めた。これからは인만추でいく。</t>
+          <t>最近、돌싱（バツイチ）の恋愛番組が人気だよ。</t>
         </is>
       </c>
       <c r="Q787" s="16" t="inlineStr">
         <is>
-          <t>Dating talk, news on matchmaking events and dating apps</t>
+          <t>TV, news, dating shows</t>
         </is>
       </c>
       <c r="R787" s="15" t="inlineStr">
@@ -77086,17 +77086,17 @@
     <row r="788" ht="46" customHeight="1">
       <c r="A788" s="15" t="inlineStr">
         <is>
-          <t>DAT-095</t>
+          <t>DAT-093</t>
         </is>
       </c>
       <c r="B788" s="15" t="inlineStr">
         <is>
-          <t>번따</t>
+          <t>연프</t>
         </is>
       </c>
       <c r="C788" s="15" t="inlineStr">
         <is>
-          <t>beon-tta</t>
+          <t>yeon-peu</t>
         </is>
       </c>
       <c r="D788" s="15" t="inlineStr">
@@ -77111,62 +77111,62 @@
       </c>
       <c r="F788" s="16" t="inlineStr">
         <is>
-          <t>Short for 번호 따기: walking up to a stranger you find attractive and asking for their phone number.</t>
+          <t>Short for 연애 프로그램 — a dating reality show.</t>
         </is>
       </c>
       <c r="G788" s="16" t="inlineStr">
         <is>
-          <t>Abreviatura de 번호 따기: acercarte a un desconocido que te gusta y pedirle su número de teléfono.</t>
+          <t>Abreviatura de 연애 프로그램: un reality de citas.</t>
         </is>
       </c>
       <c r="H788" s="16" t="inlineStr">
         <is>
-          <t>번호 따기的縮寫：主動向心動的陌生人要電話號碼，搭訕要電話。</t>
+          <t>연애 프로그램的縮寫，戀愛實境節目。</t>
         </is>
       </c>
       <c r="I788" s="16" t="inlineStr">
         <is>
-          <t>번호 따기的缩写：主动向心动的陌生人要电话号码，搭讪要电话。</t>
+          <t>연애 프로그램的缩写，恋爱实境节目。</t>
         </is>
       </c>
       <c r="J788" s="16" t="inlineStr">
         <is>
-          <t>번호 따기の略。気になる知らない人に声をかけて電話番号を聞くこと。いわゆる逆ナン・ナンパで連絡先を聞くこと。</t>
+          <t>연애 프로그램の略。恋愛リアリティ番組（恋リア）。</t>
         </is>
       </c>
       <c r="K788" s="16" t="inlineStr">
         <is>
-          <t>카페에서 번따 당했어!</t>
+          <t>요즘 무슨 연프 봐?</t>
         </is>
       </c>
       <c r="L788" s="16" t="inlineStr">
         <is>
-          <t>Someone asked for my number at the café!</t>
+          <t>Which dating show are you watching these days?</t>
         </is>
       </c>
       <c r="M788" s="16" t="inlineStr">
         <is>
-          <t>¡Alguien me pidió el número en la cafetería!</t>
+          <t>¿Qué reality de citas estás viendo últimamente?</t>
         </is>
       </c>
       <c r="N788" s="16" t="inlineStr">
         <is>
-          <t>我在咖啡廳被要電話了！</t>
+          <t>最近在看哪個戀綜？</t>
         </is>
       </c>
       <c r="O788" s="16" t="inlineStr">
         <is>
-          <t>我在咖啡厅被要电话了！</t>
+          <t>最近在看哪个恋综？</t>
         </is>
       </c>
       <c r="P788" s="16" t="inlineStr">
         <is>
-          <t>カフェで번따されちゃった！</t>
+          <t>最近どの恋リア見てる？</t>
         </is>
       </c>
       <c r="Q788" s="16" t="inlineStr">
         <is>
-          <t>Everyday dating talk, social media, street interviews</t>
+          <t>TV and streaming talk, SNS</t>
         </is>
       </c>
       <c r="R788" s="15" t="inlineStr">
@@ -77183,102 +77183,296 @@
     <row r="789" ht="46" customHeight="1">
       <c r="A789" s="15" t="inlineStr">
         <is>
+          <t>DAT-094</t>
+        </is>
+      </c>
+      <c r="B789" s="15" t="inlineStr">
+        <is>
+          <t>인만추</t>
+        </is>
+      </c>
+      <c r="C789" s="15" t="inlineStr">
+        <is>
+          <t>in-man-chu</t>
+        </is>
+      </c>
+      <c r="D789" s="15" t="inlineStr">
+        <is>
+          <t>연애 · 썸 표현</t>
+        </is>
+      </c>
+      <c r="E789" s="15" t="inlineStr">
+        <is>
+          <t>Dating &amp; Romance</t>
+        </is>
+      </c>
+      <c r="F789" s="16" t="inlineStr">
+        <is>
+          <t>Short for 인위적인 만남 추구, "pursuing artificial meetings": preferring to meet partners through set-ups like blind dates, apps or matchmaking events instead of waiting to meet someone naturally. The opposite of 자만추.</t>
+        </is>
+      </c>
+      <c r="G789" s="16" t="inlineStr">
+        <is>
+          <t>Abreviatura de 인위적인 만남 추구, "buscar encuentros artificiales": preferir conocer pareja por citas a ciegas, apps o eventos de citas en lugar de esperar a conocer a alguien de forma natural. Lo contrario de 자만추.</t>
+        </is>
+      </c>
+      <c r="H789" s="16" t="inlineStr">
+        <is>
+          <t>인위적인 만남 추구的縮寫，「追求人為的相遇」：比起等待自然認識，更喜歡透過聯誼、交友軟體、相親活動等安排好的機會認識對象。和자만추相反。</t>
+        </is>
+      </c>
+      <c r="I789" s="16" t="inlineStr">
+        <is>
+          <t>인위적인 만남 추구的缩写，“追求人为的相遇”：比起等待自然认识，更喜欢通过联谊、交友软件、相亲活动等安排好的机会认识对象。和자만추相反。</t>
+        </is>
+      </c>
+      <c r="J789" s="16" t="inlineStr">
+        <is>
+          <t>인위적인 만남 추구の略で「作られた出会いを求める」。自然な出会いを待つより、合コン・紹介・マッチングアプリなど用意された場で相手を探すこと。자만추の反対。</t>
+        </is>
+      </c>
+      <c r="K789" s="16" t="inlineStr">
+        <is>
+          <t>자만추는 포기했어, 이제 인만추야.</t>
+        </is>
+      </c>
+      <c r="L789" s="16" t="inlineStr">
+        <is>
+          <t>I gave up on meeting someone naturally — I'm all about set-ups now.</t>
+        </is>
+      </c>
+      <c r="M789" s="16" t="inlineStr">
+        <is>
+          <t>Ya me rendí con conocer a alguien de forma natural; ahora voy a por citas organizadas.</t>
+        </is>
+      </c>
+      <c r="N789" s="16" t="inlineStr">
+        <is>
+          <t>我放棄自然相遇了，現在走인만추路線。</t>
+        </is>
+      </c>
+      <c r="O789" s="16" t="inlineStr">
+        <is>
+          <t>我放弃自然相遇了，现在走인만추路线。</t>
+        </is>
+      </c>
+      <c r="P789" s="16" t="inlineStr">
+        <is>
+          <t>自然な出会いはもう諦めた。これからは인만추でいく。</t>
+        </is>
+      </c>
+      <c r="Q789" s="16" t="inlineStr">
+        <is>
+          <t>Dating talk, news on matchmaking events and dating apps</t>
+        </is>
+      </c>
+      <c r="R789" s="15" t="inlineStr">
+        <is>
+          <t>Verified (web-checked)</t>
+        </is>
+      </c>
+      <c r="S789" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="790" ht="46" customHeight="1">
+      <c r="A790" s="15" t="inlineStr">
+        <is>
+          <t>DAT-095</t>
+        </is>
+      </c>
+      <c r="B790" s="15" t="inlineStr">
+        <is>
+          <t>번따</t>
+        </is>
+      </c>
+      <c r="C790" s="15" t="inlineStr">
+        <is>
+          <t>beon-tta</t>
+        </is>
+      </c>
+      <c r="D790" s="15" t="inlineStr">
+        <is>
+          <t>연애 · 썸 표현</t>
+        </is>
+      </c>
+      <c r="E790" s="15" t="inlineStr">
+        <is>
+          <t>Dating &amp; Romance</t>
+        </is>
+      </c>
+      <c r="F790" s="16" t="inlineStr">
+        <is>
+          <t>Short for 번호 따기: walking up to a stranger you find attractive and asking for their phone number.</t>
+        </is>
+      </c>
+      <c r="G790" s="16" t="inlineStr">
+        <is>
+          <t>Abreviatura de 번호 따기: acercarte a un desconocido que te gusta y pedirle su número de teléfono.</t>
+        </is>
+      </c>
+      <c r="H790" s="16" t="inlineStr">
+        <is>
+          <t>번호 따기的縮寫：主動向心動的陌生人要電話號碼，搭訕要電話。</t>
+        </is>
+      </c>
+      <c r="I790" s="16" t="inlineStr">
+        <is>
+          <t>번호 따기的缩写：主动向心动的陌生人要电话号码，搭讪要电话。</t>
+        </is>
+      </c>
+      <c r="J790" s="16" t="inlineStr">
+        <is>
+          <t>번호 따기の略。気になる知らない人に声をかけて電話番号を聞くこと。いわゆる逆ナン・ナンパで連絡先を聞くこと。</t>
+        </is>
+      </c>
+      <c r="K790" s="16" t="inlineStr">
+        <is>
+          <t>카페에서 번따 당했어!</t>
+        </is>
+      </c>
+      <c r="L790" s="16" t="inlineStr">
+        <is>
+          <t>Someone asked for my number at the café!</t>
+        </is>
+      </c>
+      <c r="M790" s="16" t="inlineStr">
+        <is>
+          <t>¡Alguien me pidió el número en la cafetería!</t>
+        </is>
+      </c>
+      <c r="N790" s="16" t="inlineStr">
+        <is>
+          <t>我在咖啡廳被要電話了！</t>
+        </is>
+      </c>
+      <c r="O790" s="16" t="inlineStr">
+        <is>
+          <t>我在咖啡厅被要电话了！</t>
+        </is>
+      </c>
+      <c r="P790" s="16" t="inlineStr">
+        <is>
+          <t>カフェで번따されちゃった！</t>
+        </is>
+      </c>
+      <c r="Q790" s="16" t="inlineStr">
+        <is>
+          <t>Everyday dating talk, social media, street interviews</t>
+        </is>
+      </c>
+      <c r="R790" s="15" t="inlineStr">
+        <is>
+          <t>Verified (web-checked)</t>
+        </is>
+      </c>
+      <c r="S790" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="791" ht="46" customHeight="1">
+      <c r="A791" s="15" t="inlineStr">
+        <is>
           <t>DAT-096</t>
         </is>
       </c>
-      <c r="B789" s="15" t="inlineStr">
+      <c r="B791" s="15" t="inlineStr">
         <is>
           <t>스드메</t>
         </is>
       </c>
-      <c r="C789" s="15" t="inlineStr">
+      <c r="C791" s="15" t="inlineStr">
         <is>
           <t>seu-deu-me</t>
         </is>
       </c>
-      <c r="D789" s="15" t="inlineStr">
+      <c r="D791" s="15" t="inlineStr">
         <is>
           <t>연애 · 썸 표현</t>
         </is>
       </c>
-      <c r="E789" s="15" t="inlineStr">
+      <c r="E791" s="15" t="inlineStr">
         <is>
           <t>Dating &amp; Romance</t>
         </is>
       </c>
-      <c r="F789" s="16" t="inlineStr">
+      <c r="F791" s="16" t="inlineStr">
         <is>
           <t>Short for 스튜디오·드레스·메이크업: the wedding photo studio, wedding dress and bridal makeup package that Korean couples book when planning a wedding.</t>
         </is>
       </c>
-      <c r="G789" s="16" t="inlineStr">
+      <c r="G791" s="16" t="inlineStr">
         <is>
           <t>Abreviatura de 스튜디오·드레스·메이크업: el paquete de estudio de fotos, vestido de novia y maquillaje que las parejas coreanas reservan al planear la boda.</t>
         </is>
       </c>
-      <c r="H789" s="16" t="inlineStr">
+      <c r="H791" s="16" t="inlineStr">
         <is>
           <t>스튜디오·드레스·메이크업的縮寫：韓國新人籌備婚禮時預約的婚紗攝影、婚紗禮服和新娘妝髮套組。</t>
         </is>
       </c>
-      <c r="I789" s="16" t="inlineStr">
+      <c r="I791" s="16" t="inlineStr">
         <is>
           <t>스튜디오·드레스·메이크업的缩写：韩国新人筹备婚礼时预约的婚纱摄影、婚纱礼服和新娘妆发套组。</t>
         </is>
       </c>
-      <c r="J789" s="16" t="inlineStr">
+      <c r="J791" s="16" t="inlineStr">
         <is>
           <t>스튜디오·드레스·메이크업の略。韓国のカップルが結婚準備で予約する、ウェディングフォトスタジオ・ドレス・ブライダルメイクのセット。</t>
         </is>
       </c>
-      <c r="K789" s="16" t="inlineStr">
+      <c r="K791" s="16" t="inlineStr">
         <is>
           <t>결혼 준비 중인데 스드메 견적이 너무 비싸.</t>
         </is>
       </c>
-      <c r="L789" s="16" t="inlineStr">
+      <c r="L791" s="16" t="inlineStr">
         <is>
           <t>We're planning the wedding and the studio-dress-makeup quotes are so expensive.</t>
         </is>
       </c>
-      <c r="M789" s="16" t="inlineStr">
+      <c r="M791" s="16" t="inlineStr">
         <is>
           <t>Estamos preparando la boda y los presupuestos de estudio, vestido y maquillaje son carísimos.</t>
         </is>
       </c>
-      <c r="N789" s="16" t="inlineStr">
+      <c r="N791" s="16" t="inlineStr">
         <is>
           <t>正在準備婚禮，스드메的報價好貴。</t>
         </is>
       </c>
-      <c r="O789" s="16" t="inlineStr">
+      <c r="O791" s="16" t="inlineStr">
         <is>
           <t>正在准备婚礼，스드메的报价好贵。</t>
         </is>
       </c>
-      <c r="P789" s="16" t="inlineStr">
+      <c r="P791" s="16" t="inlineStr">
         <is>
           <t>結婚準備中なんだけど、스드메の見積もりが高すぎる。</t>
         </is>
       </c>
-      <c r="Q789" s="16" t="inlineStr">
+      <c r="Q791" s="16" t="inlineStr">
         <is>
           <t>Wedding planning talk, wedding fairs, news on wedding costs</t>
         </is>
       </c>
-      <c r="R789" s="15" t="inlineStr">
+      <c r="R791" s="15" t="inlineStr">
         <is>
           <t>Verified (web-checked)</t>
         </is>
       </c>
-      <c r="S789" s="15" t="inlineStr">
+      <c r="S791" s="15" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S789"/>
+  <autoFilter ref="A1:S791"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$791</definedName>
